--- a/MECÂNICAS/PAUTA D/JOHNSON/Campanha Johnson - Top Contas Q4 FY26.xlsx
+++ b/MECÂNICAS/PAUTA D/JOHNSON/Campanha Johnson - Top Contas Q4 FY26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\Nicolas\Acompanhamentos\JOHNSON\2025.26\Q4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354857A0-3D55-4C3B-AF83-A1F9FD9DD673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B28979-38E8-44AF-848E-E3936EA8A852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="705" firstSheet="1" activeTab="3" xr2:uid="{1E3193F5-9832-4B59-8D54-14EFCF6055F0}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4073" uniqueCount="1054">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4130" uniqueCount="1113">
   <si>
     <t>EQUIPE</t>
   </si>
@@ -2487,730 +2487,907 @@
     <t xml:space="preserve">MOCAM SUPERMERCADOS LTDA FILIAL 01 </t>
   </si>
   <si>
-    <t>59886337 GREGORI VINICIUS DA SILVA DOS SANTOS</t>
-  </si>
-  <si>
     <t>ENERIO VENTURA</t>
   </si>
   <si>
-    <t>MERCADO BORBA LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO PR LTDA</t>
-  </si>
-  <si>
     <t>PADARIA DANINE LTDA</t>
   </si>
   <si>
-    <t>PAULO SERGIO RODRIGUES</t>
-  </si>
-  <si>
     <t>SUPERMERCADO FISCHER EIRELI</t>
   </si>
   <si>
-    <t>CARLOS EDUARDO STEVANATO</t>
-  </si>
-  <si>
-    <t>DAS RAMOS LTDA</t>
-  </si>
-  <si>
-    <t>MARINO THEISGES LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO DI CASA EIRELI</t>
-  </si>
-  <si>
-    <t>MERCADO MINATAO LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO ZANON LTDA</t>
-  </si>
-  <si>
     <t>PSM SUPERMERCADOS LTDA</t>
   </si>
   <si>
-    <t>SUPERMERCADO SERRA E MAR LTDA</t>
-  </si>
-  <si>
-    <t>ATUALIZADO: 11/06/2026</t>
-  </si>
-  <si>
-    <t>TOTAL: 253 linhas</t>
-  </si>
-  <si>
-    <t>60.818.206 LARISSA FARIA LOPES</t>
-  </si>
-  <si>
-    <t>A2 MERCADO E ACOUGUE LTDA</t>
-  </si>
-  <si>
-    <t>ADRIANA DE CARVALHO</t>
-  </si>
-  <si>
-    <t>ADRIANO FRANCISCO BARBOSA DA SILVA</t>
-  </si>
-  <si>
-    <t>ALTAIR GERMANN AGUIAR</t>
-  </si>
-  <si>
-    <t>ALVANIA MARIA BONAFIN ME</t>
-  </si>
-  <si>
-    <t>AMANDA MACHADO ELIAS</t>
-  </si>
-  <si>
-    <t>ANDREAMARA TOGNI DE OLIVEIRA MERCADO</t>
-  </si>
-  <si>
-    <t>ANITO BONIKOSKI</t>
-  </si>
-  <si>
     <t>ANTONIO BALTAZAR DA LUZ</t>
   </si>
   <si>
     <t>ANTONIO VOLPATO EPP</t>
   </si>
   <si>
-    <t>ARNALDO SILVEIRA LIMA ME</t>
-  </si>
-  <si>
-    <t>ATRIO HOTEIS S A</t>
-  </si>
-  <si>
-    <t>AUTO POSTO PENHA LTDA</t>
-  </si>
-  <si>
-    <t>AUTO POSTO PINHEIRO LTDA</t>
-  </si>
-  <si>
-    <t>BAR E MERCEARIA CAIXA D AGUA LTDA</t>
-  </si>
-  <si>
-    <t>BAR E MERCEARIA LEMKE LTDA</t>
-  </si>
-  <si>
-    <t>BAR E MERCEARIA NELSON JUST LTDA</t>
-  </si>
-  <si>
-    <t>BAR E MINI MERCADO LIDIANI ELAISE LTDA</t>
-  </si>
-  <si>
-    <t>BASICOISAS COMERCIO LTDA</t>
-  </si>
-  <si>
     <t>BEACH STOP MINI MERCADO LTDA</t>
   </si>
   <si>
-    <t>BEMARI MERCADO LTDA</t>
-  </si>
-  <si>
-    <t>BERTELI FELIPETTO E ZAMPRONIO LTDA</t>
-  </si>
-  <si>
-    <t>BORBA E CORREA COM DE ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>BRAULIO SILVA</t>
-  </si>
-  <si>
-    <t>BRUNA TAINA DA SILVA DRUSIAN</t>
-  </si>
-  <si>
-    <t>BRUNO SAUNA LTDA</t>
-  </si>
-  <si>
-    <t>CAFE DOS LAGOS LTDA</t>
-  </si>
-  <si>
-    <t>CAMILA GABRIELA DIETRICH DALLA GIACOMASSA</t>
-  </si>
-  <si>
-    <t>CANDIDA COM DE PROD DE LIMPEZA E EMBALAG LTDA</t>
-  </si>
-  <si>
-    <t>CB COMERCIO DE UTILIDADES LTDA</t>
-  </si>
-  <si>
-    <t>CECHINEL &amp; CECHINEL CASA DE CARNES LTDA</t>
-  </si>
-  <si>
-    <t>CILEDA REGINA ZUNINO SILVEIRA ME</t>
-  </si>
-  <si>
-    <t>CINTIA MARIA PEREIRA</t>
-  </si>
-  <si>
-    <t>CLINICA NEUROVOZ LTDA</t>
-  </si>
-  <si>
-    <t>COM DE QUEIJOS E FRIOS MEDEIROS LTDA</t>
-  </si>
-  <si>
-    <t>COMERCIAL DE ALIMENTOS DE ANGELINA LTDA</t>
-  </si>
-  <si>
-    <t>COMERCIAL DUBAI BRASIL LTDA</t>
-  </si>
-  <si>
-    <t>COMERCIAL IMIGRANTES LTDA</t>
-  </si>
-  <si>
-    <t>COMERCIAL JATIVOCA LTDA</t>
-  </si>
-  <si>
-    <t>COMERCIAL JTS LTDA</t>
-  </si>
-  <si>
-    <t>COMERCIAL REINALDO ARTUR SOARES LTDA</t>
-  </si>
-  <si>
-    <t>COMERCIO DE ALIMENTOS E BEBIDAS SPRENGER LTDA</t>
-  </si>
-  <si>
-    <t>COMERCIO DE CEREAIS ALTO VALE LTDA</t>
-  </si>
-  <si>
-    <t>COMERCIO DE FRUTAS E VERDURAS SCHMITT LTDA</t>
-  </si>
-  <si>
-    <t>COMERCIO DE PRODUTOS ALIMENTICIOS HEMMER LTDA</t>
-  </si>
-  <si>
-    <t>COMERCIO DE PRODUTOS ALIMENTICIOS R. M.</t>
-  </si>
-  <si>
-    <t>CONFEITARIA E PADARIA TIMBO LTDA</t>
-  </si>
-  <si>
-    <t>COSTA MERCADO LTDA</t>
-  </si>
-  <si>
-    <t>CRISTIANO MESSIAS PALOCO SEIVISH</t>
-  </si>
-  <si>
-    <t>DALBOSCO MARKET LTDA</t>
-  </si>
-  <si>
-    <t>DELICIAS GOURMET LTDA</t>
-  </si>
-  <si>
-    <t>DELLAZERI E DELLAZERI BARBEARIA LTDA</t>
-  </si>
-  <si>
-    <t>DEMOOP PROD DE LIMP DESCART E VARIE LTDA</t>
-  </si>
-  <si>
-    <t>DENILSON SOUSA CARDOSO</t>
-  </si>
-  <si>
-    <t>DOCA PADARIA E MINI MERCADO LTDA</t>
-  </si>
-  <si>
-    <t>DOCTOR CAFETERIA LTDA</t>
-  </si>
-  <si>
-    <t>DROGARIA MATRIZ LTDA</t>
-  </si>
-  <si>
-    <t>ECOLIMPOS PROD DE LIMP E DESCARTAVE LTDA</t>
-  </si>
-  <si>
-    <t>EDINA MARIA ANACLETO</t>
-  </si>
-  <si>
-    <t>EDNA SILVA MONTAGNA MACHADO</t>
-  </si>
-  <si>
-    <t>EMPORIO NATURAL COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>EMPORIO PETRY PRIME LTDA</t>
-  </si>
-  <si>
-    <t>ENZO COMERCIO DE ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>ESPETINHOS CURITIBA ARAUCARIA LTDA</t>
-  </si>
-  <si>
-    <t>F.C COMERCIO ALIMENTICIO LTDA</t>
-  </si>
-  <si>
-    <t>FARMACIA POPULAR PICARRAS LTDA</t>
-  </si>
-  <si>
-    <t>FEDER COMERCIAL LTDA</t>
-  </si>
-  <si>
     <t>FLNG DRINKS E CONVENIENCIA LTDA</t>
   </si>
   <si>
-    <t>FLORA ITOUPAVA GARDEN LTDA</t>
-  </si>
-  <si>
-    <t>FNB COMERCIO VAREJISTA DE ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>FORTALEZA CONVENIENCIA LTDA</t>
-  </si>
-  <si>
-    <t>FRANCIANE CARDOSO FERREIRA</t>
-  </si>
-  <si>
-    <t>G R U P O BIANCHINI LTDA</t>
-  </si>
-  <si>
-    <t>GASTON PEREYRA PAULUCCI</t>
-  </si>
-  <si>
-    <t>GILCEA DOS SANTOS BERETA</t>
-  </si>
-  <si>
-    <t>GILDASIO PEREIRA JOAO</t>
-  </si>
-  <si>
-    <t>GISLAINE DE CAMARGO ORSO</t>
-  </si>
-  <si>
-    <t>GISLEI EIDT MACHADO ME</t>
-  </si>
-  <si>
-    <t>HENRIQUE COM HORTIFRUTIGRANJEIRO EIRELI</t>
-  </si>
-  <si>
-    <t>HOTEIS EDR LTDA</t>
-  </si>
-  <si>
-    <t>I S COMERCIO E DISTRIBUICAO LTDA</t>
-  </si>
-  <si>
-    <t>INOVE COMERCIOS DE ALIMENTOS EIRELI</t>
-  </si>
-  <si>
-    <t>JANETE APARECIDA HILLESHEIM</t>
-  </si>
-  <si>
-    <t>JOSIANARA COMERCIO DE ALIMENTOS LTDA</t>
-  </si>
-  <si>
     <t>JP DE MENECH LTDA</t>
   </si>
   <si>
     <t>JULIEN COMERCIO DE ALIMENTOS LTDA</t>
   </si>
   <si>
-    <t>JVP COMERCIA EIRELI</t>
-  </si>
-  <si>
-    <t>LANCHONETE E MERCEARIA TII LTDA</t>
-  </si>
-  <si>
     <t>LARISSA POITE STAROSCKY</t>
   </si>
   <si>
-    <t>LEANDRO MERCADO LTDA</t>
-  </si>
-  <si>
-    <t>LEILA FLAVIA LUCKT GOMES</t>
-  </si>
-  <si>
-    <t>LOURIVAL RIBEIRO DA SILVA</t>
-  </si>
-  <si>
-    <t>LP COMERCIO E ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>LUAN DE FREITAS MATOS</t>
-  </si>
-  <si>
-    <t>LUANA ANTUNES MAIA</t>
-  </si>
-  <si>
-    <t>LUCAS FIGUEIRO VARELA</t>
-  </si>
-  <si>
-    <t>LUCELIA BERNARDO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>LUIZ ANTONIO DOS SANTOS OLIVEIRA</t>
-  </si>
-  <si>
-    <t>M A S PADARIA E CONFEITARIA LTDA</t>
-  </si>
-  <si>
-    <t>M633 COMERCIO DE ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>MAGALI WILL</t>
-  </si>
-  <si>
-    <t>MARCILEIA GAMBETA LAURINDO</t>
-  </si>
-  <si>
-    <t>MARCOS ROBERTO DA CRUZ RENKE</t>
-  </si>
-  <si>
-    <t>MARGOTTI PAES E DOCES LTDA</t>
-  </si>
-  <si>
-    <t>MARIA APARECIDA FERNANDES</t>
-  </si>
-  <si>
-    <t>MATHEUS LUCHINI</t>
-  </si>
-  <si>
-    <t>MAYSON R DE CONTO PASQUALOTO E CIA LTDA</t>
-  </si>
-  <si>
     <t>MEGA BRASIL DISTRIBUIDORA DE GENEROS ALIMENTICIOS LTDA</t>
   </si>
   <si>
-    <t>MERCADINHO DO ALEMAO LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO AGUAS NEGRAS LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO AVENIDA PEREQUE LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO BARROS LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO CEDRO CENTRAL LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO CHIODINI LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO DA TORRE LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO E ACOUGUE AMF LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO E ACOUGUE CENTRO OESTE LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO E ACOUGUE COPA LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO E ACOUGUE SBEGHEN EIRELI</t>
-  </si>
-  <si>
-    <t>MERCADO E ACOUGUE VERDI LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO E CONVENIENCIA KAUANI LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO ESQUINA LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO FELLER LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO JPS LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO LANDINHO LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO LITORANEA LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO M E E LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO PIOVEZAN LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO RIO BONITO LIMITADA</t>
-  </si>
-  <si>
-    <t>MERCADO SAO GABRIEL LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO SILVA LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO SPERANDIO LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO SUPER FACIL LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO TRAVESSAO LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO VERDE LTDA</t>
-  </si>
-  <si>
-    <t>MERCEARIA DO NOCA LTDA</t>
-  </si>
-  <si>
     <t>MERCEARIA DONA JO LTDA</t>
   </si>
   <si>
-    <t>MINI MERCADO ALIDOR LTDA</t>
-  </si>
-  <si>
-    <t>MINI MERCADO E ACOUGUE GUESSER LTDA</t>
-  </si>
-  <si>
-    <t>MINI MERCADO E BAR SOUZA LTDA</t>
-  </si>
-  <si>
-    <t>MINI MERCADO EMPORIO ECONOMICO LTDA</t>
-  </si>
-  <si>
-    <t>MINI MERCADO GHR LTDA</t>
-  </si>
-  <si>
-    <t>MINI MERCADO IRMAOS INACIO LTDA</t>
-  </si>
-  <si>
-    <t>MINI MERCADO KAUFHAUS LTDA</t>
-  </si>
-  <si>
-    <t>MINI MERCADO KETLYN LTDA</t>
-  </si>
-  <si>
     <t>MINI MERCADO RCA LTDA</t>
   </si>
   <si>
-    <t>MINI SUPER CRISTINA LTDA</t>
-  </si>
-  <si>
-    <t>MINIMERCADO D MAIS LTDA</t>
-  </si>
-  <si>
-    <t>MINIMERCADO ELIANE LTDA</t>
-  </si>
-  <si>
-    <t>MINIMERCADO KI MASSA LTDA</t>
-  </si>
-  <si>
-    <t>MINIMERCADO SILVA E KNOBLAUCH LTDA</t>
-  </si>
-  <si>
-    <t>MOKA LANCHONETE E CAFE LTDA</t>
-  </si>
-  <si>
-    <t>NILSE RIZZI ALDENGUE MINIMERCADO EIRELI</t>
-  </si>
-  <si>
-    <t>NOELI ZENAIR VIEIRA BITTENCOURT ME</t>
-  </si>
-  <si>
-    <t>NONA DITA LTDA</t>
-  </si>
-  <si>
-    <t>NOVA BRASLIMPE COMERCIO DE PAPEIS E HIGIENE LTDA</t>
-  </si>
-  <si>
-    <t>PADARIA E CONFEITARIA CASTELINHO LTDA</t>
-  </si>
-  <si>
-    <t>PAMELA DOS SANTOS DE ALMEIDA</t>
-  </si>
-  <si>
-    <t>PANIFICADORA AS LTDA</t>
-  </si>
-  <si>
-    <t>PANIFICADORA E CONFEITARIA NEUMANN LTDA</t>
-  </si>
-  <si>
-    <t>PANIFICADORA E CONFEITARIA VO ILDA LTDA</t>
-  </si>
-  <si>
-    <t>PANIFICADORA E MERCEARIA IRMAOS ROSA LTDA</t>
-  </si>
-  <si>
-    <t>PANIFICADORA EMERCEARIA PATRICIA LTDA</t>
-  </si>
-  <si>
-    <t>PAOLA KATIELY DOS SANTOS DA SILVA</t>
-  </si>
-  <si>
-    <t>PAULO HENRIQUE BENATO</t>
-  </si>
-  <si>
-    <t>PEREIRA COMERCIO EM GERAL LTDA</t>
-  </si>
-  <si>
-    <t>PLASLIMP COMERCIO DE EMBALAGENS E MATERIAIS DE LIMPEZA LTDA</t>
-  </si>
-  <si>
-    <t>PORTO SUPERMERCADO LTDA</t>
-  </si>
-  <si>
-    <t>POSTO DE ABASTC PELLEGRIN LTDA</t>
-  </si>
-  <si>
-    <t>POSTO DE COMBUSTIVEIS ZE LUCAS LTDA</t>
-  </si>
-  <si>
-    <t>POSTO DE GASOLINA MORETTO LTDA</t>
-  </si>
-  <si>
-    <t>POSTO DE SERVICOS BR BLU LTDA</t>
-  </si>
-  <si>
-    <t>POSTO GRID LTDA</t>
-  </si>
-  <si>
-    <t>POSTO MAZO LTDA</t>
-  </si>
-  <si>
-    <t>POSTO SANTA TEREZA LTDA</t>
-  </si>
-  <si>
-    <t>PRADO SUPERMERCADO LTDA</t>
-  </si>
-  <si>
-    <t>PRIME CASA DE CARNES LTDA</t>
-  </si>
-  <si>
     <t>PROGRESSO COMERCIO DE ALIMENTOS LTDA</t>
   </si>
   <si>
-    <t>QUEBRA GALHO 24 HORAS ARMAZEM LTDA</t>
-  </si>
-  <si>
-    <t>QUIRINO E QUIRINO LTDA</t>
-  </si>
-  <si>
-    <t>R M DE LARA OLIVEIRA MINIMERCADO ME</t>
-  </si>
-  <si>
-    <t>RESTAURANTE LANCHONETE E MERCEARIA BAGGIO LTDA</t>
-  </si>
-  <si>
-    <t>RESTAURANTE LE BON GOURMET LTDA</t>
-  </si>
-  <si>
-    <t>ROBSON FELIPPI</t>
-  </si>
-  <si>
-    <t>RODINALDO HOLLUP</t>
-  </si>
-  <si>
-    <t>RONALDO MENDES LUIZ</t>
-  </si>
-  <si>
-    <t>RONI PEREIRA DA LUZ E CIA LTDA</t>
-  </si>
-  <si>
-    <t>ROSANGELA PACHECO REBELO</t>
-  </si>
-  <si>
-    <t>ROSEMERI WILHELM STEINERT</t>
-  </si>
-  <si>
-    <t>S C CABRAL RESTAURANTE EIRELI</t>
-  </si>
-  <si>
-    <t>SABRINA L DOS SANTOS MERCEARIA</t>
-  </si>
-  <si>
-    <t>SANTIAGO COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>SANTINHO LTDA</t>
-  </si>
-  <si>
-    <t>SC LUCAS COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>SCHNEIDER E CIA LTDA</t>
-  </si>
-  <si>
-    <t>SILVA COSTA MERCADO LTDA</t>
-  </si>
-  <si>
-    <t>SIMAO DISTRIBUICAO E COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t>SIMONE APARECIDA HAMES DE SOUSA</t>
-  </si>
-  <si>
-    <t>SINUELO SUPERMERCADO E MAT DE CONS LTDA</t>
-  </si>
-  <si>
-    <t>SOLUPLAST SOLUCOES EM DESCARTAVEIS LTDA</t>
-  </si>
-  <si>
-    <t>SUELEN CRISTINA MARTTINI</t>
-  </si>
-  <si>
-    <t>SUPERMERCADO CAMPOS NOVOS LTDA</t>
-  </si>
-  <si>
     <t>SUPERMERCADO M A LTDA</t>
   </si>
   <si>
-    <t>SUPERMERCADO MENESTRINA LTDA</t>
-  </si>
-  <si>
-    <t>SUPERMERCADO MERCOCENTRO LTDA</t>
-  </si>
-  <si>
-    <t>SUPERMERCADO MONTIBELLER LTDA</t>
-  </si>
-  <si>
-    <t>SUPERMERCADO MZB LTDA</t>
-  </si>
-  <si>
-    <t>SUPERMERCADO RERMI LTDA</t>
-  </si>
-  <si>
-    <t>SUPERMERCADO SERRAMAR LTDA</t>
-  </si>
-  <si>
     <t>SUPERMERCADO VICENTI LTDA</t>
   </si>
   <si>
-    <t>SUPERMERCADOS NATHAN LTDA</t>
-  </si>
-  <si>
     <t>TABULEIRO SUPERMERCADO LTDA</t>
   </si>
   <si>
-    <t>THAYSA JAEGER COMERCIO ATACADISTA LTDA</t>
-  </si>
-  <si>
-    <t>TOP LIMP PRODUTOS DE LIMPEZA LTDA</t>
-  </si>
-  <si>
-    <t>TRINDADE COMERCIO VAREJISTA LTDA</t>
-  </si>
-  <si>
-    <t>VALENTIM TAMBOSI</t>
-  </si>
-  <si>
-    <t>VARLEY SOUZA BUENO</t>
-  </si>
-  <si>
-    <t>VIECELI SALVETTI E CIA LTDA</t>
-  </si>
-  <si>
-    <t>VILMA DE FATIMA BORGES MINIMERCADO</t>
-  </si>
-  <si>
-    <t>VITOR DE SOUZA E CIA LTDA</t>
-  </si>
-  <si>
     <t>VIVIANE CRISTINA CAVICHIONI CORDEIRO</t>
   </si>
   <si>
-    <t>WERNER SCHROEDER</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 318 linhas</t>
   </si>
   <si>
     <t xml:space="preserve"> 113 linhas</t>
+  </si>
+  <si>
+    <t>TOTAL: 310 linhas</t>
+  </si>
+  <si>
+    <t>58.049.133 GRAZIELA STECANELLA IZAGUIRRE</t>
+  </si>
+  <si>
+    <t>A J POTTER E CIA LTDA</t>
+  </si>
+  <si>
+    <t>ABRAO JOSE DE SOUZA</t>
+  </si>
+  <si>
+    <t>ACIEL LAUDELINO ROZAR ME</t>
+  </si>
+  <si>
+    <t>ACOUGUE SANTA TEREZINHA LTDA</t>
+  </si>
+  <si>
+    <t>ADEMIR JOSE ZATTI ME</t>
+  </si>
+  <si>
+    <t>ADESIO PEREIRA</t>
+  </si>
+  <si>
+    <t>ADRIANI MARIA HEMING</t>
+  </si>
+  <si>
+    <t>AGRO COMERCIAL KORB LTDA</t>
+  </si>
+  <si>
+    <t>ALCEU RODRIGUES DE LIMA</t>
+  </si>
+  <si>
+    <t>ALCIONE ZANOLLA ME</t>
+  </si>
+  <si>
+    <t>ALDO DAL MOLIN</t>
+  </si>
+  <si>
+    <t>ALEXANDRA APARECIDA DA SILVA</t>
+  </si>
+  <si>
+    <t>ALEXSANDRO DA SILVA CAMPOS</t>
+  </si>
+  <si>
+    <t>ALICE ALBINO</t>
+  </si>
+  <si>
+    <t>ALMIR CARLOS BECKER</t>
+  </si>
+  <si>
+    <t>ANA CLAUDIA VENTURINI DE GODOY PEREIRA</t>
+  </si>
+  <si>
+    <t>ANA PAULA BENTO E CIA LTDA</t>
+  </si>
+  <si>
+    <t>ANDERSON LUIS GOULART FERNANDES MINI MERCADO</t>
+  </si>
+  <si>
+    <t>ANDRESA MARIA DA SILVA</t>
+  </si>
+  <si>
+    <t>ANTONIA LUIZ CARDOSO</t>
+  </si>
+  <si>
+    <t>ANTONIO S CONVENIENCIA E MERCEARIA LTDA</t>
+  </si>
+  <si>
+    <t>ASATOMA COMERCIO VAREJISTA LTDA</t>
+  </si>
+  <si>
+    <t>ATACA RIO ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>ATACADAO DA LIMPEZA LTDA</t>
+  </si>
+  <si>
+    <t>AUTO POSTO CAFE NO BULE LTDA</t>
+  </si>
+  <si>
+    <t>AUTO POSTO DAMINELLI LTDA</t>
+  </si>
+  <si>
+    <t>AUTO POSTO MEDITERRANEO LTDA</t>
+  </si>
+  <si>
+    <t>AUTO POSTO NOVA TRENTO LTDA</t>
+  </si>
+  <si>
+    <t>AUTO POSTO RAIMONDI LTDA</t>
+  </si>
+  <si>
+    <t>AZISO JOSE HECK</t>
+  </si>
+  <si>
+    <t>BAR E MERCEARIA J P PROGRESSO LTDA</t>
+  </si>
+  <si>
+    <t>BARON COM DE GENEROS ALIMENTICIOS LTDA</t>
+  </si>
+  <si>
+    <t>BAZAR JHONNY LTDA</t>
+  </si>
+  <si>
+    <t>BELLA PANY PADARIA E CONFEITARIA LTDA</t>
+  </si>
+  <si>
+    <t>BLUMENKAFFEE PADARIA E CAFEITARIA LTDA</t>
+  </si>
+  <si>
+    <t>BRUSAMOLIN COM DE MEDICAMENTOS</t>
+  </si>
+  <si>
+    <t>BUREI SUPERMERCADOS LTDA</t>
+  </si>
+  <si>
+    <t>BURGUER HOUSE GOURMET LTDA</t>
+  </si>
+  <si>
+    <t>BUSS E OURIQUES LTDA</t>
+  </si>
+  <si>
+    <t>CARINE MATOS CASAGRANDE CAVALER</t>
+  </si>
+  <si>
+    <t>CARLOS ROBERTO RIEG</t>
+  </si>
+  <si>
+    <t>CAROLINA SILVA AZEVEDO</t>
+  </si>
+  <si>
+    <t>CASA DE CARNE FORMIGA LTDA</t>
+  </si>
+  <si>
+    <t>CELIO DE SOUZA MINIMERCADO ME</t>
+  </si>
+  <si>
+    <t>CHARLES DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>CIRLENE MARTINS</t>
+  </si>
+  <si>
+    <t>CLEIA CRISTINA COELHO</t>
+  </si>
+  <si>
+    <t>COMERCIAL COISA DE LOUCO LTDA</t>
+  </si>
+  <si>
+    <t>COMERCIAL MN LTDA</t>
+  </si>
+  <si>
+    <t>COMERCIAL PRECO BOM LTDA</t>
+  </si>
+  <si>
+    <t>COMERCIAL ZINDARS LTDA</t>
+  </si>
+  <si>
+    <t>COMERCIO DE ALIM IRMAOS BARRIM LTDA</t>
+  </si>
+  <si>
+    <t>COMERCIO DE GENEROS ALIM MALDANE</t>
+  </si>
+  <si>
+    <t>COMERCIO DE GENEROS ALIMENTICIOS CL LTDA</t>
+  </si>
+  <si>
+    <t>CONVENIENCIA BELLA LTDA</t>
+  </si>
+  <si>
+    <t>CONVENIENCIA RANCHO BEER LTDA</t>
+  </si>
+  <si>
+    <t>COOP CONS OPERARIOS REGIAO CARBONIF LTDA</t>
+  </si>
+  <si>
+    <t>CORDOVA E PRUDENCIO COM DE GEN ALIM LTDA</t>
+  </si>
+  <si>
+    <t>CRISTIANO DA SILVA MINI MERCADO</t>
+  </si>
+  <si>
+    <t>CRISTIANO STALOCH</t>
+  </si>
+  <si>
+    <t>DAMIAN E SILVA COM DE GEN ALIMENT LTDA</t>
+  </si>
+  <si>
+    <t>DEBORA CRISTINA STANGE</t>
+  </si>
+  <si>
+    <t>DECORO ARTIGOS PARA FESTAS LTDA</t>
+  </si>
+  <si>
+    <t>DIEGO SIMAO</t>
+  </si>
+  <si>
+    <t>DISAMPA BARBEARIA LTDA</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA LIMPO LTDA</t>
+  </si>
+  <si>
+    <t>DOCIKADO PADARIA LTDA</t>
+  </si>
+  <si>
+    <t>DORACI APARECIDA DE SOUZA CRIMINACIO</t>
+  </si>
+  <si>
+    <t>DORACI DUWE SCHULZ E CIA LTDA</t>
+  </si>
+  <si>
+    <t>DOUGLAS ANTUNES JACQUES</t>
+  </si>
+  <si>
+    <t>DOUGLAS DE MIRANDA ZOMER</t>
+  </si>
+  <si>
+    <t>DOUGLAS HENRIQUE AMERICO CARDOSO</t>
+  </si>
+  <si>
+    <t>DROGARIA ABNER LTDA</t>
+  </si>
+  <si>
+    <t>EDSON DE LIMA</t>
+  </si>
+  <si>
+    <t>ELIANE DA CUNHA MERCEARIA</t>
+  </si>
+  <si>
+    <t>ELIZANDRE RODIAK</t>
+  </si>
+  <si>
+    <t>EMPLASTOP CASA DAS EMBALAGENS LTDA</t>
+  </si>
+  <si>
+    <t>EMPORIO DO PASTEL LANC MERC E COM DE BEBIDAS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERALDO DIAS </t>
+  </si>
+  <si>
+    <t>ERICA SATURNINO BENVENUTTI</t>
+  </si>
+  <si>
+    <t>ESTOQUEMIX COMERCIO ATACADISTA EIRELI</t>
+  </si>
+  <si>
+    <t>ESTRACIERI E BORGES LTDA</t>
+  </si>
+  <si>
+    <t>FABIANA BICHESKI DA SILVA</t>
+  </si>
+  <si>
+    <t>FABIANO RODRIGUES DA SILVA</t>
+  </si>
+  <si>
+    <t>FARMACIA E PERFUMARIA ADIFARMA LTDA</t>
+  </si>
+  <si>
+    <t>FARMACIA VIVA MELHOR LTDA</t>
+  </si>
+  <si>
+    <t>FATIMA SUPERMERCADOS LTDA</t>
+  </si>
+  <si>
+    <t>FIFO COMPRE BEM LTDA</t>
+  </si>
+  <si>
+    <t>FIFO DO VALE LTDA</t>
+  </si>
+  <si>
+    <t>GEOVANE ROCHA DA SILVA</t>
+  </si>
+  <si>
+    <t>GERSON LUIS SANTOS DA SILVA</t>
+  </si>
+  <si>
+    <t>GIANE DIAS</t>
+  </si>
+  <si>
+    <t>GILBERTO OLIVEIRA DE SOUZA</t>
+  </si>
+  <si>
+    <t>GILNEI SCHUNKE</t>
+  </si>
+  <si>
+    <t>GRASIELA TRINDADE PISKE</t>
+  </si>
+  <si>
+    <t>GRAZIELA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>GUILHERME MALDANER BRASILEIRO EIRELI</t>
+  </si>
+  <si>
+    <t>GULLA CAFE LTDA</t>
+  </si>
+  <si>
+    <t>GUSTAVO GEMELI SERRANO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>H.R. DESCARTAVEIS LTDA</t>
+  </si>
+  <si>
+    <t>HENRY JAVIER TIAMO ROMERO</t>
+  </si>
+  <si>
+    <t>HIAGO INACIO MARCELINO</t>
+  </si>
+  <si>
+    <t>HIPPO SUPERMERCADOS LTDA</t>
+  </si>
+  <si>
+    <t>HORTIFRUTI SANTA LIDIA LTDA</t>
+  </si>
+  <si>
+    <t>IARA K RAMOS E CIA LTDA</t>
+  </si>
+  <si>
+    <t>IRINEU MANOEL DA LUZ ME</t>
+  </si>
+  <si>
+    <t>ITAMIR BRAATZ LTDA</t>
+  </si>
+  <si>
+    <t>IVONETE MACHADO OLIVEIRA MORAES</t>
+  </si>
+  <si>
+    <t>JAIME DE SOUZA FELISBINO</t>
+  </si>
+  <si>
+    <t>JANAINA SILVANO DE SOUZA</t>
+  </si>
+  <si>
+    <t>JAQUELINE DEUCHER DA SILVA</t>
+  </si>
+  <si>
+    <t>JH SILVEIRA MARQUES LTDA</t>
+  </si>
+  <si>
+    <t>JOHN ELTON DA SILVA DOS SANTOS LTDA</t>
+  </si>
+  <si>
+    <t>JOICE DA MOTTA PEREIRA BRAGA</t>
+  </si>
+  <si>
+    <t>JOSE CARDOSO ME</t>
+  </si>
+  <si>
+    <t>JOSE HERIBERTO BRUGGEMANN</t>
+  </si>
+  <si>
+    <t>JOSE JOAO MAFRA ME</t>
+  </si>
+  <si>
+    <t>JOSIANE GARCIA MINIMERCADO LTDA</t>
+  </si>
+  <si>
+    <t>JRX COMERCIO DE COMBUSTIVEIS LTDA</t>
+  </si>
+  <si>
+    <t>JUSSANE BERTAN</t>
+  </si>
+  <si>
+    <t>JVETEC INFORMATICA EIRELI</t>
+  </si>
+  <si>
+    <t>KATIA OLIVIA VICENTE</t>
+  </si>
+  <si>
+    <t>KAUA TELES LOURENCO</t>
+  </si>
+  <si>
+    <t>LANCHONETE SILVA E BORGES LTDA</t>
+  </si>
+  <si>
+    <t>LAURA LUIZA DA SILVA AMARAL PAZUCH</t>
+  </si>
+  <si>
+    <t>LEANDRO DA SILVA SEVERINO</t>
+  </si>
+  <si>
+    <t>LEONEL MISTURA</t>
+  </si>
+  <si>
+    <t>LIMA E LIMA TOP PAO LTDA</t>
+  </si>
+  <si>
+    <t>LOJAS DE DEPARTAMENTOS MILIUM LTDA</t>
+  </si>
+  <si>
+    <t>LUANDREA COME DE GEN ALIM LTDA</t>
+  </si>
+  <si>
+    <t>LUCILO DE LIMA SANTOS</t>
+  </si>
+  <si>
+    <t>LUIS ROBERTO OLIVEIRA</t>
+  </si>
+  <si>
+    <t>M M COLOSSI E CIA LTDA</t>
+  </si>
+  <si>
+    <t>MADALENA BORBA PETRI ME</t>
+  </si>
+  <si>
+    <t>MANOEL EMIDIO DE OLIVEIRA FILHO ME</t>
+  </si>
+  <si>
+    <t>MARCELI CONVENIENCIA E TABACARIA LTDA</t>
+  </si>
+  <si>
+    <t>MARCIEL AMORIM - ALICE CONFEITARIA</t>
+  </si>
+  <si>
+    <t>MARIA DAS NEVES SOUZA COMERCIO</t>
+  </si>
+  <si>
+    <t>MARIA JOSE COELHO MERLO</t>
+  </si>
+  <si>
+    <t>MARLIZE CARVALHO MARTINS</t>
+  </si>
+  <si>
+    <t>MARTA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>MB SUPERMERCADO EIRELI</t>
+  </si>
+  <si>
+    <t>MERCADO BENETTI LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO BH VILA VITORIA LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO CAMELIA LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO CUCO LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO DERETTI LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO DO CLEITON EIRELI</t>
+  </si>
+  <si>
+    <t>MERCADO DOM GREGORIO LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO DONA NETE LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO DORIT RAUH LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO E ACOUGUE DA CUNHA LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO E ACOUGUE DO POVO LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO E ACOUGUE DONA BE JOINVILLE LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO E ACOUGUE SANTA CRUZ LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO E BAR PALOMA LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO E CONVENIENCIA BISS LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO E MERCEARIA DO CRIS LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO E PADARIA VICTOR KUNST LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO E PANIF SILVIO E SILVANIA LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO FELICIANO LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO GIFER LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO GRANZOTO</t>
+  </si>
+  <si>
+    <t>MERCADO IRMAOS ROSA LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO ITAJUBA EIRELI</t>
+  </si>
+  <si>
+    <t>MERCADO JARDIM CIDADE LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO KRUPEK E KRUPEK LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO MARCOM LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO MARIANO NICARETTA LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO MCD LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO MG LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO PA EIRELI</t>
+  </si>
+  <si>
+    <t>MERCADO PEG ZENI LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO RIO CERRO LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO SCHVINN LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO SUPER PRATICO LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO VANDRESEN LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO VILLA LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO VOLTA GRANDE LTDA</t>
+  </si>
+  <si>
+    <t>MERCAVILLE COM DE ALIMENTOS EIRELI</t>
+  </si>
+  <si>
+    <t>MERCEARIA AMARAL LTDA</t>
+  </si>
+  <si>
+    <t>MERCEARIA CAMPO GRANDE LTDA</t>
+  </si>
+  <si>
+    <t>MERCEARIA CELSO KOHLER LTDA</t>
+  </si>
+  <si>
+    <t>MERCEARIA E BAR NS LTDA</t>
+  </si>
+  <si>
+    <t>MERCEARIA E VARIEDADES IVONE DIAS LTDA</t>
+  </si>
+  <si>
+    <t>MERCEARIA FIFO DA GULA LTDA</t>
+  </si>
+  <si>
+    <t>MERCEARIA SALVADOR LTDA</t>
+  </si>
+  <si>
+    <t>MINI MERCADO E HORTIFRUTI MKB LTDA</t>
+  </si>
+  <si>
+    <t>MINI MERCADO FRUTI PITANGA LTDA</t>
+  </si>
+  <si>
+    <t>MINI MERCADO KROEGER LTDA</t>
+  </si>
+  <si>
+    <t>MINI MERCADO PITANGA LTDA</t>
+  </si>
+  <si>
+    <t>MINI MERCADO RIO DA LUZ LTDA</t>
+  </si>
+  <si>
+    <t>MINIMERCADO DRUMM</t>
+  </si>
+  <si>
+    <t>MINIMERCADO E ACOUGUE CLASEN LTDA</t>
+  </si>
+  <si>
+    <t>MINIMERCADO E PADARIA TOCO LTDA</t>
+  </si>
+  <si>
+    <t>MINIMERCADO MALU MONTEIRO LTDA</t>
+  </si>
+  <si>
+    <t>MINIMERCADO MAR GROSSO LTDA</t>
+  </si>
+  <si>
+    <t>MINIMERCADO SAO PAULINHO LTDA</t>
+  </si>
+  <si>
+    <t>MODESTO DA CRUZ LICHESKI DOS SANTOS</t>
+  </si>
+  <si>
+    <t>MR ARMAZEM EXPRESS LTDA</t>
+  </si>
+  <si>
+    <t>N A SILVA COMERCIO DE REVISTAS LTDA</t>
+  </si>
+  <si>
+    <t>NEEMIAS HENRIQUE CARDOSO</t>
+  </si>
+  <si>
+    <t>NICOLAS ARMANDO ABREU DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>NILCEIA DE MORAES LIMA</t>
+  </si>
+  <si>
+    <t>NILO FERREIRA RODRIGUES</t>
+  </si>
+  <si>
+    <t>NINO MAIS SUPERMERCADO LTDA</t>
+  </si>
+  <si>
+    <t>NIVA FARMA LTDA</t>
+  </si>
+  <si>
+    <t>NUTRY FRUTARIA E MERCEARIA LTDA</t>
+  </si>
+  <si>
+    <t>OON COM VAR DE ALIM E REPRES COMERCIAIS</t>
+  </si>
+  <si>
+    <t>PACHECO E CHEIROLT CONVENIENCIA LTDA</t>
+  </si>
+  <si>
+    <t>PADARIA E CONF NUBIA LTDA</t>
+  </si>
+  <si>
+    <t>PADARIA E CONFEITARIA DOCE TRADICAO LTDA</t>
+  </si>
+  <si>
+    <t>PAES BUENO STORE LTDA</t>
+  </si>
+  <si>
+    <t>PANIFICADORA DON RODOLPHO EIRELI</t>
+  </si>
+  <si>
+    <t>PANIFICADORA E CONFEITARIA CAPARELLI LTDA</t>
+  </si>
+  <si>
+    <t>PANIFICADORA E CONFEITARIA MELANI LTDA</t>
+  </si>
+  <si>
+    <t>PANIFICADORA FATIMA LTDA</t>
+  </si>
+  <si>
+    <t>PANIFICADORA TAIS LTDA</t>
+  </si>
+  <si>
+    <t>PANIFICIO E MERCEARIA KM 60 LTDA</t>
+  </si>
+  <si>
+    <t>PANIFICIO NOSTRO PANE LTDA</t>
+  </si>
+  <si>
+    <t>PATRICIA OLIVEIRA FERREIRA</t>
+  </si>
+  <si>
+    <t>PEREIRA COMERCIO DE ARTIGOS DESCARTAVEIS LTDA</t>
+  </si>
+  <si>
+    <t>POSTO DE COMBUSTIVEIS VEH LTDA</t>
+  </si>
+  <si>
+    <t>POSTO FRATELLI LTDA</t>
+  </si>
+  <si>
+    <t>RAFAEL PEREIRA</t>
+  </si>
+  <si>
+    <t>RAFAEL ROMULO WALTER</t>
+  </si>
+  <si>
+    <t>RAPHAEL DA SILVA</t>
+  </si>
+  <si>
+    <t>RAYSSA VITORIA FERNANDES DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>REJANE FIGURSKI MINIMERCADO</t>
+  </si>
+  <si>
+    <t>ROBERTA DAIANE NOVAIS DA COSTA</t>
+  </si>
+  <si>
+    <t>RODENIR CANCELIER FUCK</t>
+  </si>
+  <si>
+    <t>RODRIGO ANTONIO COELHO</t>
+  </si>
+  <si>
+    <t>ROMANO POKREVIESKI ME</t>
+  </si>
+  <si>
+    <t>ROSA MARIA NUNES DA SILVA</t>
+  </si>
+  <si>
+    <t>ROSIANI DA SILVA VARELA</t>
+  </si>
+  <si>
+    <t>ROSIMERI ESIDIO</t>
+  </si>
+  <si>
+    <t>ROSSO E CASAGRANDE COMERCIO DE COMBUSTIVEIS LTDA</t>
+  </si>
+  <si>
+    <t>ROZANI APARECIDA KNAUL</t>
+  </si>
+  <si>
+    <t>RUDIMAR FREITAS</t>
+  </si>
+  <si>
+    <t>RZT COMERCIO DE COMBUSTIVEIS LTDA</t>
+  </si>
+  <si>
+    <t>SAO FRANCISCO COMERCIO DE ALIMENTOS E TRANSPORTE LTDA</t>
+  </si>
+  <si>
+    <t>SCHIRLEI FABIANA GONCALVES PADILHA LTDA</t>
+  </si>
+  <si>
+    <t>SCHOULTEN COMERCIO VAREJISTA E ATACADISTA DE EMBALAGENS LTDA</t>
+  </si>
+  <si>
+    <t>SHEILA GISELE BERNARDES</t>
+  </si>
+  <si>
+    <t>SID COMERCIO DE ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>SILVA E BORCHARDT COM DE PAES LTDA</t>
+  </si>
+  <si>
+    <t>SONIA MARIA MAROSTICA ME</t>
+  </si>
+  <si>
+    <t>SUPERMECADO BUNN LTDA</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO 3 IRMAOS LTDA</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO ANGELINA LTDA</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO ARY LTDA</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO BECKER LTDA</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO BUZZI LTDA</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO CAROL LTDA</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO DIASVILLE LTDA</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO EMILIA LTDA</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO GIRASSOL LTDA</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO IRMAOS ZIMMERMANN LTDA</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO KOHLER LTDA</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO LAGEADO LTDA</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO LAURINDO LTDA</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO PANATTA LTDA</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO PEREIRA LTDA</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO POLASTRO LTDA</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO VITORINO LTDA</t>
+  </si>
+  <si>
+    <t>SUPERMERCADOS SCHUTZE LTDA</t>
+  </si>
+  <si>
+    <t>TAVIANA EXPRESS LTDA</t>
+  </si>
+  <si>
+    <t>TRANSPORTES TERRAP E COM CACADORES LTDA</t>
+  </si>
+  <si>
+    <t>UPMAIS SUPRIMENTOS CORPORATIVOS EIRELI</t>
+  </si>
+  <si>
+    <t>VALDECIR ANTONIO BORTOLATTO</t>
+  </si>
+  <si>
+    <t>VANDERLEI SALESIO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>VESTA VIL JULIEN</t>
+  </si>
+  <si>
+    <t>VICELL COM DE PRODUTOS DE LIMPEZA LTDA</t>
+  </si>
+  <si>
+    <t>VICELL COMERCIO DE PRODUTOS DE LIMPEZA LTDA</t>
+  </si>
+  <si>
+    <t>VILAS MERCADO E BAZAR LTDA</t>
+  </si>
+  <si>
+    <t>WALQUIRIA SANTOS DE SOUZA</t>
+  </si>
+  <si>
+    <t>ZAQUIEL MARCA LTDA</t>
+  </si>
+  <si>
+    <t>ATUALIZADO:</t>
   </si>
 </sst>
 </file>
@@ -3927,7 +4104,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="215">
+  <cellXfs count="216">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4447,6 +4624,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7152,13 +7332,13 @@
       <c r="C1" s="134"/>
       <c r="D1" s="134"/>
       <c r="E1" s="134"/>
-      <c r="G1" s="214" t="s">
+      <c r="G1" s="215" t="s">
         <v>787</v>
       </c>
-      <c r="H1" s="214"/>
-      <c r="I1" s="214"/>
-      <c r="J1" s="214"/>
-      <c r="K1" s="214"/>
+      <c r="H1" s="215"/>
+      <c r="I1" s="215"/>
+      <c r="J1" s="215"/>
+      <c r="K1" s="215"/>
       <c r="M1" s="140" t="s">
         <v>85</v>
       </c>
@@ -7217,7 +7397,7 @@
       <c r="Q2" t="s">
         <v>14</v>
       </c>
-      <c r="T2" s="213" t="s">
+      <c r="T2" s="214" t="s">
         <v>79</v>
       </c>
       <c r="U2" t="s">
@@ -7246,27 +7426,27 @@
         <v>45</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>1052</v>
+        <v>831</v>
       </c>
       <c r="K3" s="132">
-        <v>40600.004000000001</v>
+        <v>40967.232000000004</v>
       </c>
       <c r="M3" s="32"/>
       <c r="O3" t="s">
         <v>45</v>
       </c>
       <c r="P3" t="s">
-        <v>1053</v>
+        <v>832</v>
       </c>
       <c r="Q3" s="6">
-        <v>814.33299999999997</v>
-      </c>
-      <c r="T3" s="213"/>
+        <v>820.33199999999999</v>
+      </c>
+      <c r="T3" s="214"/>
       <c r="V3" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="W3" s="6">
-        <v>639.26599999999996</v>
+        <v>3248</v>
       </c>
       <c r="X3" s="6"/>
     </row>
@@ -7318,15 +7498,15 @@
       <c r="Q4">
         <v>1</v>
       </c>
-      <c r="T4" s="213"/>
+      <c r="T4" s="214"/>
       <c r="U4">
-        <v>192291</v>
+        <v>190068</v>
       </c>
       <c r="V4" t="s">
-        <v>812</v>
+        <v>834</v>
       </c>
       <c r="W4">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.35">
@@ -7377,15 +7557,15 @@
       <c r="Q5">
         <v>11</v>
       </c>
-      <c r="T5" s="213"/>
+      <c r="T5" s="214"/>
       <c r="U5">
-        <v>189603</v>
+        <v>121446</v>
       </c>
       <c r="V5" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="W5">
-        <v>0.375</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
@@ -7436,15 +7616,15 @@
       <c r="Q6">
         <v>3</v>
       </c>
-      <c r="T6" s="213"/>
+      <c r="T6" s="214"/>
       <c r="U6">
-        <v>191023</v>
+        <v>158062</v>
       </c>
       <c r="V6" t="s">
-        <v>830</v>
+        <v>11</v>
       </c>
       <c r="W6">
-        <v>0.16700000000000001</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
@@ -7495,15 +7675,15 @@
       <c r="Q7">
         <v>1</v>
       </c>
-      <c r="T7" s="213"/>
+      <c r="T7" s="214"/>
       <c r="U7">
-        <v>184980</v>
+        <v>48231</v>
       </c>
       <c r="V7" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="W7">
-        <v>1.25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.35">
@@ -7554,15 +7734,15 @@
       <c r="Q8">
         <v>3</v>
       </c>
-      <c r="T8" s="213"/>
+      <c r="T8" s="214"/>
       <c r="U8">
-        <v>187623</v>
+        <v>134801</v>
       </c>
       <c r="V8" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="W8">
-        <v>0.16700000000000001</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.35">
@@ -7613,15 +7793,15 @@
       <c r="Q9">
         <v>16</v>
       </c>
-      <c r="T9" s="213"/>
+      <c r="T9" s="214"/>
       <c r="U9">
-        <v>180831</v>
+        <v>134840</v>
       </c>
       <c r="V9" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="W9">
-        <v>1.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7674,13 +7854,13 @@
       </c>
       <c r="T10" s="189"/>
       <c r="U10">
-        <v>114548</v>
+        <v>127198</v>
       </c>
       <c r="V10" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="W10">
-        <v>0.25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
@@ -7733,13 +7913,13 @@
       </c>
       <c r="T11" s="189"/>
       <c r="U11">
-        <v>189684</v>
+        <v>71362</v>
       </c>
       <c r="V11" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="W11">
-        <v>0.56299999999999994</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.35">
@@ -7792,13 +7972,13 @@
       </c>
       <c r="T12" s="189"/>
       <c r="U12">
-        <v>180566</v>
+        <v>178230</v>
       </c>
       <c r="V12" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="W12">
-        <v>0.91700000000000004</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.35">
@@ -7851,13 +8031,13 @@
       </c>
       <c r="T13" s="189"/>
       <c r="U13">
-        <v>55369</v>
+        <v>124971</v>
       </c>
       <c r="V13" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="W13">
-        <v>2.1669999999999998</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.35">
@@ -7910,13 +8090,13 @@
       </c>
       <c r="T14" s="189"/>
       <c r="U14">
-        <v>56349</v>
+        <v>131261</v>
       </c>
       <c r="V14" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="W14" s="6">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.35">
@@ -7969,13 +8149,13 @@
       </c>
       <c r="T15" s="189"/>
       <c r="U15">
-        <v>90396</v>
+        <v>62107</v>
       </c>
       <c r="V15" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="W15">
-        <v>1.125</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.35">
@@ -8028,13 +8208,13 @@
       </c>
       <c r="T16" s="189"/>
       <c r="U16">
-        <v>168071</v>
+        <v>178317</v>
       </c>
       <c r="V16" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="W16">
-        <v>2.125</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.35">
@@ -8087,13 +8267,13 @@
       </c>
       <c r="T17" s="189"/>
       <c r="U17">
-        <v>178205</v>
+        <v>178199</v>
       </c>
       <c r="V17" t="s">
-        <v>109</v>
+        <v>846</v>
       </c>
       <c r="W17">
-        <v>85</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.35">
@@ -8146,13 +8326,13 @@
       </c>
       <c r="T18" s="189"/>
       <c r="U18">
-        <v>80812</v>
+        <v>173987</v>
       </c>
       <c r="V18" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="W18">
-        <v>0.33300000000000002</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.35">
@@ -8205,13 +8385,13 @@
       </c>
       <c r="T19" s="189"/>
       <c r="U19">
-        <v>60986</v>
+        <v>157758</v>
       </c>
       <c r="V19" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="W19">
-        <v>0.58299999999999996</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.35">
@@ -8264,13 +8444,13 @@
       </c>
       <c r="T20" s="189"/>
       <c r="U20">
-        <v>102034</v>
+        <v>170751</v>
       </c>
       <c r="V20" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="W20">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.35">
@@ -8323,13 +8503,13 @@
       </c>
       <c r="T21" s="189"/>
       <c r="U21">
-        <v>63784</v>
+        <v>141255</v>
       </c>
       <c r="V21" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="W21">
-        <v>0.72899999999999998</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.35">
@@ -8382,13 +8562,13 @@
       </c>
       <c r="T22" s="189"/>
       <c r="U22">
-        <v>124845</v>
+        <v>141927</v>
       </c>
       <c r="V22" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="W22">
-        <v>0.25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.35">
@@ -8441,13 +8621,13 @@
       </c>
       <c r="T23" s="189"/>
       <c r="U23">
-        <v>67806</v>
+        <v>171100</v>
       </c>
       <c r="V23" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="W23">
-        <v>0.16700000000000001</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.35">
@@ -8500,13 +8680,13 @@
       </c>
       <c r="T24" s="189"/>
       <c r="U24">
-        <v>170190</v>
+        <v>189559</v>
       </c>
       <c r="V24" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="W24">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.35">
@@ -8559,13 +8739,13 @@
       </c>
       <c r="T25" s="189"/>
       <c r="U25">
-        <v>180746</v>
+        <v>178250</v>
       </c>
       <c r="V25" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="W25">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.35">
@@ -8618,13 +8798,13 @@
       </c>
       <c r="T26" s="189"/>
       <c r="U26">
-        <v>186290</v>
+        <v>56349</v>
       </c>
       <c r="V26" t="s">
-        <v>849</v>
+        <v>816</v>
       </c>
       <c r="W26">
-        <v>0.33300000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.35">
@@ -8677,13 +8857,13 @@
       </c>
       <c r="T27" s="189"/>
       <c r="U27">
-        <v>147215</v>
+        <v>185863</v>
       </c>
       <c r="V27" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="W27">
-        <v>1.875</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.35">
@@ -8736,13 +8916,13 @@
       </c>
       <c r="T28" s="189"/>
       <c r="U28">
-        <v>185450</v>
+        <v>90396</v>
       </c>
       <c r="V28" t="s">
-        <v>851</v>
+        <v>817</v>
       </c>
       <c r="W28">
-        <v>0.125</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.35">
@@ -8795,13 +8975,13 @@
       </c>
       <c r="T29" s="189"/>
       <c r="U29">
-        <v>178109</v>
+        <v>185091</v>
       </c>
       <c r="V29" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.35">
@@ -8854,13 +9034,13 @@
       </c>
       <c r="T30" s="189"/>
       <c r="U30">
-        <v>76104</v>
+        <v>189905</v>
       </c>
       <c r="V30" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="W30">
-        <v>0.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.35">
@@ -8913,13 +9093,13 @@
       </c>
       <c r="T31" s="189"/>
       <c r="U31">
-        <v>188752</v>
+        <v>179519</v>
       </c>
       <c r="V31" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="W31">
-        <v>0.25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.35">
@@ -8972,13 +9152,13 @@
       </c>
       <c r="T32" s="189"/>
       <c r="U32">
-        <v>76899</v>
+        <v>178205</v>
       </c>
       <c r="V32" t="s">
-        <v>855</v>
+        <v>109</v>
       </c>
       <c r="W32">
-        <v>0.83299999999999996</v>
+        <v>220</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.35">
@@ -9031,13 +9211,13 @@
       </c>
       <c r="T33" s="189"/>
       <c r="U33">
-        <v>188707</v>
+        <v>130044</v>
       </c>
       <c r="V33" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="W33">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.35">
@@ -9090,13 +9270,13 @@
       </c>
       <c r="T34" s="189"/>
       <c r="U34">
-        <v>191336</v>
+        <v>157378</v>
       </c>
       <c r="V34" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="W34">
-        <v>0.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.35">
@@ -9149,13 +9329,13 @@
       </c>
       <c r="T35" s="189"/>
       <c r="U35">
-        <v>172566</v>
+        <v>167787</v>
       </c>
       <c r="V35" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="W35">
-        <v>0.75</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.35">
@@ -9208,13 +9388,13 @@
       </c>
       <c r="T36" s="189"/>
       <c r="U36">
-        <v>156087</v>
+        <v>75366</v>
       </c>
       <c r="V36" t="s">
-        <v>819</v>
+        <v>862</v>
       </c>
       <c r="W36">
-        <v>8.3000000000000004E-2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.35">
@@ -9267,13 +9447,13 @@
       </c>
       <c r="T37" s="189"/>
       <c r="U37">
-        <v>190337</v>
+        <v>70360</v>
       </c>
       <c r="V37" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="W37">
-        <v>0.125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.35">
@@ -9326,13 +9506,13 @@
       </c>
       <c r="T38" s="189"/>
       <c r="U38">
-        <v>175881</v>
+        <v>138877</v>
       </c>
       <c r="V38" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="W38">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.35">
@@ -9365,7 +9545,7 @@
         <v>782</v>
       </c>
       <c r="K39" s="132">
-        <v>112.5</v>
+        <v>107.021</v>
       </c>
       <c r="M39" s="29" t="str">
         <f t="shared" si="1"/>
@@ -9385,13 +9565,13 @@
       </c>
       <c r="T39" s="189"/>
       <c r="U39">
-        <v>78392</v>
+        <v>97283</v>
       </c>
       <c r="V39" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="W39">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.35">
@@ -9444,13 +9624,13 @@
       </c>
       <c r="T40" s="189"/>
       <c r="U40">
-        <v>146876</v>
+        <v>138121</v>
       </c>
       <c r="V40" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="W40">
-        <v>6.3E-2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.35">
@@ -9503,13 +9683,13 @@
       </c>
       <c r="T41" s="189"/>
       <c r="U41">
-        <v>190175</v>
+        <v>191078</v>
       </c>
       <c r="V41" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="W41">
-        <v>8.3000000000000004E-2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.35">
@@ -9562,13 +9742,13 @@
       </c>
       <c r="T42" s="189"/>
       <c r="U42">
-        <v>65847</v>
+        <v>186290</v>
       </c>
       <c r="V42" t="s">
-        <v>864</v>
+        <v>818</v>
       </c>
       <c r="W42">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.35">
@@ -9621,13 +9801,13 @@
       </c>
       <c r="T43" s="189"/>
       <c r="U43">
-        <v>83635</v>
+        <v>190430</v>
       </c>
       <c r="V43" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="W43">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.35">
@@ -9680,13 +9860,13 @@
       </c>
       <c r="T44" s="189"/>
       <c r="U44">
-        <v>166801</v>
+        <v>179875</v>
       </c>
       <c r="V44" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="W44" s="6">
-        <v>8.2919999999999998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.35">
@@ -9739,13 +9919,13 @@
       </c>
       <c r="T45" s="189"/>
       <c r="U45">
-        <v>185793</v>
+        <v>160349</v>
       </c>
       <c r="V45" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="W45">
-        <v>1.25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.35">
@@ -9798,13 +9978,13 @@
       </c>
       <c r="T46" s="189"/>
       <c r="U46">
-        <v>171037</v>
+        <v>151562</v>
       </c>
       <c r="V46" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="W46">
-        <v>6.3E-2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.35">
@@ -9857,13 +10037,13 @@
       </c>
       <c r="T47" s="189"/>
       <c r="U47">
-        <v>76162</v>
+        <v>184315</v>
       </c>
       <c r="V47" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="W47" s="6">
-        <v>0.25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.35">
@@ -9916,13 +10096,13 @@
       </c>
       <c r="T48" s="189"/>
       <c r="U48">
-        <v>185452</v>
+        <v>78137</v>
       </c>
       <c r="V48" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="W48">
-        <v>6.3E-2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.35">
@@ -9975,13 +10155,13 @@
       </c>
       <c r="T49" s="189"/>
       <c r="U49">
-        <v>72238</v>
+        <v>180559</v>
       </c>
       <c r="V49" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="W49">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.35">
@@ -10034,13 +10214,13 @@
       </c>
       <c r="T50" s="189"/>
       <c r="U50">
-        <v>107010</v>
+        <v>49448</v>
       </c>
       <c r="V50" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="W50">
-        <v>0.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.35">
@@ -10093,13 +10273,13 @@
       </c>
       <c r="T51" s="189"/>
       <c r="U51">
-        <v>183536</v>
+        <v>191179</v>
       </c>
       <c r="V51" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="W51">
-        <v>0.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.35">
@@ -10152,13 +10332,13 @@
       </c>
       <c r="T52" s="189"/>
       <c r="U52">
-        <v>56147</v>
+        <v>187104</v>
       </c>
       <c r="V52" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="W52">
-        <v>2.9580000000000002</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.35">
@@ -10191,7 +10371,7 @@
         <v>782</v>
       </c>
       <c r="K53" s="132">
-        <v>15.542</v>
+        <v>40.542000000000002</v>
       </c>
       <c r="M53" s="29" t="str">
         <f t="shared" si="1"/>
@@ -10211,13 +10391,13 @@
       </c>
       <c r="T53" s="189"/>
       <c r="U53">
-        <v>60157</v>
+        <v>144956</v>
       </c>
       <c r="V53" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="W53">
-        <v>0.45800000000000002</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:23" x14ac:dyDescent="0.35">
@@ -10270,13 +10450,13 @@
       </c>
       <c r="T54" s="189"/>
       <c r="U54">
-        <v>189031</v>
+        <v>187739</v>
       </c>
       <c r="V54" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="W54">
-        <v>4.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:23" x14ac:dyDescent="0.35">
@@ -10329,13 +10509,13 @@
       </c>
       <c r="T55" s="189"/>
       <c r="U55">
-        <v>177360</v>
+        <v>183442</v>
       </c>
       <c r="V55" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="W55">
-        <v>2.875</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:23" x14ac:dyDescent="0.35">
@@ -10388,13 +10568,13 @@
       </c>
       <c r="T56" s="189"/>
       <c r="U56">
-        <v>183412</v>
+        <v>181198</v>
       </c>
       <c r="V56" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
       <c r="W56">
-        <v>0.66700000000000004</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.35">
@@ -10447,13 +10627,13 @@
       </c>
       <c r="T57" s="189"/>
       <c r="U57">
-        <v>186963</v>
+        <v>79483</v>
       </c>
       <c r="V57" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="W57">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:23" x14ac:dyDescent="0.35">
@@ -10502,17 +10682,17 @@
         <v>782</v>
       </c>
       <c r="Q58">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="T58" s="189"/>
       <c r="U58">
-        <v>175417</v>
+        <v>191288</v>
       </c>
       <c r="V58" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="W58">
-        <v>2.25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.35">
@@ -10565,13 +10745,13 @@
       </c>
       <c r="T59" s="189"/>
       <c r="U59">
-        <v>191588</v>
+        <v>185439</v>
       </c>
       <c r="V59" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="W59">
-        <v>0.125</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.35">
@@ -10624,13 +10804,13 @@
       </c>
       <c r="T60" s="189"/>
       <c r="U60">
-        <v>178391</v>
+        <v>52759</v>
       </c>
       <c r="V60" t="s">
-        <v>820</v>
+        <v>885</v>
       </c>
       <c r="W60">
-        <v>8.0000000000000002E-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.35">
@@ -10683,13 +10863,13 @@
       </c>
       <c r="T61" s="189"/>
       <c r="U61">
-        <v>191110</v>
+        <v>95880</v>
       </c>
       <c r="V61" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="W61">
-        <v>1.3129999999999999</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62" spans="1:23" x14ac:dyDescent="0.35">
@@ -10742,13 +10922,13 @@
       </c>
       <c r="T62" s="189"/>
       <c r="U62">
-        <v>187551</v>
+        <v>81763</v>
       </c>
       <c r="V62" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="W62">
-        <v>0.33300000000000002</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63" spans="1:23" x14ac:dyDescent="0.35">
@@ -10801,13 +10981,13 @@
       </c>
       <c r="T63" s="189"/>
       <c r="U63">
-        <v>177082</v>
+        <v>49155</v>
       </c>
       <c r="V63" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="W63">
-        <v>4.8330000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:23" x14ac:dyDescent="0.35">
@@ -10860,13 +11040,13 @@
       </c>
       <c r="T64" s="189"/>
       <c r="U64">
-        <v>188815</v>
+        <v>192271</v>
       </c>
       <c r="V64" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
       <c r="W64">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.35">
@@ -10919,13 +11099,13 @@
       </c>
       <c r="T65" s="189"/>
       <c r="U65">
-        <v>59054</v>
+        <v>179847</v>
       </c>
       <c r="V65" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="W65">
-        <v>0.375</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:23" x14ac:dyDescent="0.35">
@@ -10978,13 +11158,13 @@
       </c>
       <c r="T66" s="189"/>
       <c r="U66">
-        <v>173081</v>
+        <v>53564</v>
       </c>
       <c r="V66" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="W66">
-        <v>6.3E-2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.35">
@@ -11037,13 +11217,13 @@
       </c>
       <c r="T67" s="189"/>
       <c r="U67">
-        <v>186941</v>
+        <v>53486</v>
       </c>
       <c r="V67" t="s">
-        <v>886</v>
+        <v>152</v>
       </c>
       <c r="W67">
-        <v>0.33300000000000002</v>
+        <v>278</v>
       </c>
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.35">
@@ -11096,13 +11276,13 @@
       </c>
       <c r="T68" s="189"/>
       <c r="U68">
-        <v>178092</v>
+        <v>159244</v>
       </c>
       <c r="V68" t="s">
-        <v>887</v>
+        <v>892</v>
       </c>
       <c r="W68" s="6">
-        <v>3.125</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69" spans="1:23" x14ac:dyDescent="0.35">
@@ -11155,13 +11335,13 @@
       </c>
       <c r="T69" s="189"/>
       <c r="U69">
-        <v>177066</v>
+        <v>103548</v>
       </c>
       <c r="V69" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="W69">
-        <v>0.25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.35">
@@ -11214,13 +11394,13 @@
       </c>
       <c r="T70" s="189"/>
       <c r="U70">
-        <v>149309</v>
+        <v>170536</v>
       </c>
       <c r="V70" t="s">
-        <v>889</v>
+        <v>894</v>
       </c>
       <c r="W70">
-        <v>1.667</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71" spans="1:23" x14ac:dyDescent="0.35">
@@ -11273,13 +11453,13 @@
       </c>
       <c r="T71" s="189"/>
       <c r="U71">
-        <v>169951</v>
+        <v>175546</v>
       </c>
       <c r="V71" t="s">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="W71">
-        <v>0.25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72" spans="1:23" x14ac:dyDescent="0.35">
@@ -11332,13 +11512,13 @@
       </c>
       <c r="T72" s="189"/>
       <c r="U72">
-        <v>188958</v>
+        <v>118812</v>
       </c>
       <c r="V72" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="W72">
-        <v>0.29199999999999998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:23" x14ac:dyDescent="0.35">
@@ -11387,17 +11567,17 @@
         <v>782</v>
       </c>
       <c r="Q73">
-        <v>12.125</v>
+        <v>15.958</v>
       </c>
       <c r="T73" s="189"/>
       <c r="U73">
-        <v>56267</v>
+        <v>187232</v>
       </c>
       <c r="V73" t="s">
-        <v>813</v>
+        <v>897</v>
       </c>
       <c r="W73">
-        <v>0.875</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:23" x14ac:dyDescent="0.35">
@@ -11450,13 +11630,13 @@
       </c>
       <c r="T74" s="189"/>
       <c r="U74">
-        <v>191893</v>
+        <v>104374</v>
       </c>
       <c r="V74" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="W74">
-        <v>1.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:23" x14ac:dyDescent="0.35">
@@ -11509,13 +11689,13 @@
       </c>
       <c r="T75" s="189"/>
       <c r="U75">
-        <v>190706</v>
+        <v>184901</v>
       </c>
       <c r="V75" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="W75">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.35">
@@ -11568,13 +11748,13 @@
       </c>
       <c r="T76" s="189"/>
       <c r="U76">
-        <v>177185</v>
+        <v>182083</v>
       </c>
       <c r="V76" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="W76" s="6">
-        <v>0.125</v>
+        <v>31</v>
       </c>
     </row>
     <row r="77" spans="1:23" x14ac:dyDescent="0.35">
@@ -11627,13 +11807,13 @@
       </c>
       <c r="T77" s="189"/>
       <c r="U77">
-        <v>172223</v>
+        <v>175581</v>
       </c>
       <c r="V77" t="s">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="W77">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:23" x14ac:dyDescent="0.35">
@@ -11686,13 +11866,13 @@
       </c>
       <c r="T78" s="189"/>
       <c r="U78">
-        <v>187406</v>
+        <v>187550</v>
       </c>
       <c r="V78" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="W78">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:23" x14ac:dyDescent="0.35">
@@ -11745,13 +11925,13 @@
       </c>
       <c r="T79" s="189"/>
       <c r="U79">
-        <v>183952</v>
+        <v>120720</v>
       </c>
       <c r="V79" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="W79">
-        <v>0.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.35">
@@ -11800,17 +11980,17 @@
         <v>782</v>
       </c>
       <c r="Q80">
-        <v>1.167</v>
+        <v>1.417</v>
       </c>
       <c r="T80" s="189"/>
       <c r="U80">
-        <v>186861</v>
+        <v>185387</v>
       </c>
       <c r="V80" t="s">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="W80">
-        <v>0.125</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:23" x14ac:dyDescent="0.35">
@@ -11863,13 +12043,13 @@
       </c>
       <c r="T81" s="189"/>
       <c r="U81">
-        <v>183483</v>
+        <v>110299</v>
       </c>
       <c r="V81" t="s">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="W81">
-        <v>0.125</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82" spans="1:23" x14ac:dyDescent="0.35">
@@ -11922,13 +12102,13 @@
       </c>
       <c r="T82" s="189"/>
       <c r="U82">
-        <v>185701</v>
+        <v>183684</v>
       </c>
       <c r="V82" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="W82">
-        <v>1.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:23" x14ac:dyDescent="0.35">
@@ -11981,13 +12161,13 @@
       </c>
       <c r="T83" s="189"/>
       <c r="U83">
-        <v>179892</v>
+        <v>157070</v>
       </c>
       <c r="V83" t="s">
-        <v>901</v>
+        <v>907</v>
       </c>
       <c r="W83">
-        <v>0.625</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.35">
@@ -12040,13 +12220,13 @@
       </c>
       <c r="T84" s="189"/>
       <c r="U84">
-        <v>190026</v>
+        <v>143434</v>
       </c>
       <c r="V84" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="W84">
-        <v>1.625</v>
+        <v>54</v>
       </c>
     </row>
     <row r="85" spans="1:23" x14ac:dyDescent="0.35">
@@ -12095,17 +12275,17 @@
         <v>782</v>
       </c>
       <c r="Q85">
-        <v>1.417</v>
+        <v>1.833</v>
       </c>
       <c r="T85" s="189"/>
       <c r="U85">
-        <v>185943</v>
+        <v>86590</v>
       </c>
       <c r="V85" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="W85">
-        <v>0.91700000000000004</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:23" x14ac:dyDescent="0.35">
@@ -12158,13 +12338,13 @@
       </c>
       <c r="T86" s="189"/>
       <c r="U86">
-        <v>178456</v>
+        <v>189435</v>
       </c>
       <c r="V86" t="s">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="W86" s="6">
-        <v>0.41699999999999998</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.35">
@@ -12217,13 +12397,13 @@
       </c>
       <c r="T87" s="189"/>
       <c r="U87">
-        <v>178900</v>
+        <v>174943</v>
       </c>
       <c r="V87" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="W87">
-        <v>1.208</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:23" x14ac:dyDescent="0.35">
@@ -12276,13 +12456,13 @@
       </c>
       <c r="T88" s="189"/>
       <c r="U88">
-        <v>192181</v>
+        <v>173892</v>
       </c>
       <c r="V88" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="W88">
-        <v>0.33300000000000002</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89" spans="1:23" x14ac:dyDescent="0.35">
@@ -12335,13 +12515,13 @@
       </c>
       <c r="T89" s="189"/>
       <c r="U89">
-        <v>115827</v>
+        <v>56267</v>
       </c>
       <c r="V89" t="s">
-        <v>907</v>
+        <v>812</v>
       </c>
       <c r="W89">
-        <v>0.41699999999999998</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90" spans="1:23" x14ac:dyDescent="0.35">
@@ -12394,13 +12574,13 @@
       </c>
       <c r="T90" s="189"/>
       <c r="U90">
-        <v>173883</v>
+        <v>49058</v>
       </c>
       <c r="V90" t="s">
-        <v>908</v>
+        <v>913</v>
       </c>
       <c r="W90">
-        <v>0.125</v>
+        <v>14</v>
       </c>
     </row>
     <row r="91" spans="1:23" x14ac:dyDescent="0.35">
@@ -12453,13 +12633,13 @@
       </c>
       <c r="T91" s="189"/>
       <c r="U91">
-        <v>174507</v>
+        <v>187645</v>
       </c>
       <c r="V91" t="s">
-        <v>909</v>
+        <v>914</v>
       </c>
       <c r="W91">
-        <v>1.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:23" x14ac:dyDescent="0.35">
@@ -12512,13 +12692,13 @@
       </c>
       <c r="T92" s="189"/>
       <c r="U92">
-        <v>175300</v>
+        <v>177256</v>
       </c>
       <c r="V92" t="s">
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="W92">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93" spans="1:23" x14ac:dyDescent="0.35">
@@ -12571,13 +12751,13 @@
       </c>
       <c r="T93" s="189"/>
       <c r="U93">
-        <v>179471</v>
+        <v>190435</v>
       </c>
       <c r="V93" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="W93">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:23" x14ac:dyDescent="0.35">
@@ -12630,13 +12810,13 @@
       </c>
       <c r="T94" s="189"/>
       <c r="U94">
-        <v>176368</v>
+        <v>182855</v>
       </c>
       <c r="V94" t="s">
-        <v>911</v>
+        <v>917</v>
       </c>
       <c r="W94">
-        <v>0.29199999999999998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:23" x14ac:dyDescent="0.35">
@@ -12689,13 +12869,13 @@
       </c>
       <c r="T95" s="189"/>
       <c r="U95">
-        <v>176084</v>
+        <v>180290</v>
       </c>
       <c r="V95" t="s">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="W95">
-        <v>0.66700000000000004</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96" spans="1:23" x14ac:dyDescent="0.35">
@@ -12748,13 +12928,13 @@
       </c>
       <c r="T96" s="189"/>
       <c r="U96">
-        <v>151842</v>
+        <v>182461</v>
       </c>
       <c r="V96" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="W96">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:23" x14ac:dyDescent="0.35">
@@ -12807,13 +12987,13 @@
       </c>
       <c r="T97" s="189"/>
       <c r="U97">
-        <v>187934</v>
+        <v>130361</v>
       </c>
       <c r="V97" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="W97">
-        <v>0.125</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98" spans="1:23" x14ac:dyDescent="0.35">
@@ -12866,13 +13046,13 @@
       </c>
       <c r="T98" s="189"/>
       <c r="U98">
-        <v>191183</v>
+        <v>60558</v>
       </c>
       <c r="V98" t="s">
-        <v>915</v>
+        <v>921</v>
       </c>
       <c r="W98">
-        <v>0.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99" spans="1:23" x14ac:dyDescent="0.35">
@@ -12925,13 +13105,13 @@
       </c>
       <c r="T99" s="189"/>
       <c r="U99">
-        <v>175490</v>
+        <v>190725</v>
       </c>
       <c r="V99" t="s">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="W99">
-        <v>10.458</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100" spans="1:23" x14ac:dyDescent="0.35">
@@ -12984,13 +13164,13 @@
       </c>
       <c r="T100" s="189"/>
       <c r="U100">
-        <v>151902</v>
+        <v>185258</v>
       </c>
       <c r="V100" t="s">
-        <v>917</v>
+        <v>923</v>
       </c>
       <c r="W100">
-        <v>1.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:23" x14ac:dyDescent="0.35">
@@ -13043,13 +13223,13 @@
       </c>
       <c r="T101" s="189"/>
       <c r="U101">
-        <v>191572</v>
+        <v>183952</v>
       </c>
       <c r="V101" t="s">
-        <v>918</v>
+        <v>819</v>
       </c>
       <c r="W101">
-        <v>3.125</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:23" x14ac:dyDescent="0.35">
@@ -13102,13 +13282,13 @@
       </c>
       <c r="T102" s="189"/>
       <c r="U102">
-        <v>179297</v>
+        <v>170747</v>
       </c>
       <c r="V102" t="s">
-        <v>919</v>
+        <v>924</v>
       </c>
       <c r="W102">
-        <v>0.16700000000000001</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103" spans="1:23" x14ac:dyDescent="0.35">
@@ -13161,13 +13341,13 @@
       </c>
       <c r="T103" s="189"/>
       <c r="U103">
-        <v>171477</v>
+        <v>184667</v>
       </c>
       <c r="V103" t="s">
-        <v>920</v>
+        <v>925</v>
       </c>
       <c r="W103" s="6">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:23" x14ac:dyDescent="0.35">
@@ -13220,13 +13400,13 @@
       </c>
       <c r="T104" s="189"/>
       <c r="U104">
-        <v>172399</v>
+        <v>172345</v>
       </c>
       <c r="V104" t="s">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="W104">
-        <v>0.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:23" x14ac:dyDescent="0.35">
@@ -13279,13 +13459,13 @@
       </c>
       <c r="T105" s="189"/>
       <c r="U105">
-        <v>175491</v>
+        <v>177610</v>
       </c>
       <c r="V105" t="s">
-        <v>922</v>
+        <v>927</v>
       </c>
       <c r="W105">
-        <v>0.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106" spans="1:23" x14ac:dyDescent="0.35">
@@ -13338,13 +13518,13 @@
       </c>
       <c r="T106" s="189"/>
       <c r="U106">
-        <v>184478</v>
+        <v>185652</v>
       </c>
       <c r="V106" t="s">
-        <v>923</v>
+        <v>928</v>
       </c>
       <c r="W106">
-        <v>0.16700000000000001</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107" spans="1:23" x14ac:dyDescent="0.35">
@@ -13397,13 +13577,13 @@
       </c>
       <c r="T107" s="189"/>
       <c r="U107">
-        <v>187214</v>
+        <v>176772</v>
       </c>
       <c r="V107" t="s">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="W107">
-        <v>0.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="108" spans="1:23" x14ac:dyDescent="0.35">
@@ -13456,13 +13636,13 @@
       </c>
       <c r="T108" s="189"/>
       <c r="U108">
-        <v>184041</v>
+        <v>128290</v>
       </c>
       <c r="V108" t="s">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="W108">
-        <v>0.125</v>
+        <v>11</v>
       </c>
     </row>
     <row r="109" spans="1:23" x14ac:dyDescent="0.35">
@@ -13515,13 +13695,13 @@
       </c>
       <c r="T109" s="189"/>
       <c r="U109">
-        <v>142238</v>
+        <v>167523</v>
       </c>
       <c r="V109" t="s">
-        <v>926</v>
+        <v>931</v>
       </c>
       <c r="W109">
-        <v>0.45800000000000002</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110" spans="1:23" x14ac:dyDescent="0.35">
@@ -13574,13 +13754,13 @@
       </c>
       <c r="T110" s="189"/>
       <c r="U110">
-        <v>170644</v>
+        <v>190025</v>
       </c>
       <c r="V110" t="s">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="W110" s="6">
-        <v>1.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:23" x14ac:dyDescent="0.35">
@@ -13633,13 +13813,13 @@
       </c>
       <c r="T111" s="189"/>
       <c r="U111">
-        <v>110431</v>
+        <v>188213</v>
       </c>
       <c r="V111" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="W111">
-        <v>4.2000000000000003E-2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="112" spans="1:23" x14ac:dyDescent="0.35">
@@ -13672,7 +13852,7 @@
         <v>782</v>
       </c>
       <c r="K112" s="131">
-        <v>-1.194</v>
+        <v>90.471999999999994</v>
       </c>
       <c r="M112" s="29" t="str">
         <f t="shared" si="3"/>
@@ -13692,13 +13872,13 @@
       </c>
       <c r="T112" s="189"/>
       <c r="U112">
-        <v>178798</v>
+        <v>188820</v>
       </c>
       <c r="V112" t="s">
-        <v>929</v>
+        <v>934</v>
       </c>
       <c r="W112">
-        <v>0.188</v>
+        <v>13</v>
       </c>
     </row>
     <row r="113" spans="1:23" x14ac:dyDescent="0.35">
@@ -13751,13 +13931,13 @@
       </c>
       <c r="T113" s="189"/>
       <c r="U113">
-        <v>178959</v>
+        <v>189869</v>
       </c>
       <c r="V113" t="s">
-        <v>930</v>
+        <v>935</v>
       </c>
       <c r="W113">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:23" x14ac:dyDescent="0.35">
@@ -13810,13 +13990,13 @@
       </c>
       <c r="T114" s="189"/>
       <c r="U114">
-        <v>150803</v>
+        <v>166881</v>
       </c>
       <c r="V114" t="s">
-        <v>931</v>
+        <v>936</v>
       </c>
       <c r="W114">
-        <v>2.25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115" spans="1:23" x14ac:dyDescent="0.35">
@@ -13869,13 +14049,13 @@
       </c>
       <c r="T115" s="189"/>
       <c r="U115">
-        <v>190011</v>
+        <v>149666</v>
       </c>
       <c r="V115" t="s">
-        <v>932</v>
+        <v>937</v>
       </c>
       <c r="W115">
-        <v>0.25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="116" spans="1:23" x14ac:dyDescent="0.35">
@@ -13928,13 +14108,13 @@
       </c>
       <c r="T116" s="189"/>
       <c r="U116">
-        <v>192329</v>
+        <v>178697</v>
       </c>
       <c r="V116" t="s">
-        <v>933</v>
+        <v>938</v>
       </c>
       <c r="W116">
-        <v>0.125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:23" x14ac:dyDescent="0.35">
@@ -13971,13 +14151,13 @@
       </c>
       <c r="T117" s="189"/>
       <c r="U117">
-        <v>48656</v>
+        <v>136382</v>
       </c>
       <c r="V117" t="s">
-        <v>934</v>
+        <v>939</v>
       </c>
       <c r="W117">
-        <v>0.33300000000000002</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:23" x14ac:dyDescent="0.35">
@@ -14014,13 +14194,13 @@
       </c>
       <c r="T118" s="189"/>
       <c r="U118">
-        <v>167220</v>
+        <v>78885</v>
       </c>
       <c r="V118" t="s">
-        <v>821</v>
+        <v>940</v>
       </c>
       <c r="W118">
-        <v>1.75</v>
+        <v>4</v>
       </c>
     </row>
     <row r="119" spans="1:23" x14ac:dyDescent="0.35">
@@ -14057,13 +14237,13 @@
       </c>
       <c r="T119" s="189"/>
       <c r="U119">
-        <v>186132</v>
+        <v>81753</v>
       </c>
       <c r="V119" t="s">
-        <v>935</v>
+        <v>941</v>
       </c>
       <c r="W119">
-        <v>0.125</v>
+        <v>15</v>
       </c>
     </row>
     <row r="120" spans="1:23" x14ac:dyDescent="0.35">
@@ -14100,13 +14280,13 @@
       </c>
       <c r="T120" s="189"/>
       <c r="U120">
-        <v>71688</v>
+        <v>191269</v>
       </c>
       <c r="V120" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="W120">
-        <v>0.75</v>
+        <v>4</v>
       </c>
     </row>
     <row r="121" spans="1:23" x14ac:dyDescent="0.35">
@@ -14143,13 +14323,13 @@
       </c>
       <c r="T121" s="189"/>
       <c r="U121">
-        <v>189787</v>
+        <v>176072</v>
       </c>
       <c r="V121" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="W121">
-        <v>1.167</v>
+        <v>4</v>
       </c>
     </row>
     <row r="122" spans="1:23" x14ac:dyDescent="0.35">
@@ -14186,13 +14366,13 @@
       </c>
       <c r="T122" s="189"/>
       <c r="U122">
-        <v>171102</v>
+        <v>181571</v>
       </c>
       <c r="V122" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="W122">
-        <v>0.58299999999999996</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:23" x14ac:dyDescent="0.35">
@@ -14229,13 +14409,13 @@
       </c>
       <c r="T123" s="189"/>
       <c r="U123">
-        <v>84513</v>
+        <v>177136</v>
       </c>
       <c r="V123" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="W123">
-        <v>1.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:23" x14ac:dyDescent="0.35">
@@ -14272,13 +14452,13 @@
       </c>
       <c r="T124" s="189"/>
       <c r="U124">
-        <v>190885</v>
+        <v>185514</v>
       </c>
       <c r="V124" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="W124">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:23" x14ac:dyDescent="0.35">
@@ -14315,13 +14495,13 @@
       </c>
       <c r="T125" s="189"/>
       <c r="U125">
-        <v>176583</v>
+        <v>173639</v>
       </c>
       <c r="V125" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="W125">
-        <v>0.33300000000000002</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126" spans="1:23" x14ac:dyDescent="0.35">
@@ -14358,13 +14538,13 @@
       </c>
       <c r="T126" s="189"/>
       <c r="U126">
-        <v>189499</v>
+        <v>177239</v>
       </c>
       <c r="V126" t="s">
-        <v>814</v>
+        <v>948</v>
       </c>
       <c r="W126">
-        <v>1.167</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127" spans="1:23" x14ac:dyDescent="0.35">
@@ -14401,13 +14581,13 @@
       </c>
       <c r="T127" s="189"/>
       <c r="U127">
-        <v>107809</v>
+        <v>50408</v>
       </c>
       <c r="V127" t="s">
-        <v>942</v>
+        <v>949</v>
       </c>
       <c r="W127">
-        <v>0.33300000000000002</v>
+        <v>8</v>
       </c>
     </row>
     <row r="128" spans="1:23" x14ac:dyDescent="0.35">
@@ -14444,13 +14624,13 @@
       </c>
       <c r="T128" s="189"/>
       <c r="U128">
-        <v>122250</v>
+        <v>53658</v>
       </c>
       <c r="V128" t="s">
-        <v>943</v>
+        <v>950</v>
       </c>
       <c r="W128">
-        <v>2.0830000000000002</v>
+        <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:23" x14ac:dyDescent="0.35">
@@ -14487,13 +14667,13 @@
       </c>
       <c r="T129" s="189"/>
       <c r="U129">
-        <v>60240</v>
+        <v>113279</v>
       </c>
       <c r="V129" t="s">
-        <v>944</v>
+        <v>951</v>
       </c>
       <c r="W129">
-        <v>0.75</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130" spans="1:23" x14ac:dyDescent="0.35">
@@ -14530,13 +14710,13 @@
       </c>
       <c r="T130" s="189"/>
       <c r="U130">
-        <v>171213</v>
+        <v>186822</v>
       </c>
       <c r="V130" t="s">
-        <v>822</v>
+        <v>952</v>
       </c>
       <c r="W130">
-        <v>0.56299999999999994</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131" spans="1:23" x14ac:dyDescent="0.35">
@@ -14573,13 +14753,13 @@
       </c>
       <c r="T131" s="189"/>
       <c r="U131">
-        <v>185534</v>
+        <v>187934</v>
       </c>
       <c r="V131" t="s">
-        <v>945</v>
+        <v>820</v>
       </c>
       <c r="W131">
-        <v>1.583</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132" spans="1:23" x14ac:dyDescent="0.35">
@@ -14616,13 +14796,13 @@
       </c>
       <c r="T132" s="189"/>
       <c r="U132">
-        <v>188295</v>
+        <v>81686</v>
       </c>
       <c r="V132" t="s">
-        <v>946</v>
+        <v>953</v>
       </c>
       <c r="W132">
-        <v>0.375</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:23" x14ac:dyDescent="0.35">
@@ -14659,13 +14839,13 @@
       </c>
       <c r="T133" s="189"/>
       <c r="U133">
-        <v>181235</v>
+        <v>191183</v>
       </c>
       <c r="V133" t="s">
-        <v>947</v>
+        <v>821</v>
       </c>
       <c r="W133">
-        <v>0.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="134" spans="1:23" x14ac:dyDescent="0.35">
@@ -14702,13 +14882,13 @@
       </c>
       <c r="T134" s="189"/>
       <c r="U134">
-        <v>157335</v>
+        <v>187604</v>
       </c>
       <c r="V134" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="W134">
-        <v>0.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="135" spans="1:23" x14ac:dyDescent="0.35">
@@ -14745,13 +14925,13 @@
       </c>
       <c r="T135" s="189"/>
       <c r="U135">
-        <v>67547</v>
+        <v>162459</v>
       </c>
       <c r="V135" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="W135">
-        <v>0.81299999999999994</v>
+        <v>8</v>
       </c>
     </row>
     <row r="136" spans="1:23" x14ac:dyDescent="0.35">
@@ -14788,13 +14968,13 @@
       </c>
       <c r="T136" s="189"/>
       <c r="U136">
-        <v>179655</v>
+        <v>189371</v>
       </c>
       <c r="V136" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="W136">
-        <v>0.25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="137" spans="1:23" x14ac:dyDescent="0.35">
@@ -14831,13 +15011,13 @@
       </c>
       <c r="T137" s="189"/>
       <c r="U137">
-        <v>185105</v>
+        <v>185310</v>
       </c>
       <c r="V137" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
       <c r="W137">
-        <v>1.417</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138" spans="1:23" x14ac:dyDescent="0.35">
@@ -14874,13 +15054,13 @@
       </c>
       <c r="T138" s="189"/>
       <c r="U138">
-        <v>57400</v>
+        <v>181383</v>
       </c>
       <c r="V138" t="s">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="W138">
-        <v>2.125</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139" spans="1:23" x14ac:dyDescent="0.35">
@@ -14917,13 +15097,13 @@
       </c>
       <c r="T139" s="189"/>
       <c r="U139">
-        <v>179207</v>
+        <v>191572</v>
       </c>
       <c r="V139" t="s">
-        <v>953</v>
+        <v>822</v>
       </c>
       <c r="W139">
-        <v>0.16700000000000001</v>
+        <v>15</v>
       </c>
     </row>
     <row r="140" spans="1:23" x14ac:dyDescent="0.35">
@@ -14960,13 +15140,13 @@
       </c>
       <c r="T140" s="189"/>
       <c r="U140">
-        <v>192217</v>
+        <v>183044</v>
       </c>
       <c r="V140" t="s">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="W140">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:23" x14ac:dyDescent="0.35">
@@ -15003,13 +15183,13 @@
       </c>
       <c r="T141" s="189"/>
       <c r="U141">
-        <v>170081</v>
+        <v>177072</v>
       </c>
       <c r="V141" t="s">
-        <v>955</v>
+        <v>960</v>
       </c>
       <c r="W141">
-        <v>2.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:23" x14ac:dyDescent="0.35">
@@ -15046,13 +15226,13 @@
       </c>
       <c r="T142" s="189"/>
       <c r="U142">
-        <v>181867</v>
+        <v>190956</v>
       </c>
       <c r="V142" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="W142">
-        <v>8.3000000000000004E-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:23" x14ac:dyDescent="0.35">
@@ -15089,13 +15269,13 @@
       </c>
       <c r="T143" s="189"/>
       <c r="U143">
-        <v>53597</v>
+        <v>166295</v>
       </c>
       <c r="V143" t="s">
-        <v>823</v>
+        <v>962</v>
       </c>
       <c r="W143">
-        <v>1.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144" spans="1:23" x14ac:dyDescent="0.35">
@@ -15132,13 +15312,13 @@
       </c>
       <c r="T144" s="189"/>
       <c r="U144">
-        <v>178844</v>
+        <v>126070</v>
       </c>
       <c r="V144" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="W144">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:23" x14ac:dyDescent="0.35">
@@ -15175,13 +15355,13 @@
       </c>
       <c r="T145" s="189"/>
       <c r="U145">
-        <v>133018</v>
+        <v>110898</v>
       </c>
       <c r="V145" t="s">
-        <v>815</v>
+        <v>964</v>
       </c>
       <c r="W145">
-        <v>0.375</v>
+        <v>6</v>
       </c>
     </row>
     <row r="146" spans="1:23" x14ac:dyDescent="0.35">
@@ -15218,13 +15398,13 @@
       </c>
       <c r="T146" s="189"/>
       <c r="U146">
-        <v>170766</v>
+        <v>189286</v>
       </c>
       <c r="V146" t="s">
-        <v>958</v>
+        <v>965</v>
       </c>
       <c r="W146">
-        <v>0.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147" spans="1:23" x14ac:dyDescent="0.35">
@@ -15261,13 +15441,13 @@
       </c>
       <c r="T147" s="189"/>
       <c r="U147">
-        <v>188162</v>
+        <v>184987</v>
       </c>
       <c r="V147" t="s">
-        <v>959</v>
+        <v>966</v>
       </c>
       <c r="W147">
-        <v>0.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148" spans="1:23" x14ac:dyDescent="0.35">
@@ -15304,13 +15484,13 @@
       </c>
       <c r="T148" s="189"/>
       <c r="U148">
-        <v>186857</v>
+        <v>63095</v>
       </c>
       <c r="V148" t="s">
-        <v>960</v>
+        <v>967</v>
       </c>
       <c r="W148">
-        <v>0.625</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:23" x14ac:dyDescent="0.35">
@@ -15347,13 +15527,13 @@
       </c>
       <c r="T149" s="189"/>
       <c r="U149">
-        <v>171110</v>
+        <v>78883</v>
       </c>
       <c r="V149" t="s">
-        <v>961</v>
+        <v>968</v>
       </c>
       <c r="W149">
-        <v>0.625</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150" spans="1:23" x14ac:dyDescent="0.35">
@@ -15390,13 +15570,13 @@
       </c>
       <c r="T150" s="189"/>
       <c r="U150">
-        <v>190930</v>
+        <v>132954</v>
       </c>
       <c r="V150" t="s">
-        <v>962</v>
+        <v>969</v>
       </c>
       <c r="W150">
-        <v>1.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="151" spans="1:23" x14ac:dyDescent="0.35">
@@ -15433,13 +15613,13 @@
       </c>
       <c r="T151" s="189"/>
       <c r="U151">
-        <v>186610</v>
+        <v>179631</v>
       </c>
       <c r="V151" t="s">
-        <v>963</v>
+        <v>970</v>
       </c>
       <c r="W151">
-        <v>2.125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:23" x14ac:dyDescent="0.35">
@@ -15476,13 +15656,13 @@
       </c>
       <c r="T152" s="189"/>
       <c r="U152">
-        <v>186110</v>
+        <v>188372</v>
       </c>
       <c r="V152" t="s">
-        <v>964</v>
+        <v>971</v>
       </c>
       <c r="W152">
-        <v>0.33300000000000002</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:23" x14ac:dyDescent="0.35">
@@ -15519,13 +15699,13 @@
       </c>
       <c r="T153" s="189"/>
       <c r="U153">
-        <v>186166</v>
+        <v>191842</v>
       </c>
       <c r="V153" t="s">
-        <v>964</v>
+        <v>972</v>
       </c>
       <c r="W153">
-        <v>4.7919999999999998</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154" spans="1:23" x14ac:dyDescent="0.35">
@@ -15562,13 +15742,13 @@
       </c>
       <c r="T154" s="189"/>
       <c r="U154">
-        <v>191696</v>
+        <v>81470</v>
       </c>
       <c r="V154" t="s">
-        <v>824</v>
+        <v>973</v>
       </c>
       <c r="W154">
-        <v>2.25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155" spans="1:23" x14ac:dyDescent="0.35">
@@ -15605,13 +15785,13 @@
       </c>
       <c r="T155" s="189"/>
       <c r="U155">
-        <v>72858</v>
+        <v>96057</v>
       </c>
       <c r="V155" t="s">
-        <v>965</v>
+        <v>974</v>
       </c>
       <c r="W155">
-        <v>0.75</v>
+        <v>17</v>
       </c>
     </row>
     <row r="156" spans="1:23" x14ac:dyDescent="0.35">
@@ -15648,13 +15828,13 @@
       </c>
       <c r="T156" s="189"/>
       <c r="U156">
-        <v>191879</v>
+        <v>191461</v>
       </c>
       <c r="V156" t="s">
-        <v>966</v>
+        <v>975</v>
       </c>
       <c r="W156">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="157" spans="1:23" x14ac:dyDescent="0.35">
@@ -15691,13 +15871,13 @@
       </c>
       <c r="T157" s="189"/>
       <c r="U157">
-        <v>90366</v>
+        <v>176933</v>
       </c>
       <c r="V157" t="s">
-        <v>967</v>
+        <v>976</v>
       </c>
       <c r="W157">
-        <v>1.208</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:23" x14ac:dyDescent="0.35">
@@ -15734,13 +15914,13 @@
       </c>
       <c r="T158" s="189"/>
       <c r="U158">
-        <v>57999</v>
+        <v>189787</v>
       </c>
       <c r="V158" t="s">
-        <v>968</v>
+        <v>823</v>
       </c>
       <c r="W158">
-        <v>0.68799999999999994</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:23" x14ac:dyDescent="0.35">
@@ -15777,13 +15957,13 @@
       </c>
       <c r="T159" s="189"/>
       <c r="U159">
-        <v>187520</v>
+        <v>190012</v>
       </c>
       <c r="V159" t="s">
-        <v>969</v>
+        <v>977</v>
       </c>
       <c r="W159">
-        <v>0.188</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160" spans="1:23" x14ac:dyDescent="0.35">
@@ -15820,13 +16000,13 @@
       </c>
       <c r="T160" s="189"/>
       <c r="U160">
-        <v>146387</v>
+        <v>191246</v>
       </c>
       <c r="V160" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
       <c r="W160">
-        <v>0.58299999999999996</v>
+        <v>16</v>
       </c>
     </row>
     <row r="161" spans="1:23" x14ac:dyDescent="0.35">
@@ -15863,13 +16043,13 @@
       </c>
       <c r="T161" s="189"/>
       <c r="U161">
-        <v>99686</v>
+        <v>179244</v>
       </c>
       <c r="V161" t="s">
-        <v>971</v>
+        <v>979</v>
       </c>
       <c r="W161">
-        <v>0.25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162" spans="1:23" x14ac:dyDescent="0.35">
@@ -15906,13 +16086,13 @@
       </c>
       <c r="T162" s="189"/>
       <c r="U162">
-        <v>55925</v>
+        <v>117571</v>
       </c>
       <c r="V162" t="s">
-        <v>972</v>
+        <v>980</v>
       </c>
       <c r="W162">
-        <v>0.875</v>
+        <v>4</v>
       </c>
     </row>
     <row r="163" spans="1:23" x14ac:dyDescent="0.35">
@@ -15949,13 +16129,13 @@
       </c>
       <c r="T163" s="189"/>
       <c r="U163">
-        <v>124686</v>
+        <v>112612</v>
       </c>
       <c r="V163" t="s">
-        <v>973</v>
+        <v>981</v>
       </c>
       <c r="W163">
-        <v>0.54200000000000004</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164" spans="1:23" x14ac:dyDescent="0.35">
@@ -15992,13 +16172,13 @@
       </c>
       <c r="T164" s="189"/>
       <c r="U164">
-        <v>181202</v>
+        <v>168638</v>
       </c>
       <c r="V164" t="s">
-        <v>974</v>
+        <v>982</v>
       </c>
       <c r="W164">
-        <v>0.125</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165" spans="1:23" x14ac:dyDescent="0.35">
@@ -16035,13 +16215,13 @@
       </c>
       <c r="T165" s="189"/>
       <c r="U165">
-        <v>185944</v>
+        <v>129937</v>
       </c>
       <c r="V165" t="s">
-        <v>975</v>
+        <v>983</v>
       </c>
       <c r="W165">
-        <v>1.25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="166" spans="1:23" x14ac:dyDescent="0.35">
@@ -16078,13 +16258,13 @@
       </c>
       <c r="T166" s="189"/>
       <c r="U166">
-        <v>184617</v>
+        <v>191982</v>
       </c>
       <c r="V166" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
       <c r="W166">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:23" x14ac:dyDescent="0.35">
@@ -16121,13 +16301,13 @@
       </c>
       <c r="T167" s="189"/>
       <c r="U167">
-        <v>65370</v>
+        <v>49837</v>
       </c>
       <c r="V167" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
       <c r="W167">
-        <v>0.25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168" spans="1:23" x14ac:dyDescent="0.35">
@@ -16164,13 +16344,13 @@
       </c>
       <c r="T168" s="189"/>
       <c r="U168">
-        <v>94355</v>
+        <v>189481</v>
       </c>
       <c r="V168" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
       <c r="W168">
-        <v>0.25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="169" spans="1:23" x14ac:dyDescent="0.35">
@@ -16207,13 +16387,13 @@
       </c>
       <c r="T169" s="189"/>
       <c r="U169">
-        <v>68160</v>
+        <v>189270</v>
       </c>
       <c r="V169" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="W169">
-        <v>1.25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="170" spans="1:23" x14ac:dyDescent="0.35">
@@ -16250,13 +16430,13 @@
       </c>
       <c r="T170" s="189"/>
       <c r="U170">
-        <v>179024</v>
+        <v>187468</v>
       </c>
       <c r="V170" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
       <c r="W170">
-        <v>2.4380000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171" spans="1:23" x14ac:dyDescent="0.35">
@@ -16293,13 +16473,13 @@
       </c>
       <c r="T171" s="189"/>
       <c r="U171">
-        <v>191534</v>
+        <v>121530</v>
       </c>
       <c r="V171" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
       <c r="W171">
-        <v>0.625</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:23" x14ac:dyDescent="0.35">
@@ -16336,13 +16516,13 @@
       </c>
       <c r="T172" s="189"/>
       <c r="U172">
-        <v>174479</v>
+        <v>107896</v>
       </c>
       <c r="V172" t="s">
-        <v>982</v>
+        <v>990</v>
       </c>
       <c r="W172">
-        <v>1.375</v>
+        <v>6</v>
       </c>
     </row>
     <row r="173" spans="1:23" x14ac:dyDescent="0.35">
@@ -16379,13 +16559,13 @@
       </c>
       <c r="T173" s="189"/>
       <c r="U173">
-        <v>56532</v>
+        <v>164076</v>
       </c>
       <c r="V173" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="W173">
-        <v>0.188</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174" spans="1:23" x14ac:dyDescent="0.35">
@@ -16422,13 +16602,13 @@
       </c>
       <c r="T174" s="189"/>
       <c r="U174">
-        <v>191546</v>
+        <v>179842</v>
       </c>
       <c r="V174" t="s">
-        <v>984</v>
+        <v>992</v>
       </c>
       <c r="W174">
-        <v>0.68799999999999994</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:23" x14ac:dyDescent="0.35">
@@ -16465,13 +16645,13 @@
       </c>
       <c r="T175" s="189"/>
       <c r="U175">
-        <v>186006</v>
+        <v>182600</v>
       </c>
       <c r="V175" t="s">
-        <v>985</v>
+        <v>993</v>
       </c>
       <c r="W175">
-        <v>8.5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="176" spans="1:23" x14ac:dyDescent="0.35">
@@ -16508,13 +16688,13 @@
       </c>
       <c r="T176" s="189"/>
       <c r="U176">
-        <v>97252</v>
+        <v>67814</v>
       </c>
       <c r="V176" t="s">
-        <v>816</v>
+        <v>994</v>
       </c>
       <c r="W176">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177" spans="1:23" x14ac:dyDescent="0.35">
@@ -16551,13 +16731,13 @@
       </c>
       <c r="T177" s="189"/>
       <c r="U177">
-        <v>173116</v>
+        <v>118024</v>
       </c>
       <c r="V177" t="s">
-        <v>986</v>
+        <v>995</v>
       </c>
       <c r="W177">
-        <v>6.3E-2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="178" spans="1:23" x14ac:dyDescent="0.35">
@@ -16594,13 +16774,13 @@
       </c>
       <c r="T178" s="189"/>
       <c r="U178">
-        <v>170833</v>
+        <v>102288</v>
       </c>
       <c r="V178" t="s">
-        <v>987</v>
+        <v>996</v>
       </c>
       <c r="W178">
-        <v>1.167</v>
+        <v>16</v>
       </c>
     </row>
     <row r="179" spans="1:23" x14ac:dyDescent="0.35">
@@ -16637,13 +16817,13 @@
       </c>
       <c r="T179" s="189"/>
       <c r="U179">
-        <v>78425</v>
+        <v>187559</v>
       </c>
       <c r="V179" t="s">
-        <v>988</v>
+        <v>997</v>
       </c>
       <c r="W179">
-        <v>0.16700000000000001</v>
+        <v>31</v>
       </c>
     </row>
     <row r="180" spans="1:23" x14ac:dyDescent="0.35">
@@ -16680,13 +16860,13 @@
       </c>
       <c r="T180" s="189"/>
       <c r="U180">
-        <v>71424</v>
+        <v>166835</v>
       </c>
       <c r="V180" t="s">
-        <v>989</v>
+        <v>998</v>
       </c>
       <c r="W180" s="6">
-        <v>0.16700000000000001</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181" spans="1:23" x14ac:dyDescent="0.35">
@@ -16723,13 +16903,13 @@
       </c>
       <c r="T181" s="189"/>
       <c r="U181">
-        <v>132944</v>
+        <v>169839</v>
       </c>
       <c r="V181" t="s">
-        <v>990</v>
+        <v>999</v>
       </c>
       <c r="W181">
-        <v>0.25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="182" spans="1:23" x14ac:dyDescent="0.35">
@@ -16766,13 +16946,13 @@
       </c>
       <c r="T182" s="189"/>
       <c r="U182">
-        <v>68219</v>
+        <v>187042</v>
       </c>
       <c r="V182" t="s">
-        <v>991</v>
+        <v>1000</v>
       </c>
       <c r="W182">
-        <v>0.25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="183" spans="1:23" x14ac:dyDescent="0.35">
@@ -16809,13 +16989,13 @@
       </c>
       <c r="T183" s="189"/>
       <c r="U183">
-        <v>81308</v>
+        <v>188606</v>
       </c>
       <c r="V183" t="s">
-        <v>992</v>
+        <v>1001</v>
       </c>
       <c r="W183">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:23" x14ac:dyDescent="0.35">
@@ -16852,13 +17032,13 @@
       </c>
       <c r="T184" s="189"/>
       <c r="U184">
-        <v>182016</v>
+        <v>50502</v>
       </c>
       <c r="V184" t="s">
-        <v>993</v>
+        <v>1002</v>
       </c>
       <c r="W184">
-        <v>0.5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="185" spans="1:23" x14ac:dyDescent="0.35">
@@ -16895,13 +17075,13 @@
       </c>
       <c r="T185" s="184"/>
       <c r="U185">
-        <v>177577</v>
+        <v>49350</v>
       </c>
       <c r="V185" t="s">
-        <v>994</v>
+        <v>1003</v>
       </c>
       <c r="W185">
-        <v>1.375</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186" spans="1:23" x14ac:dyDescent="0.35">
@@ -16938,13 +17118,13 @@
       </c>
       <c r="T186" s="184"/>
       <c r="U186">
-        <v>155689</v>
+        <v>190285</v>
       </c>
       <c r="V186" t="s">
-        <v>817</v>
+        <v>1004</v>
       </c>
       <c r="W186">
-        <v>1.167</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187" spans="1:23" x14ac:dyDescent="0.35">
@@ -16981,13 +17161,13 @@
       </c>
       <c r="T187" s="184"/>
       <c r="U187">
-        <v>191402</v>
+        <v>126732</v>
       </c>
       <c r="V187" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="W187">
-        <v>0.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188" spans="1:23" x14ac:dyDescent="0.35">
@@ -17024,13 +17204,13 @@
       </c>
       <c r="T188" s="184"/>
       <c r="U188">
-        <v>191081</v>
+        <v>167101</v>
       </c>
       <c r="V188" t="s">
-        <v>996</v>
+        <v>1006</v>
       </c>
       <c r="W188">
-        <v>0.16700000000000001</v>
+        <v>20</v>
       </c>
     </row>
     <row r="189" spans="1:23" x14ac:dyDescent="0.35">
@@ -17063,17 +17243,17 @@
         <v>782</v>
       </c>
       <c r="K189">
-        <v>78.167000000000002</v>
+        <v>103.333</v>
       </c>
       <c r="T189" s="184"/>
       <c r="U189">
-        <v>189060</v>
+        <v>189055</v>
       </c>
       <c r="V189" t="s">
-        <v>997</v>
+        <v>1007</v>
       </c>
       <c r="W189" s="6">
-        <v>0.25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="190" spans="1:23" x14ac:dyDescent="0.35">
@@ -17110,13 +17290,13 @@
       </c>
       <c r="T190" s="184"/>
       <c r="U190">
-        <v>116252</v>
+        <v>186069</v>
       </c>
       <c r="V190" t="s">
-        <v>998</v>
+        <v>1008</v>
       </c>
       <c r="W190">
-        <v>8.3000000000000004E-2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:23" x14ac:dyDescent="0.35">
@@ -17153,13 +17333,13 @@
       </c>
       <c r="T191" s="184"/>
       <c r="U191">
-        <v>167201</v>
+        <v>191618</v>
       </c>
       <c r="V191" t="s">
-        <v>999</v>
+        <v>1009</v>
       </c>
       <c r="W191">
-        <v>8.3000000000000004E-2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="192" spans="1:23" x14ac:dyDescent="0.35">
@@ -17196,13 +17376,13 @@
       </c>
       <c r="T192" s="184"/>
       <c r="U192">
-        <v>97075</v>
+        <v>143381</v>
       </c>
       <c r="V192" t="s">
-        <v>1000</v>
+        <v>1010</v>
       </c>
       <c r="W192">
-        <v>6.3E-2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="193" spans="1:23" x14ac:dyDescent="0.35">
@@ -17239,13 +17419,13 @@
       </c>
       <c r="T193" s="184"/>
       <c r="U193">
-        <v>76125</v>
+        <v>54494</v>
       </c>
       <c r="V193" t="s">
-        <v>1001</v>
+        <v>1011</v>
       </c>
       <c r="W193">
-        <v>6.3E-2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="194" spans="1:23" x14ac:dyDescent="0.35">
@@ -17282,13 +17462,13 @@
       </c>
       <c r="T194" s="184"/>
       <c r="U194">
-        <v>156331</v>
+        <v>164874</v>
       </c>
       <c r="V194" t="s">
-        <v>1002</v>
+        <v>1012</v>
       </c>
       <c r="W194">
-        <v>0.33300000000000002</v>
+        <v>9</v>
       </c>
     </row>
     <row r="195" spans="1:23" x14ac:dyDescent="0.35">
@@ -17325,13 +17505,13 @@
       </c>
       <c r="T195" s="184"/>
       <c r="U195">
-        <v>188984</v>
+        <v>182890</v>
       </c>
       <c r="V195" t="s">
-        <v>1003</v>
+        <v>1012</v>
       </c>
       <c r="W195">
-        <v>0.375</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196" spans="1:23" x14ac:dyDescent="0.35">
@@ -17368,13 +17548,13 @@
       </c>
       <c r="T196" s="184"/>
       <c r="U196">
-        <v>107898</v>
+        <v>117175</v>
       </c>
       <c r="V196" t="s">
-        <v>1004</v>
+        <v>1013</v>
       </c>
       <c r="W196">
-        <v>0.33300000000000002</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:23" x14ac:dyDescent="0.35">
@@ -17411,13 +17591,13 @@
       </c>
       <c r="T197" s="184"/>
       <c r="U197">
-        <v>169080</v>
+        <v>169917</v>
       </c>
       <c r="V197" t="s">
-        <v>1005</v>
+        <v>1014</v>
       </c>
       <c r="W197">
-        <v>2.25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="198" spans="1:23" x14ac:dyDescent="0.35">
@@ -17454,13 +17634,13 @@
       </c>
       <c r="T198" s="184"/>
       <c r="U198">
-        <v>184835</v>
+        <v>181972</v>
       </c>
       <c r="V198" t="s">
-        <v>1005</v>
+        <v>1015</v>
       </c>
       <c r="W198">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199" spans="1:23" x14ac:dyDescent="0.35">
@@ -17497,13 +17677,13 @@
       </c>
       <c r="T199" s="184"/>
       <c r="U199">
-        <v>189548</v>
+        <v>188082</v>
       </c>
       <c r="V199" t="s">
-        <v>1005</v>
+        <v>1016</v>
       </c>
       <c r="W199">
-        <v>7.5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="200" spans="1:23" x14ac:dyDescent="0.35">
@@ -17540,13 +17720,13 @@
       </c>
       <c r="T200" s="184"/>
       <c r="U200">
-        <v>185532</v>
+        <v>51634</v>
       </c>
       <c r="V200" t="s">
-        <v>1006</v>
+        <v>1017</v>
       </c>
       <c r="W200">
-        <v>2.1669999999999998</v>
+        <v>14</v>
       </c>
     </row>
     <row r="201" spans="1:23" x14ac:dyDescent="0.35">
@@ -17583,13 +17763,13 @@
       </c>
       <c r="T201" s="184"/>
       <c r="U201">
-        <v>172089</v>
+        <v>191879</v>
       </c>
       <c r="V201" t="s">
-        <v>1007</v>
+        <v>824</v>
       </c>
       <c r="W201">
-        <v>4.25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="202" spans="1:23" x14ac:dyDescent="0.35">
@@ -17626,13 +17806,13 @@
       </c>
       <c r="T202" s="184"/>
       <c r="U202">
-        <v>190976</v>
+        <v>147972</v>
       </c>
       <c r="V202" t="s">
-        <v>825</v>
+        <v>1018</v>
       </c>
       <c r="W202">
-        <v>0.625</v>
+        <v>3</v>
       </c>
     </row>
     <row r="203" spans="1:23" x14ac:dyDescent="0.35">
@@ -17669,13 +17849,13 @@
       </c>
       <c r="T203" s="184"/>
       <c r="U203">
-        <v>160473</v>
+        <v>191958</v>
       </c>
       <c r="V203" t="s">
-        <v>1008</v>
+        <v>1019</v>
       </c>
       <c r="W203">
-        <v>0.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="204" spans="1:23" x14ac:dyDescent="0.35">
@@ -17712,13 +17892,13 @@
       </c>
       <c r="T204" s="184"/>
       <c r="U204">
-        <v>83923</v>
+        <v>176904</v>
       </c>
       <c r="V204" t="s">
-        <v>1009</v>
+        <v>1020</v>
       </c>
       <c r="W204">
-        <v>0.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="205" spans="1:23" x14ac:dyDescent="0.35">
@@ -17755,13 +17935,13 @@
       </c>
       <c r="T205" s="184"/>
       <c r="U205">
-        <v>164521</v>
+        <v>182784</v>
       </c>
       <c r="V205" t="s">
-        <v>1010</v>
+        <v>1021</v>
       </c>
       <c r="W205">
-        <v>1.667</v>
+        <v>4</v>
       </c>
     </row>
     <row r="206" spans="1:23" x14ac:dyDescent="0.35">
@@ -17798,13 +17978,13 @@
       </c>
       <c r="T206" s="184"/>
       <c r="U206">
-        <v>111305</v>
+        <v>182858</v>
       </c>
       <c r="V206" t="s">
-        <v>1011</v>
+        <v>1022</v>
       </c>
       <c r="W206">
-        <v>0.83299999999999996</v>
+        <v>27</v>
       </c>
     </row>
     <row r="207" spans="1:23" x14ac:dyDescent="0.35">
@@ -17841,13 +18021,13 @@
       </c>
       <c r="T207" s="184"/>
       <c r="U207">
-        <v>72303</v>
+        <v>140216</v>
       </c>
       <c r="V207" t="s">
-        <v>1012</v>
+        <v>1023</v>
       </c>
       <c r="W207">
-        <v>8.3000000000000004E-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208" spans="1:23" x14ac:dyDescent="0.35">
@@ -17884,13 +18064,13 @@
       </c>
       <c r="T208" s="184"/>
       <c r="U208">
-        <v>171652</v>
+        <v>49382</v>
       </c>
       <c r="V208" t="s">
-        <v>1013</v>
+        <v>1024</v>
       </c>
       <c r="W208">
-        <v>0.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="209" spans="1:23" x14ac:dyDescent="0.35">
@@ -17927,13 +18107,13 @@
       </c>
       <c r="T209" s="184"/>
       <c r="U209">
-        <v>182586</v>
+        <v>52370</v>
       </c>
       <c r="V209" t="s">
-        <v>1014</v>
+        <v>1025</v>
       </c>
       <c r="W209">
-        <v>6.3E-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210" spans="1:23" x14ac:dyDescent="0.35">
@@ -17970,13 +18150,13 @@
       </c>
       <c r="T210" s="184"/>
       <c r="U210">
-        <v>191802</v>
+        <v>62901</v>
       </c>
       <c r="V210" t="s">
-        <v>1015</v>
+        <v>825</v>
       </c>
       <c r="W210">
-        <v>0.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="211" spans="1:23" x14ac:dyDescent="0.35">
@@ -18013,13 +18193,13 @@
       </c>
       <c r="T211" s="184"/>
       <c r="U211">
-        <v>81875</v>
+        <v>178540</v>
       </c>
       <c r="V211" t="s">
-        <v>1016</v>
+        <v>1026</v>
       </c>
       <c r="W211">
-        <v>1.083</v>
+        <v>8</v>
       </c>
     </row>
     <row r="212" spans="1:23" x14ac:dyDescent="0.35">
@@ -18056,13 +18236,13 @@
       </c>
       <c r="T212" s="184"/>
       <c r="U212">
-        <v>181539</v>
+        <v>125510</v>
       </c>
       <c r="V212" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="W212">
-        <v>0.66700000000000004</v>
+        <v>3</v>
       </c>
     </row>
     <row r="213" spans="1:23" x14ac:dyDescent="0.35">
@@ -18099,13 +18279,13 @@
       </c>
       <c r="T213" s="184"/>
       <c r="U213">
-        <v>112151</v>
+        <v>167649</v>
       </c>
       <c r="V213" t="s">
-        <v>1018</v>
+        <v>1028</v>
       </c>
       <c r="W213">
-        <v>0.33300000000000002</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:23" x14ac:dyDescent="0.35">
@@ -18142,13 +18322,13 @@
       </c>
       <c r="T214" s="184"/>
       <c r="U214">
-        <v>175526</v>
+        <v>57547</v>
       </c>
       <c r="V214" t="s">
-        <v>1019</v>
+        <v>1029</v>
       </c>
       <c r="W214">
-        <v>8.3000000000000004E-2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="215" spans="1:23" x14ac:dyDescent="0.35">
@@ -18185,13 +18365,13 @@
       </c>
       <c r="T215" s="184"/>
       <c r="U215">
-        <v>66561</v>
+        <v>172422</v>
       </c>
       <c r="V215" t="s">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="W215">
-        <v>0.45800000000000002</v>
+        <v>4</v>
       </c>
     </row>
     <row r="216" spans="1:23" x14ac:dyDescent="0.35">
@@ -18228,10 +18408,10 @@
       </c>
       <c r="T216" s="184"/>
       <c r="U216">
-        <v>183603</v>
+        <v>180053</v>
       </c>
       <c r="V216" t="s">
-        <v>1021</v>
+        <v>1031</v>
       </c>
       <c r="W216">
         <v>1</v>
@@ -18271,13 +18451,13 @@
       </c>
       <c r="T217" s="184"/>
       <c r="U217">
-        <v>190582</v>
+        <v>63529</v>
       </c>
       <c r="V217" t="s">
-        <v>1022</v>
+        <v>1032</v>
       </c>
       <c r="W217">
-        <v>1.0629999999999999</v>
+        <v>6</v>
       </c>
     </row>
     <row r="218" spans="1:23" x14ac:dyDescent="0.35">
@@ -18314,13 +18494,13 @@
       </c>
       <c r="T218" s="184"/>
       <c r="U218">
-        <v>129230</v>
+        <v>182987</v>
       </c>
       <c r="V218" t="s">
-        <v>1023</v>
+        <v>1033</v>
       </c>
       <c r="W218">
-        <v>0.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="219" spans="1:23" x14ac:dyDescent="0.35">
@@ -18357,13 +18537,13 @@
       </c>
       <c r="T219" s="184"/>
       <c r="U219">
-        <v>49106</v>
+        <v>188691</v>
       </c>
       <c r="V219" t="s">
-        <v>1024</v>
+        <v>1034</v>
       </c>
       <c r="W219">
-        <v>0.58299999999999996</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220" spans="1:23" x14ac:dyDescent="0.35">
@@ -18400,13 +18580,13 @@
       </c>
       <c r="T220" s="184"/>
       <c r="U220">
-        <v>161194</v>
+        <v>52480</v>
       </c>
       <c r="V220" t="s">
-        <v>1025</v>
+        <v>1035</v>
       </c>
       <c r="W220" s="6">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221" spans="1:23" x14ac:dyDescent="0.35">
@@ -18443,13 +18623,13 @@
       </c>
       <c r="T221" s="184"/>
       <c r="U221">
-        <v>182230</v>
+        <v>189663</v>
       </c>
       <c r="V221" t="s">
-        <v>1026</v>
+        <v>1036</v>
       </c>
       <c r="W221">
-        <v>6.3E-2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="222" spans="1:23" x14ac:dyDescent="0.35">
@@ -18486,13 +18666,13 @@
       </c>
       <c r="T222" s="184"/>
       <c r="U222">
-        <v>125576</v>
+        <v>186887</v>
       </c>
       <c r="V222" t="s">
-        <v>1027</v>
+        <v>1037</v>
       </c>
       <c r="W222">
-        <v>0.77100000000000002</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223" spans="1:23" x14ac:dyDescent="0.35">
@@ -18529,13 +18709,13 @@
       </c>
       <c r="T223" s="184"/>
       <c r="U223">
-        <v>155030</v>
+        <v>186720</v>
       </c>
       <c r="V223" t="s">
-        <v>1028</v>
+        <v>1038</v>
       </c>
       <c r="W223">
-        <v>1.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224" spans="1:23" x14ac:dyDescent="0.35">
@@ -18572,13 +18752,13 @@
       </c>
       <c r="T224" s="184"/>
       <c r="U224">
-        <v>169958</v>
+        <v>129761</v>
       </c>
       <c r="V224" t="s">
-        <v>1029</v>
+        <v>1039</v>
       </c>
       <c r="W224">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="225" spans="1:23" x14ac:dyDescent="0.35">
@@ -18615,13 +18795,13 @@
       </c>
       <c r="T225" s="184"/>
       <c r="U225">
-        <v>189228</v>
+        <v>132039</v>
       </c>
       <c r="V225" t="s">
-        <v>1030</v>
+        <v>26</v>
       </c>
       <c r="W225">
-        <v>0.35399999999999998</v>
+        <v>22</v>
       </c>
     </row>
     <row r="226" spans="1:23" x14ac:dyDescent="0.35">
@@ -18658,13 +18838,13 @@
       </c>
       <c r="T226" s="184"/>
       <c r="U226">
-        <v>52811</v>
+        <v>168551</v>
       </c>
       <c r="V226" t="s">
-        <v>1031</v>
+        <v>26</v>
       </c>
       <c r="W226">
-        <v>0.75</v>
+        <v>15</v>
       </c>
     </row>
     <row r="227" spans="1:23" x14ac:dyDescent="0.35">
@@ -18701,13 +18881,13 @@
       </c>
       <c r="T227" s="184"/>
       <c r="U227">
-        <v>133968</v>
+        <v>177226</v>
       </c>
       <c r="V227" t="s">
-        <v>818</v>
+        <v>1040</v>
       </c>
       <c r="W227">
-        <v>2.2080000000000002</v>
+        <v>85</v>
       </c>
     </row>
     <row r="228" spans="1:23" x14ac:dyDescent="0.35">
@@ -18744,13 +18924,13 @@
       </c>
       <c r="T228" s="184"/>
       <c r="U228">
-        <v>178885</v>
+        <v>166470</v>
       </c>
       <c r="V228" t="s">
-        <v>1032</v>
+        <v>1041</v>
       </c>
       <c r="W228">
-        <v>1.417</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229" spans="1:23" x14ac:dyDescent="0.35">
@@ -18787,13 +18967,13 @@
       </c>
       <c r="T229" s="184"/>
       <c r="U229">
-        <v>119172</v>
+        <v>183258</v>
       </c>
       <c r="V229" t="s">
-        <v>1033</v>
+        <v>1042</v>
       </c>
       <c r="W229" s="6">
-        <v>1.583</v>
+        <v>4</v>
       </c>
     </row>
     <row r="230" spans="1:23" x14ac:dyDescent="0.35">
@@ -18830,13 +19010,13 @@
       </c>
       <c r="T230" s="184"/>
       <c r="U230">
-        <v>111922</v>
+        <v>181925</v>
       </c>
       <c r="V230" t="s">
-        <v>1034</v>
+        <v>1043</v>
       </c>
       <c r="W230">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231" spans="1:23" x14ac:dyDescent="0.35">
@@ -18873,13 +19053,13 @@
       </c>
       <c r="T231" s="184"/>
       <c r="U231">
-        <v>144260</v>
+        <v>177189</v>
       </c>
       <c r="V231" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
       <c r="W231">
-        <v>16.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232" spans="1:23" x14ac:dyDescent="0.35">
@@ -18916,13 +19096,13 @@
       </c>
       <c r="T232" s="184"/>
       <c r="U232">
-        <v>176546</v>
+        <v>97252</v>
       </c>
       <c r="V232" t="s">
-        <v>1035</v>
+        <v>813</v>
       </c>
       <c r="W232">
-        <v>1.833</v>
+        <v>3</v>
       </c>
     </row>
     <row r="233" spans="1:23" x14ac:dyDescent="0.35">
@@ -18959,13 +19139,13 @@
       </c>
       <c r="T233" s="184"/>
       <c r="U233">
-        <v>188637</v>
+        <v>56006</v>
       </c>
       <c r="V233" t="s">
-        <v>1036</v>
+        <v>1045</v>
       </c>
       <c r="W233">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234" spans="1:23" x14ac:dyDescent="0.35">
@@ -19002,13 +19182,13 @@
       </c>
       <c r="T234" s="184"/>
       <c r="U234">
-        <v>113922</v>
+        <v>174876</v>
       </c>
       <c r="V234" t="s">
-        <v>1037</v>
+        <v>1046</v>
       </c>
       <c r="W234">
-        <v>3.6669999999999998</v>
+        <v>10</v>
       </c>
     </row>
     <row r="235" spans="1:23" x14ac:dyDescent="0.35">
@@ -19045,13 +19225,13 @@
       </c>
       <c r="T235" s="184"/>
       <c r="U235">
-        <v>167604</v>
+        <v>188983</v>
       </c>
       <c r="V235" t="s">
-        <v>826</v>
+        <v>1047</v>
       </c>
       <c r="W235">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236" spans="1:23" x14ac:dyDescent="0.35">
@@ -19088,13 +19268,13 @@
       </c>
       <c r="T236" s="184"/>
       <c r="U236">
-        <v>184494</v>
+        <v>176854</v>
       </c>
       <c r="V236" t="s">
-        <v>1038</v>
+        <v>1048</v>
       </c>
       <c r="W236">
-        <v>0.33300000000000002</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237" spans="1:23" x14ac:dyDescent="0.35">
@@ -19127,17 +19307,17 @@
         <v>782</v>
       </c>
       <c r="K237" s="6">
-        <v>7</v>
+        <v>12.375</v>
       </c>
       <c r="T237" s="184"/>
       <c r="U237">
-        <v>136856</v>
+        <v>148970</v>
       </c>
       <c r="V237" t="s">
-        <v>9</v>
+        <v>1049</v>
       </c>
       <c r="W237">
-        <v>5.375</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238" spans="1:23" x14ac:dyDescent="0.35">
@@ -19174,13 +19354,13 @@
       </c>
       <c r="T238" s="184"/>
       <c r="U238">
-        <v>74369</v>
+        <v>146298</v>
       </c>
       <c r="V238" t="s">
-        <v>8</v>
+        <v>1050</v>
       </c>
       <c r="W238">
-        <v>9.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239" spans="1:23" x14ac:dyDescent="0.35">
@@ -19217,13 +19397,13 @@
       </c>
       <c r="T239" s="184"/>
       <c r="U239">
-        <v>53581</v>
+        <v>191347</v>
       </c>
       <c r="V239" t="s">
-        <v>100</v>
+        <v>1051</v>
       </c>
       <c r="W239">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240" spans="1:23" x14ac:dyDescent="0.35">
@@ -19260,13 +19440,13 @@
       </c>
       <c r="T240" s="184"/>
       <c r="U240">
-        <v>58007</v>
+        <v>71900</v>
       </c>
       <c r="V240" t="s">
-        <v>1039</v>
+        <v>1052</v>
       </c>
       <c r="W240">
-        <v>0.41699999999999998</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241" spans="1:23" x14ac:dyDescent="0.35">
@@ -19303,13 +19483,13 @@
       </c>
       <c r="T241" s="184"/>
       <c r="U241">
-        <v>57679</v>
+        <v>122903</v>
       </c>
       <c r="V241" t="s">
-        <v>112</v>
+        <v>1053</v>
       </c>
       <c r="W241">
-        <v>209</v>
+        <v>5</v>
       </c>
     </row>
     <row r="242" spans="1:23" x14ac:dyDescent="0.35">
@@ -19346,13 +19526,13 @@
       </c>
       <c r="T242" s="184"/>
       <c r="U242">
-        <v>128748</v>
+        <v>104396</v>
       </c>
       <c r="V242" t="s">
-        <v>1040</v>
+        <v>1054</v>
       </c>
       <c r="W242">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243" spans="1:23" x14ac:dyDescent="0.35">
@@ -19389,13 +19569,13 @@
       </c>
       <c r="T243" s="184"/>
       <c r="U243">
-        <v>190491</v>
+        <v>168028</v>
       </c>
       <c r="V243" t="s">
-        <v>1040</v>
+        <v>1055</v>
       </c>
       <c r="W243">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="244" spans="1:23" x14ac:dyDescent="0.35">
@@ -19432,13 +19612,13 @@
       </c>
       <c r="T244" s="184"/>
       <c r="U244">
-        <v>113031</v>
+        <v>129372</v>
       </c>
       <c r="V244" t="s">
-        <v>1041</v>
+        <v>1056</v>
       </c>
       <c r="W244">
-        <v>1.9379999999999999</v>
+        <v>12</v>
       </c>
     </row>
     <row r="245" spans="1:23" x14ac:dyDescent="0.35">
@@ -19475,13 +19655,13 @@
       </c>
       <c r="T245" s="184"/>
       <c r="U245">
-        <v>184985</v>
+        <v>168444</v>
       </c>
       <c r="V245" t="s">
-        <v>1042</v>
+        <v>1057</v>
       </c>
       <c r="W245">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="246" spans="1:23" x14ac:dyDescent="0.35">
@@ -19518,13 +19698,13 @@
       </c>
       <c r="T246" s="184"/>
       <c r="U246">
-        <v>169887</v>
+        <v>95664</v>
       </c>
       <c r="V246" t="s">
-        <v>1043</v>
+        <v>1058</v>
       </c>
       <c r="W246">
-        <v>4.8330000000000002</v>
+        <v>6</v>
       </c>
     </row>
     <row r="247" spans="1:23" x14ac:dyDescent="0.35">
@@ -19561,13 +19741,13 @@
       </c>
       <c r="T247" s="184"/>
       <c r="U247">
-        <v>178284</v>
+        <v>172089</v>
       </c>
       <c r="V247" t="s">
-        <v>1044</v>
+        <v>826</v>
       </c>
       <c r="W247">
-        <v>2.5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="248" spans="1:23" x14ac:dyDescent="0.35">
@@ -19604,13 +19784,13 @@
       </c>
       <c r="T248" s="184"/>
       <c r="U248">
-        <v>158250</v>
+        <v>190976</v>
       </c>
       <c r="V248" t="s">
-        <v>1045</v>
+        <v>815</v>
       </c>
       <c r="W248">
-        <v>0.16700000000000001</v>
+        <v>4</v>
       </c>
     </row>
     <row r="249" spans="1:23" x14ac:dyDescent="0.35">
@@ -19643,17 +19823,17 @@
         <v>782</v>
       </c>
       <c r="K249" s="6">
-        <v>8.5</v>
+        <v>18</v>
       </c>
       <c r="T249" s="184"/>
       <c r="U249">
-        <v>176154</v>
+        <v>181838</v>
       </c>
       <c r="V249" t="s">
-        <v>1046</v>
+        <v>1059</v>
       </c>
       <c r="W249">
-        <v>0.25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="250" spans="1:23" x14ac:dyDescent="0.35">
@@ -19690,13 +19870,13 @@
       </c>
       <c r="T250" s="184"/>
       <c r="U250">
-        <v>109929</v>
+        <v>109798</v>
       </c>
       <c r="V250" t="s">
-        <v>1047</v>
+        <v>1060</v>
       </c>
       <c r="W250">
-        <v>2.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="251" spans="1:23" x14ac:dyDescent="0.35">
@@ -19733,13 +19913,13 @@
       </c>
       <c r="T251" s="184"/>
       <c r="U251">
-        <v>170523</v>
+        <v>183057</v>
       </c>
       <c r="V251" t="s">
-        <v>1047</v>
+        <v>1061</v>
       </c>
       <c r="W251">
-        <v>1.458</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252" spans="1:23" x14ac:dyDescent="0.35">
@@ -19776,13 +19956,13 @@
       </c>
       <c r="T252" s="184"/>
       <c r="U252">
-        <v>187956</v>
+        <v>182208</v>
       </c>
       <c r="V252" t="s">
-        <v>1047</v>
+        <v>1062</v>
       </c>
       <c r="W252">
-        <v>5.75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253" spans="1:23" x14ac:dyDescent="0.35">
@@ -19819,13 +19999,13 @@
       </c>
       <c r="T253" s="184"/>
       <c r="U253">
-        <v>177344</v>
+        <v>136718</v>
       </c>
       <c r="V253" t="s">
-        <v>1048</v>
+        <v>1063</v>
       </c>
       <c r="W253">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="254" spans="1:23" x14ac:dyDescent="0.35">
@@ -19862,13 +20042,13 @@
       </c>
       <c r="T254" s="184"/>
       <c r="U254">
-        <v>184702</v>
+        <v>190381</v>
       </c>
       <c r="V254" t="s">
-        <v>1049</v>
+        <v>1064</v>
       </c>
       <c r="W254">
-        <v>0.16700000000000001</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255" spans="1:23" x14ac:dyDescent="0.35">
@@ -19905,13 +20085,13 @@
       </c>
       <c r="T255" s="184"/>
       <c r="U255">
-        <v>143146</v>
+        <v>113254</v>
       </c>
       <c r="V255" t="s">
-        <v>1050</v>
+        <v>1065</v>
       </c>
       <c r="W255">
-        <v>8.3000000000000004E-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256" spans="1:23" x14ac:dyDescent="0.35">
@@ -19948,16 +20128,16 @@
       </c>
       <c r="T256" s="184"/>
       <c r="U256">
-        <v>49799</v>
+        <v>179861</v>
       </c>
       <c r="V256" t="s">
-        <v>1051</v>
+        <v>1066</v>
       </c>
       <c r="W256">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="257" spans="1:20" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="257" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A257" s="30" t="s">
         <v>766</v>
       </c>
@@ -19990,8 +20170,17 @@
         <v>15.417</v>
       </c>
       <c r="T257" s="184"/>
-    </row>
-    <row r="258" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U257">
+        <v>132093</v>
+      </c>
+      <c r="V257" t="s">
+        <v>1067</v>
+      </c>
+      <c r="W257">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A258" s="30" t="s">
         <v>767</v>
       </c>
@@ -20024,8 +20213,17 @@
         <v>63.125</v>
       </c>
       <c r="T258" s="184"/>
-    </row>
-    <row r="259" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U258">
+        <v>165750</v>
+      </c>
+      <c r="V258" t="s">
+        <v>1068</v>
+      </c>
+      <c r="W258">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="259" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A259" s="30" t="s">
         <v>768</v>
       </c>
@@ -20058,8 +20256,17 @@
         <v>20.457999999999998</v>
       </c>
       <c r="T259" s="184"/>
-    </row>
-    <row r="260" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U259">
+        <v>171416</v>
+      </c>
+      <c r="V259" t="s">
+        <v>1069</v>
+      </c>
+      <c r="W259">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A260" s="30" t="s">
         <v>769</v>
       </c>
@@ -20092,8 +20299,17 @@
         <v>22</v>
       </c>
       <c r="T260" s="184"/>
-    </row>
-    <row r="261" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U260">
+        <v>80736</v>
+      </c>
+      <c r="V260" t="s">
+        <v>1070</v>
+      </c>
+      <c r="W260">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="261" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A261" s="30" t="s">
         <v>770</v>
       </c>
@@ -20123,11 +20339,20 @@
         <v>782</v>
       </c>
       <c r="K261">
-        <v>8.0830000000000002</v>
+        <v>19.082999999999998</v>
       </c>
       <c r="T261" s="184"/>
-    </row>
-    <row r="262" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U261">
+        <v>185005</v>
+      </c>
+      <c r="V261" t="s">
+        <v>1071</v>
+      </c>
+      <c r="W261">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="262" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A262" s="30" t="s">
         <v>771</v>
       </c>
@@ -20160,8 +20385,17 @@
         <v>109</v>
       </c>
       <c r="T262" s="184"/>
-    </row>
-    <row r="263" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U262">
+        <v>137698</v>
+      </c>
+      <c r="V262" t="s">
+        <v>1072</v>
+      </c>
+      <c r="W262">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="263" spans="1:23" x14ac:dyDescent="0.35">
       <c r="G263" s="29" t="str">
         <f t="shared" si="6"/>
         <v>57679 AGO/2025</v>
@@ -20179,8 +20413,17 @@
         <v>1458</v>
       </c>
       <c r="T263" s="184"/>
-    </row>
-    <row r="264" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U263">
+        <v>48812</v>
+      </c>
+      <c r="V263" t="s">
+        <v>1073</v>
+      </c>
+      <c r="W263">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="264" spans="1:23" x14ac:dyDescent="0.35">
       <c r="G264" s="29" t="str">
         <f t="shared" si="6"/>
         <v>57679 SET/2025</v>
@@ -20198,8 +20441,17 @@
         <v>261</v>
       </c>
       <c r="T264" s="184"/>
-    </row>
-    <row r="265" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U264">
+        <v>125824</v>
+      </c>
+      <c r="V264" t="s">
+        <v>1074</v>
+      </c>
+      <c r="W264">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:23" x14ac:dyDescent="0.35">
       <c r="G265" s="29" t="str">
         <f t="shared" si="6"/>
         <v>57679 OUT/2025</v>
@@ -20217,8 +20469,17 @@
         <v>548.75</v>
       </c>
       <c r="T265" s="184"/>
-    </row>
-    <row r="266" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U265">
+        <v>187525</v>
+      </c>
+      <c r="V265" t="s">
+        <v>1075</v>
+      </c>
+      <c r="W265">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="266" spans="1:23" x14ac:dyDescent="0.35">
       <c r="G266" s="29" t="str">
         <f t="shared" si="6"/>
         <v>57679 NOV/2025</v>
@@ -20236,8 +20497,17 @@
         <v>578</v>
       </c>
       <c r="T266" s="184"/>
-    </row>
-    <row r="267" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U266">
+        <v>178791</v>
+      </c>
+      <c r="V266" t="s">
+        <v>1076</v>
+      </c>
+      <c r="W266">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:23" x14ac:dyDescent="0.35">
       <c r="G267" s="29" t="str">
         <f t="shared" si="6"/>
         <v>57679 DEZ/2025</v>
@@ -20255,8 +20525,17 @@
         <v>615</v>
       </c>
       <c r="T267" s="184"/>
-    </row>
-    <row r="268" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U267">
+        <v>191108</v>
+      </c>
+      <c r="V267" t="s">
+        <v>1077</v>
+      </c>
+      <c r="W267">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="268" spans="1:23" x14ac:dyDescent="0.35">
       <c r="G268" s="29" t="str">
         <f t="shared" si="6"/>
         <v>57679 JAN/2026</v>
@@ -20274,8 +20553,17 @@
         <v>235.917</v>
       </c>
       <c r="T268" s="184"/>
-    </row>
-    <row r="269" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U268">
+        <v>185149</v>
+      </c>
+      <c r="V268" t="s">
+        <v>1078</v>
+      </c>
+      <c r="W268">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="269" spans="1:23" x14ac:dyDescent="0.35">
       <c r="G269" s="29" t="str">
         <f t="shared" si="6"/>
         <v>57679 FEV/2026</v>
@@ -20293,8 +20581,17 @@
         <v>790.95799999999997</v>
       </c>
       <c r="T269" s="184"/>
-    </row>
-    <row r="270" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U269">
+        <v>79008</v>
+      </c>
+      <c r="V269" t="s">
+        <v>1079</v>
+      </c>
+      <c r="W269">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="270" spans="1:23" x14ac:dyDescent="0.35">
       <c r="G270" s="29" t="str">
         <f t="shared" si="6"/>
         <v>57679 MAR/2026</v>
@@ -20312,8 +20609,17 @@
         <v>688</v>
       </c>
       <c r="T270" s="184"/>
-    </row>
-    <row r="271" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U270">
+        <v>152232</v>
+      </c>
+      <c r="V270" t="s">
+        <v>1080</v>
+      </c>
+      <c r="W270">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:23" x14ac:dyDescent="0.35">
       <c r="G271" s="29" t="str">
         <f t="shared" si="6"/>
         <v>57679 ABR/2026</v>
@@ -20331,8 +20637,17 @@
         <v>365</v>
       </c>
       <c r="T271" s="184"/>
-    </row>
-    <row r="272" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U271">
+        <v>166190</v>
+      </c>
+      <c r="V271" t="s">
+        <v>1081</v>
+      </c>
+      <c r="W271">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="272" spans="1:23" x14ac:dyDescent="0.35">
       <c r="G272" s="29" t="str">
         <f t="shared" si="6"/>
         <v>57679 MAI/2026</v>
@@ -20350,6 +20665,15 @@
         <v>518</v>
       </c>
       <c r="T272" s="184"/>
+      <c r="U272">
+        <v>50796</v>
+      </c>
+      <c r="V272" t="s">
+        <v>1082</v>
+      </c>
+      <c r="W272">
+        <v>9</v>
+      </c>
     </row>
     <row r="273" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G273" s="29" t="str">
@@ -20366,10 +20690,18 @@
         <v>782</v>
       </c>
       <c r="K273" s="6">
-        <v>-1</v>
+        <v>204</v>
       </c>
       <c r="T273" s="184"/>
-      <c r="W273" s="6"/>
+      <c r="U273">
+        <v>187181</v>
+      </c>
+      <c r="V273" t="s">
+        <v>1083</v>
+      </c>
+      <c r="W273" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="274" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G274" s="29" t="str">
@@ -20389,6 +20721,15 @@
         <v>5.875</v>
       </c>
       <c r="T274" s="184"/>
+      <c r="U274">
+        <v>120514</v>
+      </c>
+      <c r="V274" t="s">
+        <v>1084</v>
+      </c>
+      <c r="W274">
+        <v>20</v>
+      </c>
     </row>
     <row r="275" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G275" s="29" t="str">
@@ -20408,6 +20749,15 @@
         <v>3</v>
       </c>
       <c r="T275" s="184"/>
+      <c r="U275">
+        <v>54512</v>
+      </c>
+      <c r="V275" t="s">
+        <v>1085</v>
+      </c>
+      <c r="W275">
+        <v>28</v>
+      </c>
     </row>
     <row r="276" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G276" s="29" t="str">
@@ -20427,6 +20777,15 @@
         <v>5.375</v>
       </c>
       <c r="T276" s="184"/>
+      <c r="U276">
+        <v>53616</v>
+      </c>
+      <c r="V276" t="s">
+        <v>1086</v>
+      </c>
+      <c r="W276">
+        <v>17</v>
+      </c>
     </row>
     <row r="277" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G277" s="29" t="str">
@@ -20446,6 +20805,15 @@
         <v>0.5</v>
       </c>
       <c r="T277" s="184"/>
+      <c r="U277">
+        <v>115039</v>
+      </c>
+      <c r="V277" t="s">
+        <v>1087</v>
+      </c>
+      <c r="W277">
+        <v>10</v>
+      </c>
     </row>
     <row r="278" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G278" s="29" t="str">
@@ -20465,6 +20833,15 @@
         <v>3</v>
       </c>
       <c r="T278" s="184"/>
+      <c r="U278">
+        <v>131746</v>
+      </c>
+      <c r="V278" t="s">
+        <v>1088</v>
+      </c>
+      <c r="W278">
+        <v>87</v>
+      </c>
     </row>
     <row r="279" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G279" s="29" t="str">
@@ -20484,6 +20861,15 @@
         <v>397.625</v>
       </c>
       <c r="T279" s="184"/>
+      <c r="U279">
+        <v>55677</v>
+      </c>
+      <c r="V279" t="s">
+        <v>1089</v>
+      </c>
+      <c r="W279">
+        <v>24</v>
+      </c>
     </row>
     <row r="280" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G280" s="29" t="str">
@@ -20503,6 +20889,15 @@
         <v>49.146000000000001</v>
       </c>
       <c r="T280" s="184"/>
+      <c r="U280">
+        <v>187856</v>
+      </c>
+      <c r="V280" t="s">
+        <v>1090</v>
+      </c>
+      <c r="W280">
+        <v>2</v>
+      </c>
     </row>
     <row r="281" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G281" s="29" t="str">
@@ -20522,6 +20917,15 @@
         <v>1314.6669999999999</v>
       </c>
       <c r="T281" s="184"/>
+      <c r="U281">
+        <v>133968</v>
+      </c>
+      <c r="V281" t="s">
+        <v>814</v>
+      </c>
+      <c r="W281">
+        <v>25</v>
+      </c>
     </row>
     <row r="282" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G282" s="29" t="str">
@@ -20541,6 +20945,15 @@
         <v>74.082999999999998</v>
       </c>
       <c r="T282" s="184"/>
+      <c r="U282">
+        <v>188333</v>
+      </c>
+      <c r="V282" t="s">
+        <v>1091</v>
+      </c>
+      <c r="W282">
+        <v>89</v>
+      </c>
     </row>
     <row r="283" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G283" s="29" t="str">
@@ -20560,6 +20973,15 @@
         <v>397.76400000000001</v>
       </c>
       <c r="T283" s="184"/>
+      <c r="U283">
+        <v>89921</v>
+      </c>
+      <c r="V283" t="s">
+        <v>1092</v>
+      </c>
+      <c r="W283">
+        <v>53</v>
+      </c>
     </row>
     <row r="284" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G284" s="29" t="str">
@@ -20579,6 +21001,15 @@
         <v>592.20799999999997</v>
       </c>
       <c r="T284" s="184"/>
+      <c r="U284">
+        <v>50633</v>
+      </c>
+      <c r="V284" t="s">
+        <v>1093</v>
+      </c>
+      <c r="W284">
+        <v>3</v>
+      </c>
     </row>
     <row r="285" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G285" s="29" t="str">
@@ -20598,6 +21029,15 @@
         <v>294.02100000000002</v>
       </c>
       <c r="T285" s="184"/>
+      <c r="U285">
+        <v>155935</v>
+      </c>
+      <c r="V285" t="s">
+        <v>1094</v>
+      </c>
+      <c r="W285">
+        <v>19</v>
+      </c>
     </row>
     <row r="286" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G286" s="29" t="str">
@@ -20617,6 +21057,15 @@
         <v>80.582999999999998</v>
       </c>
       <c r="T286" s="184"/>
+      <c r="U286">
+        <v>122531</v>
+      </c>
+      <c r="V286" t="s">
+        <v>1095</v>
+      </c>
+      <c r="W286">
+        <v>3</v>
+      </c>
     </row>
     <row r="287" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G287" s="29" t="str">
@@ -20636,6 +21085,15 @@
         <v>397.25</v>
       </c>
       <c r="T287" s="184"/>
+      <c r="U287">
+        <v>174122</v>
+      </c>
+      <c r="V287" t="s">
+        <v>827</v>
+      </c>
+      <c r="W287">
+        <v>38</v>
+      </c>
     </row>
     <row r="288" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G288" s="29" t="str">
@@ -20655,6 +21113,15 @@
         <v>220.667</v>
       </c>
       <c r="T288" s="184"/>
+      <c r="U288">
+        <v>178885</v>
+      </c>
+      <c r="V288" t="s">
+        <v>827</v>
+      </c>
+      <c r="W288">
+        <v>11</v>
+      </c>
     </row>
     <row r="289" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G289" s="29" t="str">
@@ -20674,6 +21141,15 @@
         <v>215.179</v>
       </c>
       <c r="T289" s="184"/>
+      <c r="U289">
+        <v>162069</v>
+      </c>
+      <c r="V289" t="s">
+        <v>1096</v>
+      </c>
+      <c r="W289">
+        <v>4</v>
+      </c>
     </row>
     <row r="290" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G290" s="29" t="str">
@@ -20693,6 +21169,15 @@
         <v>-6.4459999999999997</v>
       </c>
       <c r="T290" s="184"/>
+      <c r="U290">
+        <v>192039</v>
+      </c>
+      <c r="V290" t="s">
+        <v>1097</v>
+      </c>
+      <c r="W290">
+        <v>5</v>
+      </c>
     </row>
     <row r="291" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G291" s="29" t="str">
@@ -20712,6 +21197,15 @@
         <v>5.875</v>
       </c>
       <c r="T291" s="184"/>
+      <c r="U291">
+        <v>162319</v>
+      </c>
+      <c r="V291" t="s">
+        <v>1098</v>
+      </c>
+      <c r="W291">
+        <v>30</v>
+      </c>
     </row>
     <row r="292" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G292" s="29" t="str">
@@ -20731,7 +21225,15 @@
         <v>3</v>
       </c>
       <c r="T292" s="184"/>
-      <c r="W292" s="6"/>
+      <c r="U292">
+        <v>74369</v>
+      </c>
+      <c r="V292" t="s">
+        <v>8</v>
+      </c>
+      <c r="W292" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="293" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G293" s="29" t="str">
@@ -20751,7 +21253,15 @@
         <v>5.875</v>
       </c>
       <c r="T293" s="184"/>
-      <c r="W293" s="6"/>
+      <c r="U293">
+        <v>53581</v>
+      </c>
+      <c r="V293" t="s">
+        <v>100</v>
+      </c>
+      <c r="W293" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="294" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G294" s="29" t="str">
@@ -20771,6 +21281,15 @@
         <v>3</v>
       </c>
       <c r="T294" s="184"/>
+      <c r="U294">
+        <v>58007</v>
+      </c>
+      <c r="V294" t="s">
+        <v>828</v>
+      </c>
+      <c r="W294">
+        <v>4</v>
+      </c>
     </row>
     <row r="295" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G295" s="29" t="str">
@@ -20790,6 +21309,15 @@
         <v>5.875</v>
       </c>
       <c r="T295" s="184"/>
+      <c r="U295">
+        <v>60905</v>
+      </c>
+      <c r="V295" t="s">
+        <v>1099</v>
+      </c>
+      <c r="W295">
+        <v>11</v>
+      </c>
     </row>
     <row r="296" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G296" s="29" t="str">
@@ -20809,6 +21337,15 @@
         <v>3</v>
       </c>
       <c r="T296" s="184"/>
+      <c r="U296">
+        <v>146875</v>
+      </c>
+      <c r="V296" t="s">
+        <v>1099</v>
+      </c>
+      <c r="W296">
+        <v>6</v>
+      </c>
     </row>
     <row r="297" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G297" s="29" t="str">
@@ -20828,6 +21365,15 @@
         <v>5.875</v>
       </c>
       <c r="T297" s="184"/>
+      <c r="U297">
+        <v>170854</v>
+      </c>
+      <c r="V297" t="s">
+        <v>1099</v>
+      </c>
+      <c r="W297">
+        <v>1</v>
+      </c>
     </row>
     <row r="298" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G298" s="29" t="str">
@@ -20847,6 +21393,15 @@
         <v>3</v>
       </c>
       <c r="T298" s="184"/>
+      <c r="U298">
+        <v>185862</v>
+      </c>
+      <c r="V298" t="s">
+        <v>1099</v>
+      </c>
+      <c r="W298">
+        <v>2</v>
+      </c>
     </row>
     <row r="299" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G299" s="29" t="str">
@@ -20866,6 +21421,15 @@
         <v>5.875</v>
       </c>
       <c r="T299" s="184"/>
+      <c r="U299">
+        <v>189581</v>
+      </c>
+      <c r="V299" t="s">
+        <v>1099</v>
+      </c>
+      <c r="W299">
+        <v>2</v>
+      </c>
     </row>
     <row r="300" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G300" s="29" t="str">
@@ -20885,6 +21449,15 @@
         <v>3</v>
       </c>
       <c r="T300" s="184"/>
+      <c r="U300">
+        <v>61742</v>
+      </c>
+      <c r="V300" t="s">
+        <v>1100</v>
+      </c>
+      <c r="W300">
+        <v>59</v>
+      </c>
     </row>
     <row r="301" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G301" s="29" t="str">
@@ -20904,6 +21477,15 @@
         <v>5.625</v>
       </c>
       <c r="T301" s="184"/>
+      <c r="U301">
+        <v>113031</v>
+      </c>
+      <c r="V301" t="s">
+        <v>829</v>
+      </c>
+      <c r="W301">
+        <v>15</v>
+      </c>
     </row>
     <row r="302" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G302" s="29" t="str">
@@ -20923,6 +21505,15 @@
         <v>-0.25</v>
       </c>
       <c r="T302" s="184"/>
+      <c r="U302">
+        <v>187072</v>
+      </c>
+      <c r="V302" t="s">
+        <v>1101</v>
+      </c>
+      <c r="W302">
+        <v>5</v>
+      </c>
     </row>
     <row r="303" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G303" s="29" t="str">
@@ -20942,6 +21533,15 @@
         <v>0.5</v>
       </c>
       <c r="T303" s="184"/>
+      <c r="U303">
+        <v>177235</v>
+      </c>
+      <c r="V303" t="s">
+        <v>1102</v>
+      </c>
+      <c r="W303">
+        <v>1</v>
+      </c>
     </row>
     <row r="304" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G304" s="29" t="str">
@@ -20961,8 +21561,17 @@
         <v>3</v>
       </c>
       <c r="T304" s="184"/>
-    </row>
-    <row r="305" spans="7:20" x14ac:dyDescent="0.35">
+      <c r="U304">
+        <v>180218</v>
+      </c>
+      <c r="V304" t="s">
+        <v>1103</v>
+      </c>
+      <c r="W304">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="305" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G305" s="29" t="str">
         <f t="shared" si="6"/>
         <v>164006 JUL/2025</v>
@@ -20980,8 +21589,17 @@
         <v>5.875</v>
       </c>
       <c r="T305" s="184"/>
-    </row>
-    <row r="306" spans="7:20" x14ac:dyDescent="0.35">
+      <c r="U305">
+        <v>181715</v>
+      </c>
+      <c r="V305" t="s">
+        <v>1104</v>
+      </c>
+      <c r="W305">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="306" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G306" s="29" t="str">
         <f t="shared" si="6"/>
         <v>164006 FEV/2026</v>
@@ -20999,8 +21617,17 @@
         <v>3</v>
       </c>
       <c r="T306" s="184"/>
-    </row>
-    <row r="307" spans="7:20" x14ac:dyDescent="0.35">
+      <c r="U306">
+        <v>109838</v>
+      </c>
+      <c r="V306" t="s">
+        <v>1105</v>
+      </c>
+      <c r="W306">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G307" s="29" t="str">
         <f t="shared" si="6"/>
         <v>167265 JUL/2025</v>
@@ -21018,8 +21645,17 @@
         <v>5.375</v>
       </c>
       <c r="T307" s="184"/>
-    </row>
-    <row r="308" spans="7:20" x14ac:dyDescent="0.35">
+      <c r="U307">
+        <v>187644</v>
+      </c>
+      <c r="V307" t="s">
+        <v>1106</v>
+      </c>
+      <c r="W307">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="308" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G308" s="29" t="str">
         <f t="shared" si="6"/>
         <v>167265 AGO/2025</v>
@@ -21037,8 +21673,17 @@
         <v>0.5</v>
       </c>
       <c r="T308" s="184"/>
-    </row>
-    <row r="309" spans="7:20" x14ac:dyDescent="0.35">
+      <c r="U308">
+        <v>155862</v>
+      </c>
+      <c r="V308" t="s">
+        <v>1107</v>
+      </c>
+      <c r="W308">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="309" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G309" s="29" t="str">
         <f t="shared" si="6"/>
         <v>167265 FEV/2026</v>
@@ -21056,8 +21701,17 @@
         <v>3</v>
       </c>
       <c r="T309" s="184"/>
-    </row>
-    <row r="310" spans="7:20" x14ac:dyDescent="0.35">
+      <c r="U309">
+        <v>185967</v>
+      </c>
+      <c r="V309" t="s">
+        <v>1108</v>
+      </c>
+      <c r="W309">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="310" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G310" s="29" t="str">
         <f t="shared" si="6"/>
         <v>48374 JUL/2025</v>
@@ -21075,8 +21729,17 @@
         <v>130.708</v>
       </c>
       <c r="T310" s="184"/>
-    </row>
-    <row r="311" spans="7:20" x14ac:dyDescent="0.35">
+      <c r="U310">
+        <v>83173</v>
+      </c>
+      <c r="V310" t="s">
+        <v>1109</v>
+      </c>
+      <c r="W310">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="311" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G311" s="29" t="str">
         <f t="shared" si="6"/>
         <v>48374 AGO/2025</v>
@@ -21094,8 +21757,17 @@
         <v>64</v>
       </c>
       <c r="T311" s="184"/>
-    </row>
-    <row r="312" spans="7:20" x14ac:dyDescent="0.35">
+      <c r="U311">
+        <v>143146</v>
+      </c>
+      <c r="V311" t="s">
+        <v>830</v>
+      </c>
+      <c r="W311">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G312" s="29" t="str">
         <f t="shared" si="6"/>
         <v>48374 SET/2025</v>
@@ -21113,8 +21785,17 @@
         <v>136.542</v>
       </c>
       <c r="T312" s="184"/>
-    </row>
-    <row r="313" spans="7:20" x14ac:dyDescent="0.35">
+      <c r="U312">
+        <v>184237</v>
+      </c>
+      <c r="V312" t="s">
+        <v>1110</v>
+      </c>
+      <c r="W312">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G313" s="29" t="str">
         <f t="shared" si="6"/>
         <v>48374 OUT/2025</v>
@@ -21132,8 +21813,17 @@
         <v>214</v>
       </c>
       <c r="T313" s="184"/>
-    </row>
-    <row r="314" spans="7:20" x14ac:dyDescent="0.35">
+      <c r="U313">
+        <v>183529</v>
+      </c>
+      <c r="V313" t="s">
+        <v>1111</v>
+      </c>
+      <c r="W313">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="314" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G314" s="29" t="str">
         <f t="shared" si="6"/>
         <v>48374 NOV/2025</v>
@@ -21152,7 +21842,7 @@
       </c>
       <c r="T314" s="184"/>
     </row>
-    <row r="315" spans="7:20" x14ac:dyDescent="0.35">
+    <row r="315" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G315" s="29" t="str">
         <f t="shared" si="6"/>
         <v>48374 DEZ/2025</v>
@@ -21171,7 +21861,7 @@
       </c>
       <c r="T315" s="184"/>
     </row>
-    <row r="316" spans="7:20" x14ac:dyDescent="0.35">
+    <row r="316" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G316" s="29" t="str">
         <f t="shared" si="6"/>
         <v>48374 JAN/2026</v>
@@ -21190,7 +21880,7 @@
       </c>
       <c r="T316" s="184"/>
     </row>
-    <row r="317" spans="7:20" x14ac:dyDescent="0.35">
+    <row r="317" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G317" s="29" t="str">
         <f t="shared" si="6"/>
         <v>48374 FEV/2026</v>
@@ -21209,7 +21899,7 @@
       </c>
       <c r="T317" s="184"/>
     </row>
-    <row r="318" spans="7:20" x14ac:dyDescent="0.35">
+    <row r="318" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G318" s="29" t="str">
         <f t="shared" si="6"/>
         <v>48374 MAR/2026</v>
@@ -21228,7 +21918,7 @@
       </c>
       <c r="T318" s="184"/>
     </row>
-    <row r="319" spans="7:20" x14ac:dyDescent="0.35">
+    <row r="319" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G319" s="29" t="str">
         <f t="shared" si="6"/>
         <v>48374 ABR/2026</v>
@@ -21247,7 +21937,7 @@
       </c>
       <c r="T319" s="184"/>
     </row>
-    <row r="320" spans="7:20" x14ac:dyDescent="0.35">
+    <row r="320" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G320" s="29" t="str">
         <f t="shared" si="6"/>
         <v>48374 MAI/2026</v>
@@ -22370,138 +23060,138 @@
       <c r="B2" s="150"/>
     </row>
     <row r="3" spans="2:99" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="E3" s="192" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" s="190" t="s">
+      <c r="E3" s="193" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="191" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="201" t="s">
+      <c r="G3" s="202" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="202"/>
-      <c r="I3" s="202"/>
-      <c r="J3" s="202"/>
-      <c r="K3" s="202"/>
-      <c r="L3" s="202"/>
-      <c r="M3" s="202"/>
-      <c r="N3" s="203"/>
-      <c r="O3" s="197" t="s">
+      <c r="H3" s="203"/>
+      <c r="I3" s="203"/>
+      <c r="J3" s="203"/>
+      <c r="K3" s="203"/>
+      <c r="L3" s="203"/>
+      <c r="M3" s="203"/>
+      <c r="N3" s="204"/>
+      <c r="O3" s="198" t="s">
         <v>23</v>
       </c>
-      <c r="P3" s="198"/>
-      <c r="Q3" s="198"/>
-      <c r="R3" s="199"/>
-      <c r="S3" s="197" t="s">
+      <c r="P3" s="199"/>
+      <c r="Q3" s="199"/>
+      <c r="R3" s="200"/>
+      <c r="S3" s="198" t="s">
         <v>24</v>
       </c>
-      <c r="T3" s="198"/>
-      <c r="U3" s="198"/>
-      <c r="V3" s="199"/>
-      <c r="W3" s="197" t="s">
+      <c r="T3" s="199"/>
+      <c r="U3" s="199"/>
+      <c r="V3" s="200"/>
+      <c r="W3" s="198" t="s">
         <v>25</v>
       </c>
-      <c r="X3" s="198"/>
-      <c r="Y3" s="198"/>
-      <c r="Z3" s="200"/>
-      <c r="AB3" s="201" t="s">
+      <c r="X3" s="199"/>
+      <c r="Y3" s="199"/>
+      <c r="Z3" s="201"/>
+      <c r="AB3" s="202" t="s">
         <v>30</v>
       </c>
-      <c r="AC3" s="202"/>
-      <c r="AD3" s="202"/>
-      <c r="AE3" s="202"/>
-      <c r="AF3" s="202"/>
-      <c r="AG3" s="202"/>
-      <c r="AH3" s="202"/>
-      <c r="AI3" s="203"/>
-      <c r="AJ3" s="197" t="s">
+      <c r="AC3" s="203"/>
+      <c r="AD3" s="203"/>
+      <c r="AE3" s="203"/>
+      <c r="AF3" s="203"/>
+      <c r="AG3" s="203"/>
+      <c r="AH3" s="203"/>
+      <c r="AI3" s="204"/>
+      <c r="AJ3" s="198" t="s">
         <v>27</v>
       </c>
-      <c r="AK3" s="198"/>
-      <c r="AL3" s="198"/>
-      <c r="AM3" s="199"/>
-      <c r="AN3" s="197" t="s">
+      <c r="AK3" s="199"/>
+      <c r="AL3" s="199"/>
+      <c r="AM3" s="200"/>
+      <c r="AN3" s="198" t="s">
         <v>28</v>
       </c>
-      <c r="AO3" s="198"/>
-      <c r="AP3" s="198"/>
-      <c r="AQ3" s="199"/>
-      <c r="AR3" s="197" t="s">
+      <c r="AO3" s="199"/>
+      <c r="AP3" s="199"/>
+      <c r="AQ3" s="200"/>
+      <c r="AR3" s="198" t="s">
         <v>29</v>
       </c>
-      <c r="AS3" s="198"/>
-      <c r="AT3" s="198"/>
-      <c r="AU3" s="200"/>
-      <c r="AW3" s="201" t="s">
+      <c r="AS3" s="199"/>
+      <c r="AT3" s="199"/>
+      <c r="AU3" s="201"/>
+      <c r="AW3" s="202" t="s">
         <v>66</v>
       </c>
-      <c r="AX3" s="202"/>
-      <c r="AY3" s="202"/>
-      <c r="AZ3" s="202"/>
-      <c r="BA3" s="202"/>
-      <c r="BB3" s="202"/>
-      <c r="BC3" s="202"/>
-      <c r="BD3" s="203"/>
-      <c r="BE3" s="197" t="s">
+      <c r="AX3" s="203"/>
+      <c r="AY3" s="203"/>
+      <c r="AZ3" s="203"/>
+      <c r="BA3" s="203"/>
+      <c r="BB3" s="203"/>
+      <c r="BC3" s="203"/>
+      <c r="BD3" s="204"/>
+      <c r="BE3" s="198" t="s">
         <v>67</v>
       </c>
-      <c r="BF3" s="198"/>
-      <c r="BG3" s="198"/>
-      <c r="BH3" s="199"/>
-      <c r="BI3" s="197" t="s">
+      <c r="BF3" s="199"/>
+      <c r="BG3" s="199"/>
+      <c r="BH3" s="200"/>
+      <c r="BI3" s="198" t="s">
         <v>68</v>
       </c>
-      <c r="BJ3" s="198"/>
-      <c r="BK3" s="198"/>
-      <c r="BL3" s="199"/>
-      <c r="BM3" s="197" t="s">
+      <c r="BJ3" s="199"/>
+      <c r="BK3" s="199"/>
+      <c r="BL3" s="200"/>
+      <c r="BM3" s="198" t="s">
         <v>72</v>
       </c>
-      <c r="BN3" s="198"/>
-      <c r="BO3" s="198"/>
-      <c r="BP3" s="200"/>
-      <c r="BR3" s="201" t="s">
+      <c r="BN3" s="199"/>
+      <c r="BO3" s="199"/>
+      <c r="BP3" s="201"/>
+      <c r="BR3" s="202" t="s">
         <v>73</v>
       </c>
-      <c r="BS3" s="202"/>
-      <c r="BT3" s="202"/>
-      <c r="BU3" s="202"/>
-      <c r="BV3" s="202"/>
-      <c r="BW3" s="202"/>
-      <c r="BX3" s="202"/>
-      <c r="BY3" s="203"/>
+      <c r="BS3" s="203"/>
+      <c r="BT3" s="203"/>
+      <c r="BU3" s="203"/>
+      <c r="BV3" s="203"/>
+      <c r="BW3" s="203"/>
+      <c r="BX3" s="203"/>
+      <c r="BY3" s="204"/>
       <c r="BZ3" s="185" t="s">
         <v>69</v>
       </c>
       <c r="CA3" s="186"/>
       <c r="CB3" s="186"/>
       <c r="CC3" s="186"/>
-      <c r="CD3" s="197" t="s">
+      <c r="CD3" s="198" t="s">
         <v>70</v>
       </c>
-      <c r="CE3" s="198"/>
-      <c r="CF3" s="198"/>
-      <c r="CG3" s="199"/>
-      <c r="CH3" s="197" t="s">
+      <c r="CE3" s="199"/>
+      <c r="CF3" s="199"/>
+      <c r="CG3" s="200"/>
+      <c r="CH3" s="198" t="s">
         <v>71</v>
       </c>
-      <c r="CI3" s="198"/>
-      <c r="CJ3" s="198"/>
-      <c r="CK3" s="200"/>
-      <c r="CM3" s="194" t="s">
+      <c r="CI3" s="199"/>
+      <c r="CJ3" s="199"/>
+      <c r="CK3" s="201"/>
+      <c r="CM3" s="195" t="s">
         <v>783</v>
       </c>
-      <c r="CN3" s="195"/>
-      <c r="CO3" s="195"/>
-      <c r="CP3" s="195"/>
-      <c r="CQ3" s="195"/>
-      <c r="CR3" s="195"/>
-      <c r="CS3" s="195"/>
-      <c r="CT3" s="196"/>
+      <c r="CN3" s="196"/>
+      <c r="CO3" s="196"/>
+      <c r="CP3" s="196"/>
+      <c r="CQ3" s="196"/>
+      <c r="CR3" s="196"/>
+      <c r="CS3" s="196"/>
+      <c r="CT3" s="197"/>
     </row>
     <row r="4" spans="2:99" ht="26" x14ac:dyDescent="0.3">
-      <c r="E4" s="193"/>
-      <c r="F4" s="191"/>
+      <c r="E4" s="194"/>
+      <c r="F4" s="192"/>
       <c r="G4" s="146" t="s">
         <v>169</v>
       </c>
@@ -23029,27 +23719,27 @@
       </c>
       <c r="BT5" s="34">
         <f>SUMIF(Rede!$C:$C,Geral!E5,Rede!$BT:$BT)</f>
-        <v>1461.5400000000002</v>
+        <v>1604.0810000000001</v>
       </c>
       <c r="BU5" s="34">
         <f>SUMIF(Rede!$C:$C,Geral!E5,Rede!$BU:$BU)</f>
-        <v>25.875</v>
+        <v>584</v>
       </c>
       <c r="BV5" s="34">
         <f>SUMIF(Rede!$C:$C,Geral!E5,Rede!$BV:$BV)</f>
-        <v>59.167000000000002</v>
+        <v>61.332999999999998</v>
       </c>
       <c r="BW5" s="36">
         <f>(BT5+BU5+BV5)/BS5</f>
-        <v>0.35875249362096961</v>
+        <v>0.52178473672001857</v>
       </c>
       <c r="BX5" s="37">
         <f>IFERROR(((BT5+BU5+BV5)/BR5-1),0)</f>
-        <v>0.12048993206416414</v>
+        <v>0.62968775017695777</v>
       </c>
       <c r="BY5" s="40">
         <f>BS5-BT5-BU5-BV5</f>
-        <v>2764.4180000000001</v>
+        <v>2061.5859999999998</v>
       </c>
       <c r="BZ5" s="67">
         <f>SUMIF(Rede!$C:$C,Geral!E5,Rede!$BZ:$BZ)</f>
@@ -23089,15 +23779,15 @@
       </c>
       <c r="CI5" s="64">
         <f>SUMIF(Rede!$C:$C,Geral!E5,Rede!$CI:$CI)</f>
-        <v>34.11</v>
+        <v>176.65099999999998</v>
       </c>
       <c r="CJ5" s="64">
         <f>SUMIF(Rede!$C:$C,Geral!E5,Rede!$CJ:$CJ)</f>
-        <v>13.334</v>
+        <v>15.5</v>
       </c>
       <c r="CK5" s="64">
         <f>SUMIF(Rede!$C:$C,Geral!E5,Rede!$CK:$CK)</f>
-        <v>25.875</v>
+        <v>584</v>
       </c>
       <c r="CL5" s="7"/>
       <c r="CM5" s="39">
@@ -23110,27 +23800,27 @@
       </c>
       <c r="CO5" s="34">
         <f t="shared" si="1"/>
-        <v>18953.956000000002</v>
+        <v>19096.497000000003</v>
       </c>
       <c r="CP5" s="34">
         <f t="shared" si="1"/>
-        <v>455.20699999999999</v>
+        <v>1013.332</v>
       </c>
       <c r="CQ5" s="34">
         <f t="shared" si="1"/>
-        <v>59.167000000000002</v>
+        <v>61.332999999999998</v>
       </c>
       <c r="CR5" s="36">
         <f t="shared" ref="CR5:CR6" si="2">(CO5+CP5+CQ5)/CN5</f>
-        <v>1.1019860308565208</v>
+        <v>1.1417691579166718</v>
       </c>
       <c r="CS5" s="37">
         <f t="shared" ref="CS5:CS6" si="3">IFERROR(((CO5+CP5+CQ5)/CM5-1),0)</f>
-        <v>0.16089562998897744</v>
+        <v>0.20280547009423611</v>
       </c>
       <c r="CT5" s="40">
         <f t="shared" ref="CT5:CT6" si="4">CN5-CO5-CQ5-CP5</f>
-        <v>-1801.7448937730151</v>
+        <v>-2504.5768937730163</v>
       </c>
       <c r="CU5" s="21"/>
     </row>
@@ -23394,27 +24084,27 @@
       </c>
       <c r="BT6" s="34">
         <f>SUMIF(Rede!$C:$C,Geral!E6,Rede!$BT:$BT)</f>
-        <v>2939.1889999999999</v>
+        <v>3163.8760000000002</v>
       </c>
       <c r="BU6" s="34">
         <f>SUMIF(Rede!$C:$C,Geral!E6,Rede!$BU:$BU)</f>
-        <v>294</v>
+        <v>257</v>
       </c>
       <c r="BV6" s="34">
         <f>SUMIF(Rede!$C:$C,Geral!E6,Rede!$BV:$BV)</f>
-        <v>88.584000000000003</v>
+        <v>92.417000000000002</v>
       </c>
       <c r="BW6" s="36">
         <f>(BT6+BU6+BV6)/BS6</f>
-        <v>0.50745080965475098</v>
+        <v>0.53670837152459516</v>
       </c>
       <c r="BX6" s="37">
         <f>IFERROR(((BT6+BU6+BV6)/BR6-1),0)</f>
-        <v>-7.4309955693703356E-2</v>
+        <v>-2.0938410652683981E-2</v>
       </c>
       <c r="BY6" s="40">
         <f>BS6-BT6-BU6-BV6</f>
-        <v>3224.2270000000003</v>
+        <v>3032.7069999999999</v>
       </c>
       <c r="BZ6" s="67">
         <f>SUMIF(Rede!$C:$C,Geral!E6,Rede!$BZ:$BZ)</f>
@@ -23454,15 +24144,15 @@
       </c>
       <c r="CI6" s="64">
         <f>SUMIF(Rede!$C:$C,Geral!E6,Rede!$CI:$CI)</f>
-        <v>257.66700000000003</v>
+        <v>482.35400000000004</v>
       </c>
       <c r="CJ6" s="64">
         <f>SUMIF(Rede!$C:$C,Geral!E6,Rede!$CJ:$CJ)</f>
-        <v>27.875</v>
+        <v>31.707999999999998</v>
       </c>
       <c r="CK6" s="64">
         <f>SUMIF(Rede!$C:$C,Geral!E6,Rede!$CK:$CK)</f>
-        <v>294</v>
+        <v>257</v>
       </c>
       <c r="CL6" s="7"/>
       <c r="CM6" s="39">
@@ -23475,27 +24165,27 @@
       </c>
       <c r="CO6" s="34">
         <f t="shared" si="1"/>
-        <v>21451.547999999999</v>
+        <v>21676.235000000001</v>
       </c>
       <c r="CP6" s="34">
         <f t="shared" si="1"/>
-        <v>531.25</v>
+        <v>494.25</v>
       </c>
       <c r="CQ6" s="34">
         <f t="shared" si="1"/>
-        <v>88.584000000000003</v>
+        <v>92.417000000000002</v>
       </c>
       <c r="CR6" s="36">
         <f t="shared" si="2"/>
-        <v>0.821747495851465</v>
+        <v>0.82887804528445819</v>
       </c>
       <c r="CS6" s="37">
         <f t="shared" si="3"/>
-        <v>-0.12983263041590565</v>
+        <v>-0.12228192721921649</v>
       </c>
       <c r="CT6" s="40">
         <f t="shared" si="4"/>
-        <v>4787.698327504294</v>
+        <v>4596.1783275042917</v>
       </c>
       <c r="CU6" s="21"/>
     </row>
@@ -23760,27 +24450,27 @@
       </c>
       <c r="BT7" s="49">
         <f>SUM(BT5:BT6)</f>
-        <v>4400.7290000000003</v>
+        <v>4767.9570000000003</v>
       </c>
       <c r="BU7" s="49">
         <f>SUM(BU5:BU6)</f>
-        <v>319.875</v>
+        <v>841</v>
       </c>
       <c r="BV7" s="49">
         <f>SUM(BV5:BV6)</f>
-        <v>147.751</v>
+        <v>153.75</v>
       </c>
       <c r="BW7" s="48">
         <f t="shared" ref="BW7" si="12">(BT7+BU7+BV7)/BS7</f>
-        <v>0.44840701851340153</v>
+        <v>0.530782628718799</v>
       </c>
       <c r="BX7" s="47">
         <f t="shared" ref="BX7" si="13">IFERROR(((BT7+BU7+BV7)/BR7-1),0)</f>
-        <v>-2.0195817740729871E-2</v>
+        <v>0.15980129216845773</v>
       </c>
       <c r="BY7" s="46">
         <f t="shared" ref="BY7" si="14">BS7-BT7-BU7-BV7</f>
-        <v>5988.6449999999995</v>
+        <v>5094.2929999999997</v>
       </c>
       <c r="BZ7" s="68">
         <f t="shared" ref="BZ7:CK7" si="15">SUM(BZ5:BZ6)</f>
@@ -23820,15 +24510,15 @@
       </c>
       <c r="CI7" s="69">
         <f t="shared" si="15"/>
-        <v>291.77700000000004</v>
+        <v>659.005</v>
       </c>
       <c r="CJ7" s="69">
         <f t="shared" si="15"/>
-        <v>41.209000000000003</v>
+        <v>47.207999999999998</v>
       </c>
       <c r="CK7" s="69">
         <f t="shared" si="15"/>
-        <v>319.875</v>
+        <v>841</v>
       </c>
       <c r="CL7" s="8"/>
       <c r="CM7" s="41">
@@ -23841,27 +24531,27 @@
       </c>
       <c r="CO7" s="49">
         <f>SUM(CO5:CO6)</f>
-        <v>40405.504000000001</v>
+        <v>40772.732000000004</v>
       </c>
       <c r="CP7" s="49">
         <f>SUM(CP5:CP6)</f>
-        <v>986.45699999999999</v>
+        <v>1507.5819999999999</v>
       </c>
       <c r="CQ7" s="49">
         <f>SUM(CQ5:CQ6)</f>
-        <v>147.751</v>
+        <v>153.75</v>
       </c>
       <c r="CR7" s="48">
         <f t="shared" ref="CR7" si="16">(CO7+CP7+CQ7)/CN7</f>
-        <v>0.93293860058811806</v>
+        <v>0.95302481359106783</v>
       </c>
       <c r="CS7" s="47">
         <f t="shared" ref="CS7" si="17">IFERROR(((CO7+CP7+CQ7)/CM7-1),0)</f>
-        <v>-1.4119220726328985E-2</v>
+        <v>7.1068399335276755E-3</v>
       </c>
       <c r="CT7" s="46">
         <f>CN7-CO7-CQ7-CP7</f>
-        <v>2985.9534337312784</v>
+        <v>2091.6014337312758</v>
       </c>
       <c r="CU7" s="21"/>
     </row>
@@ -23869,12 +24559,15 @@
       <c r="B8" s="3"/>
       <c r="C8" s="2"/>
       <c r="E8" s="133" t="s">
-        <v>827</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="9" spans="2:99" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="3"/>
       <c r="C9" s="2"/>
+      <c r="E9" s="190">
+        <v>46191</v>
+      </c>
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
       <c r="U9" s="11"/>
@@ -23901,137 +24594,137 @@
       <c r="CK9" s="11"/>
     </row>
     <row r="10" spans="2:99" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="207" t="s">
+      <c r="B10" s="208" t="s">
         <v>784</v>
       </c>
-      <c r="C10" s="208"/>
-      <c r="D10" s="208"/>
-      <c r="E10" s="209"/>
-      <c r="F10" s="190" t="s">
+      <c r="C10" s="209"/>
+      <c r="D10" s="209"/>
+      <c r="E10" s="210"/>
+      <c r="F10" s="191" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="201" t="s">
+      <c r="G10" s="202" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="202"/>
-      <c r="I10" s="202"/>
-      <c r="J10" s="202"/>
-      <c r="K10" s="202"/>
-      <c r="L10" s="202"/>
-      <c r="M10" s="202"/>
-      <c r="N10" s="203"/>
-      <c r="O10" s="197" t="s">
+      <c r="H10" s="203"/>
+      <c r="I10" s="203"/>
+      <c r="J10" s="203"/>
+      <c r="K10" s="203"/>
+      <c r="L10" s="203"/>
+      <c r="M10" s="203"/>
+      <c r="N10" s="204"/>
+      <c r="O10" s="198" t="s">
         <v>23</v>
       </c>
-      <c r="P10" s="198"/>
-      <c r="Q10" s="198"/>
-      <c r="R10" s="199"/>
-      <c r="S10" s="197" t="s">
+      <c r="P10" s="199"/>
+      <c r="Q10" s="199"/>
+      <c r="R10" s="200"/>
+      <c r="S10" s="198" t="s">
         <v>24</v>
       </c>
-      <c r="T10" s="198"/>
-      <c r="U10" s="198"/>
-      <c r="V10" s="199"/>
-      <c r="W10" s="197" t="s">
+      <c r="T10" s="199"/>
+      <c r="U10" s="199"/>
+      <c r="V10" s="200"/>
+      <c r="W10" s="198" t="s">
         <v>25</v>
       </c>
-      <c r="X10" s="198"/>
-      <c r="Y10" s="198"/>
-      <c r="Z10" s="200"/>
-      <c r="AB10" s="201" t="s">
+      <c r="X10" s="199"/>
+      <c r="Y10" s="199"/>
+      <c r="Z10" s="201"/>
+      <c r="AB10" s="202" t="s">
         <v>30</v>
       </c>
-      <c r="AC10" s="202"/>
-      <c r="AD10" s="202"/>
-      <c r="AE10" s="202"/>
-      <c r="AF10" s="202"/>
-      <c r="AG10" s="202"/>
-      <c r="AH10" s="202"/>
-      <c r="AI10" s="203"/>
-      <c r="AJ10" s="197" t="s">
+      <c r="AC10" s="203"/>
+      <c r="AD10" s="203"/>
+      <c r="AE10" s="203"/>
+      <c r="AF10" s="203"/>
+      <c r="AG10" s="203"/>
+      <c r="AH10" s="203"/>
+      <c r="AI10" s="204"/>
+      <c r="AJ10" s="198" t="s">
         <v>27</v>
       </c>
-      <c r="AK10" s="198"/>
-      <c r="AL10" s="198"/>
-      <c r="AM10" s="199"/>
-      <c r="AN10" s="197" t="s">
+      <c r="AK10" s="199"/>
+      <c r="AL10" s="199"/>
+      <c r="AM10" s="200"/>
+      <c r="AN10" s="198" t="s">
         <v>28</v>
       </c>
-      <c r="AO10" s="198"/>
-      <c r="AP10" s="198"/>
-      <c r="AQ10" s="199"/>
-      <c r="AR10" s="197" t="s">
+      <c r="AO10" s="199"/>
+      <c r="AP10" s="199"/>
+      <c r="AQ10" s="200"/>
+      <c r="AR10" s="198" t="s">
         <v>29</v>
       </c>
-      <c r="AS10" s="198"/>
-      <c r="AT10" s="198"/>
-      <c r="AU10" s="200"/>
-      <c r="AW10" s="201" t="s">
+      <c r="AS10" s="199"/>
+      <c r="AT10" s="199"/>
+      <c r="AU10" s="201"/>
+      <c r="AW10" s="202" t="s">
         <v>66</v>
       </c>
-      <c r="AX10" s="202"/>
-      <c r="AY10" s="202"/>
-      <c r="AZ10" s="202"/>
-      <c r="BA10" s="202"/>
-      <c r="BB10" s="202"/>
-      <c r="BC10" s="202"/>
-      <c r="BD10" s="203"/>
-      <c r="BE10" s="197" t="s">
+      <c r="AX10" s="203"/>
+      <c r="AY10" s="203"/>
+      <c r="AZ10" s="203"/>
+      <c r="BA10" s="203"/>
+      <c r="BB10" s="203"/>
+      <c r="BC10" s="203"/>
+      <c r="BD10" s="204"/>
+      <c r="BE10" s="198" t="s">
         <v>67</v>
       </c>
-      <c r="BF10" s="198"/>
-      <c r="BG10" s="198"/>
-      <c r="BH10" s="199"/>
-      <c r="BI10" s="197" t="s">
+      <c r="BF10" s="199"/>
+      <c r="BG10" s="199"/>
+      <c r="BH10" s="200"/>
+      <c r="BI10" s="198" t="s">
         <v>68</v>
       </c>
-      <c r="BJ10" s="198"/>
-      <c r="BK10" s="198"/>
-      <c r="BL10" s="199"/>
-      <c r="BM10" s="197" t="s">
+      <c r="BJ10" s="199"/>
+      <c r="BK10" s="199"/>
+      <c r="BL10" s="200"/>
+      <c r="BM10" s="198" t="s">
         <v>72</v>
       </c>
-      <c r="BN10" s="198"/>
-      <c r="BO10" s="198"/>
-      <c r="BP10" s="200"/>
-      <c r="BR10" s="201" t="s">
+      <c r="BN10" s="199"/>
+      <c r="BO10" s="199"/>
+      <c r="BP10" s="201"/>
+      <c r="BR10" s="202" t="s">
         <v>73</v>
       </c>
-      <c r="BS10" s="202"/>
-      <c r="BT10" s="202"/>
-      <c r="BU10" s="202"/>
-      <c r="BV10" s="202"/>
-      <c r="BW10" s="202"/>
-      <c r="BX10" s="202"/>
-      <c r="BY10" s="203"/>
+      <c r="BS10" s="203"/>
+      <c r="BT10" s="203"/>
+      <c r="BU10" s="203"/>
+      <c r="BV10" s="203"/>
+      <c r="BW10" s="203"/>
+      <c r="BX10" s="203"/>
+      <c r="BY10" s="204"/>
       <c r="BZ10" s="185" t="s">
         <v>69</v>
       </c>
       <c r="CA10" s="186"/>
       <c r="CB10" s="186"/>
       <c r="CC10" s="186"/>
-      <c r="CD10" s="197" t="s">
+      <c r="CD10" s="198" t="s">
         <v>70</v>
       </c>
-      <c r="CE10" s="198"/>
-      <c r="CF10" s="198"/>
-      <c r="CG10" s="199"/>
-      <c r="CH10" s="197" t="s">
+      <c r="CE10" s="199"/>
+      <c r="CF10" s="199"/>
+      <c r="CG10" s="200"/>
+      <c r="CH10" s="198" t="s">
         <v>71</v>
       </c>
-      <c r="CI10" s="198"/>
-      <c r="CJ10" s="198"/>
-      <c r="CK10" s="200"/>
-      <c r="CM10" s="194" t="s">
+      <c r="CI10" s="199"/>
+      <c r="CJ10" s="199"/>
+      <c r="CK10" s="201"/>
+      <c r="CM10" s="195" t="s">
         <v>783</v>
       </c>
-      <c r="CN10" s="195"/>
-      <c r="CO10" s="195"/>
-      <c r="CP10" s="195"/>
-      <c r="CQ10" s="195"/>
-      <c r="CR10" s="195"/>
-      <c r="CS10" s="195"/>
-      <c r="CT10" s="196"/>
+      <c r="CN10" s="196"/>
+      <c r="CO10" s="196"/>
+      <c r="CP10" s="196"/>
+      <c r="CQ10" s="196"/>
+      <c r="CR10" s="196"/>
+      <c r="CS10" s="196"/>
+      <c r="CT10" s="197"/>
     </row>
     <row r="11" spans="2:99" ht="26" x14ac:dyDescent="0.3">
       <c r="B11" s="52" t="s">
@@ -24046,7 +24739,7 @@
       <c r="E11" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="191"/>
+      <c r="F11" s="192"/>
       <c r="G11" s="38" t="s">
         <v>169</v>
       </c>
@@ -24582,7 +25275,7 @@
       </c>
       <c r="BT12" s="35">
         <f>SUMIF(Rede!$D:$D,Geral!C12,Rede!$BT:$BT)</f>
-        <v>-11.777000000000001</v>
+        <v>79.888999999999996</v>
       </c>
       <c r="BU12" s="35">
         <f>SUMIF(Rede!$D:$D,Geral!C12,Rede!$BU:$BU)</f>
@@ -24594,15 +25287,15 @@
       </c>
       <c r="BW12" s="36">
         <f t="shared" ref="BW12:BW20" si="24">(BT12+BU12+BV12)/BS12</f>
-        <v>-1.527496757457847E-2</v>
+        <v>0.10361738002594033</v>
       </c>
       <c r="BX12" s="37">
         <f t="shared" ref="BX12:BX20" si="25">IFERROR(((BT12+BU12+BV12)/BR12-1),0)</f>
-        <v>-1.0776821344942449</v>
+        <v>-0.47304508426503089</v>
       </c>
       <c r="BY12" s="40">
         <f t="shared" ref="BY12:BY20" si="26">BS12-BT12-BU12-BV12</f>
-        <v>782.77700000000004</v>
+        <v>691.11099999999999</v>
       </c>
       <c r="BZ12" s="67">
         <f>SUMIF(Rede!$D:$D,Geral!C12,Rede!$BZ:$BZ)</f>
@@ -24642,7 +25335,7 @@
       </c>
       <c r="CI12" s="64">
         <f>SUMIF(Rede!$D:$D,Geral!C12,Rede!$CI:$CI)</f>
-        <v>-2.0270000000000001</v>
+        <v>89.638999999999996</v>
       </c>
       <c r="CJ12" s="64">
         <f>SUMIF(Rede!$D:$D,Geral!C12,Rede!$CJ:$CJ)</f>
@@ -24663,7 +25356,7 @@
       </c>
       <c r="CO12" s="34">
         <f t="shared" si="27"/>
-        <v>1997.9570000000001</v>
+        <v>2089.623</v>
       </c>
       <c r="CP12" s="34">
         <f t="shared" si="27"/>
@@ -24675,15 +25368,15 @@
       </c>
       <c r="CR12" s="36">
         <f>(CO12+CP12+CQ12)/CN12</f>
-        <v>0.63145419728489571</v>
+        <v>0.66042523142042375</v>
       </c>
       <c r="CS12" s="37">
         <f>IFERROR(((CO12+CP12+CQ12)/CM12-1),0)</f>
-        <v>-0.39938289623319589</v>
+        <v>-0.37182666382484686</v>
       </c>
       <c r="CT12" s="40">
         <f>CN12-CO12-CQ12-CP12</f>
-        <v>1166.0998842375968</v>
+        <v>1074.4338842375969</v>
       </c>
       <c r="CU12" s="21"/>
     </row>
@@ -24959,23 +25652,23 @@
       </c>
       <c r="BU13" s="35">
         <f>SUMIF(Rede!$D:$D,Geral!C13,Rede!$BU:$BU)</f>
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="BV13" s="35">
         <f>SUMIF(Rede!$D:$D,Geral!C13,Rede!$BV:$BV)</f>
-        <v>55.082999999999998</v>
+        <v>56.582999999999998</v>
       </c>
       <c r="BW13" s="36">
         <f t="shared" si="24"/>
-        <v>0.47324329004329002</v>
+        <v>0.60636017316017321</v>
       </c>
       <c r="BX13" s="37">
         <f t="shared" si="25"/>
-        <v>0.70810716216511826</v>
+        <v>1.1885744107049665</v>
       </c>
       <c r="BY13" s="40">
         <f t="shared" si="26"/>
-        <v>1216.808</v>
+        <v>909.30800000000011</v>
       </c>
       <c r="BZ13" s="67">
         <f>SUMIF(Rede!$D:$D,Geral!C13,Rede!$BZ:$BZ)</f>
@@ -25019,11 +25712,11 @@
       </c>
       <c r="CJ13" s="64">
         <f>SUMIF(Rede!$D:$D,Geral!C13,Rede!$CJ:$CJ)</f>
-        <v>9.25</v>
+        <v>10.75</v>
       </c>
       <c r="CK13" s="64">
         <f>SUMIF(Rede!$D:$D,Geral!C13,Rede!$CK:$CK)</f>
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="CL13" s="7"/>
       <c r="CM13" s="39">
@@ -25040,23 +25733,23 @@
       </c>
       <c r="CP13" s="34">
         <f t="shared" si="27"/>
-        <v>333.62400000000002</v>
+        <v>639.62400000000002</v>
       </c>
       <c r="CQ13" s="34">
         <f t="shared" si="27"/>
-        <v>55.082999999999998</v>
+        <v>56.582999999999998</v>
       </c>
       <c r="CR13" s="36">
         <f t="shared" ref="CR13:CR19" si="31">(CO13+CP13+CQ13)/CN13</f>
-        <v>1.318556990790781</v>
+        <v>1.3510471639310482</v>
       </c>
       <c r="CS13" s="37">
         <f t="shared" ref="CS13:CS19" si="32">IFERROR(((CO13+CP13+CQ13)/CM13-1),0)</f>
-        <v>0.42218553876625831</v>
+        <v>0.45722919233210679</v>
       </c>
       <c r="CT13" s="40">
         <f t="shared" ref="CT13:CT19" si="33">CN13-CO13-CQ13-CP13</f>
-        <v>-3014.9508359117335</v>
+        <v>-3322.4508359117335</v>
       </c>
       <c r="CU13" s="21"/>
     </row>
@@ -25328,27 +26021,27 @@
       </c>
       <c r="BT14" s="35">
         <f>SUMIF(Rede!$D:$D,Geral!C14,Rede!$BT:$BT)</f>
-        <v>176.208</v>
+        <v>202.083</v>
       </c>
       <c r="BU14" s="35">
         <f>SUMIF(Rede!$D:$D,Geral!C14,Rede!$BU:$BU)</f>
-        <v>25.875</v>
+        <v>0</v>
       </c>
       <c r="BV14" s="35">
         <f>SUMIF(Rede!$D:$D,Geral!C14,Rede!$BV:$BV)</f>
-        <v>4.0839999999999996</v>
+        <v>4.75</v>
       </c>
       <c r="BW14" s="36">
         <f t="shared" si="24"/>
-        <v>0.35062414965986394</v>
+        <v>0.35175680272108845</v>
       </c>
       <c r="BX14" s="37">
         <f t="shared" si="25"/>
-        <v>0.13382609317340632</v>
+        <v>0.13748879466323505</v>
       </c>
       <c r="BY14" s="40">
         <f t="shared" si="26"/>
-        <v>381.83300000000003</v>
+        <v>381.16700000000003</v>
       </c>
       <c r="BZ14" s="67">
         <f>SUMIF(Rede!$D:$D,Geral!C14,Rede!$BZ:$BZ)</f>
@@ -25388,15 +26081,15 @@
       </c>
       <c r="CI14" s="64">
         <f>SUMIF(Rede!$D:$D,Geral!C14,Rede!$CI:$CI)</f>
-        <v>23.582999999999998</v>
+        <v>49.457999999999998</v>
       </c>
       <c r="CJ14" s="64">
         <f>SUMIF(Rede!$D:$D,Geral!C14,Rede!$CJ:$CJ)</f>
-        <v>4.0839999999999996</v>
+        <v>4.75</v>
       </c>
       <c r="CK14" s="64">
         <f>SUMIF(Rede!$D:$D,Geral!C14,Rede!$CK:$CK)</f>
-        <v>25.875</v>
+        <v>0</v>
       </c>
       <c r="CL14" s="7"/>
       <c r="CM14" s="39">
@@ -25409,27 +26102,27 @@
       </c>
       <c r="CO14" s="34">
         <f t="shared" si="27"/>
-        <v>2051.1469999999999</v>
+        <v>2077.0219999999999</v>
       </c>
       <c r="CP14" s="34">
         <f t="shared" si="27"/>
-        <v>35.957999999999998</v>
+        <v>10.083</v>
       </c>
       <c r="CQ14" s="34">
         <f t="shared" si="27"/>
-        <v>4.0839999999999996</v>
+        <v>4.75</v>
       </c>
       <c r="CR14" s="36">
         <f t="shared" si="31"/>
-        <v>0.86724518068666212</v>
+        <v>0.86752138015516422</v>
       </c>
       <c r="CS14" s="37">
         <f t="shared" si="32"/>
-        <v>-5.512322275523962E-2</v>
+        <v>-5.4822299245386952E-2</v>
       </c>
       <c r="CT14" s="40">
         <f t="shared" si="33"/>
-        <v>320.11180232241929</v>
+        <v>319.4458023224193</v>
       </c>
       <c r="CU14" s="21"/>
     </row>
@@ -25701,11 +26394,11 @@
       </c>
       <c r="BT15" s="35">
         <f>SUMIF(Rede!$D:$D,Geral!C15,Rede!$BT:$BT)</f>
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="BU15" s="35">
         <f>SUMIF(Rede!$D:$D,Geral!C15,Rede!$BU:$BU)</f>
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="BV15" s="35">
         <f>SUMIF(Rede!$D:$D,Geral!C15,Rede!$BV:$BV)</f>
@@ -25713,15 +26406,15 @@
       </c>
       <c r="BW15" s="36">
         <f t="shared" si="24"/>
-        <v>0.40342679127725856</v>
+        <v>0.87538940809968846</v>
       </c>
       <c r="BX15" s="37">
         <f t="shared" si="25"/>
-        <v>-0.36337514410089644</v>
+        <v>0.38140219697025568</v>
       </c>
       <c r="BY15" s="40">
         <f t="shared" si="26"/>
-        <v>383</v>
+        <v>80</v>
       </c>
       <c r="BZ15" s="67">
         <f>SUMIF(Rede!$D:$D,Geral!C15,Rede!$BZ:$BZ)</f>
@@ -25761,7 +26454,7 @@
       </c>
       <c r="CI15" s="64">
         <f>SUMIF(Rede!$D:$D,Geral!C15,Rede!$CI:$CI)</f>
-        <v>15.542</v>
+        <v>40.542000000000002</v>
       </c>
       <c r="CJ15" s="64">
         <f>SUMIF(Rede!$D:$D,Geral!C15,Rede!$CJ:$CJ)</f>
@@ -25769,7 +26462,7 @@
       </c>
       <c r="CK15" s="64">
         <f>SUMIF(Rede!$D:$D,Geral!C15,Rede!$CK:$CK)</f>
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="CL15" s="7"/>
       <c r="CM15" s="39">
@@ -25782,11 +26475,11 @@
       </c>
       <c r="CO15" s="34">
         <f t="shared" si="27"/>
-        <v>2814.2080000000001</v>
+        <v>2839.2080000000001</v>
       </c>
       <c r="CP15" s="34">
         <f t="shared" si="27"/>
-        <v>85.625</v>
+        <v>363.625</v>
       </c>
       <c r="CQ15" s="34">
         <f t="shared" si="27"/>
@@ -25794,15 +26487,15 @@
       </c>
       <c r="CR15" s="36">
         <f t="shared" si="31"/>
-        <v>1.1039298430612454</v>
+        <v>1.2192781208577796</v>
       </c>
       <c r="CS15" s="37">
         <f t="shared" si="32"/>
-        <v>0.18089118438397289</v>
+        <v>0.30428105851408449</v>
       </c>
       <c r="CT15" s="40">
         <f t="shared" si="33"/>
-        <v>-273.00574442129664</v>
+        <v>-576.00574442129664</v>
       </c>
       <c r="CU15" s="21"/>
     </row>
@@ -26074,11 +26767,11 @@
       </c>
       <c r="BT16" s="35">
         <f>SUMIF(Rede!$D:$D,Geral!C16,Rede!$BT:$BT)</f>
-        <v>882</v>
+        <v>1087</v>
       </c>
       <c r="BU16" s="35">
         <f>SUMIF(Rede!$D:$D,Geral!C16,Rede!$BU:$BU)</f>
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="BV16" s="35">
         <f>SUMIF(Rede!$D:$D,Geral!C16,Rede!$BV:$BV)</f>
@@ -26086,15 +26779,15 @@
       </c>
       <c r="BW16" s="36">
         <f t="shared" si="24"/>
-        <v>0.59241452991452992</v>
+        <v>0.59027777777777779</v>
       </c>
       <c r="BX16" s="37">
         <f t="shared" si="25"/>
-        <v>2.8518432645490366E-2</v>
+        <v>2.4808717829816862E-2</v>
       </c>
       <c r="BY16" s="40">
         <f t="shared" si="26"/>
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="BZ16" s="67">
         <f>SUMIF(Rede!$D:$D,Geral!C16,Rede!$BZ:$BZ)</f>
@@ -26134,7 +26827,7 @@
       </c>
       <c r="CI16" s="64">
         <f>SUMIF(Rede!$D:$D,Geral!C16,Rede!$CI:$CI)</f>
-        <v>-1</v>
+        <v>204</v>
       </c>
       <c r="CJ16" s="64">
         <f>SUMIF(Rede!$D:$D,Geral!C16,Rede!$CJ:$CJ)</f>
@@ -26142,7 +26835,7 @@
       </c>
       <c r="CK16" s="64">
         <f>SUMIF(Rede!$D:$D,Geral!C16,Rede!$CK:$CK)</f>
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="CL16" s="7"/>
       <c r="CM16" s="39">
@@ -26155,11 +26848,11 @@
       </c>
       <c r="CO16" s="34">
         <f t="shared" si="27"/>
-        <v>6166.625</v>
+        <v>6371.625</v>
       </c>
       <c r="CP16" s="34">
         <f t="shared" si="27"/>
-        <v>252</v>
+        <v>43</v>
       </c>
       <c r="CQ16" s="34">
         <f t="shared" si="27"/>
@@ -26167,15 +26860,15 @@
       </c>
       <c r="CR16" s="36">
         <f t="shared" si="31"/>
-        <v>0.83795490482112078</v>
+        <v>0.83743416303186247</v>
       </c>
       <c r="CS16" s="37">
         <f t="shared" si="32"/>
-        <v>-9.1850231918308323E-2</v>
+        <v>-9.2414595862506888E-2</v>
       </c>
       <c r="CT16" s="40">
         <f t="shared" si="33"/>
-        <v>1244.7251096148293</v>
+        <v>1248.7251096148293</v>
       </c>
       <c r="CU16" s="21"/>
     </row>
@@ -26447,11 +27140,11 @@
       </c>
       <c r="BT17" s="35">
         <f>SUMIF(Rede!$D:$D,Geral!C17,Rede!$BT:$BT)</f>
-        <v>693.18799999999999</v>
+        <v>687.70900000000006</v>
       </c>
       <c r="BU17" s="35">
         <f>SUMIF(Rede!$D:$D,Geral!C17,Rede!$BU:$BU)</f>
-        <v>85</v>
+        <v>257</v>
       </c>
       <c r="BV17" s="35">
         <f>SUMIF(Rede!$D:$D,Geral!C17,Rede!$BV:$BV)</f>
@@ -26459,15 +27152,15 @@
       </c>
       <c r="BW17" s="36">
         <f t="shared" ref="BW17" si="42">(BT17+BU17+BV17)/BS17</f>
-        <v>0.38872408963585431</v>
+        <v>0.46646498599439784</v>
       </c>
       <c r="BX17" s="37">
         <f t="shared" ref="BX17" si="43">IFERROR(((BT17+BU17+BV17)/BR17-1),0)</f>
-        <v>-0.28943636009871887</v>
+        <v>-0.14733080050383496</v>
       </c>
       <c r="BY17" s="40">
         <f t="shared" ref="BY17" si="44">BS17-BT17-BU17-BV17</f>
-        <v>1309.3529999999998</v>
+        <v>1142.8319999999999</v>
       </c>
       <c r="BZ17" s="67">
         <f>SUMIF(Rede!$D:$D,Geral!C17,Rede!$BZ:$BZ)</f>
@@ -26507,7 +27200,7 @@
       </c>
       <c r="CI17" s="64">
         <f>SUMIF(Rede!$D:$D,Geral!C17,Rede!$CI:$CI)</f>
-        <v>184.5</v>
+        <v>179.02100000000002</v>
       </c>
       <c r="CJ17" s="64">
         <f>SUMIF(Rede!$D:$D,Geral!C17,Rede!$CJ:$CJ)</f>
@@ -26515,7 +27208,7 @@
       </c>
       <c r="CK17" s="64">
         <f>SUMIF(Rede!$D:$D,Geral!C17,Rede!$CK:$CK)</f>
-        <v>85</v>
+        <v>257</v>
       </c>
       <c r="CL17" s="7"/>
       <c r="CM17" s="39">
@@ -26528,11 +27221,11 @@
       </c>
       <c r="CO17" s="34">
         <f t="shared" si="27"/>
-        <v>5178.1469999999999</v>
+        <v>5172.6679999999997</v>
       </c>
       <c r="CP17" s="34">
         <f t="shared" si="27"/>
-        <v>214.583</v>
+        <v>386.58299999999997</v>
       </c>
       <c r="CQ17" s="34">
         <f t="shared" si="27"/>
@@ -26540,15 +27233,15 @@
       </c>
       <c r="CR17" s="36">
         <f t="shared" si="31"/>
-        <v>0.61966157109476916</v>
+        <v>0.63860467449732627</v>
       </c>
       <c r="CS17" s="37">
         <f t="shared" si="32"/>
-        <v>-0.34523988967428532</v>
+        <v>-0.32522382114213999</v>
       </c>
       <c r="CT17" s="40">
         <f t="shared" si="33"/>
-        <v>3343.3980786473589</v>
+        <v>3176.8770786473592</v>
       </c>
       <c r="CU17" s="21"/>
     </row>
@@ -26820,7 +27513,7 @@
       </c>
       <c r="BT18" s="35">
         <f>SUMIF(Rede!$D:$D,Geral!C18,Rede!$BT:$BT)</f>
-        <v>135.501</v>
+        <v>160.667</v>
       </c>
       <c r="BU18" s="35">
         <f>SUMIF(Rede!$D:$D,Geral!C18,Rede!$BU:$BU)</f>
@@ -26828,19 +27521,19 @@
       </c>
       <c r="BV18" s="35">
         <f>SUMIF(Rede!$D:$D,Geral!C18,Rede!$BV:$BV)</f>
-        <v>16.125</v>
+        <v>19.957999999999998</v>
       </c>
       <c r="BW18" s="36">
         <f t="shared" ref="BW18" si="53">(BT18+BU18+BV18)/BS18</f>
-        <v>0.4433508771929825</v>
+        <v>0.52814327485380119</v>
       </c>
       <c r="BX18" s="37">
         <f t="shared" ref="BX18" si="54">IFERROR(((BT18+BU18+BV18)/BR18-1),0)</f>
-        <v>0.25181424148606824</v>
+        <v>0.49122807017543857</v>
       </c>
       <c r="BY18" s="40">
         <f t="shared" ref="BY18" si="55">BS18-BT18-BU18-BV18</f>
-        <v>190.374</v>
+        <v>161.375</v>
       </c>
       <c r="BZ18" s="67">
         <f>SUMIF(Rede!$D:$D,Geral!C18,Rede!$BZ:$BZ)</f>
@@ -26880,11 +27573,11 @@
       </c>
       <c r="CI18" s="64">
         <f>SUMIF(Rede!$D:$D,Geral!C18,Rede!$CI:$CI)</f>
-        <v>78.167000000000002</v>
+        <v>103.333</v>
       </c>
       <c r="CJ18" s="64">
         <f>SUMIF(Rede!$D:$D,Geral!C18,Rede!$CJ:$CJ)</f>
-        <v>12.125</v>
+        <v>15.958</v>
       </c>
       <c r="CK18" s="64">
         <f>SUMIF(Rede!$D:$D,Geral!C18,Rede!$CK:$CK)</f>
@@ -26901,7 +27594,7 @@
       </c>
       <c r="CO18" s="34">
         <f t="shared" si="27"/>
-        <v>1019.792</v>
+        <v>1044.9580000000001</v>
       </c>
       <c r="CP18" s="34">
         <f t="shared" si="27"/>
@@ -26909,19 +27602,19 @@
       </c>
       <c r="CQ18" s="34">
         <f t="shared" si="27"/>
-        <v>16.125</v>
+        <v>19.957999999999998</v>
       </c>
       <c r="CR18" s="36">
         <f t="shared" si="31"/>
-        <v>0.76973631302836187</v>
+        <v>0.79043958380321366</v>
       </c>
       <c r="CS18" s="37">
         <f t="shared" si="32"/>
-        <v>-0.17705028146169266</v>
+        <v>-0.15491575231371035</v>
       </c>
       <c r="CT18" s="40">
         <f t="shared" si="33"/>
-        <v>322.52955250924026</v>
+        <v>293.53055250924024</v>
       </c>
       <c r="CU18" s="21"/>
     </row>
@@ -27299,12 +27992,12 @@
       <c r="CU19" s="21"/>
     </row>
     <row r="20" spans="2:99" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="204" t="s">
+      <c r="B20" s="205" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="205"/>
-      <c r="D20" s="205"/>
-      <c r="E20" s="206"/>
+      <c r="C20" s="206"/>
+      <c r="D20" s="206"/>
+      <c r="E20" s="207"/>
       <c r="F20" s="113">
         <f>SUM(F12:F19)</f>
         <v>14</v>
@@ -27559,27 +28252,27 @@
       </c>
       <c r="BT20" s="56">
         <f>SUBTOTAL(9,BT12:BT19)</f>
-        <v>4400.7290000000003</v>
+        <v>4767.9570000000003</v>
       </c>
       <c r="BU20" s="56">
         <f>SUBTOTAL(9,BU12:BU19)</f>
-        <v>319.875</v>
+        <v>841</v>
       </c>
       <c r="BV20" s="56">
         <f>SUBTOTAL(9,BV12:BV19)</f>
-        <v>147.751</v>
+        <v>153.75</v>
       </c>
       <c r="BW20" s="47">
         <f t="shared" si="24"/>
-        <v>0.44840701851340153</v>
+        <v>0.530782628718799</v>
       </c>
       <c r="BX20" s="47">
         <f t="shared" si="25"/>
-        <v>-2.0195817740729871E-2</v>
+        <v>0.15980129216845773</v>
       </c>
       <c r="BY20" s="57">
         <f t="shared" si="26"/>
-        <v>5988.6449999999995</v>
+        <v>5094.2929999999997</v>
       </c>
       <c r="BZ20" s="70">
         <f t="shared" ref="BZ20:CK20" si="59">SUM(BZ12:BZ19)</f>
@@ -27619,15 +28312,15 @@
       </c>
       <c r="CI20" s="71">
         <f t="shared" si="59"/>
-        <v>291.77700000000004</v>
+        <v>659.005</v>
       </c>
       <c r="CJ20" s="71">
         <f t="shared" si="59"/>
-        <v>41.209000000000003</v>
+        <v>47.207999999999998</v>
       </c>
       <c r="CK20" s="71">
         <f t="shared" si="59"/>
-        <v>319.875</v>
+        <v>841</v>
       </c>
       <c r="CM20" s="55">
         <f>SUBTOTAL(9,CM12:CM19)</f>
@@ -27639,27 +28332,27 @@
       </c>
       <c r="CO20" s="56">
         <f>SUBTOTAL(9,CO12:CO19)</f>
-        <v>40405.504000000001</v>
+        <v>40772.732000000004</v>
       </c>
       <c r="CP20" s="56">
         <f>SUBTOTAL(9,CP12:CP19)</f>
-        <v>986.45699999999999</v>
+        <v>1507.5819999999999</v>
       </c>
       <c r="CQ20" s="56">
         <f>SUBTOTAL(9,CQ12:CQ19)</f>
-        <v>147.751</v>
+        <v>153.75</v>
       </c>
       <c r="CR20" s="47">
         <f t="shared" ref="CR20" si="60">(CO20+CP20+CQ20)/CN20</f>
-        <v>0.93293860058811817</v>
+        <v>0.95302481359106805</v>
       </c>
       <c r="CS20" s="47">
         <f t="shared" ref="CS20" si="61">IFERROR(((CO20+CP20+CQ20)/CM20-1),0)</f>
-        <v>-1.4119220726329207E-2</v>
+        <v>7.1068399335274535E-3</v>
       </c>
       <c r="CT20" s="57">
         <f>CN20-CO20-CQ20-CP20</f>
-        <v>2985.9534337312712</v>
+        <v>2091.6014337312686</v>
       </c>
       <c r="CU20" s="21"/>
     </row>
@@ -29140,27 +29833,27 @@
       </c>
       <c r="BT7" s="75">
         <f>SUBTOTAL(9,BT10:BT23)</f>
-        <v>4400.7290000000003</v>
+        <v>4767.9570000000003</v>
       </c>
       <c r="BU7" s="75">
         <f>SUBTOTAL(9,BU10:BU23)</f>
-        <v>319.875</v>
+        <v>841</v>
       </c>
       <c r="BV7" s="75">
         <f>SUBTOTAL(9,BV10:BV23)</f>
-        <v>147.751</v>
+        <v>153.75</v>
       </c>
       <c r="BW7" s="76">
         <f>IFERROR(((BT7+BV7+BU7)/BS7),0)</f>
-        <v>0.44840701851340153</v>
+        <v>0.530782628718799</v>
       </c>
       <c r="BX7" s="77">
         <f>IFERROR(((BT7+BU7+BV7)/BR7-1),0)</f>
-        <v>-2.0195817740729871E-2</v>
+        <v>0.15980129216845773</v>
       </c>
       <c r="BY7" s="78">
         <f>BS7-BT7-BU7-BV7</f>
-        <v>5988.6449999999995</v>
+        <v>5094.2929999999997</v>
       </c>
       <c r="BZ7" s="74">
         <f t="shared" ref="BZ7:CK7" si="3">SUBTOTAL(9,BZ10:BZ23)</f>
@@ -29200,15 +29893,15 @@
       </c>
       <c r="CI7" s="75">
         <f t="shared" si="3"/>
-        <v>291.77700000000004</v>
+        <v>659.005</v>
       </c>
       <c r="CJ7" s="75">
         <f t="shared" si="3"/>
-        <v>41.209000000000003</v>
+        <v>47.207999999999998</v>
       </c>
       <c r="CK7" s="75">
         <f t="shared" si="3"/>
-        <v>319.875</v>
+        <v>841</v>
       </c>
       <c r="CM7" s="74">
         <f>SUBTOTAL(9,CM10:CM23)</f>
@@ -29220,27 +29913,27 @@
       </c>
       <c r="CO7" s="75">
         <f>SUBTOTAL(9,CO10:CO23)</f>
-        <v>40405.504000000001</v>
+        <v>40772.732000000004</v>
       </c>
       <c r="CP7" s="75">
         <f>SUBTOTAL(9,CP10:CP23)</f>
-        <v>986.45699999999999</v>
+        <v>1507.5819999999999</v>
       </c>
       <c r="CQ7" s="75">
         <f>SUBTOTAL(9,CQ10:CQ23)</f>
-        <v>147.751</v>
+        <v>153.75</v>
       </c>
       <c r="CR7" s="76">
         <f>IFERROR(((CO7+CQ7+CP7)/CN7),0)</f>
-        <v>0.93293860058811817</v>
+        <v>0.95302481359106805</v>
       </c>
       <c r="CS7" s="77">
         <f>IFERROR(((CO7+CP7+CQ7)/CM7-1),0)</f>
-        <v>-1.4119220726328985E-2</v>
+        <v>7.1068399335276755E-3</v>
       </c>
       <c r="CT7" s="78">
         <f>CN7-CO7-CP7-CQ7</f>
-        <v>2985.9534337312712</v>
+        <v>2091.6014337312686</v>
       </c>
     </row>
     <row r="8" spans="2:102" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -29916,7 +30609,7 @@
       </c>
       <c r="BT10" s="73">
         <f>CA10+CE10+CI10</f>
-        <v>-11.777000000000001</v>
+        <v>79.888999999999996</v>
       </c>
       <c r="BU10" s="73">
         <f>CB10+CF10+CJ10</f>
@@ -29928,15 +30621,15 @@
       </c>
       <c r="BW10" s="37">
         <f>IFERROR(((BT10+BV10+BU10)/BS10),0)</f>
-        <v>-1.527496757457847E-2</v>
+        <v>0.10361738002594033</v>
       </c>
       <c r="BX10" s="37">
         <f>IFERROR(((BT10+BU10+BV10)/BR10-1),0)</f>
-        <v>-1.0776821344942449</v>
+        <v>-0.47304508426503089</v>
       </c>
       <c r="BY10" s="80">
         <f>BS10-BT10-BU10-BV10</f>
-        <v>782.77700000000004</v>
+        <v>691.11099999999999</v>
       </c>
       <c r="BZ10" s="79">
         <f>SUMIF(Cliente!$H:$H,Rede!F10,Cliente!$BM:$BM)</f>
@@ -29976,7 +30669,7 @@
       </c>
       <c r="CI10" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F10,Cliente!$BV:$BV)</f>
-        <v>-2.0270000000000001</v>
+        <v>89.638999999999996</v>
       </c>
       <c r="CJ10" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F10,Cliente!$BW:$BW)</f>
@@ -29996,7 +30689,7 @@
       </c>
       <c r="CO10" s="73">
         <f t="shared" ref="CO10:CO23" si="19">I10+AD10+AY10+BT10</f>
-        <v>1997.9570000000001</v>
+        <v>2089.623</v>
       </c>
       <c r="CP10" s="73">
         <f t="shared" ref="CP10:CP23" si="20">J10+AE10+AZ10+BU10</f>
@@ -30008,15 +30701,15 @@
       </c>
       <c r="CR10" s="37">
         <f>IFERROR(((CO10+CQ10+CP10)/CN10),0)</f>
-        <v>0.63145419728489571</v>
+        <v>0.66042523142042375</v>
       </c>
       <c r="CS10" s="37">
         <f>IFERROR(((CO10+CP10+CQ10)/CM10-1),0)</f>
-        <v>-0.39938289623319589</v>
+        <v>-0.37182666382484686</v>
       </c>
       <c r="CT10" s="80">
         <f>CN10-CO10-CP10-CQ10</f>
-        <v>1166.0998842375968</v>
+        <v>1074.4338842375969</v>
       </c>
       <c r="CU10" s="139"/>
       <c r="CV10" s="139"/>
@@ -30297,19 +30990,19 @@
       </c>
       <c r="BV11" s="73">
         <f t="shared" ref="BV11:BV23" si="33">CB11+CF11+CJ11</f>
-        <v>21.5</v>
+        <v>23</v>
       </c>
       <c r="BW11" s="37">
         <f t="shared" ref="BW11" si="34">IFERROR(((BT11+BV11+BU11)/BS11),0)</f>
-        <v>0.40909090909090912</v>
+        <v>0.41212121212121211</v>
       </c>
       <c r="BX11" s="37">
         <f t="shared" ref="BX11" si="35">IFERROR(((BT11+BU11+BV11)/BR11-1),0)</f>
-        <v>8.3368553957103853E-2</v>
+        <v>9.1393506208637953E-2</v>
       </c>
       <c r="BY11" s="80">
         <f t="shared" ref="BY11" si="36">BS11-BT11-BU11-BV11</f>
-        <v>292.5</v>
+        <v>291</v>
       </c>
       <c r="BZ11" s="79">
         <f>SUMIF(Cliente!$H:$H,Rede!F11,Cliente!$BM:$BM)</f>
@@ -30353,7 +31046,7 @@
       </c>
       <c r="CJ11" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F11,Cliente!$BW:$BW)</f>
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="CK11" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F11,Cliente!$BX:$BX)</f>
@@ -30377,19 +31070,19 @@
       </c>
       <c r="CQ11" s="73">
         <f t="shared" si="21"/>
-        <v>21.5</v>
+        <v>23</v>
       </c>
       <c r="CR11" s="37">
         <f t="shared" ref="CR11" si="37">IFERROR(((CO11+CQ11+CP11)/CN11),0)</f>
-        <v>1.7425319073823158</v>
+        <v>1.7432724869607064</v>
       </c>
       <c r="CS11" s="37">
         <f t="shared" ref="CS11" si="38">IFERROR(((CO11+CP11+CQ11)/CM11-1),0)</f>
-        <v>0.88764955367887333</v>
+        <v>0.88845180854989758</v>
       </c>
       <c r="CT11" s="80">
         <f>CN11-CO11-CP11-CQ11</f>
-        <v>-1503.9543265480204</v>
+        <v>-1505.4543265480204</v>
       </c>
       <c r="CU11" s="139"/>
       <c r="CV11" s="139"/>
@@ -31412,7 +32105,7 @@
       </c>
       <c r="BU14" s="73">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="BV14" s="73">
         <f t="shared" si="33"/>
@@ -31420,15 +32113,15 @@
       </c>
       <c r="BW14" s="37">
         <f t="shared" ref="BW14" si="57">IFERROR(((BT14+BV14+BU14)/BS14),0)</f>
-        <v>0.49370718232044192</v>
+        <v>1.0572430939226518</v>
       </c>
       <c r="BX14" s="37">
         <f t="shared" ref="BX14" si="58">IFERROR(((BT14+BU14+BV14)/BR14-1),0)</f>
-        <v>3.7135472527472526</v>
+        <v>9.0937670329670333</v>
       </c>
       <c r="BY14" s="80">
         <f t="shared" ref="BY14" si="59">BS14-BT14-BU14-BV14</f>
-        <v>274.91700000000003</v>
+        <v>-31.082999999999998</v>
       </c>
       <c r="BZ14" s="79">
         <f>SUMIF(Cliente!$H:$H,Rede!F14,Cliente!$BM:$BM)</f>
@@ -31476,7 +32169,7 @@
       </c>
       <c r="CK14" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F14,Cliente!$BX:$BX)</f>
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="CM14" s="79">
         <f t="shared" si="17"/>
@@ -31492,7 +32185,7 @@
       </c>
       <c r="CP14" s="73">
         <f t="shared" si="20"/>
-        <v>72</v>
+        <v>378</v>
       </c>
       <c r="CQ14" s="73">
         <f t="shared" si="21"/>
@@ -31500,15 +32193,15 @@
       </c>
       <c r="CR14" s="37">
         <f t="shared" si="51"/>
-        <v>1.4305296103933309</v>
+        <v>1.5678667435703673</v>
       </c>
       <c r="CS14" s="37">
         <f t="shared" si="52"/>
-        <v>0.55480910459868982</v>
+        <v>0.70407761572334038</v>
       </c>
       <c r="CT14" s="80">
         <f t="shared" si="53"/>
-        <v>-959.26030879452981</v>
+        <v>-1265.2603087945299</v>
       </c>
       <c r="CU14" s="139"/>
       <c r="CV14" s="139"/>
@@ -31781,27 +32474,27 @@
       </c>
       <c r="BT15" s="73">
         <f t="shared" si="31"/>
-        <v>176.208</v>
+        <v>202.083</v>
       </c>
       <c r="BU15" s="73">
         <f t="shared" si="32"/>
-        <v>25.875</v>
+        <v>0</v>
       </c>
       <c r="BV15" s="73">
         <f t="shared" si="33"/>
-        <v>4.0839999999999996</v>
+        <v>4.75</v>
       </c>
       <c r="BW15" s="37">
         <f t="shared" si="48"/>
-        <v>0.35062414965986394</v>
+        <v>0.35175680272108845</v>
       </c>
       <c r="BX15" s="37">
         <f t="shared" si="49"/>
-        <v>0.13382609317340632</v>
+        <v>0.13748879466323505</v>
       </c>
       <c r="BY15" s="80">
         <f t="shared" si="50"/>
-        <v>381.83300000000003</v>
+        <v>381.16700000000003</v>
       </c>
       <c r="BZ15" s="79">
         <f>SUMIF(Cliente!$H:$H,Rede!F15,Cliente!$BM:$BM)</f>
@@ -31841,15 +32534,15 @@
       </c>
       <c r="CI15" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F15,Cliente!$BV:$BV)</f>
-        <v>23.582999999999998</v>
+        <v>49.457999999999998</v>
       </c>
       <c r="CJ15" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F15,Cliente!$BW:$BW)</f>
-        <v>4.0839999999999996</v>
+        <v>4.75</v>
       </c>
       <c r="CK15" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F15,Cliente!$BX:$BX)</f>
-        <v>25.875</v>
+        <v>0</v>
       </c>
       <c r="CM15" s="79">
         <f t="shared" si="17"/>
@@ -31861,27 +32554,27 @@
       </c>
       <c r="CO15" s="73">
         <f t="shared" si="19"/>
-        <v>2051.1469999999999</v>
+        <v>2077.0219999999999</v>
       </c>
       <c r="CP15" s="73">
         <f t="shared" si="20"/>
-        <v>35.957999999999998</v>
+        <v>10.083</v>
       </c>
       <c r="CQ15" s="73">
         <f t="shared" si="21"/>
-        <v>4.0839999999999996</v>
+        <v>4.75</v>
       </c>
       <c r="CR15" s="37">
         <f t="shared" si="51"/>
-        <v>0.86724518068666212</v>
+        <v>0.86752138015516422</v>
       </c>
       <c r="CS15" s="37">
         <f t="shared" si="52"/>
-        <v>-5.512322275523962E-2</v>
+        <v>-5.4822299245386952E-2</v>
       </c>
       <c r="CT15" s="80">
         <f t="shared" si="53"/>
-        <v>320.11180232241935</v>
+        <v>319.4458023224193</v>
       </c>
       <c r="CU15" s="139"/>
       <c r="CV15" s="139"/>
@@ -32158,7 +32851,7 @@
       </c>
       <c r="BU16" s="73">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="BV16" s="73">
         <f t="shared" si="33"/>
@@ -32166,15 +32859,15 @@
       </c>
       <c r="BW16" s="37">
         <f t="shared" si="48"/>
-        <v>0.19849444444444445</v>
+        <v>0.97071666666666656</v>
       </c>
       <c r="BX16" s="37">
         <f t="shared" si="49"/>
-        <v>-0.77564207221350079</v>
+        <v>9.7199372056514743E-2</v>
       </c>
       <c r="BY16" s="80">
         <f t="shared" si="50"/>
-        <v>288.54200000000003</v>
+        <v>10.54200000000003</v>
       </c>
       <c r="BZ16" s="79">
         <f>SUMIF(Cliente!$H:$H,Rede!F16,Cliente!$BM:$BM)</f>
@@ -32222,7 +32915,7 @@
       </c>
       <c r="CK16" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F16,Cliente!$BX:$BX)</f>
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="CM16" s="79">
         <f t="shared" si="17"/>
@@ -32238,7 +32931,7 @@
       </c>
       <c r="CP16" s="73">
         <f t="shared" si="20"/>
-        <v>66</v>
+        <v>344</v>
       </c>
       <c r="CQ16" s="73">
         <f t="shared" si="21"/>
@@ -32246,15 +32939,15 @@
       </c>
       <c r="CR16" s="37">
         <f t="shared" si="51"/>
-        <v>1.5239600852682671</v>
+        <v>1.7122016145972792</v>
       </c>
       <c r="CS16" s="37">
         <f t="shared" si="52"/>
-        <v>0.61424271048730161</v>
+        <v>0.81363606695887136</v>
       </c>
       <c r="CT16" s="80">
         <f t="shared" si="53"/>
-        <v>-773.79791921467813</v>
+        <v>-1051.7979192146781</v>
       </c>
       <c r="CU16" s="139"/>
       <c r="CV16" s="139"/>
@@ -32527,7 +33220,7 @@
       </c>
       <c r="BT17" s="73">
         <f t="shared" si="31"/>
-        <v>187.542</v>
+        <v>212.542</v>
       </c>
       <c r="BU17" s="73">
         <f t="shared" si="32"/>
@@ -32539,15 +33232,15 @@
       </c>
       <c r="BW17" s="37">
         <f t="shared" si="48"/>
-        <v>0.66504255319148942</v>
+        <v>0.75369503546099292</v>
       </c>
       <c r="BX17" s="37">
         <f t="shared" si="49"/>
-        <v>1.1231249929245015</v>
+        <v>1.4061449288487884</v>
       </c>
       <c r="BY17" s="80">
         <f t="shared" si="50"/>
-        <v>94.457999999999998</v>
+        <v>69.457999999999998</v>
       </c>
       <c r="BZ17" s="79">
         <f>SUMIF(Cliente!$H:$H,Rede!F17,Cliente!$BM:$BM)</f>
@@ -32587,7 +33280,7 @@
       </c>
       <c r="CI17" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F17,Cliente!$BV:$BV)</f>
-        <v>15.542</v>
+        <v>40.542000000000002</v>
       </c>
       <c r="CJ17" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F17,Cliente!$BW:$BW)</f>
@@ -32607,7 +33300,7 @@
       </c>
       <c r="CO17" s="73">
         <f t="shared" si="19"/>
-        <v>629.58400000000006</v>
+        <v>654.58400000000006</v>
       </c>
       <c r="CP17" s="73">
         <f t="shared" si="20"/>
@@ -32619,15 +33312,15 @@
       </c>
       <c r="CR17" s="37">
         <f t="shared" si="51"/>
-        <v>0.56452898851746169</v>
+        <v>0.58626809674445257</v>
       </c>
       <c r="CS17" s="37">
         <f t="shared" si="52"/>
-        <v>-0.3883476759983493</v>
+        <v>-0.36479392350871764</v>
       </c>
       <c r="CT17" s="80">
         <f t="shared" si="53"/>
-        <v>500.79217479338104</v>
+        <v>475.79217479338104</v>
       </c>
       <c r="CU17" s="139"/>
       <c r="CV17" s="139"/>
@@ -32900,11 +33593,11 @@
       </c>
       <c r="BT18" s="73">
         <f t="shared" si="31"/>
-        <v>882</v>
+        <v>1087</v>
       </c>
       <c r="BU18" s="73">
         <f t="shared" si="32"/>
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="BV18" s="73">
         <f t="shared" si="33"/>
@@ -32912,15 +33605,15 @@
       </c>
       <c r="BW18" s="37">
         <f t="shared" si="48"/>
-        <v>0.59241452991452992</v>
+        <v>0.59027777777777779</v>
       </c>
       <c r="BX18" s="37">
         <f t="shared" si="49"/>
-        <v>2.8518432645490366E-2</v>
+        <v>2.4808717829816862E-2</v>
       </c>
       <c r="BY18" s="80">
         <f t="shared" si="50"/>
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="BZ18" s="79">
         <f>SUMIF(Cliente!$H:$H,Rede!F18,Cliente!$BM:$BM)</f>
@@ -32960,7 +33653,7 @@
       </c>
       <c r="CI18" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F18,Cliente!$BV:$BV)</f>
-        <v>-1</v>
+        <v>204</v>
       </c>
       <c r="CJ18" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F18,Cliente!$BW:$BW)</f>
@@ -32968,7 +33661,7 @@
       </c>
       <c r="CK18" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F18,Cliente!$BX:$BX)</f>
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="CM18" s="79">
         <f t="shared" si="17"/>
@@ -32980,11 +33673,11 @@
       </c>
       <c r="CO18" s="73">
         <f t="shared" si="19"/>
-        <v>6166.625</v>
+        <v>6371.625</v>
       </c>
       <c r="CP18" s="73">
         <f t="shared" si="20"/>
-        <v>252</v>
+        <v>43</v>
       </c>
       <c r="CQ18" s="73">
         <f t="shared" si="21"/>
@@ -32992,15 +33685,15 @@
       </c>
       <c r="CR18" s="37">
         <f t="shared" si="51"/>
-        <v>0.83795490482112078</v>
+        <v>0.83743416303186247</v>
       </c>
       <c r="CS18" s="37">
         <f t="shared" si="52"/>
-        <v>-9.1850231918308323E-2</v>
+        <v>-9.2414595862506888E-2</v>
       </c>
       <c r="CT18" s="80">
         <f t="shared" si="53"/>
-        <v>1244.7251096148293</v>
+        <v>1248.7251096148293</v>
       </c>
       <c r="CU18" s="139"/>
       <c r="CV18" s="139"/>
@@ -33277,7 +33970,7 @@
       </c>
       <c r="BU19" s="73">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="BV19" s="73">
         <f t="shared" si="33"/>
@@ -33285,15 +33978,15 @@
       </c>
       <c r="BW19" s="37">
         <f t="shared" si="48"/>
-        <v>0.216987922705314</v>
+        <v>0.30635990338164248</v>
       </c>
       <c r="BX19" s="37">
         <f t="shared" si="49"/>
-        <v>-0.62089062196676204</v>
+        <v>-0.46474480709661625</v>
       </c>
       <c r="BY19" s="80">
         <f t="shared" si="50"/>
-        <v>324.16700000000003</v>
+        <v>287.16700000000003</v>
       </c>
       <c r="BZ19" s="79">
         <f>SUMIF(Cliente!$H:$H,Rede!F19,Cliente!$BM:$BM)</f>
@@ -33341,7 +34034,7 @@
       </c>
       <c r="CK19" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F19,Cliente!$BX:$BX)</f>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="CM19" s="79">
         <f t="shared" si="17"/>
@@ -33357,7 +34050,7 @@
       </c>
       <c r="CP19" s="73">
         <f t="shared" si="20"/>
-        <v>24.625</v>
+        <v>61.625</v>
       </c>
       <c r="CQ19" s="73">
         <f t="shared" si="21"/>
@@ -33365,15 +34058,15 @@
       </c>
       <c r="CR19" s="37">
         <f t="shared" si="51"/>
-        <v>0.54712801951219892</v>
+        <v>0.56890622695216275</v>
       </c>
       <c r="CS19" s="37">
         <f t="shared" si="52"/>
-        <v>-0.41218664511551495</v>
+        <v>-0.38878897451171601</v>
       </c>
       <c r="CT19" s="80">
         <f t="shared" si="53"/>
-        <v>769.40507267371845</v>
+        <v>732.40507267371845</v>
       </c>
       <c r="CU19" s="139"/>
       <c r="CV19" s="139"/>
@@ -33646,11 +34339,11 @@
       </c>
       <c r="BT20" s="73">
         <f t="shared" si="31"/>
-        <v>364.18799999999999</v>
+        <v>358.709</v>
       </c>
       <c r="BU20" s="73">
         <f t="shared" si="32"/>
-        <v>85</v>
+        <v>220</v>
       </c>
       <c r="BV20" s="73">
         <f t="shared" si="33"/>
@@ -33658,15 +34351,15 @@
       </c>
       <c r="BW20" s="37">
         <f t="shared" si="48"/>
-        <v>0.58114302600472811</v>
+        <v>0.73424113475177311</v>
       </c>
       <c r="BX20" s="37">
         <f t="shared" si="49"/>
-        <v>0.19398160628116101</v>
+        <v>0.5085277982179417</v>
       </c>
       <c r="BY20" s="80">
         <f t="shared" si="50"/>
-        <v>354.35300000000001</v>
+        <v>224.83199999999999</v>
       </c>
       <c r="BZ20" s="79">
         <f>SUMIF(Cliente!$H:$H,Rede!F20,Cliente!$BM:$BM)</f>
@@ -33706,7 +34399,7 @@
       </c>
       <c r="CI20" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F20,Cliente!$BV:$BV)</f>
-        <v>112.5</v>
+        <v>107.021</v>
       </c>
       <c r="CJ20" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F20,Cliente!$BW:$BW)</f>
@@ -33714,7 +34407,7 @@
       </c>
       <c r="CK20" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F20,Cliente!$BX:$BX)</f>
-        <v>85</v>
+        <v>220</v>
       </c>
       <c r="CM20" s="79">
         <f t="shared" si="17"/>
@@ -33726,11 +34419,11 @@
       </c>
       <c r="CO20" s="73">
         <f t="shared" si="19"/>
-        <v>1942.855</v>
+        <v>1937.376</v>
       </c>
       <c r="CP20" s="73">
         <f t="shared" si="20"/>
-        <v>185.958</v>
+        <v>320.95799999999997</v>
       </c>
       <c r="CQ20" s="73">
         <f t="shared" si="21"/>
@@ -33738,15 +34431,15 @@
       </c>
       <c r="CR20" s="37">
         <f t="shared" si="51"/>
-        <v>0.6256219749718559</v>
+        <v>0.66294165846629127</v>
       </c>
       <c r="CS20" s="37">
         <f t="shared" si="52"/>
-        <v>-0.33972361878574853</v>
+        <v>-0.30033672613883422</v>
       </c>
       <c r="CT20" s="80">
         <f t="shared" si="53"/>
-        <v>1299.3094163539834</v>
+        <v>1169.7884163539836</v>
       </c>
       <c r="CU20" s="139"/>
       <c r="CV20" s="139"/>
@@ -34392,7 +35085,7 @@
       </c>
       <c r="BT22" s="73">
         <f t="shared" si="31"/>
-        <v>135.501</v>
+        <v>160.667</v>
       </c>
       <c r="BU22" s="73">
         <f t="shared" si="32"/>
@@ -34400,19 +35093,19 @@
       </c>
       <c r="BV22" s="73">
         <f t="shared" si="33"/>
-        <v>16.125</v>
+        <v>19.957999999999998</v>
       </c>
       <c r="BW22" s="37">
         <f t="shared" si="48"/>
-        <v>0.4433508771929825</v>
+        <v>0.52814327485380119</v>
       </c>
       <c r="BX22" s="37">
         <f t="shared" si="49"/>
-        <v>0.25181424148606824</v>
+        <v>0.49122807017543857</v>
       </c>
       <c r="BY22" s="80">
         <f t="shared" si="50"/>
-        <v>190.374</v>
+        <v>161.375</v>
       </c>
       <c r="BZ22" s="79">
         <f>SUMIF(Cliente!$H:$H,Rede!F22,Cliente!$BM:$BM)</f>
@@ -34452,11 +35145,11 @@
       </c>
       <c r="CI22" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F22,Cliente!$BV:$BV)</f>
-        <v>78.167000000000002</v>
+        <v>103.333</v>
       </c>
       <c r="CJ22" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F22,Cliente!$BW:$BW)</f>
-        <v>12.125</v>
+        <v>15.958</v>
       </c>
       <c r="CK22" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F22,Cliente!$BX:$BX)</f>
@@ -34472,7 +35165,7 @@
       </c>
       <c r="CO22" s="73">
         <f t="shared" si="19"/>
-        <v>1019.792</v>
+        <v>1044.9580000000001</v>
       </c>
       <c r="CP22" s="73">
         <f t="shared" si="20"/>
@@ -34480,19 +35173,19 @@
       </c>
       <c r="CQ22" s="73">
         <f t="shared" si="21"/>
-        <v>16.125</v>
+        <v>19.957999999999998</v>
       </c>
       <c r="CR22" s="37">
         <f t="shared" si="51"/>
-        <v>0.76973631302836187</v>
+        <v>0.79043958380321366</v>
       </c>
       <c r="CS22" s="37">
         <f t="shared" si="52"/>
-        <v>-0.17705028146169266</v>
+        <v>-0.15491575231371035</v>
       </c>
       <c r="CT22" s="80">
         <f t="shared" si="53"/>
-        <v>322.52955250924026</v>
+        <v>293.53055250924024</v>
       </c>
       <c r="CU22" s="139"/>
       <c r="CV22" s="139"/>
@@ -36299,15 +36992,15 @@
       </c>
       <c r="BJ7" s="75">
         <f t="shared" si="0"/>
-        <v>4400.7290000000003</v>
+        <v>4767.9570000000003</v>
       </c>
       <c r="BK7" s="75">
         <f t="shared" si="0"/>
-        <v>147.751</v>
+        <v>153.75</v>
       </c>
       <c r="BL7" s="78">
         <f t="shared" si="0"/>
-        <v>319.875</v>
+        <v>841</v>
       </c>
       <c r="BM7" s="74">
         <f t="shared" si="0"/>
@@ -36347,25 +37040,25 @@
       </c>
       <c r="BV7" s="75">
         <f t="shared" si="0"/>
-        <v>291.77700000000004</v>
+        <v>659.005</v>
       </c>
       <c r="BW7" s="75">
         <f t="shared" ref="BW7:BX7" si="1">SUBTOTAL(9,BW10:BW107)</f>
-        <v>41.209000000000003</v>
+        <v>47.207999999999998</v>
       </c>
       <c r="BX7" s="78">
         <f t="shared" si="1"/>
-        <v>319.875</v>
+        <v>841</v>
       </c>
     </row>
     <row r="8" spans="2:76" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="H8" s="26"/>
-      <c r="J8" s="210" t="s">
+      <c r="J8" s="211" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="211"/>
-      <c r="L8" s="211"/>
-      <c r="M8" s="212"/>
+      <c r="K8" s="212"/>
+      <c r="L8" s="212"/>
+      <c r="M8" s="213"/>
       <c r="N8" s="106" t="s">
         <v>23</v>
       </c>
@@ -36432,12 +37125,12 @@
       <c r="BE8" s="102"/>
       <c r="BF8" s="102"/>
       <c r="BG8" s="107"/>
-      <c r="BI8" s="210" t="s">
+      <c r="BI8" s="211" t="s">
         <v>73</v>
       </c>
-      <c r="BJ8" s="211"/>
-      <c r="BK8" s="211"/>
-      <c r="BL8" s="212"/>
+      <c r="BJ8" s="212"/>
+      <c r="BK8" s="212"/>
+      <c r="BL8" s="213"/>
       <c r="BM8" s="106" t="s">
         <v>69</v>
       </c>
@@ -40244,7 +40937,7 @@
       </c>
       <c r="BJ23" s="99">
         <f t="shared" si="15"/>
-        <v>-10.776999999999997</v>
+        <v>80.888999999999996</v>
       </c>
       <c r="BK23" s="99">
         <f t="shared" si="16"/>
@@ -40290,7 +40983,7 @@
       </c>
       <c r="BV23" s="101">
         <f>IFERROR(VLOOKUP($E23&amp;BV$6,Base!$G:$K,5,0),0)</f>
-        <v>-1.194</v>
+        <v>90.471999999999994</v>
       </c>
       <c r="BW23" s="101">
         <f>IFERROR(VLOOKUP($E23&amp;BV$6,Base!$M:$Q,5,0),0)</f>
@@ -42838,7 +43531,7 @@
       </c>
       <c r="BK33" s="99">
         <f t="shared" si="16"/>
-        <v>21.5</v>
+        <v>23</v>
       </c>
       <c r="BL33" s="111">
         <f t="shared" si="17"/>
@@ -42884,7 +43577,7 @@
       </c>
       <c r="BW33" s="101">
         <f>IFERROR(VLOOKUP($E33&amp;BV$6,Base!$M:$Q,5,0),0)</f>
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BX33" s="109">
         <f>IFERROR(VLOOKUP($E33,Base!$U:$W,3,0),0)</f>
@@ -46209,7 +46902,7 @@
       </c>
       <c r="BL46" s="111">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="BM46" s="108">
         <f>IFERROR(VLOOKUP($E46&amp;BM$6,Base!$A:$E,5,0),0)</f>
@@ -46255,7 +46948,7 @@
       </c>
       <c r="BX46" s="109">
         <f>IFERROR(VLOOKUP($E46,Base!$U:$W,3,0),0)</f>
-        <v>0</v>
+        <v>306</v>
       </c>
     </row>
     <row r="47" spans="2:76" x14ac:dyDescent="0.35">
@@ -47496,15 +48189,15 @@
       </c>
       <c r="BJ51" s="99">
         <f t="shared" si="45"/>
-        <v>50.540999999999997</v>
+        <v>61.540999999999997</v>
       </c>
       <c r="BK51" s="99">
         <f t="shared" si="46"/>
-        <v>1.417</v>
+        <v>1.833</v>
       </c>
       <c r="BL51" s="111">
         <f t="shared" si="47"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BM51" s="108">
         <f>IFERROR(VLOOKUP($E51&amp;BM$6,Base!$A:$E,5,0),0)</f>
@@ -47542,15 +48235,15 @@
       </c>
       <c r="BV51" s="101">
         <f>IFERROR(VLOOKUP($E51&amp;BV$6,Base!$G:$K,5,0),0)</f>
-        <v>8.0830000000000002</v>
+        <v>19.082999999999998</v>
       </c>
       <c r="BW51" s="101">
         <f>IFERROR(VLOOKUP($E51&amp;BV$6,Base!$M:$Q,5,0),0)</f>
-        <v>1.417</v>
+        <v>1.833</v>
       </c>
       <c r="BX51" s="109">
         <f>IFERROR(VLOOKUP($E51,Base!$U:$W,3,0),0)</f>
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="2:76" x14ac:dyDescent="0.35">
@@ -47755,15 +48448,15 @@
       </c>
       <c r="BJ52" s="99">
         <f t="shared" si="45"/>
-        <v>49.542000000000002</v>
+        <v>54.917000000000002</v>
       </c>
       <c r="BK52" s="99">
         <f t="shared" si="46"/>
-        <v>1.167</v>
+        <v>1.417</v>
       </c>
       <c r="BL52" s="111">
         <f t="shared" si="47"/>
-        <v>5.375</v>
+        <v>0</v>
       </c>
       <c r="BM52" s="108">
         <f>IFERROR(VLOOKUP($E52&amp;BM$6,Base!$A:$E,5,0),0)</f>
@@ -47801,15 +48494,15 @@
       </c>
       <c r="BV52" s="101">
         <f>IFERROR(VLOOKUP($E52&amp;BV$6,Base!$G:$K,5,0),0)</f>
-        <v>7</v>
+        <v>12.375</v>
       </c>
       <c r="BW52" s="101">
         <f>IFERROR(VLOOKUP($E52&amp;BV$6,Base!$M:$Q,5,0),0)</f>
-        <v>1.167</v>
+        <v>1.417</v>
       </c>
       <c r="BX52" s="109">
         <f>IFERROR(VLOOKUP($E52,Base!$U:$W,3,0),0)</f>
-        <v>5.375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="2:76" x14ac:dyDescent="0.35">
@@ -48014,7 +48707,7 @@
       </c>
       <c r="BJ53" s="99">
         <f t="shared" si="45"/>
-        <v>76.125</v>
+        <v>85.625</v>
       </c>
       <c r="BK53" s="99">
         <f t="shared" si="46"/>
@@ -48022,7 +48715,7 @@
       </c>
       <c r="BL53" s="111">
         <f t="shared" si="47"/>
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="BM53" s="108">
         <f>IFERROR(VLOOKUP($E53&amp;BM$6,Base!$A:$E,5,0),0)</f>
@@ -48060,7 +48753,7 @@
       </c>
       <c r="BV53" s="101">
         <f>IFERROR(VLOOKUP($E53&amp;BV$6,Base!$G:$K,5,0),0)</f>
-        <v>8.5</v>
+        <v>18</v>
       </c>
       <c r="BW53" s="101">
         <f>IFERROR(VLOOKUP($E53&amp;BV$6,Base!$M:$Q,5,0),0)</f>
@@ -48068,7 +48761,7 @@
       </c>
       <c r="BX53" s="109">
         <f>IFERROR(VLOOKUP($E53,Base!$U:$W,3,0),0)</f>
-        <v>9.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="2:76" x14ac:dyDescent="0.35">
@@ -48791,7 +49484,7 @@
       </c>
       <c r="BJ56" s="99">
         <f t="shared" si="45"/>
-        <v>187.542</v>
+        <v>212.542</v>
       </c>
       <c r="BK56" s="99">
         <f t="shared" si="46"/>
@@ -48837,7 +49530,7 @@
       </c>
       <c r="BV56" s="101">
         <f>IFERROR(VLOOKUP($E56&amp;BV$6,Base!$G:$K,5,0),0)</f>
-        <v>15.542</v>
+        <v>40.542000000000002</v>
       </c>
       <c r="BW56" s="101">
         <f>IFERROR(VLOOKUP($E56&amp;BV$6,Base!$M:$Q,5,0),0)</f>
@@ -49317,7 +50010,7 @@
       </c>
       <c r="BL58" s="111">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="BM58" s="108">
         <f>IFERROR(VLOOKUP($E58&amp;BM$6,Base!$A:$E,5,0),0)</f>
@@ -49363,7 +50056,7 @@
       </c>
       <c r="BX58" s="109">
         <f>IFERROR(VLOOKUP($E58,Base!$U:$W,3,0),0)</f>
-        <v>0</v>
+        <v>278</v>
       </c>
     </row>
     <row r="59" spans="2:76" x14ac:dyDescent="0.35">
@@ -51640,7 +52333,7 @@
       </c>
       <c r="BJ67" s="99">
         <f t="shared" si="45"/>
-        <v>882</v>
+        <v>1087</v>
       </c>
       <c r="BK67" s="99">
         <f t="shared" si="46"/>
@@ -51648,7 +52341,7 @@
       </c>
       <c r="BL67" s="111">
         <f t="shared" si="47"/>
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="BM67" s="108">
         <f>IFERROR(VLOOKUP($E67&amp;BM$6,Base!$A:$E,5,0),0)</f>
@@ -51686,7 +52379,7 @@
       </c>
       <c r="BV67" s="101">
         <f>IFERROR(VLOOKUP($E67&amp;BV$6,Base!$G:$K,5,0),0)</f>
-        <v>-1</v>
+        <v>204</v>
       </c>
       <c r="BW67" s="101">
         <f>IFERROR(VLOOKUP($E67&amp;BV$6,Base!$M:$Q,5,0),0)</f>
@@ -51694,7 +52387,7 @@
       </c>
       <c r="BX67" s="109">
         <f>IFERROR(VLOOKUP($E67,Base!$U:$W,3,0),0)</f>
-        <v>209</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="2:76" x14ac:dyDescent="0.35">
@@ -52943,7 +53636,7 @@
       </c>
       <c r="BL72" s="111">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BM72" s="108">
         <f>IFERROR(VLOOKUP($E72&amp;BM$6,Base!$A:$E,5,0),0)</f>
@@ -52989,7 +53682,7 @@
       </c>
       <c r="BX72" s="109">
         <f>IFERROR(VLOOKUP($E72,Base!$U:$W,3,0),0)</f>
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73" spans="2:76" x14ac:dyDescent="0.35">
@@ -53202,7 +53895,7 @@
       </c>
       <c r="BL73" s="111">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BM73" s="108">
         <f>IFERROR(VLOOKUP($E73&amp;BM$6,Base!$A:$E,5,0),0)</f>
@@ -53248,7 +53941,7 @@
       </c>
       <c r="BX73" s="109">
         <f>IFERROR(VLOOKUP($E73,Base!$U:$W,3,0),0)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74" spans="2:76" x14ac:dyDescent="0.35">
@@ -53453,7 +54146,7 @@
       </c>
       <c r="BJ74" s="99">
         <f t="shared" si="45"/>
-        <v>364.18799999999999</v>
+        <v>358.709</v>
       </c>
       <c r="BK74" s="99">
         <f t="shared" si="46"/>
@@ -53461,7 +54154,7 @@
       </c>
       <c r="BL74" s="111">
         <f t="shared" si="47"/>
-        <v>85</v>
+        <v>220</v>
       </c>
       <c r="BM74" s="108">
         <f>IFERROR(VLOOKUP($E74&amp;BM$6,Base!$A:$E,5,0),0)</f>
@@ -53499,7 +54192,7 @@
       </c>
       <c r="BV74" s="101">
         <f>IFERROR(VLOOKUP($E74&amp;BV$6,Base!$G:$K,5,0),0)</f>
-        <v>112.5</v>
+        <v>107.021</v>
       </c>
       <c r="BW74" s="101">
         <f>IFERROR(VLOOKUP($E74&amp;BV$6,Base!$M:$Q,5,0),0)</f>
@@ -53507,7 +54200,7 @@
       </c>
       <c r="BX74" s="109">
         <f>IFERROR(VLOOKUP($E74,Base!$U:$W,3,0),0)</f>
-        <v>85</v>
+        <v>220</v>
       </c>
     </row>
     <row r="75" spans="2:76" x14ac:dyDescent="0.35">
@@ -54748,11 +55441,11 @@
       </c>
       <c r="BJ79" s="99">
         <f t="shared" si="45"/>
-        <v>135.501</v>
+        <v>160.667</v>
       </c>
       <c r="BK79" s="99">
         <f t="shared" si="46"/>
-        <v>16.125</v>
+        <v>19.957999999999998</v>
       </c>
       <c r="BL79" s="111">
         <f t="shared" si="47"/>
@@ -54794,11 +55487,11 @@
       </c>
       <c r="BV79" s="101">
         <f>IFERROR(VLOOKUP($E79&amp;BV$6,Base!$G:$K,5,0),0)</f>
-        <v>78.167000000000002</v>
+        <v>103.333</v>
       </c>
       <c r="BW79" s="101">
         <f>IFERROR(VLOOKUP($E79&amp;BV$6,Base!$M:$Q,5,0),0)</f>
-        <v>12.125</v>
+        <v>15.958</v>
       </c>
       <c r="BX79" s="109">
         <f>IFERROR(VLOOKUP($E79,Base!$U:$W,3,0),0)</f>

--- a/MECÂNICAS/PAUTA D/JOHNSON/Campanha Johnson - Top Contas Q4 FY26.xlsx
+++ b/MECÂNICAS/PAUTA D/JOHNSON/Campanha Johnson - Top Contas Q4 FY26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\Nicolas\Acompanhamentos\JOHNSON\2025.26\Q4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1847E364-9C30-4477-87AB-A54E20678A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66338DCD-7F7F-4F46-93A9-5B20DB448963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="705" firstSheet="1" activeTab="3" xr2:uid="{1E3193F5-9832-4B59-8D54-14EFCF6055F0}"/>
   </bookViews>
@@ -4436,6 +4436,27 @@
     <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4446,6 +4467,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4464,36 +4494,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="11" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -22473,138 +22473,138 @@
       <c r="B2" s="150"/>
     </row>
     <row r="3" spans="2:99" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="E3" s="206" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" s="201" t="s">
+      <c r="E3" s="193" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="191" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="203" t="s">
+      <c r="G3" s="202" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="204"/>
-      <c r="I3" s="204"/>
-      <c r="J3" s="204"/>
-      <c r="K3" s="204"/>
-      <c r="L3" s="204"/>
-      <c r="M3" s="204"/>
-      <c r="N3" s="205"/>
-      <c r="O3" s="191" t="s">
+      <c r="H3" s="203"/>
+      <c r="I3" s="203"/>
+      <c r="J3" s="203"/>
+      <c r="K3" s="203"/>
+      <c r="L3" s="203"/>
+      <c r="M3" s="203"/>
+      <c r="N3" s="204"/>
+      <c r="O3" s="198" t="s">
         <v>23</v>
       </c>
-      <c r="P3" s="192"/>
-      <c r="Q3" s="192"/>
-      <c r="R3" s="193"/>
-      <c r="S3" s="191" t="s">
+      <c r="P3" s="199"/>
+      <c r="Q3" s="199"/>
+      <c r="R3" s="200"/>
+      <c r="S3" s="198" t="s">
         <v>24</v>
       </c>
-      <c r="T3" s="192"/>
-      <c r="U3" s="192"/>
-      <c r="V3" s="193"/>
-      <c r="W3" s="191" t="s">
+      <c r="T3" s="199"/>
+      <c r="U3" s="199"/>
+      <c r="V3" s="200"/>
+      <c r="W3" s="198" t="s">
         <v>25</v>
       </c>
-      <c r="X3" s="192"/>
-      <c r="Y3" s="192"/>
-      <c r="Z3" s="194"/>
-      <c r="AB3" s="203" t="s">
+      <c r="X3" s="199"/>
+      <c r="Y3" s="199"/>
+      <c r="Z3" s="201"/>
+      <c r="AB3" s="202" t="s">
         <v>30</v>
       </c>
-      <c r="AC3" s="204"/>
-      <c r="AD3" s="204"/>
-      <c r="AE3" s="204"/>
-      <c r="AF3" s="204"/>
-      <c r="AG3" s="204"/>
-      <c r="AH3" s="204"/>
-      <c r="AI3" s="205"/>
-      <c r="AJ3" s="191" t="s">
+      <c r="AC3" s="203"/>
+      <c r="AD3" s="203"/>
+      <c r="AE3" s="203"/>
+      <c r="AF3" s="203"/>
+      <c r="AG3" s="203"/>
+      <c r="AH3" s="203"/>
+      <c r="AI3" s="204"/>
+      <c r="AJ3" s="198" t="s">
         <v>27</v>
       </c>
-      <c r="AK3" s="192"/>
-      <c r="AL3" s="192"/>
-      <c r="AM3" s="193"/>
-      <c r="AN3" s="191" t="s">
+      <c r="AK3" s="199"/>
+      <c r="AL3" s="199"/>
+      <c r="AM3" s="200"/>
+      <c r="AN3" s="198" t="s">
         <v>28</v>
       </c>
-      <c r="AO3" s="192"/>
-      <c r="AP3" s="192"/>
-      <c r="AQ3" s="193"/>
-      <c r="AR3" s="191" t="s">
+      <c r="AO3" s="199"/>
+      <c r="AP3" s="199"/>
+      <c r="AQ3" s="200"/>
+      <c r="AR3" s="198" t="s">
         <v>29</v>
       </c>
-      <c r="AS3" s="192"/>
-      <c r="AT3" s="192"/>
-      <c r="AU3" s="194"/>
-      <c r="AW3" s="203" t="s">
+      <c r="AS3" s="199"/>
+      <c r="AT3" s="199"/>
+      <c r="AU3" s="201"/>
+      <c r="AW3" s="202" t="s">
         <v>66</v>
       </c>
-      <c r="AX3" s="204"/>
-      <c r="AY3" s="204"/>
-      <c r="AZ3" s="204"/>
-      <c r="BA3" s="204"/>
-      <c r="BB3" s="204"/>
-      <c r="BC3" s="204"/>
-      <c r="BD3" s="205"/>
-      <c r="BE3" s="191" t="s">
+      <c r="AX3" s="203"/>
+      <c r="AY3" s="203"/>
+      <c r="AZ3" s="203"/>
+      <c r="BA3" s="203"/>
+      <c r="BB3" s="203"/>
+      <c r="BC3" s="203"/>
+      <c r="BD3" s="204"/>
+      <c r="BE3" s="198" t="s">
         <v>67</v>
       </c>
-      <c r="BF3" s="192"/>
-      <c r="BG3" s="192"/>
-      <c r="BH3" s="193"/>
-      <c r="BI3" s="191" t="s">
+      <c r="BF3" s="199"/>
+      <c r="BG3" s="199"/>
+      <c r="BH3" s="200"/>
+      <c r="BI3" s="198" t="s">
         <v>68</v>
       </c>
-      <c r="BJ3" s="192"/>
-      <c r="BK3" s="192"/>
-      <c r="BL3" s="193"/>
-      <c r="BM3" s="191" t="s">
+      <c r="BJ3" s="199"/>
+      <c r="BK3" s="199"/>
+      <c r="BL3" s="200"/>
+      <c r="BM3" s="198" t="s">
         <v>72</v>
       </c>
-      <c r="BN3" s="192"/>
-      <c r="BO3" s="192"/>
-      <c r="BP3" s="194"/>
-      <c r="BR3" s="203" t="s">
+      <c r="BN3" s="199"/>
+      <c r="BO3" s="199"/>
+      <c r="BP3" s="201"/>
+      <c r="BR3" s="202" t="s">
         <v>73</v>
       </c>
-      <c r="BS3" s="204"/>
-      <c r="BT3" s="204"/>
-      <c r="BU3" s="204"/>
-      <c r="BV3" s="204"/>
-      <c r="BW3" s="204"/>
-      <c r="BX3" s="204"/>
-      <c r="BY3" s="205"/>
+      <c r="BS3" s="203"/>
+      <c r="BT3" s="203"/>
+      <c r="BU3" s="203"/>
+      <c r="BV3" s="203"/>
+      <c r="BW3" s="203"/>
+      <c r="BX3" s="203"/>
+      <c r="BY3" s="204"/>
       <c r="BZ3" s="185" t="s">
         <v>69</v>
       </c>
       <c r="CA3" s="186"/>
       <c r="CB3" s="186"/>
       <c r="CC3" s="186"/>
-      <c r="CD3" s="191" t="s">
+      <c r="CD3" s="198" t="s">
         <v>70</v>
       </c>
-      <c r="CE3" s="192"/>
-      <c r="CF3" s="192"/>
-      <c r="CG3" s="193"/>
-      <c r="CH3" s="191" t="s">
+      <c r="CE3" s="199"/>
+      <c r="CF3" s="199"/>
+      <c r="CG3" s="200"/>
+      <c r="CH3" s="198" t="s">
         <v>71</v>
       </c>
-      <c r="CI3" s="192"/>
-      <c r="CJ3" s="192"/>
-      <c r="CK3" s="194"/>
-      <c r="CM3" s="208" t="s">
+      <c r="CI3" s="199"/>
+      <c r="CJ3" s="199"/>
+      <c r="CK3" s="201"/>
+      <c r="CM3" s="195" t="s">
         <v>783</v>
       </c>
-      <c r="CN3" s="209"/>
-      <c r="CO3" s="209"/>
-      <c r="CP3" s="209"/>
-      <c r="CQ3" s="209"/>
-      <c r="CR3" s="209"/>
-      <c r="CS3" s="209"/>
-      <c r="CT3" s="210"/>
+      <c r="CN3" s="196"/>
+      <c r="CO3" s="196"/>
+      <c r="CP3" s="196"/>
+      <c r="CQ3" s="196"/>
+      <c r="CR3" s="196"/>
+      <c r="CS3" s="196"/>
+      <c r="CT3" s="197"/>
     </row>
     <row r="4" spans="2:99" ht="26" x14ac:dyDescent="0.3">
-      <c r="E4" s="207"/>
-      <c r="F4" s="202"/>
+      <c r="E4" s="194"/>
+      <c r="F4" s="192"/>
       <c r="G4" s="146" t="s">
         <v>169</v>
       </c>
@@ -24007,137 +24007,137 @@
       <c r="CK9" s="11"/>
     </row>
     <row r="10" spans="2:99" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="198" t="s">
+      <c r="B10" s="208" t="s">
         <v>784</v>
       </c>
-      <c r="C10" s="199"/>
-      <c r="D10" s="199"/>
-      <c r="E10" s="200"/>
-      <c r="F10" s="201" t="s">
+      <c r="C10" s="209"/>
+      <c r="D10" s="209"/>
+      <c r="E10" s="210"/>
+      <c r="F10" s="191" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="203" t="s">
+      <c r="G10" s="202" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="204"/>
-      <c r="I10" s="204"/>
-      <c r="J10" s="204"/>
-      <c r="K10" s="204"/>
-      <c r="L10" s="204"/>
-      <c r="M10" s="204"/>
-      <c r="N10" s="205"/>
-      <c r="O10" s="191" t="s">
+      <c r="H10" s="203"/>
+      <c r="I10" s="203"/>
+      <c r="J10" s="203"/>
+      <c r="K10" s="203"/>
+      <c r="L10" s="203"/>
+      <c r="M10" s="203"/>
+      <c r="N10" s="204"/>
+      <c r="O10" s="198" t="s">
         <v>23</v>
       </c>
-      <c r="P10" s="192"/>
-      <c r="Q10" s="192"/>
-      <c r="R10" s="193"/>
-      <c r="S10" s="191" t="s">
+      <c r="P10" s="199"/>
+      <c r="Q10" s="199"/>
+      <c r="R10" s="200"/>
+      <c r="S10" s="198" t="s">
         <v>24</v>
       </c>
-      <c r="T10" s="192"/>
-      <c r="U10" s="192"/>
-      <c r="V10" s="193"/>
-      <c r="W10" s="191" t="s">
+      <c r="T10" s="199"/>
+      <c r="U10" s="199"/>
+      <c r="V10" s="200"/>
+      <c r="W10" s="198" t="s">
         <v>25</v>
       </c>
-      <c r="X10" s="192"/>
-      <c r="Y10" s="192"/>
-      <c r="Z10" s="194"/>
-      <c r="AB10" s="203" t="s">
+      <c r="X10" s="199"/>
+      <c r="Y10" s="199"/>
+      <c r="Z10" s="201"/>
+      <c r="AB10" s="202" t="s">
         <v>30</v>
       </c>
-      <c r="AC10" s="204"/>
-      <c r="AD10" s="204"/>
-      <c r="AE10" s="204"/>
-      <c r="AF10" s="204"/>
-      <c r="AG10" s="204"/>
-      <c r="AH10" s="204"/>
-      <c r="AI10" s="205"/>
-      <c r="AJ10" s="191" t="s">
+      <c r="AC10" s="203"/>
+      <c r="AD10" s="203"/>
+      <c r="AE10" s="203"/>
+      <c r="AF10" s="203"/>
+      <c r="AG10" s="203"/>
+      <c r="AH10" s="203"/>
+      <c r="AI10" s="204"/>
+      <c r="AJ10" s="198" t="s">
         <v>27</v>
       </c>
-      <c r="AK10" s="192"/>
-      <c r="AL10" s="192"/>
-      <c r="AM10" s="193"/>
-      <c r="AN10" s="191" t="s">
+      <c r="AK10" s="199"/>
+      <c r="AL10" s="199"/>
+      <c r="AM10" s="200"/>
+      <c r="AN10" s="198" t="s">
         <v>28</v>
       </c>
-      <c r="AO10" s="192"/>
-      <c r="AP10" s="192"/>
-      <c r="AQ10" s="193"/>
-      <c r="AR10" s="191" t="s">
+      <c r="AO10" s="199"/>
+      <c r="AP10" s="199"/>
+      <c r="AQ10" s="200"/>
+      <c r="AR10" s="198" t="s">
         <v>29</v>
       </c>
-      <c r="AS10" s="192"/>
-      <c r="AT10" s="192"/>
-      <c r="AU10" s="194"/>
-      <c r="AW10" s="203" t="s">
+      <c r="AS10" s="199"/>
+      <c r="AT10" s="199"/>
+      <c r="AU10" s="201"/>
+      <c r="AW10" s="202" t="s">
         <v>66</v>
       </c>
-      <c r="AX10" s="204"/>
-      <c r="AY10" s="204"/>
-      <c r="AZ10" s="204"/>
-      <c r="BA10" s="204"/>
-      <c r="BB10" s="204"/>
-      <c r="BC10" s="204"/>
-      <c r="BD10" s="205"/>
-      <c r="BE10" s="191" t="s">
+      <c r="AX10" s="203"/>
+      <c r="AY10" s="203"/>
+      <c r="AZ10" s="203"/>
+      <c r="BA10" s="203"/>
+      <c r="BB10" s="203"/>
+      <c r="BC10" s="203"/>
+      <c r="BD10" s="204"/>
+      <c r="BE10" s="198" t="s">
         <v>67</v>
       </c>
-      <c r="BF10" s="192"/>
-      <c r="BG10" s="192"/>
-      <c r="BH10" s="193"/>
-      <c r="BI10" s="191" t="s">
+      <c r="BF10" s="199"/>
+      <c r="BG10" s="199"/>
+      <c r="BH10" s="200"/>
+      <c r="BI10" s="198" t="s">
         <v>68</v>
       </c>
-      <c r="BJ10" s="192"/>
-      <c r="BK10" s="192"/>
-      <c r="BL10" s="193"/>
-      <c r="BM10" s="191" t="s">
+      <c r="BJ10" s="199"/>
+      <c r="BK10" s="199"/>
+      <c r="BL10" s="200"/>
+      <c r="BM10" s="198" t="s">
         <v>72</v>
       </c>
-      <c r="BN10" s="192"/>
-      <c r="BO10" s="192"/>
-      <c r="BP10" s="194"/>
-      <c r="BR10" s="203" t="s">
+      <c r="BN10" s="199"/>
+      <c r="BO10" s="199"/>
+      <c r="BP10" s="201"/>
+      <c r="BR10" s="202" t="s">
         <v>73</v>
       </c>
-      <c r="BS10" s="204"/>
-      <c r="BT10" s="204"/>
-      <c r="BU10" s="204"/>
-      <c r="BV10" s="204"/>
-      <c r="BW10" s="204"/>
-      <c r="BX10" s="204"/>
-      <c r="BY10" s="205"/>
+      <c r="BS10" s="203"/>
+      <c r="BT10" s="203"/>
+      <c r="BU10" s="203"/>
+      <c r="BV10" s="203"/>
+      <c r="BW10" s="203"/>
+      <c r="BX10" s="203"/>
+      <c r="BY10" s="204"/>
       <c r="BZ10" s="185" t="s">
         <v>69</v>
       </c>
       <c r="CA10" s="186"/>
       <c r="CB10" s="186"/>
       <c r="CC10" s="186"/>
-      <c r="CD10" s="191" t="s">
+      <c r="CD10" s="198" t="s">
         <v>70</v>
       </c>
-      <c r="CE10" s="192"/>
-      <c r="CF10" s="192"/>
-      <c r="CG10" s="193"/>
-      <c r="CH10" s="191" t="s">
+      <c r="CE10" s="199"/>
+      <c r="CF10" s="199"/>
+      <c r="CG10" s="200"/>
+      <c r="CH10" s="198" t="s">
         <v>71</v>
       </c>
-      <c r="CI10" s="192"/>
-      <c r="CJ10" s="192"/>
-      <c r="CK10" s="194"/>
-      <c r="CM10" s="208" t="s">
+      <c r="CI10" s="199"/>
+      <c r="CJ10" s="199"/>
+      <c r="CK10" s="201"/>
+      <c r="CM10" s="195" t="s">
         <v>783</v>
       </c>
-      <c r="CN10" s="209"/>
-      <c r="CO10" s="209"/>
-      <c r="CP10" s="209"/>
-      <c r="CQ10" s="209"/>
-      <c r="CR10" s="209"/>
-      <c r="CS10" s="209"/>
-      <c r="CT10" s="210"/>
+      <c r="CN10" s="196"/>
+      <c r="CO10" s="196"/>
+      <c r="CP10" s="196"/>
+      <c r="CQ10" s="196"/>
+      <c r="CR10" s="196"/>
+      <c r="CS10" s="196"/>
+      <c r="CT10" s="197"/>
     </row>
     <row r="11" spans="2:99" ht="26" x14ac:dyDescent="0.3">
       <c r="B11" s="52" t="s">
@@ -24152,7 +24152,7 @@
       <c r="E11" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="202"/>
+      <c r="F11" s="192"/>
       <c r="G11" s="38" t="s">
         <v>169</v>
       </c>
@@ -27405,12 +27405,12 @@
       <c r="CU19" s="21"/>
     </row>
     <row r="20" spans="2:99" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="195" t="s">
+      <c r="B20" s="205" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="196"/>
-      <c r="D20" s="196"/>
-      <c r="E20" s="197"/>
+      <c r="C20" s="206"/>
+      <c r="D20" s="206"/>
+      <c r="E20" s="207"/>
       <c r="F20" s="113">
         <f>SUM(F12:F19)</f>
         <v>14</v>
@@ -27987,6 +27987,27 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="AN10:AQ10"/>
+    <mergeCell ref="AR10:AU10"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="BM10:BP10"/>
+    <mergeCell ref="AW3:BD3"/>
+    <mergeCell ref="G3:N3"/>
+    <mergeCell ref="G10:N10"/>
+    <mergeCell ref="AB3:AI3"/>
+    <mergeCell ref="AB10:AI10"/>
+    <mergeCell ref="AJ3:AM3"/>
+    <mergeCell ref="O10:R10"/>
+    <mergeCell ref="S10:V10"/>
+    <mergeCell ref="W10:Z10"/>
+    <mergeCell ref="AJ10:AM10"/>
+    <mergeCell ref="AN3:AQ3"/>
+    <mergeCell ref="AR3:AU3"/>
+    <mergeCell ref="O3:R3"/>
+    <mergeCell ref="S3:V3"/>
+    <mergeCell ref="W3:Z3"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="CM3:CT3"/>
@@ -28003,27 +28024,6 @@
     <mergeCell ref="BE10:BH10"/>
     <mergeCell ref="AW10:BD10"/>
     <mergeCell ref="BI10:BL10"/>
-    <mergeCell ref="BM10:BP10"/>
-    <mergeCell ref="AW3:BD3"/>
-    <mergeCell ref="G3:N3"/>
-    <mergeCell ref="G10:N10"/>
-    <mergeCell ref="AB3:AI3"/>
-    <mergeCell ref="AB10:AI10"/>
-    <mergeCell ref="AJ3:AM3"/>
-    <mergeCell ref="O10:R10"/>
-    <mergeCell ref="S10:V10"/>
-    <mergeCell ref="W10:Z10"/>
-    <mergeCell ref="AJ10:AM10"/>
-    <mergeCell ref="AN3:AQ3"/>
-    <mergeCell ref="AR3:AU3"/>
-    <mergeCell ref="O3:R3"/>
-    <mergeCell ref="S3:V3"/>
-    <mergeCell ref="W3:Z3"/>
-    <mergeCell ref="AN10:AQ10"/>
-    <mergeCell ref="AR10:AU10"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="F10:F11"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="L5:L7 AG5:AG7 BB5:BB7 BW5:BW7 CR5:CR7 L12:L20 AG12:AG20 BB12:BB20 BW12:BW20 CR12:CR20">

--- a/MECÂNICAS/PAUTA D/JOHNSON/Campanha Johnson - Top Contas Q4 FY26.xlsx
+++ b/MECÂNICAS/PAUTA D/JOHNSON/Campanha Johnson - Top Contas Q4 FY26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\Nicolas\Acompanhamentos\JOHNSON\2025.26\Q4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66338DCD-7F7F-4F46-93A9-5B20DB448963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C70782EA-2AFD-4C11-847E-2A1D75BDC714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="705" firstSheet="1" activeTab="3" xr2:uid="{1E3193F5-9832-4B59-8D54-14EFCF6055F0}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4086" uniqueCount="1049">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4089" uniqueCount="1041">
   <si>
     <t>EQUIPE</t>
   </si>
@@ -2487,15 +2487,6 @@
     <t xml:space="preserve">MOCAM SUPERMERCADOS LTDA FILIAL 01 </t>
   </si>
   <si>
-    <t>BEACH STOP MINI MERCADO LTDA</t>
-  </si>
-  <si>
-    <t>LARISSA POITE STAROSCKY</t>
-  </si>
-  <si>
-    <t>MERCEARIA DONA JO LTDA</t>
-  </si>
-  <si>
     <t>PROGRESSO COMERCIO DE ALIMENTOS LTDA</t>
   </si>
   <si>
@@ -2505,78 +2496,30 @@
     <t xml:space="preserve"> 113 linhas</t>
   </si>
   <si>
-    <t>ALCIONE ZANOLLA ME</t>
-  </si>
-  <si>
     <t>AUTO POSTO MEDITERRANEO LTDA</t>
   </si>
   <si>
-    <t>AUTO POSTO NOVA TRENTO LTDA</t>
-  </si>
-  <si>
-    <t>BLUMENKAFFEE PADARIA E CAFEITARIA LTDA</t>
-  </si>
-  <si>
-    <t>CONVENIENCIA BELLA LTDA</t>
-  </si>
-  <si>
     <t>COOP CONS OPERARIOS REGIAO CARBONIF LTDA</t>
   </si>
   <si>
-    <t>CORDOVA E PRUDENCIO COM DE GEN ALIM LTDA</t>
-  </si>
-  <si>
     <t>DROGARIA ABNER LTDA</t>
   </si>
   <si>
-    <t>EDSON DE LIMA</t>
-  </si>
-  <si>
-    <t>FARMACIA E PERFUMARIA ADIFARMA LTDA</t>
-  </si>
-  <si>
-    <t>H.R. DESCARTAVEIS LTDA</t>
-  </si>
-  <si>
-    <t>JANAINA SILVANO DE SOUZA</t>
-  </si>
-  <si>
     <t>JH SILVEIRA MARQUES LTDA</t>
   </si>
   <si>
     <t>KAUA TELES LOURENCO</t>
   </si>
   <si>
-    <t>LOJAS DE DEPARTAMENTOS MILIUM LTDA</t>
-  </si>
-  <si>
     <t>MERCADO CAMELIA LTDA</t>
   </si>
   <si>
     <t>MERCADO DO CLEITON EIRELI</t>
   </si>
   <si>
-    <t>MERCADO E ACOUGUE DONA BE JOINVILLE LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO E PANIF SILVIO E SILVANIA LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO VILLA LTDA</t>
-  </si>
-  <si>
     <t>MINIMERCADO E ACOUGUE CLASEN LTDA</t>
   </si>
   <si>
-    <t>NUTRY FRUTARIA E MERCEARIA LTDA</t>
-  </si>
-  <si>
-    <t>ROSA MARIA NUNES DA SILVA</t>
-  </si>
-  <si>
-    <t>ROSIMERI ESIDIO</t>
-  </si>
-  <si>
     <t>SHEILA GISELE BERNARDES</t>
   </si>
   <si>
@@ -2595,51 +2538,21 @@
     <t>ATUALIZADO:</t>
   </si>
   <si>
-    <t xml:space="preserve"> 319 linhas</t>
-  </si>
-  <si>
     <t>58.911.277 GABRIEL JAQUES LUZ</t>
   </si>
   <si>
-    <t>ABASTECEDORA AVENIDA DE COMBUSTIVEL LTDA</t>
-  </si>
-  <si>
     <t>ADRIANO FRANCISCO BARBOSA DA SILVA</t>
   </si>
   <si>
-    <t>AGRO TROPICAL LTDA</t>
-  </si>
-  <si>
-    <t>ALESSANDRA SCARIOT CECHINEL</t>
-  </si>
-  <si>
     <t>ALEXANDRE DOS SANTOS DIATEL</t>
   </si>
   <si>
-    <t>ALTAMIR SERRAO E CIA LTDA</t>
-  </si>
-  <si>
-    <t>ALTHOFF SUPERMERCADOS LTDA</t>
-  </si>
-  <si>
     <t>AMANDA CARVALHO POLLHEIM</t>
   </si>
   <si>
-    <t>ANDERSON PIMENTEL SUPERMERCADO LTDA</t>
-  </si>
-  <si>
-    <t>ARCELINA MARIA ELIAS SEIDEL ME</t>
-  </si>
-  <si>
     <t>ARLINDO MENDES</t>
   </si>
   <si>
-    <t>ARMAZEM SOUPAC LTDA</t>
-  </si>
-  <si>
-    <t>ARNALDO SILVEIRA LIMA ME</t>
-  </si>
-  <si>
     <t>AURI LOPES DE SOUZA</t>
   </si>
   <si>
@@ -2649,21 +2562,12 @@
     <t>AUTO POSTO FORQUILHINHA LTDA</t>
   </si>
   <si>
-    <t>AUTO POSTO M LTDA</t>
-  </si>
-  <si>
     <t>BELLO SUPERMERCADOS 01 LTDA</t>
   </si>
   <si>
     <t>BIG CAFETERIA LTDA</t>
   </si>
   <si>
-    <t>BMI PROSPER EIRELI</t>
-  </si>
-  <si>
-    <t>BRAVA MARKET LTDA</t>
-  </si>
-  <si>
     <t>BURIGO E BURIGO LTDA</t>
   </si>
   <si>
@@ -2676,42 +2580,18 @@
     <t>CECHINEL &amp; CECHINEL CASA DE CARNES LTDA</t>
   </si>
   <si>
-    <t>CL10 COMERCIO DE MERCADORIAS LTDA</t>
-  </si>
-  <si>
-    <t>COM DE PROD LIMPEZA PEDRA BRANCA LTDA</t>
-  </si>
-  <si>
-    <t>COMERCIAL DE ALIMENTOS URUSSANGA LTDA</t>
-  </si>
-  <si>
-    <t>COMERCIAL DUTRA LTDA</t>
-  </si>
-  <si>
-    <t>COMERCIO DE FRUTAS H PAULI LTDA</t>
-  </si>
-  <si>
-    <t>COMERCIO E LANCHONETE BRACO DO SUL LTDA</t>
-  </si>
-  <si>
     <t>COMPRE PAN PANIFICADORA E MERCEARIA LTDA</t>
   </si>
   <si>
     <t>CRISTIANO MESSIAS PALOCO SEIVISH</t>
   </si>
   <si>
-    <t>CRISTIANO PETROSKI MERCEARIA</t>
-  </si>
-  <si>
     <t>D MARIA MERCADO E PADARIA LTDA</t>
   </si>
   <si>
     <t>DAIANA BRIZOLLA MAMEDIO</t>
   </si>
   <si>
-    <t>DAIANA MACHADO VOLLERT</t>
-  </si>
-  <si>
     <t>DEISE FELISBERTO</t>
   </si>
   <si>
@@ -2724,9 +2604,6 @@
     <t>E DE CASA SUPERMERCADOS EIRELI</t>
   </si>
   <si>
-    <t>ECOLIMPOS PROD DE LIMP E DESCARTAVE LTDA</t>
-  </si>
-  <si>
     <t>EDER CAZUNI DE ARAUJO LTDA</t>
   </si>
   <si>
@@ -2736,30 +2613,9 @@
     <t>EMBALAGENS SETE DE SETEMBRO LTDA</t>
   </si>
   <si>
-    <t>EURICO MARCOS OSMARI EIRELI</t>
-  </si>
-  <si>
-    <t>FABRICIO MATIAS CARDOSO</t>
-  </si>
-  <si>
-    <t>FATIMA LUCENEA BUDSKE</t>
-  </si>
-  <si>
-    <t>FERNANDA MEIER IDALINO</t>
-  </si>
-  <si>
-    <t>FERNANDO JESSE BORBA</t>
-  </si>
-  <si>
-    <t>FERNANDO RIBEIRO DE SOUZA</t>
-  </si>
-  <si>
     <t>FEZ SUPERMERCADO LTDA</t>
   </si>
   <si>
-    <t>FLAMARION RAULINO</t>
-  </si>
-  <si>
     <t>GATTIS COMERCIO ALIMENTICIOS LTDA</t>
   </si>
   <si>
@@ -2772,120 +2628,36 @@
     <t>GOEDERT LTDA</t>
   </si>
   <si>
-    <t>HELIO BLOEMER MEURER</t>
-  </si>
-  <si>
     <t>I S COMERCIO E DISTRIBUICAO LTDA</t>
   </si>
   <si>
-    <t>INVICTA BEBIDAS LTDA</t>
-  </si>
-  <si>
-    <t>IVANY BATISTA MERCADO</t>
-  </si>
-  <si>
-    <t>JAIME NICOLAU FUCHIER</t>
-  </si>
-  <si>
-    <t>JAKSON SILVA DE QUADRO EIRELI</t>
-  </si>
-  <si>
-    <t>JANICIO DA ROCHA</t>
-  </si>
-  <si>
     <t>JC FLORES FLORICULTURA E PAISAGISMO LTDA</t>
   </si>
   <si>
-    <t>JEFERSON DA SILVA LIMA</t>
-  </si>
-  <si>
     <t>JEFFERSON SILVA DE OLIVEIRA</t>
   </si>
   <si>
-    <t>JGS MERCEARIA LTDA</t>
-  </si>
-  <si>
-    <t>JOAZA FLORES E PAISAGISMO LTDA</t>
-  </si>
-  <si>
-    <t>JOCEMAR DUARTE BRAATZ PANIF CONF E MERCEARIA LTDA</t>
-  </si>
-  <si>
-    <t>JONAS BARDINI QUIRINO ME</t>
-  </si>
-  <si>
-    <t>JORGE DELA JUSTINA ASCARI</t>
-  </si>
-  <si>
-    <t>JOSE CLEZIO GENEROSO</t>
-  </si>
-  <si>
-    <t>JOSE LEONARDO DA SILVA COMERCIANTE</t>
-  </si>
-  <si>
     <t>JOSE MENDES FILHO</t>
   </si>
   <si>
-    <t>JOSE PEREIRA</t>
-  </si>
-  <si>
     <t>JOTA KA SUPERMERCADO LTDA</t>
   </si>
   <si>
-    <t>JUNETE COMERCIO DE ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>K E V COMERCIO DE FRUTAS E VERDURAS LTDA</t>
-  </si>
-  <si>
-    <t>LANCHONETE DO ITALIANO LTDA</t>
-  </si>
-  <si>
-    <t>LEONIDA BORGEVER LOCH OENNING</t>
-  </si>
-  <si>
-    <t>LIDIANE VILMA DE SOUZA</t>
-  </si>
-  <si>
-    <t>LIRA MERCADO E TOMAZINI LTDA</t>
-  </si>
-  <si>
     <t>LM CLEAN SHOP DISTRIBUIDORA LTDA</t>
   </si>
   <si>
     <t>LOC MANIA SORVETERIA LTDA</t>
   </si>
   <si>
-    <t>LOJAS ADELINO LTDA</t>
-  </si>
-  <si>
-    <t>LP COMERCIO E ALIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>LUCAS SANTANA DOS SANTOS</t>
-  </si>
-  <si>
-    <t>LUCIA MARIA INNOCENTI LIMA</t>
-  </si>
-  <si>
     <t>LUCIANA DA ROSA</t>
   </si>
   <si>
     <t>MANOEL FERREIRA ANDRADE</t>
   </si>
   <si>
-    <t>MAQ TEM MERCADO LTDA</t>
-  </si>
-  <si>
-    <t>MARCELO QUELUZ MULLER</t>
-  </si>
-  <si>
     <t>MARCIO AUGUSTO BRINA</t>
   </si>
   <si>
-    <t>MARIA TARCILA GESSELE</t>
-  </si>
-  <si>
     <t>MARIZIE HELENA DA SILVA ANGELI</t>
   </si>
   <si>
@@ -2898,102 +2670,39 @@
     <t>MERCADO C MAIS LTDA</t>
   </si>
   <si>
-    <t>MERCADO CAMPOS SALLES LTDA</t>
-  </si>
-  <si>
     <t>MERCADO CARIJOS LTDA</t>
   </si>
   <si>
     <t>MERCADO CARLINHOS LTDA</t>
   </si>
   <si>
-    <t>MERCADO CAROLINA LTDA.</t>
-  </si>
-  <si>
-    <t>MERCADO CD LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO CONGONHAS LTDA</t>
-  </si>
-  <si>
     <t>MERCADO DO CLEITON II LTDA</t>
   </si>
   <si>
-    <t>MERCADO E ACOGUE SAO MIGUEL LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO E ACOUGUE ANDRADE LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO E ACOUGUE BSP LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO E ACOUGUE NOSSA SRA DA GLORIA LTDA</t>
-  </si>
-  <si>
     <t>MERCADO E ACOUGUE TR LTDA</t>
   </si>
   <si>
-    <t>MERCADO HRUSCHKA LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO KAMMERS LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO KAUE LTDA</t>
-  </si>
-  <si>
-    <t>MERCADO LISANDRA EIRELI</t>
-  </si>
-  <si>
     <t>MERCADO MELHOR PRECO LTDA</t>
   </si>
   <si>
     <t>MERCADO PEDROSA LTDA</t>
   </si>
   <si>
-    <t>MERCADO PICKLER LTDA</t>
-  </si>
-  <si>
     <t>MERCADO RIO BELO LTDA</t>
   </si>
   <si>
     <t>MERCADO ROBERTA E ROSANA LTDA</t>
   </si>
   <si>
-    <t>MERCEARIA DUARTE LTDA</t>
-  </si>
-  <si>
     <t>MEU VIZINHO ATACADO E VAREJO LTDA</t>
   </si>
   <si>
-    <t>MICHEL BUSSOLO ALBERTON</t>
-  </si>
-  <si>
     <t>MIMIM DISTRIBUIDORA E SERVICOS LTDA.</t>
   </si>
   <si>
-    <t>MINI MERCADO E ARMAZEM RABAJ EIRELI</t>
-  </si>
-  <si>
-    <t>MINIMERCADO MANOS LTDA</t>
-  </si>
-  <si>
-    <t>MINIMERCADO PONATH LTDA</t>
-  </si>
-  <si>
-    <t>MURILO SCHMITT ME</t>
-  </si>
-  <si>
-    <t>MV COM ATACADISTA E VAREJ DE ALIM LTDA</t>
-  </si>
-  <si>
     <t>MV COMERCIO ATACADISTA E VAREJISTA DE ALIMENTOS LIMITADA</t>
   </si>
   <si>
-    <t>NELSI PERSCH ZILS</t>
-  </si>
-  <si>
     <t>NILZA PORTO COMUNELLO</t>
   </si>
   <si>
@@ -3003,114 +2712,54 @@
     <t>ORLI HENK MAIER ME</t>
   </si>
   <si>
-    <t>PANIFICADORA GOMES LTDA</t>
-  </si>
-  <si>
-    <t>PANIFICADORA LOCA LTDA</t>
-  </si>
-  <si>
-    <t>PAO DA HORA PANIFICADORA LTDA</t>
-  </si>
-  <si>
     <t>PAPA RANCHO COMERCIO LTDA</t>
   </si>
   <si>
-    <t>PAULO CESAR CARDOSO ME</t>
-  </si>
-  <si>
-    <t>PEDRO PERRARO SOBRINHO</t>
-  </si>
-  <si>
-    <t>PEKA SUPERMERCADOS LTDA</t>
-  </si>
-  <si>
-    <t>POSTO BARRA NORTE LTDA</t>
-  </si>
-  <si>
-    <t>POSTO GLORIA LTDA</t>
-  </si>
-  <si>
-    <t>POSTO PAULINHO LTDA</t>
-  </si>
-  <si>
     <t>PRADO SUPERMERCADO LTDA</t>
   </si>
   <si>
     <t>PRAIA E MAR COMERCIO DE ALIMENTOS LTDA</t>
   </si>
   <si>
-    <t>R E M SUPERMERCADO LTDA</t>
-  </si>
-  <si>
     <t>RAFAEL PEREIRA BERNARDO</t>
   </si>
   <si>
     <t>RANCHO BOM SUPERMERCADOS LTDA</t>
   </si>
   <si>
-    <t>REBECA COSTA DIAS</t>
-  </si>
-  <si>
     <t>RECH E SILVA SUPERMERCADO LTDA</t>
   </si>
   <si>
     <t>REPRESENTACOES FAUST LTDA</t>
   </si>
   <si>
-    <t>RG PET DISTRIBUIDORA LTDA</t>
-  </si>
-  <si>
-    <t>RGP LIMPEZA COM VAR DE PROD DE LIMP EIRELI</t>
-  </si>
-  <si>
     <t>ROBSON CELINGA</t>
   </si>
   <si>
-    <t>RONALDO PORTO NUNES</t>
-  </si>
-  <si>
     <t>ROSA ESTER AUTO POSTO EIRELI</t>
   </si>
   <si>
     <t>ROSANE SEBASTIANA FERREIRA DE LIMA</t>
   </si>
   <si>
-    <t>ROSEMERI BUENO DE LIMA ME</t>
-  </si>
-  <si>
     <t>ROSINETE FRANCISCO ANTONIO BERNARDO</t>
   </si>
   <si>
     <t>SAIONARA MACHADO TORQUATO</t>
   </si>
   <si>
-    <t>SANTANA E ALBANAZ LTDA</t>
-  </si>
-  <si>
-    <t>SEBASTIAO KREMER</t>
-  </si>
-  <si>
     <t>SERGIO RODRIGUES ATANAZIO</t>
   </si>
   <si>
     <t>SILVIERI SUPERMERCADOS LTDA</t>
   </si>
   <si>
-    <t>SM SUPERMERCADO LTDA</t>
-  </si>
-  <si>
-    <t>SUPERMERCADO ALIANCA LTDA</t>
-  </si>
-  <si>
     <t>SUPERMERCADO ALIANDES EIRELI</t>
   </si>
   <si>
     <t>SUPERMERCADO ALIANDES LTDA</t>
   </si>
   <si>
-    <t>SUPERMERCADO BITTENCOURT LTDA</t>
-  </si>
-  <si>
     <t>SUPERMERCADO BOI GORDO LTDA</t>
   </si>
   <si>
@@ -3120,36 +2769,12 @@
     <t>SUPERMERCADO CAMPESTRINI LTDA</t>
   </si>
   <si>
-    <t>SUPERMERCADO ENGENHO LTDA</t>
-  </si>
-  <si>
-    <t>SUPERMERCADO FARIAS LTDA</t>
-  </si>
-  <si>
-    <t>SUPERMERCADO GADOTTI LTDA</t>
-  </si>
-  <si>
-    <t>SUPERMERCADO IRMAOS WENDORF LTDA</t>
-  </si>
-  <si>
-    <t>SUPERMERCADO IRMAOS WENDORF LTDA.</t>
-  </si>
-  <si>
     <t>SUPERMERCADO J K LTDA</t>
   </si>
   <si>
     <t>SUPERMERCADO MERCOCENTRO LTDA</t>
   </si>
   <si>
-    <t>SUPERMERCADO MINUANO LTDA</t>
-  </si>
-  <si>
-    <t>SUPERMERCADO MUNHOZ LTDA</t>
-  </si>
-  <si>
-    <t>SUPERMERCADO PC LTDA</t>
-  </si>
-  <si>
     <t>SUPERMERCADO RONCHI LTDA</t>
   </si>
   <si>
@@ -3159,43 +2784,394 @@
     <t>SUPERMERCADO SETE LTDA</t>
   </si>
   <si>
-    <t>SUPERMERCADO SUL DO RIO 02 LTDA</t>
-  </si>
-  <si>
-    <t>SUPERMERCADO SUL DO RIO LTDA</t>
-  </si>
-  <si>
     <t>SUPERMERCADO VALDIR EIRELI</t>
   </si>
   <si>
-    <t>SUPERMERCADO VIANA LTDA</t>
-  </si>
-  <si>
-    <t>SUPERMERCADOS BAGGIO LTDA</t>
-  </si>
-  <si>
-    <t>SUPERMERCADOS NATHAN LTDA</t>
-  </si>
-  <si>
     <t>TACIANI CARLA DE COSTA ROCHA TORQUATO</t>
   </si>
   <si>
     <t>VALDA ELEUTERIO</t>
   </si>
   <si>
-    <t>VALDENIR PERICO</t>
-  </si>
-  <si>
     <t>VALERIA ROBERTA DE MELO MONTEIRO</t>
   </si>
   <si>
     <t>VARLENE RODRIGUES FISCHER</t>
   </si>
   <si>
-    <t>VILLA PAPEIS LTDA</t>
-  </si>
-  <si>
-    <t>TOTAL: 264 linhas</t>
+    <t xml:space="preserve"> 320 linhas</t>
+  </si>
+  <si>
+    <t>53.897.304 MIRTES NADIR GOMES DA ROSA</t>
+  </si>
+  <si>
+    <t>AGROAVICOLA POMERODE LTDA</t>
+  </si>
+  <si>
+    <t>AMIGO PAUL PAN E EMPORIO LTDA</t>
+  </si>
+  <si>
+    <t>ANA BEATRIS CITTADIN</t>
+  </si>
+  <si>
+    <t>ANDERSON DA SILVA MINIMERCADO</t>
+  </si>
+  <si>
+    <t>ANITO BONIKOSKI</t>
+  </si>
+  <si>
+    <t>ANTONINHO DE SOUZA MERCADINHO</t>
+  </si>
+  <si>
+    <t>ARMAZEM DA LIMPEZA COM VAR DE PROD LIMPEZA LTDA</t>
+  </si>
+  <si>
+    <t>AUTO POSTO SANTANA EIRELI</t>
+  </si>
+  <si>
+    <t>BAR E MERCEARIA CAIXA D AGUA LTDA</t>
+  </si>
+  <si>
+    <t>BAR E MERCEARIA LEMKE LTDA</t>
+  </si>
+  <si>
+    <t>BAR E MERCEARIA NELSON JUST LTDA</t>
+  </si>
+  <si>
+    <t>BAR E MERCEARIA POMERANIA LTDA</t>
+  </si>
+  <si>
+    <t>BC LOG TRANSPORTADORA LTD</t>
+  </si>
+  <si>
+    <t>BOTECO BC 2300 LTDA</t>
+  </si>
+  <si>
+    <t>CALDO DE CANA PONTO CERTO LTDA</t>
+  </si>
+  <si>
+    <t>CARMEN MARTINS MERCADO</t>
+  </si>
+  <si>
+    <t>CLAUDIA DE ANDRADE PINHEIRO 00420243070</t>
+  </si>
+  <si>
+    <t>CLEUSA DA ROSA</t>
+  </si>
+  <si>
+    <t>COMERCIAL DE ALIMENTOS DE ANGELINA LTDA</t>
+  </si>
+  <si>
+    <t>COMERCIAL DE ALIMENTOS R P J LTDA</t>
+  </si>
+  <si>
+    <t>COMERCIAL FRONZA LTDA</t>
+  </si>
+  <si>
+    <t>COMERCIAL SARETTO LTDA</t>
+  </si>
+  <si>
+    <t>COMERCIO DE CEREAIS ALTO VALE LTDA</t>
+  </si>
+  <si>
+    <t>COMERCIO DE GEN ALIMENTICIOS KUNZ LTDA</t>
+  </si>
+  <si>
+    <t>COMERCIO DE GENEROS ALIMENT REIS LTDA</t>
+  </si>
+  <si>
+    <t>COMERCIO VAR DE PROD ALIM EM GERAL BARRA DE IBIRAQUERA LTDA</t>
+  </si>
+  <si>
+    <t>CONRADI COMERCIO DE ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>CV CARARO MERCADO</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDORA DE DOCES SO GULA LTDA</t>
+  </si>
+  <si>
+    <t>DROGARIA MED FARMA LTDA</t>
+  </si>
+  <si>
+    <t>ELADIR MARIA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>ERICO JOSE DA SILVA FILHO</t>
+  </si>
+  <si>
+    <t>ERIELSON SILVA DA ROSA</t>
+  </si>
+  <si>
+    <t>FABRICIO BAESSO</t>
+  </si>
+  <si>
+    <t>FAMILIA CAMARGO MERCADO LTDA</t>
+  </si>
+  <si>
+    <t>FLOR DE LIBANO COM DE PROD ALIM E BEBIDAS EIRELI</t>
+  </si>
+  <si>
+    <t>FNB COMERCIO VAREJISTA DE ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>GENILSON GARCIA DA CUNHA</t>
+  </si>
+  <si>
+    <t>GIOVANNI ZANCO LTDA</t>
+  </si>
+  <si>
+    <t>GLAUCIA CUSTODIO DA SILVA</t>
+  </si>
+  <si>
+    <t>GUMZ COMERCIO E INDUSTRIAL LTDA</t>
+  </si>
+  <si>
+    <t>HOLLYWOOD COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>ILHABEL DISTR DE LIVROS JORNAIS E REV LTDA</t>
+  </si>
+  <si>
+    <t>IRMAOS JC MINIMERCADO E ACOUGUE LTDA</t>
+  </si>
+  <si>
+    <t>IRMAOS MIRANDA LTDA</t>
+  </si>
+  <si>
+    <t>IVANOR DEPLA DE SOUZA ME</t>
+  </si>
+  <si>
+    <t>JAIME HOSTINS EPP</t>
+  </si>
+  <si>
+    <t>JAMAEL JOAQUIM DA SILVA</t>
+  </si>
+  <si>
+    <t>JEF COMERCIO E PODOLOGIA LTDA</t>
+  </si>
+  <si>
+    <t>JOAO VICTOR MIRIN</t>
+  </si>
+  <si>
+    <t>JOSE FRANCISCO OURIQUES PANIFICADORA</t>
+  </si>
+  <si>
+    <t>JULIANO BONA</t>
+  </si>
+  <si>
+    <t>JULIUS CESAR MORETTI</t>
+  </si>
+  <si>
+    <t>JVP COMERCIA EIRELI</t>
+  </si>
+  <si>
+    <t>L.S SUPERMERCADOS LTDA</t>
+  </si>
+  <si>
+    <t>LANCHONETE VIEIRA LTDA</t>
+  </si>
+  <si>
+    <t>LEILA FLAVIA LUCKT GOMES</t>
+  </si>
+  <si>
+    <t>LENISE MELLO QUINTINO</t>
+  </si>
+  <si>
+    <t>LIMPAMIX LTDA</t>
+  </si>
+  <si>
+    <t>LUAN DE FREITAS MATOS</t>
+  </si>
+  <si>
+    <t>LUIZ ANTONIO DOS SANTOS OLIVEIRA</t>
+  </si>
+  <si>
+    <t>M E V MINIMERCADO LTDA</t>
+  </si>
+  <si>
+    <t>MARCILEIA GAMBETA LAURINDO</t>
+  </si>
+  <si>
+    <t>MARCOS ROBERTO DA CRUZ RENKE</t>
+  </si>
+  <si>
+    <t>MARLI TORMENA ME</t>
+  </si>
+  <si>
+    <t>MERCADAO DONEDA LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO 4 MARES LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO AK LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO BORGES NUNES LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO CHIODINI LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO CONQUISTA LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO E ACOUGUE AMF LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO E PANIFICADORA LITORAL</t>
+  </si>
+  <si>
+    <t>MERCADO LITORANEA LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO MARQUES EXPRESS LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO PATRICK LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO SUPER PRATICO LTDA</t>
+  </si>
+  <si>
+    <t>MERCADO SUPERSILVA ACOUGUE E PADARIA EIRELI</t>
+  </si>
+  <si>
+    <t>MERCADO ZANATTA LTDA</t>
+  </si>
+  <si>
+    <t>MERCEARIA JANING EIRELI</t>
+  </si>
+  <si>
+    <t>MERCEARIA POMERODE LTDA</t>
+  </si>
+  <si>
+    <t>MIGUEL MOTA DESCARTAVEIS LTDA</t>
+  </si>
+  <si>
+    <t>MINI MERCADO EMPORIO ECONOMICO LTDA</t>
+  </si>
+  <si>
+    <t>MINI MERCADO GRASEL LTDA</t>
+  </si>
+  <si>
+    <t>MINI MERCADO RCA LTDA</t>
+  </si>
+  <si>
+    <t>MINIMERCADO E UTILIDADES JJD LTDA</t>
+  </si>
+  <si>
+    <t>MINIMERCADO KI MASSA LTDA</t>
+  </si>
+  <si>
+    <t>MINIMERCADO MOHR LTDA</t>
+  </si>
+  <si>
+    <t>MINIMERCADO PANTERA LTDA</t>
+  </si>
+  <si>
+    <t>NATALINO JOSE DA SILVA</t>
+  </si>
+  <si>
+    <t>ORLI VIEIRA</t>
+  </si>
+  <si>
+    <t>PADARIA HEIDEMANN LTDA</t>
+  </si>
+  <si>
+    <t>PANIFICADORA E CONFEITARIA SCHWAAB EIRELI</t>
+  </si>
+  <si>
+    <t>PANIFICADORA E MERCEARIA AOKI LTDA</t>
+  </si>
+  <si>
+    <t>PANIFICADORA SAO ROQUE LTDA</t>
+  </si>
+  <si>
+    <t>PIZZA E BBQ BEACH BAR LTDA</t>
+  </si>
+  <si>
+    <t>PLASLIMP COMERCIO DE EMBALAGENS E MATERIAIS DE LIMPEZA LTDA</t>
+  </si>
+  <si>
+    <t>POLACO HOTEL RESTAURANTE E LANCHONETE LTDA</t>
+  </si>
+  <si>
+    <t>POSTO CIDADE LTDA</t>
+  </si>
+  <si>
+    <t>PP COMERCIO DE COMBUSTIVEIS LTDA</t>
+  </si>
+  <si>
+    <t>RAIMUNDO NONATO RODRIGUES BARRETO LTDA</t>
+  </si>
+  <si>
+    <t>RESTAURANTE PONTO LIGHT LTDA</t>
+  </si>
+  <si>
+    <t>RONCHI E RONCHI LTDA</t>
+  </si>
+  <si>
+    <t>SABRINA L DOS SANTOS MERCEARIA</t>
+  </si>
+  <si>
+    <t>SCHNEIDER E CIA LTDA</t>
+  </si>
+  <si>
+    <t>SIMAO DISTRIBUICAO E COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t>SIRLENE DA SILVA ME</t>
+  </si>
+  <si>
+    <t>SMART RUDNICK LTDA</t>
+  </si>
+  <si>
+    <t>SUELEN CRISTINA MARTTINI</t>
+  </si>
+  <si>
+    <t>SUPER LIDER ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>SUPER MIRA SUPERMERCADO LTDA</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO CAROL LTDA</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO E ACOUGUE BETO PICKLER EIRELI</t>
+  </si>
+  <si>
+    <t>SUPERMERCADO RERMI LTDA</t>
+  </si>
+  <si>
+    <t>THAYNE DE OLIVEIRA MERCADO ME</t>
+  </si>
+  <si>
+    <t>TIELI SUPERMERCADO LTDA</t>
+  </si>
+  <si>
+    <t>TIELI SUPERMERCADO LTDA LJ 02</t>
+  </si>
+  <si>
+    <t>TIELI SUPERMERCADO LTDA LJ 05</t>
+  </si>
+  <si>
+    <t>TIELI SUPERMERCADO LTDA LJ 06</t>
+  </si>
+  <si>
+    <t>TIMONEIRO DIST DE ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>TRADICAO MERCADO E PANIFICADORA LTDA</t>
+  </si>
+  <si>
+    <t>VENANCIO RIBEIRO LTDA</t>
+  </si>
+  <si>
+    <t>TOTAL: 265 linhas</t>
   </si>
 </sst>
 </file>
@@ -4436,27 +4412,6 @@
     <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4467,15 +4422,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4494,6 +4440,36 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="11" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6280,9 +6256,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>963627</xdr:colOff>
+      <xdr:colOff>960452</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>6407</xdr:rowOff>
+      <xdr:rowOff>9582</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6360,9 +6336,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>600517</xdr:colOff>
+      <xdr:colOff>597342</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>125895</xdr:rowOff>
+      <xdr:rowOff>122720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7234,27 +7210,27 @@
         <v>45</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>848</v>
+        <v>916</v>
       </c>
       <c r="K3" s="132">
-        <v>41914.983</v>
+        <v>41919.983</v>
       </c>
       <c r="M3" s="32"/>
       <c r="O3" t="s">
         <v>45</v>
       </c>
       <c r="P3" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="Q3" s="6">
         <v>866.41499999999996</v>
       </c>
       <c r="T3" s="214"/>
       <c r="V3" t="s">
-        <v>1048</v>
+        <v>1040</v>
       </c>
       <c r="W3" s="6">
-        <v>1005.657</v>
+        <v>2065.2959999999998</v>
       </c>
       <c r="X3" s="6"/>
     </row>
@@ -7308,13 +7284,13 @@
       </c>
       <c r="T4" s="214"/>
       <c r="U4">
-        <v>189555</v>
+        <v>190295</v>
       </c>
       <c r="V4" t="s">
-        <v>849</v>
+        <v>917</v>
       </c>
       <c r="W4">
-        <v>0.16700000000000001</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.35">
@@ -7367,13 +7343,13 @@
       </c>
       <c r="T5" s="214"/>
       <c r="U5">
-        <v>67567</v>
+        <v>189555</v>
       </c>
       <c r="V5" t="s">
-        <v>850</v>
+        <v>829</v>
       </c>
       <c r="W5">
-        <v>8.3000000000000004E-2</v>
+        <v>0.16700000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
@@ -7429,7 +7405,7 @@
         <v>187623</v>
       </c>
       <c r="V6" t="s">
-        <v>851</v>
+        <v>830</v>
       </c>
       <c r="W6">
         <v>0.25</v>
@@ -7485,13 +7461,13 @@
       </c>
       <c r="T7" s="214"/>
       <c r="U7">
-        <v>187482</v>
+        <v>73792</v>
       </c>
       <c r="V7" t="s">
-        <v>852</v>
+        <v>918</v>
       </c>
       <c r="W7">
-        <v>0.14599999999999999</v>
+        <v>2.1459999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.35">
@@ -7544,13 +7520,13 @@
       </c>
       <c r="T8" s="214"/>
       <c r="U8">
-        <v>62107</v>
+        <v>191283</v>
       </c>
       <c r="V8" t="s">
-        <v>818</v>
+        <v>831</v>
       </c>
       <c r="W8">
-        <v>0.5</v>
+        <v>0.16700000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.35">
@@ -7603,13 +7579,13 @@
       </c>
       <c r="T9" s="214"/>
       <c r="U9">
-        <v>136970</v>
+        <v>190591</v>
       </c>
       <c r="V9" t="s">
-        <v>853</v>
+        <v>832</v>
       </c>
       <c r="W9">
-        <v>0.75</v>
+        <v>0.95799999999999996</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7662,13 +7638,13 @@
       </c>
       <c r="T10" s="189"/>
       <c r="U10">
-        <v>191283</v>
+        <v>152530</v>
       </c>
       <c r="V10" t="s">
-        <v>854</v>
+        <v>919</v>
       </c>
       <c r="W10">
-        <v>0.16700000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
@@ -7721,13 +7697,13 @@
       </c>
       <c r="T11" s="189"/>
       <c r="U11">
-        <v>126883</v>
+        <v>185456</v>
       </c>
       <c r="V11" t="s">
-        <v>855</v>
+        <v>920</v>
       </c>
       <c r="W11">
-        <v>0.375</v>
+        <v>0.33300000000000002</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.35">
@@ -7780,13 +7756,13 @@
       </c>
       <c r="T12" s="189"/>
       <c r="U12">
-        <v>68379</v>
+        <v>122466</v>
       </c>
       <c r="V12" t="s">
-        <v>856</v>
+        <v>921</v>
       </c>
       <c r="W12">
-        <v>53</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.35">
@@ -7839,13 +7815,13 @@
       </c>
       <c r="T13" s="189"/>
       <c r="U13">
-        <v>190591</v>
+        <v>55369</v>
       </c>
       <c r="V13" t="s">
-        <v>857</v>
+        <v>922</v>
       </c>
       <c r="W13">
-        <v>0.125</v>
+        <v>0.16700000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.35">
@@ -7898,13 +7874,13 @@
       </c>
       <c r="T14" s="189"/>
       <c r="U14">
-        <v>138135</v>
+        <v>52281</v>
       </c>
       <c r="V14" t="s">
-        <v>858</v>
+        <v>923</v>
       </c>
       <c r="W14" s="6">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.35">
@@ -7957,13 +7933,13 @@
       </c>
       <c r="T15" s="189"/>
       <c r="U15">
-        <v>80160</v>
+        <v>47964</v>
       </c>
       <c r="V15" t="s">
-        <v>859</v>
+        <v>833</v>
       </c>
       <c r="W15">
-        <v>1.4379999999999999</v>
+        <v>0.33300000000000002</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.35">
@@ -8016,13 +7992,13 @@
       </c>
       <c r="T16" s="189"/>
       <c r="U16">
-        <v>47964</v>
+        <v>178038</v>
       </c>
       <c r="V16" t="s">
-        <v>860</v>
+        <v>924</v>
       </c>
       <c r="W16">
-        <v>0.33300000000000002</v>
+        <v>0.58299999999999996</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.35">
@@ -8075,13 +8051,13 @@
       </c>
       <c r="T17" s="189"/>
       <c r="U17">
-        <v>49782</v>
+        <v>180985</v>
       </c>
       <c r="V17" t="s">
-        <v>861</v>
+        <v>834</v>
       </c>
       <c r="W17">
-        <v>1.125</v>
+        <v>1.1879999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.35">
@@ -8134,13 +8110,13 @@
       </c>
       <c r="T18" s="189"/>
       <c r="U18">
-        <v>168071</v>
+        <v>184439</v>
       </c>
       <c r="V18" t="s">
-        <v>862</v>
+        <v>835</v>
       </c>
       <c r="W18">
-        <v>0.75</v>
+        <v>0.91700000000000004</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.35">
@@ -8193,13 +8169,13 @@
       </c>
       <c r="T19" s="189"/>
       <c r="U19">
-        <v>180985</v>
+        <v>181304</v>
       </c>
       <c r="V19" t="s">
-        <v>863</v>
+        <v>836</v>
       </c>
       <c r="W19">
-        <v>1.1879999999999999</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.35">
@@ -8252,13 +8228,13 @@
       </c>
       <c r="T20" s="189"/>
       <c r="U20">
-        <v>184439</v>
+        <v>167787</v>
       </c>
       <c r="V20" t="s">
-        <v>864</v>
+        <v>815</v>
       </c>
       <c r="W20">
-        <v>0.91700000000000004</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.35">
@@ -8311,13 +8287,13 @@
       </c>
       <c r="T21" s="189"/>
       <c r="U21">
-        <v>181304</v>
+        <v>172235</v>
       </c>
       <c r="V21" t="s">
-        <v>865</v>
+        <v>925</v>
       </c>
       <c r="W21">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.35">
@@ -8370,13 +8346,13 @@
       </c>
       <c r="T22" s="189"/>
       <c r="U22">
-        <v>177041</v>
+        <v>63784</v>
       </c>
       <c r="V22" t="s">
-        <v>866</v>
+        <v>926</v>
       </c>
       <c r="W22">
-        <v>8.3000000000000004E-2</v>
+        <v>0.22900000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.35">
@@ -8429,10 +8405,10 @@
       </c>
       <c r="T23" s="189"/>
       <c r="U23">
-        <v>167787</v>
+        <v>124845</v>
       </c>
       <c r="V23" t="s">
-        <v>819</v>
+        <v>927</v>
       </c>
       <c r="W23">
         <v>0.5</v>
@@ -8488,13 +8464,13 @@
       </c>
       <c r="T24" s="189"/>
       <c r="U24">
-        <v>75366</v>
+        <v>67806</v>
       </c>
       <c r="V24" t="s">
-        <v>820</v>
+        <v>928</v>
       </c>
       <c r="W24">
-        <v>0.58299999999999996</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.35">
@@ -8547,13 +8523,13 @@
       </c>
       <c r="T25" s="189"/>
       <c r="U25">
-        <v>186290</v>
+        <v>65026</v>
       </c>
       <c r="V25" t="s">
-        <v>812</v>
+        <v>929</v>
       </c>
       <c r="W25">
-        <v>0.33300000000000002</v>
+        <v>1.375</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.35">
@@ -8606,13 +8582,13 @@
       </c>
       <c r="T26" s="189"/>
       <c r="U26">
-        <v>189032</v>
+        <v>183125</v>
       </c>
       <c r="V26" t="s">
-        <v>867</v>
+        <v>930</v>
       </c>
       <c r="W26">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.35">
@@ -8665,13 +8641,13 @@
       </c>
       <c r="T27" s="189"/>
       <c r="U27">
-        <v>79692</v>
+        <v>189032</v>
       </c>
       <c r="V27" t="s">
-        <v>868</v>
+        <v>837</v>
       </c>
       <c r="W27">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.35">
@@ -8724,10 +8700,10 @@
       </c>
       <c r="T28" s="189"/>
       <c r="U28">
-        <v>179875</v>
+        <v>79692</v>
       </c>
       <c r="V28" t="s">
-        <v>821</v>
+        <v>838</v>
       </c>
       <c r="W28">
         <v>6.3E-2</v>
@@ -8783,13 +8759,13 @@
       </c>
       <c r="T29" s="189"/>
       <c r="U29">
-        <v>170636</v>
+        <v>189146</v>
       </c>
       <c r="V29" t="s">
-        <v>869</v>
+        <v>931</v>
       </c>
       <c r="W29">
-        <v>2.2919999999999998</v>
+        <v>0.54200000000000004</v>
       </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.35">
@@ -8842,13 +8818,13 @@
       </c>
       <c r="T30" s="189"/>
       <c r="U30">
-        <v>186388</v>
+        <v>146696</v>
       </c>
       <c r="V30" t="s">
-        <v>870</v>
+        <v>839</v>
       </c>
       <c r="W30">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.35">
@@ -8901,13 +8877,13 @@
       </c>
       <c r="T31" s="189"/>
       <c r="U31">
-        <v>146696</v>
+        <v>172012</v>
       </c>
       <c r="V31" t="s">
-        <v>871</v>
+        <v>932</v>
       </c>
       <c r="W31">
-        <v>0.25</v>
+        <v>8.3000000000000004E-2</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.35">
@@ -8963,7 +8939,7 @@
         <v>167602</v>
       </c>
       <c r="V32" t="s">
-        <v>872</v>
+        <v>840</v>
       </c>
       <c r="W32">
         <v>0.83299999999999996</v>
@@ -9019,13 +8995,13 @@
       </c>
       <c r="T33" s="189"/>
       <c r="U33">
-        <v>138503</v>
+        <v>131520</v>
       </c>
       <c r="V33" t="s">
-        <v>873</v>
+        <v>933</v>
       </c>
       <c r="W33">
-        <v>0.75</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.35">
@@ -9078,13 +9054,13 @@
       </c>
       <c r="T34" s="189"/>
       <c r="U34">
-        <v>175881</v>
+        <v>138503</v>
       </c>
       <c r="V34" t="s">
-        <v>874</v>
+        <v>841</v>
       </c>
       <c r="W34">
-        <v>2</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.35">
@@ -9137,13 +9113,13 @@
       </c>
       <c r="T35" s="189"/>
       <c r="U35">
-        <v>187453</v>
+        <v>175881</v>
       </c>
       <c r="V35" t="s">
-        <v>875</v>
+        <v>842</v>
       </c>
       <c r="W35">
-        <v>1.125</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.35">
@@ -9196,13 +9172,13 @@
       </c>
       <c r="T36" s="189"/>
       <c r="U36">
-        <v>139172</v>
+        <v>189990</v>
       </c>
       <c r="V36" t="s">
-        <v>876</v>
+        <v>934</v>
       </c>
       <c r="W36">
-        <v>1.125</v>
+        <v>0.41699999999999998</v>
       </c>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.35">
@@ -9255,13 +9231,13 @@
       </c>
       <c r="T37" s="189"/>
       <c r="U37">
-        <v>188704</v>
+        <v>189292</v>
       </c>
       <c r="V37" t="s">
-        <v>877</v>
+        <v>935</v>
       </c>
       <c r="W37">
-        <v>1.5</v>
+        <v>0.16700000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.35">
@@ -9314,13 +9290,13 @@
       </c>
       <c r="T38" s="189"/>
       <c r="U38">
-        <v>120313</v>
+        <v>166801</v>
       </c>
       <c r="V38" t="s">
-        <v>878</v>
+        <v>936</v>
       </c>
       <c r="W38">
-        <v>1.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.35">
@@ -9373,13 +9349,13 @@
       </c>
       <c r="T39" s="189"/>
       <c r="U39">
-        <v>56076</v>
+        <v>185793</v>
       </c>
       <c r="V39" t="s">
-        <v>879</v>
+        <v>936</v>
       </c>
       <c r="W39">
-        <v>0.75</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.35">
@@ -9432,13 +9408,13 @@
       </c>
       <c r="T40" s="189"/>
       <c r="U40">
-        <v>58494</v>
+        <v>122099</v>
       </c>
       <c r="V40" t="s">
-        <v>880</v>
+        <v>937</v>
       </c>
       <c r="W40">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.35">
@@ -9491,13 +9467,13 @@
       </c>
       <c r="T41" s="189"/>
       <c r="U41">
-        <v>179828</v>
+        <v>83791</v>
       </c>
       <c r="V41" t="s">
-        <v>881</v>
+        <v>938</v>
       </c>
       <c r="W41">
-        <v>0.25</v>
+        <v>26.562999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.35">
@@ -9550,10 +9526,10 @@
       </c>
       <c r="T42" s="189"/>
       <c r="U42">
-        <v>192271</v>
+        <v>49446</v>
       </c>
       <c r="V42" t="s">
-        <v>822</v>
+        <v>939</v>
       </c>
       <c r="W42">
         <v>0.25</v>
@@ -9609,13 +9585,13 @@
       </c>
       <c r="T43" s="189"/>
       <c r="U43">
-        <v>53564</v>
+        <v>56147</v>
       </c>
       <c r="V43" t="s">
-        <v>823</v>
+        <v>940</v>
       </c>
       <c r="W43">
-        <v>30</v>
+        <v>1.292</v>
       </c>
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.35">
@@ -9668,13 +9644,13 @@
       </c>
       <c r="T44" s="189"/>
       <c r="U44">
-        <v>159244</v>
+        <v>59292</v>
       </c>
       <c r="V44" t="s">
-        <v>824</v>
+        <v>941</v>
       </c>
       <c r="W44" s="6">
-        <v>0.25</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.35">
@@ -9727,13 +9703,13 @@
       </c>
       <c r="T45" s="189"/>
       <c r="U45">
-        <v>175417</v>
+        <v>159240</v>
       </c>
       <c r="V45" t="s">
-        <v>882</v>
+        <v>941</v>
       </c>
       <c r="W45">
-        <v>1.75</v>
+        <v>8.5830000000000002</v>
       </c>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.35">
@@ -9786,13 +9762,13 @@
       </c>
       <c r="T46" s="189"/>
       <c r="U46">
-        <v>136341</v>
+        <v>177623</v>
       </c>
       <c r="V46" t="s">
-        <v>883</v>
+        <v>941</v>
       </c>
       <c r="W46">
-        <v>0.125</v>
+        <v>11.813000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.35">
@@ -9845,13 +9821,13 @@
       </c>
       <c r="T47" s="189"/>
       <c r="U47">
-        <v>190534</v>
+        <v>109503</v>
       </c>
       <c r="V47" t="s">
-        <v>884</v>
+        <v>942</v>
       </c>
       <c r="W47" s="6">
-        <v>1.083</v>
+        <v>0.91700000000000004</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.35">
@@ -9904,13 +9880,13 @@
       </c>
       <c r="T48" s="189"/>
       <c r="U48">
-        <v>190047</v>
+        <v>158073</v>
       </c>
       <c r="V48" t="s">
-        <v>885</v>
+        <v>943</v>
       </c>
       <c r="W48">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.35">
@@ -9963,13 +9939,13 @@
       </c>
       <c r="T49" s="189"/>
       <c r="U49">
-        <v>189740</v>
+        <v>179828</v>
       </c>
       <c r="V49" t="s">
-        <v>886</v>
+        <v>843</v>
       </c>
       <c r="W49">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.35">
@@ -10022,13 +9998,13 @@
       </c>
       <c r="T50" s="189"/>
       <c r="U50">
-        <v>188084</v>
+        <v>59497</v>
       </c>
       <c r="V50" t="s">
-        <v>887</v>
+        <v>944</v>
       </c>
       <c r="W50">
-        <v>0.25</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.35">
@@ -10081,13 +10057,13 @@
       </c>
       <c r="T51" s="189"/>
       <c r="U51">
-        <v>188815</v>
+        <v>53564</v>
       </c>
       <c r="V51" t="s">
-        <v>888</v>
+        <v>816</v>
       </c>
       <c r="W51">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.35">
@@ -10140,13 +10116,13 @@
       </c>
       <c r="T52" s="189"/>
       <c r="U52">
-        <v>158202</v>
+        <v>175417</v>
       </c>
       <c r="V52" t="s">
-        <v>889</v>
+        <v>844</v>
       </c>
       <c r="W52">
-        <v>0.25</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.35">
@@ -10199,13 +10175,13 @@
       </c>
       <c r="T53" s="189"/>
       <c r="U53">
-        <v>157070</v>
+        <v>142638</v>
       </c>
       <c r="V53" t="s">
-        <v>825</v>
+        <v>945</v>
       </c>
       <c r="W53">
-        <v>0.16700000000000001</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="54" spans="1:23" x14ac:dyDescent="0.35">
@@ -10258,13 +10234,13 @@
       </c>
       <c r="T54" s="189"/>
       <c r="U54">
-        <v>180852</v>
+        <v>190534</v>
       </c>
       <c r="V54" t="s">
-        <v>890</v>
+        <v>845</v>
       </c>
       <c r="W54">
-        <v>61</v>
+        <v>1.083</v>
       </c>
     </row>
     <row r="55" spans="1:23" x14ac:dyDescent="0.35">
@@ -10317,13 +10293,13 @@
       </c>
       <c r="T55" s="189"/>
       <c r="U55">
-        <v>178092</v>
+        <v>190047</v>
       </c>
       <c r="V55" t="s">
-        <v>891</v>
+        <v>846</v>
       </c>
       <c r="W55">
-        <v>3</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="56" spans="1:23" x14ac:dyDescent="0.35">
@@ -10376,13 +10352,13 @@
       </c>
       <c r="T56" s="189"/>
       <c r="U56">
-        <v>183965</v>
+        <v>188084</v>
       </c>
       <c r="V56" t="s">
-        <v>892</v>
+        <v>847</v>
       </c>
       <c r="W56">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.35">
@@ -10435,13 +10411,13 @@
       </c>
       <c r="T57" s="189"/>
       <c r="U57">
-        <v>151733</v>
+        <v>188815</v>
       </c>
       <c r="V57" t="s">
-        <v>893</v>
+        <v>848</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:23" x14ac:dyDescent="0.35">
@@ -10494,13 +10470,13 @@
       </c>
       <c r="T58" s="189"/>
       <c r="U58">
-        <v>143434</v>
+        <v>60849</v>
       </c>
       <c r="V58" t="s">
-        <v>826</v>
+        <v>946</v>
       </c>
       <c r="W58">
-        <v>15.167</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.35">
@@ -10553,13 +10529,13 @@
       </c>
       <c r="T59" s="189"/>
       <c r="U59">
-        <v>189970</v>
+        <v>167819</v>
       </c>
       <c r="V59" t="s">
-        <v>894</v>
+        <v>849</v>
       </c>
       <c r="W59">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.35">
@@ -10612,13 +10588,13 @@
       </c>
       <c r="T60" s="189"/>
       <c r="U60">
-        <v>92167</v>
+        <v>157070</v>
       </c>
       <c r="V60" t="s">
-        <v>895</v>
+        <v>817</v>
       </c>
       <c r="W60">
-        <v>5.7</v>
+        <v>0.16700000000000001</v>
       </c>
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.35">
@@ -10671,13 +10647,13 @@
       </c>
       <c r="T61" s="189"/>
       <c r="U61">
-        <v>184521</v>
+        <v>187730</v>
       </c>
       <c r="V61" t="s">
-        <v>896</v>
+        <v>947</v>
       </c>
       <c r="W61">
-        <v>0.16700000000000001</v>
+        <v>8.3000000000000004E-2</v>
       </c>
     </row>
     <row r="62" spans="1:23" x14ac:dyDescent="0.35">
@@ -10730,13 +10706,13 @@
       </c>
       <c r="T62" s="189"/>
       <c r="U62">
-        <v>182461</v>
+        <v>180852</v>
       </c>
       <c r="V62" t="s">
-        <v>827</v>
+        <v>850</v>
       </c>
       <c r="W62">
-        <v>1.7000000000000001E-2</v>
+        <v>61</v>
       </c>
     </row>
     <row r="63" spans="1:23" x14ac:dyDescent="0.35">
@@ -10789,13 +10765,13 @@
       </c>
       <c r="T63" s="189"/>
       <c r="U63">
-        <v>190466</v>
+        <v>183965</v>
       </c>
       <c r="V63" t="s">
-        <v>897</v>
+        <v>851</v>
       </c>
       <c r="W63">
-        <v>0.20799999999999999</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="64" spans="1:23" x14ac:dyDescent="0.35">
@@ -10848,13 +10824,13 @@
       </c>
       <c r="T64" s="189"/>
       <c r="U64">
-        <v>190475</v>
+        <v>151733</v>
       </c>
       <c r="V64" t="s">
-        <v>898</v>
+        <v>852</v>
       </c>
       <c r="W64">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.35">
@@ -10907,13 +10883,13 @@
       </c>
       <c r="T65" s="189"/>
       <c r="U65">
-        <v>89810</v>
+        <v>73764</v>
       </c>
       <c r="V65" t="s">
-        <v>899</v>
+        <v>948</v>
       </c>
       <c r="W65">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:23" x14ac:dyDescent="0.35">
@@ -10966,13 +10942,13 @@
       </c>
       <c r="T66" s="189"/>
       <c r="U66">
-        <v>165588</v>
+        <v>189970</v>
       </c>
       <c r="V66" t="s">
-        <v>900</v>
+        <v>853</v>
       </c>
       <c r="W66">
-        <v>1.833</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.35">
@@ -11025,13 +11001,13 @@
       </c>
       <c r="T67" s="189"/>
       <c r="U67">
-        <v>185771</v>
+        <v>191591</v>
       </c>
       <c r="V67" t="s">
-        <v>901</v>
+        <v>949</v>
       </c>
       <c r="W67">
-        <v>11.333</v>
+        <v>0.33300000000000002</v>
       </c>
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.35">
@@ -11084,13 +11060,13 @@
       </c>
       <c r="T68" s="189"/>
       <c r="U68">
-        <v>190772</v>
+        <v>185210</v>
       </c>
       <c r="V68" t="s">
-        <v>902</v>
+        <v>950</v>
       </c>
       <c r="W68" s="6">
-        <v>0.25</v>
+        <v>0.83299999999999996</v>
       </c>
     </row>
     <row r="69" spans="1:23" x14ac:dyDescent="0.35">
@@ -11143,13 +11119,13 @@
       </c>
       <c r="T69" s="189"/>
       <c r="U69">
-        <v>173903</v>
+        <v>175210</v>
       </c>
       <c r="V69" t="s">
-        <v>903</v>
+        <v>951</v>
       </c>
       <c r="W69">
-        <v>0.5</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.35">
@@ -11202,13 +11178,13 @@
       </c>
       <c r="T70" s="189"/>
       <c r="U70">
-        <v>178900</v>
+        <v>161168</v>
       </c>
       <c r="V70" t="s">
-        <v>904</v>
+        <v>952</v>
       </c>
       <c r="W70">
-        <v>1.208</v>
+        <v>0.33300000000000002</v>
       </c>
     </row>
     <row r="71" spans="1:23" x14ac:dyDescent="0.35">
@@ -11261,13 +11237,13 @@
       </c>
       <c r="T71" s="189"/>
       <c r="U71">
-        <v>188509</v>
+        <v>185771</v>
       </c>
       <c r="V71" t="s">
-        <v>905</v>
+        <v>854</v>
       </c>
       <c r="W71">
-        <v>0.5</v>
+        <v>11.333</v>
       </c>
     </row>
     <row r="72" spans="1:23" x14ac:dyDescent="0.35">
@@ -11320,13 +11296,13 @@
       </c>
       <c r="T72" s="189"/>
       <c r="U72">
-        <v>116852</v>
+        <v>90026</v>
       </c>
       <c r="V72" t="s">
-        <v>906</v>
+        <v>953</v>
       </c>
       <c r="W72">
-        <v>6</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="73" spans="1:23" x14ac:dyDescent="0.35">
@@ -11379,13 +11355,13 @@
       </c>
       <c r="T73" s="189"/>
       <c r="U73">
-        <v>188820</v>
+        <v>183483</v>
       </c>
       <c r="V73" t="s">
-        <v>828</v>
+        <v>954</v>
       </c>
       <c r="W73">
-        <v>7.375</v>
+        <v>0.45800000000000002</v>
       </c>
     </row>
     <row r="74" spans="1:23" x14ac:dyDescent="0.35">
@@ -11438,13 +11414,13 @@
       </c>
       <c r="T74" s="189"/>
       <c r="U74">
-        <v>65246</v>
+        <v>173903</v>
       </c>
       <c r="V74" t="s">
-        <v>907</v>
+        <v>855</v>
       </c>
       <c r="W74">
-        <v>0.33300000000000002</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="75" spans="1:23" x14ac:dyDescent="0.35">
@@ -11497,13 +11473,13 @@
       </c>
       <c r="T75" s="189"/>
       <c r="U75">
-        <v>150369</v>
+        <v>134789</v>
       </c>
       <c r="V75" t="s">
-        <v>908</v>
+        <v>955</v>
       </c>
       <c r="W75">
-        <v>3.3330000000000002</v>
+        <v>1.625</v>
       </c>
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.35">
@@ -11556,13 +11532,13 @@
       </c>
       <c r="T76" s="189"/>
       <c r="U76">
-        <v>182198</v>
+        <v>178900</v>
       </c>
       <c r="V76" t="s">
-        <v>909</v>
+        <v>856</v>
       </c>
       <c r="W76" s="6">
-        <v>0.125</v>
+        <v>1.208</v>
       </c>
     </row>
     <row r="77" spans="1:23" x14ac:dyDescent="0.35">
@@ -11615,10 +11591,10 @@
       </c>
       <c r="T77" s="189"/>
       <c r="U77">
-        <v>148247</v>
+        <v>192352</v>
       </c>
       <c r="V77" t="s">
-        <v>910</v>
+        <v>956</v>
       </c>
       <c r="W77">
         <v>0.5</v>
@@ -11674,13 +11650,13 @@
       </c>
       <c r="T78" s="189"/>
       <c r="U78">
-        <v>57381</v>
+        <v>188509</v>
       </c>
       <c r="V78" t="s">
-        <v>911</v>
+        <v>857</v>
       </c>
       <c r="W78">
-        <v>0.33300000000000002</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="79" spans="1:23" x14ac:dyDescent="0.35">
@@ -11733,10 +11709,10 @@
       </c>
       <c r="T79" s="189"/>
       <c r="U79">
-        <v>144994</v>
+        <v>178837</v>
       </c>
       <c r="V79" t="s">
-        <v>912</v>
+        <v>957</v>
       </c>
       <c r="W79">
         <v>0.25</v>
@@ -11792,13 +11768,13 @@
       </c>
       <c r="T80" s="189"/>
       <c r="U80">
-        <v>181571</v>
+        <v>116852</v>
       </c>
       <c r="V80" t="s">
-        <v>829</v>
+        <v>858</v>
       </c>
       <c r="W80">
-        <v>1.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:23" x14ac:dyDescent="0.35">
@@ -11851,13 +11827,13 @@
       </c>
       <c r="T81" s="189"/>
       <c r="U81">
-        <v>184543</v>
+        <v>165045</v>
       </c>
       <c r="V81" t="s">
-        <v>913</v>
+        <v>274</v>
       </c>
       <c r="W81">
-        <v>0.875</v>
+        <v>906</v>
       </c>
     </row>
     <row r="82" spans="1:23" x14ac:dyDescent="0.35">
@@ -11910,13 +11886,13 @@
       </c>
       <c r="T82" s="189"/>
       <c r="U82">
-        <v>178813</v>
+        <v>66218</v>
       </c>
       <c r="V82" t="s">
-        <v>914</v>
+        <v>958</v>
       </c>
       <c r="W82">
-        <v>0.33300000000000002</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="83" spans="1:23" x14ac:dyDescent="0.35">
@@ -11969,13 +11945,13 @@
       </c>
       <c r="T83" s="189"/>
       <c r="U83">
-        <v>186529</v>
+        <v>186251</v>
       </c>
       <c r="V83" t="s">
-        <v>915</v>
+        <v>959</v>
       </c>
       <c r="W83">
-        <v>0.5</v>
+        <v>0.33300000000000002</v>
       </c>
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.35">
@@ -12028,13 +12004,13 @@
       </c>
       <c r="T84" s="189"/>
       <c r="U84">
-        <v>177191</v>
+        <v>150369</v>
       </c>
       <c r="V84" t="s">
-        <v>916</v>
+        <v>859</v>
       </c>
       <c r="W84">
-        <v>0.438</v>
+        <v>3.3330000000000002</v>
       </c>
     </row>
     <row r="85" spans="1:23" x14ac:dyDescent="0.35">
@@ -12087,13 +12063,13 @@
       </c>
       <c r="T85" s="189"/>
       <c r="U85">
-        <v>117336</v>
+        <v>118790</v>
       </c>
       <c r="V85" t="s">
-        <v>917</v>
+        <v>960</v>
       </c>
       <c r="W85">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="86" spans="1:23" x14ac:dyDescent="0.35">
@@ -12146,13 +12122,13 @@
       </c>
       <c r="T86" s="189"/>
       <c r="U86">
-        <v>185514</v>
+        <v>87492</v>
       </c>
       <c r="V86" t="s">
-        <v>830</v>
+        <v>961</v>
       </c>
       <c r="W86" s="6">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.35">
@@ -12205,13 +12181,13 @@
       </c>
       <c r="T87" s="189"/>
       <c r="U87">
-        <v>174189</v>
+        <v>53137</v>
       </c>
       <c r="V87" t="s">
-        <v>918</v>
+        <v>962</v>
       </c>
       <c r="W87">
-        <v>0.16700000000000001</v>
+        <v>1.583</v>
       </c>
     </row>
     <row r="88" spans="1:23" x14ac:dyDescent="0.35">
@@ -12264,13 +12240,13 @@
       </c>
       <c r="T88" s="189"/>
       <c r="U88">
-        <v>165506</v>
+        <v>134914</v>
       </c>
       <c r="V88" t="s">
-        <v>919</v>
+        <v>963</v>
       </c>
       <c r="W88">
-        <v>2.0830000000000002</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="89" spans="1:23" x14ac:dyDescent="0.35">
@@ -12323,13 +12299,13 @@
       </c>
       <c r="T89" s="189"/>
       <c r="U89">
-        <v>153350</v>
+        <v>49631</v>
       </c>
       <c r="V89" t="s">
-        <v>920</v>
+        <v>964</v>
       </c>
       <c r="W89">
-        <v>0.25</v>
+        <v>1.167</v>
       </c>
     </row>
     <row r="90" spans="1:23" x14ac:dyDescent="0.35">
@@ -12382,13 +12358,13 @@
       </c>
       <c r="T90" s="189"/>
       <c r="U90">
-        <v>183462</v>
+        <v>182062</v>
       </c>
       <c r="V90" t="s">
-        <v>921</v>
+        <v>965</v>
       </c>
       <c r="W90">
-        <v>0.75</v>
+        <v>8.3000000000000004E-2</v>
       </c>
     </row>
     <row r="91" spans="1:23" x14ac:dyDescent="0.35">
@@ -12441,13 +12417,13 @@
       </c>
       <c r="T91" s="189"/>
       <c r="U91">
-        <v>117583</v>
+        <v>178813</v>
       </c>
       <c r="V91" t="s">
-        <v>922</v>
+        <v>860</v>
       </c>
       <c r="W91">
-        <v>0.375</v>
+        <v>0.33300000000000002</v>
       </c>
     </row>
     <row r="92" spans="1:23" x14ac:dyDescent="0.35">
@@ -12500,13 +12476,13 @@
       </c>
       <c r="T92" s="189"/>
       <c r="U92">
-        <v>90831</v>
+        <v>189642</v>
       </c>
       <c r="V92" t="s">
-        <v>923</v>
+        <v>966</v>
       </c>
       <c r="W92">
-        <v>0.25</v>
+        <v>0.33300000000000002</v>
       </c>
     </row>
     <row r="93" spans="1:23" x14ac:dyDescent="0.35">
@@ -12559,13 +12535,13 @@
       </c>
       <c r="T93" s="189"/>
       <c r="U93">
-        <v>110150</v>
+        <v>177191</v>
       </c>
       <c r="V93" t="s">
-        <v>924</v>
+        <v>861</v>
       </c>
       <c r="W93">
-        <v>1</v>
+        <v>0.438</v>
       </c>
     </row>
     <row r="94" spans="1:23" x14ac:dyDescent="0.35">
@@ -12618,13 +12594,13 @@
       </c>
       <c r="T94" s="189"/>
       <c r="U94">
-        <v>191412</v>
+        <v>185514</v>
       </c>
       <c r="V94" t="s">
-        <v>925</v>
+        <v>818</v>
       </c>
       <c r="W94">
-        <v>8.3000000000000004E-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:23" x14ac:dyDescent="0.35">
@@ -12677,13 +12653,13 @@
       </c>
       <c r="T95" s="189"/>
       <c r="U95">
-        <v>175516</v>
+        <v>185520</v>
       </c>
       <c r="V95" t="s">
-        <v>926</v>
+        <v>967</v>
       </c>
       <c r="W95">
-        <v>7</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="96" spans="1:23" x14ac:dyDescent="0.35">
@@ -12736,13 +12712,13 @@
       </c>
       <c r="T96" s="189"/>
       <c r="U96">
-        <v>52334</v>
+        <v>130727</v>
       </c>
       <c r="V96" t="s">
-        <v>927</v>
+        <v>968</v>
       </c>
       <c r="W96">
-        <v>1</v>
+        <v>0.68799999999999994</v>
       </c>
     </row>
     <row r="97" spans="1:23" x14ac:dyDescent="0.35">
@@ -12795,13 +12771,13 @@
       </c>
       <c r="T97" s="189"/>
       <c r="U97">
-        <v>175703</v>
+        <v>110150</v>
       </c>
       <c r="V97" t="s">
-        <v>928</v>
+        <v>862</v>
       </c>
       <c r="W97">
-        <v>1.167</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:23" x14ac:dyDescent="0.35">
@@ -12854,13 +12830,13 @@
       </c>
       <c r="T98" s="189"/>
       <c r="U98">
-        <v>185310</v>
+        <v>175516</v>
       </c>
       <c r="V98" t="s">
-        <v>831</v>
+        <v>863</v>
       </c>
       <c r="W98">
-        <v>8.3000000000000004E-2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99" spans="1:23" x14ac:dyDescent="0.35">
@@ -12913,13 +12889,13 @@
       </c>
       <c r="T99" s="189"/>
       <c r="U99">
-        <v>171479</v>
+        <v>171803</v>
       </c>
       <c r="V99" t="s">
-        <v>929</v>
+        <v>969</v>
       </c>
       <c r="W99">
-        <v>0.875</v>
+        <v>0.33300000000000002</v>
       </c>
     </row>
     <row r="100" spans="1:23" x14ac:dyDescent="0.35">
@@ -12972,13 +12948,13 @@
       </c>
       <c r="T100" s="189"/>
       <c r="U100">
-        <v>191572</v>
+        <v>176085</v>
       </c>
       <c r="V100" t="s">
-        <v>813</v>
+        <v>969</v>
       </c>
       <c r="W100">
-        <v>0.25</v>
+        <v>3.3330000000000002</v>
       </c>
     </row>
     <row r="101" spans="1:23" x14ac:dyDescent="0.35">
@@ -13031,13 +13007,13 @@
       </c>
       <c r="T101" s="189"/>
       <c r="U101">
-        <v>191986</v>
+        <v>182505</v>
       </c>
       <c r="V101" t="s">
-        <v>930</v>
+        <v>969</v>
       </c>
       <c r="W101">
-        <v>0.5</v>
+        <v>7.2830000000000004</v>
       </c>
     </row>
     <row r="102" spans="1:23" x14ac:dyDescent="0.35">
@@ -13090,13 +13066,13 @@
       </c>
       <c r="T102" s="189"/>
       <c r="U102">
-        <v>187381</v>
+        <v>184783</v>
       </c>
       <c r="V102" t="s">
-        <v>931</v>
+        <v>969</v>
       </c>
       <c r="W102">
-        <v>0.16700000000000001</v>
+        <v>6.867</v>
       </c>
     </row>
     <row r="103" spans="1:23" x14ac:dyDescent="0.35">
@@ -13149,13 +13125,13 @@
       </c>
       <c r="T103" s="189"/>
       <c r="U103">
-        <v>188800</v>
+        <v>183551</v>
       </c>
       <c r="V103" t="s">
-        <v>932</v>
+        <v>970</v>
       </c>
       <c r="W103" s="6">
-        <v>6.3E-2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="104" spans="1:23" x14ac:dyDescent="0.35">
@@ -13208,13 +13184,13 @@
       </c>
       <c r="T104" s="189"/>
       <c r="U104">
-        <v>187617</v>
+        <v>175490</v>
       </c>
       <c r="V104" t="s">
-        <v>933</v>
+        <v>971</v>
       </c>
       <c r="W104">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105" spans="1:23" x14ac:dyDescent="0.35">
@@ -13267,13 +13243,13 @@
       </c>
       <c r="T105" s="189"/>
       <c r="U105">
-        <v>127780</v>
+        <v>185310</v>
       </c>
       <c r="V105" t="s">
-        <v>934</v>
+        <v>819</v>
       </c>
       <c r="W105">
-        <v>0.16700000000000001</v>
+        <v>8.3000000000000004E-2</v>
       </c>
     </row>
     <row r="106" spans="1:23" x14ac:dyDescent="0.35">
@@ -13326,13 +13302,13 @@
       </c>
       <c r="T106" s="189"/>
       <c r="U106">
-        <v>178403</v>
+        <v>187018</v>
       </c>
       <c r="V106" t="s">
-        <v>935</v>
+        <v>972</v>
       </c>
       <c r="W106">
-        <v>21</v>
+        <v>1.1879999999999999</v>
       </c>
     </row>
     <row r="107" spans="1:23" x14ac:dyDescent="0.35">
@@ -13385,13 +13361,13 @@
       </c>
       <c r="T107" s="189"/>
       <c r="U107">
-        <v>126070</v>
+        <v>187019</v>
       </c>
       <c r="V107" t="s">
-        <v>832</v>
+        <v>972</v>
       </c>
       <c r="W107">
-        <v>6</v>
+        <v>1.4379999999999999</v>
       </c>
     </row>
     <row r="108" spans="1:23" x14ac:dyDescent="0.35">
@@ -13444,13 +13420,13 @@
       </c>
       <c r="T108" s="189"/>
       <c r="U108">
-        <v>175491</v>
+        <v>187022</v>
       </c>
       <c r="V108" t="s">
-        <v>936</v>
+        <v>972</v>
       </c>
       <c r="W108">
-        <v>0.625</v>
+        <v>1.1879999999999999</v>
       </c>
     </row>
     <row r="109" spans="1:23" x14ac:dyDescent="0.35">
@@ -13503,13 +13479,13 @@
       </c>
       <c r="T109" s="189"/>
       <c r="U109">
-        <v>183865</v>
+        <v>60654</v>
       </c>
       <c r="V109" t="s">
-        <v>937</v>
+        <v>973</v>
       </c>
       <c r="W109">
-        <v>0.5</v>
+        <v>8.3000000000000004E-2</v>
       </c>
     </row>
     <row r="110" spans="1:23" x14ac:dyDescent="0.35">
@@ -13562,13 +13538,13 @@
       </c>
       <c r="T110" s="189"/>
       <c r="U110">
-        <v>111892</v>
+        <v>171477</v>
       </c>
       <c r="V110" t="s">
-        <v>938</v>
+        <v>974</v>
       </c>
       <c r="W110" s="6">
-        <v>0.16700000000000001</v>
+        <v>0.39600000000000002</v>
       </c>
     </row>
     <row r="111" spans="1:23" x14ac:dyDescent="0.35">
@@ -13621,13 +13597,13 @@
       </c>
       <c r="T111" s="189"/>
       <c r="U111">
-        <v>183586</v>
+        <v>180373</v>
       </c>
       <c r="V111" t="s">
-        <v>939</v>
+        <v>975</v>
       </c>
       <c r="W111">
-        <v>0.33300000000000002</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="112" spans="1:23" x14ac:dyDescent="0.35">
@@ -13680,13 +13656,13 @@
       </c>
       <c r="T112" s="189"/>
       <c r="U112">
-        <v>191864</v>
+        <v>180762</v>
       </c>
       <c r="V112" t="s">
-        <v>940</v>
+        <v>976</v>
       </c>
       <c r="W112">
-        <v>0.58299999999999996</v>
+        <v>1.708</v>
       </c>
     </row>
     <row r="113" spans="1:23" x14ac:dyDescent="0.35">
@@ -13739,13 +13715,13 @@
       </c>
       <c r="T113" s="189"/>
       <c r="U113">
-        <v>186123</v>
+        <v>187617</v>
       </c>
       <c r="V113" t="s">
-        <v>941</v>
+        <v>864</v>
       </c>
       <c r="W113">
-        <v>0.33300000000000002</v>
+        <v>13</v>
       </c>
     </row>
     <row r="114" spans="1:23" x14ac:dyDescent="0.35">
@@ -13798,13 +13774,13 @@
       </c>
       <c r="T114" s="189"/>
       <c r="U114">
-        <v>47832</v>
+        <v>127780</v>
       </c>
       <c r="V114" t="s">
-        <v>942</v>
+        <v>865</v>
       </c>
       <c r="W114">
-        <v>1.042</v>
+        <v>0.16700000000000001</v>
       </c>
     </row>
     <row r="115" spans="1:23" x14ac:dyDescent="0.35">
@@ -13857,13 +13833,13 @@
       </c>
       <c r="T115" s="189"/>
       <c r="U115">
-        <v>56411</v>
+        <v>184478</v>
       </c>
       <c r="V115" t="s">
-        <v>943</v>
+        <v>977</v>
       </c>
       <c r="W115">
-        <v>0.875</v>
+        <v>0.91700000000000004</v>
       </c>
     </row>
     <row r="116" spans="1:23" x14ac:dyDescent="0.35">
@@ -13916,13 +13892,13 @@
       </c>
       <c r="T116" s="189"/>
       <c r="U116">
-        <v>186304</v>
+        <v>183586</v>
       </c>
       <c r="V116" t="s">
-        <v>944</v>
+        <v>866</v>
       </c>
       <c r="W116">
-        <v>0.5</v>
+        <v>0.33300000000000002</v>
       </c>
     </row>
     <row r="117" spans="1:23" x14ac:dyDescent="0.35">
@@ -13959,13 +13935,13 @@
       </c>
       <c r="T117" s="189"/>
       <c r="U117">
-        <v>179564</v>
+        <v>170644</v>
       </c>
       <c r="V117" t="s">
-        <v>945</v>
+        <v>978</v>
       </c>
       <c r="W117">
-        <v>0.125</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="118" spans="1:23" x14ac:dyDescent="0.35">
@@ -14002,13 +13978,13 @@
       </c>
       <c r="T118" s="189"/>
       <c r="U118">
-        <v>168379</v>
+        <v>190386</v>
       </c>
       <c r="V118" t="s">
-        <v>946</v>
+        <v>979</v>
       </c>
       <c r="W118">
-        <v>0.875</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="119" spans="1:23" x14ac:dyDescent="0.35">
@@ -14045,13 +14021,13 @@
       </c>
       <c r="T119" s="189"/>
       <c r="U119">
-        <v>58781</v>
+        <v>134677</v>
       </c>
       <c r="V119" t="s">
-        <v>947</v>
+        <v>150</v>
       </c>
       <c r="W119">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="120" spans="1:23" x14ac:dyDescent="0.35">
@@ -14088,13 +14064,13 @@
       </c>
       <c r="T120" s="189"/>
       <c r="U120">
-        <v>171581</v>
+        <v>191864</v>
       </c>
       <c r="V120" t="s">
-        <v>948</v>
+        <v>867</v>
       </c>
       <c r="W120">
-        <v>2</v>
+        <v>0.58299999999999996</v>
       </c>
     </row>
     <row r="121" spans="1:23" x14ac:dyDescent="0.35">
@@ -14131,13 +14107,13 @@
       </c>
       <c r="T121" s="189"/>
       <c r="U121">
-        <v>179244</v>
+        <v>150803</v>
       </c>
       <c r="V121" t="s">
-        <v>833</v>
+        <v>980</v>
       </c>
       <c r="W121">
-        <v>0.29199999999999998</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="122" spans="1:23" x14ac:dyDescent="0.35">
@@ -14174,13 +14150,13 @@
       </c>
       <c r="T122" s="189"/>
       <c r="U122">
-        <v>49712</v>
+        <v>56411</v>
       </c>
       <c r="V122" t="s">
-        <v>949</v>
+        <v>868</v>
       </c>
       <c r="W122">
-        <v>1.8129999999999999</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="123" spans="1:23" x14ac:dyDescent="0.35">
@@ -14217,13 +14193,13 @@
       </c>
       <c r="T123" s="189"/>
       <c r="U123">
-        <v>170658</v>
+        <v>190011</v>
       </c>
       <c r="V123" t="s">
-        <v>950</v>
+        <v>981</v>
       </c>
       <c r="W123">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="124" spans="1:23" x14ac:dyDescent="0.35">
@@ -14260,13 +14236,13 @@
       </c>
       <c r="T124" s="189"/>
       <c r="U124">
-        <v>181368</v>
+        <v>179564</v>
       </c>
       <c r="V124" t="s">
-        <v>951</v>
+        <v>869</v>
       </c>
       <c r="W124">
-        <v>1.1040000000000001</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="125" spans="1:23" x14ac:dyDescent="0.35">
@@ -14303,13 +14279,13 @@
       </c>
       <c r="T125" s="189"/>
       <c r="U125">
-        <v>188404</v>
+        <v>98508</v>
       </c>
       <c r="V125" t="s">
-        <v>952</v>
+        <v>982</v>
       </c>
       <c r="W125">
-        <v>0.16700000000000001</v>
+        <v>0.313</v>
       </c>
     </row>
     <row r="126" spans="1:23" x14ac:dyDescent="0.35">
@@ -14346,13 +14322,13 @@
       </c>
       <c r="T126" s="189"/>
       <c r="U126">
-        <v>109724</v>
+        <v>168379</v>
       </c>
       <c r="V126" t="s">
-        <v>953</v>
+        <v>870</v>
       </c>
       <c r="W126">
-        <v>0.25</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="127" spans="1:23" x14ac:dyDescent="0.35">
@@ -14389,13 +14365,13 @@
       </c>
       <c r="T127" s="189"/>
       <c r="U127">
-        <v>148927</v>
+        <v>50544</v>
       </c>
       <c r="V127" t="s">
-        <v>954</v>
+        <v>983</v>
       </c>
       <c r="W127">
-        <v>1.25</v>
+        <v>3.9169999999999998</v>
       </c>
     </row>
     <row r="128" spans="1:23" x14ac:dyDescent="0.35">
@@ -14432,13 +14408,13 @@
       </c>
       <c r="T128" s="189"/>
       <c r="U128">
-        <v>168638</v>
+        <v>58781</v>
       </c>
       <c r="V128" t="s">
-        <v>834</v>
+        <v>871</v>
       </c>
       <c r="W128">
-        <v>0.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="129" spans="1:23" x14ac:dyDescent="0.35">
@@ -14475,13 +14451,13 @@
       </c>
       <c r="T129" s="189"/>
       <c r="U129">
-        <v>183806</v>
+        <v>127597</v>
       </c>
       <c r="V129" t="s">
-        <v>955</v>
+        <v>984</v>
       </c>
       <c r="W129">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="130" spans="1:23" x14ac:dyDescent="0.35">
@@ -14518,13 +14494,13 @@
       </c>
       <c r="T130" s="189"/>
       <c r="U130">
-        <v>185037</v>
+        <v>154330</v>
       </c>
       <c r="V130" t="s">
-        <v>956</v>
+        <v>985</v>
       </c>
       <c r="W130">
-        <v>0.45800000000000002</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="131" spans="1:23" x14ac:dyDescent="0.35">
@@ -14561,13 +14537,13 @@
       </c>
       <c r="T131" s="189"/>
       <c r="U131">
-        <v>181655</v>
+        <v>110132</v>
       </c>
       <c r="V131" t="s">
-        <v>957</v>
+        <v>986</v>
       </c>
       <c r="W131">
-        <v>0.5</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="132" spans="1:23" x14ac:dyDescent="0.35">
@@ -14604,13 +14580,13 @@
       </c>
       <c r="T132" s="189"/>
       <c r="U132">
-        <v>180396</v>
+        <v>171581</v>
       </c>
       <c r="V132" t="s">
-        <v>958</v>
+        <v>872</v>
       </c>
       <c r="W132">
-        <v>0.75</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133" spans="1:23" x14ac:dyDescent="0.35">
@@ -14647,13 +14623,13 @@
       </c>
       <c r="T133" s="189"/>
       <c r="U133">
-        <v>190320</v>
+        <v>179244</v>
       </c>
       <c r="V133" t="s">
-        <v>835</v>
+        <v>820</v>
       </c>
       <c r="W133">
-        <v>2</v>
+        <v>0.29199999999999998</v>
       </c>
     </row>
     <row r="134" spans="1:23" x14ac:dyDescent="0.35">
@@ -14690,13 +14666,13 @@
       </c>
       <c r="T134" s="189"/>
       <c r="U134">
-        <v>190326</v>
+        <v>170658</v>
       </c>
       <c r="V134" t="s">
-        <v>835</v>
+        <v>873</v>
       </c>
       <c r="W134">
-        <v>0.91700000000000004</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="135" spans="1:23" x14ac:dyDescent="0.35">
@@ -14733,13 +14709,13 @@
       </c>
       <c r="T135" s="189"/>
       <c r="U135">
-        <v>179748</v>
+        <v>181368</v>
       </c>
       <c r="V135" t="s">
-        <v>959</v>
+        <v>874</v>
       </c>
       <c r="W135">
-        <v>0.25</v>
+        <v>1.1040000000000001</v>
       </c>
     </row>
     <row r="136" spans="1:23" x14ac:dyDescent="0.35">
@@ -14776,13 +14752,13 @@
       </c>
       <c r="T136" s="189"/>
       <c r="U136">
-        <v>185361</v>
+        <v>122250</v>
       </c>
       <c r="V136" t="s">
-        <v>960</v>
+        <v>987</v>
       </c>
       <c r="W136">
-        <v>2.6459999999999999</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="137" spans="1:23" x14ac:dyDescent="0.35">
@@ -14819,13 +14795,13 @@
       </c>
       <c r="T137" s="189"/>
       <c r="U137">
-        <v>67814</v>
+        <v>184327</v>
       </c>
       <c r="V137" t="s">
-        <v>836</v>
+        <v>988</v>
       </c>
       <c r="W137">
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="138" spans="1:23" x14ac:dyDescent="0.35">
@@ -14862,13 +14838,13 @@
       </c>
       <c r="T138" s="189"/>
       <c r="U138">
-        <v>186031</v>
+        <v>168638</v>
       </c>
       <c r="V138" t="s">
-        <v>961</v>
+        <v>821</v>
       </c>
       <c r="W138">
-        <v>0.33300000000000002</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="139" spans="1:23" x14ac:dyDescent="0.35">
@@ -14905,13 +14881,13 @@
       </c>
       <c r="T139" s="189"/>
       <c r="U139">
-        <v>170598</v>
+        <v>183806</v>
       </c>
       <c r="V139" t="s">
-        <v>962</v>
+        <v>875</v>
       </c>
       <c r="W139">
-        <v>3.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="140" spans="1:23" x14ac:dyDescent="0.35">
@@ -14948,13 +14924,13 @@
       </c>
       <c r="T140" s="189"/>
       <c r="U140">
-        <v>156243</v>
+        <v>185534</v>
       </c>
       <c r="V140" t="s">
-        <v>963</v>
+        <v>989</v>
       </c>
       <c r="W140">
-        <v>0.25</v>
+        <v>0.95799999999999996</v>
       </c>
     </row>
     <row r="141" spans="1:23" x14ac:dyDescent="0.35">
@@ -14991,13 +14967,13 @@
       </c>
       <c r="T141" s="189"/>
       <c r="U141">
-        <v>175598</v>
+        <v>185361</v>
       </c>
       <c r="V141" t="s">
-        <v>964</v>
+        <v>876</v>
       </c>
       <c r="W141">
-        <v>4.6669999999999998</v>
+        <v>2.6459999999999999</v>
       </c>
     </row>
     <row r="142" spans="1:23" x14ac:dyDescent="0.35">
@@ -15034,13 +15010,13 @@
       </c>
       <c r="T142" s="189"/>
       <c r="U142">
-        <v>179379</v>
+        <v>140144</v>
       </c>
       <c r="V142" t="s">
-        <v>964</v>
+        <v>990</v>
       </c>
       <c r="W142">
-        <v>3.3330000000000002</v>
+        <v>6.617</v>
       </c>
     </row>
     <row r="143" spans="1:23" x14ac:dyDescent="0.35">
@@ -15077,13 +15053,13 @@
       </c>
       <c r="T143" s="189"/>
       <c r="U143">
-        <v>170218</v>
+        <v>170081</v>
       </c>
       <c r="V143" t="s">
-        <v>965</v>
+        <v>991</v>
       </c>
       <c r="W143">
-        <v>0.25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="144" spans="1:23" x14ac:dyDescent="0.35">
@@ -15120,13 +15096,13 @@
       </c>
       <c r="T144" s="189"/>
       <c r="U144">
-        <v>180414</v>
+        <v>183260</v>
       </c>
       <c r="V144" t="s">
-        <v>965</v>
+        <v>992</v>
       </c>
       <c r="W144">
-        <v>1.75</v>
+        <v>0.54200000000000004</v>
       </c>
     </row>
     <row r="145" spans="1:23" x14ac:dyDescent="0.35">
@@ -15163,13 +15139,13 @@
       </c>
       <c r="T145" s="189"/>
       <c r="U145">
-        <v>191112</v>
+        <v>170218</v>
       </c>
       <c r="V145" t="s">
-        <v>966</v>
+        <v>877</v>
       </c>
       <c r="W145">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="146" spans="1:23" x14ac:dyDescent="0.35">
@@ -15206,13 +15182,13 @@
       </c>
       <c r="T146" s="189"/>
       <c r="U146">
-        <v>54185</v>
+        <v>180414</v>
       </c>
       <c r="V146" t="s">
-        <v>967</v>
+        <v>877</v>
       </c>
       <c r="W146">
-        <v>0.25</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="147" spans="1:23" x14ac:dyDescent="0.35">
@@ -15249,13 +15225,13 @@
       </c>
       <c r="T147" s="189"/>
       <c r="U147">
-        <v>53484</v>
+        <v>126831</v>
       </c>
       <c r="V147" t="s">
-        <v>968</v>
+        <v>993</v>
       </c>
       <c r="W147">
-        <v>2.875</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="148" spans="1:23" x14ac:dyDescent="0.35">
@@ -15292,13 +15268,13 @@
       </c>
       <c r="T148" s="189"/>
       <c r="U148">
-        <v>55430</v>
+        <v>191112</v>
       </c>
       <c r="V148" t="s">
-        <v>969</v>
+        <v>878</v>
       </c>
       <c r="W148">
-        <v>0.41699999999999998</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="149" spans="1:23" x14ac:dyDescent="0.35">
@@ -15335,13 +15311,13 @@
       </c>
       <c r="T149" s="189"/>
       <c r="U149">
-        <v>164874</v>
+        <v>53484</v>
       </c>
       <c r="V149" t="s">
-        <v>837</v>
+        <v>879</v>
       </c>
       <c r="W149">
-        <v>0.52100000000000002</v>
+        <v>2.875</v>
       </c>
     </row>
     <row r="150" spans="1:23" x14ac:dyDescent="0.35">
@@ -15378,13 +15354,13 @@
       </c>
       <c r="T150" s="189"/>
       <c r="U150">
-        <v>191879</v>
+        <v>55430</v>
       </c>
       <c r="V150" t="s">
-        <v>814</v>
+        <v>880</v>
       </c>
       <c r="W150">
-        <v>1</v>
+        <v>0.41699999999999998</v>
       </c>
     </row>
     <row r="151" spans="1:23" x14ac:dyDescent="0.35">
@@ -15421,13 +15397,13 @@
       </c>
       <c r="T151" s="189"/>
       <c r="U151">
-        <v>191865</v>
+        <v>143381</v>
       </c>
       <c r="V151" t="s">
-        <v>970</v>
+        <v>994</v>
       </c>
       <c r="W151">
-        <v>0.20799999999999999</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="152" spans="1:23" x14ac:dyDescent="0.35">
@@ -15464,13 +15440,13 @@
       </c>
       <c r="T152" s="189"/>
       <c r="U152">
-        <v>53735</v>
+        <v>168790</v>
       </c>
       <c r="V152" t="s">
-        <v>971</v>
+        <v>995</v>
       </c>
       <c r="W152">
-        <v>9</v>
+        <v>0.93799999999999994</v>
       </c>
     </row>
     <row r="153" spans="1:23" x14ac:dyDescent="0.35">
@@ -15507,13 +15483,13 @@
       </c>
       <c r="T153" s="189"/>
       <c r="U153">
-        <v>63207</v>
+        <v>179309</v>
       </c>
       <c r="V153" t="s">
-        <v>972</v>
+        <v>996</v>
       </c>
       <c r="W153">
-        <v>0.54200000000000004</v>
+        <v>0.93799999999999994</v>
       </c>
     </row>
     <row r="154" spans="1:23" x14ac:dyDescent="0.35">
@@ -15550,13 +15526,13 @@
       </c>
       <c r="T154" s="189"/>
       <c r="U154">
-        <v>188791</v>
+        <v>172227</v>
       </c>
       <c r="V154" t="s">
-        <v>973</v>
+        <v>997</v>
       </c>
       <c r="W154">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="155" spans="1:23" x14ac:dyDescent="0.35">
@@ -15593,13 +15569,13 @@
       </c>
       <c r="T155" s="189"/>
       <c r="U155">
-        <v>163986</v>
+        <v>114004</v>
       </c>
       <c r="V155" t="s">
-        <v>974</v>
+        <v>998</v>
       </c>
       <c r="W155">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="156" spans="1:23" x14ac:dyDescent="0.35">
@@ -15636,13 +15612,13 @@
       </c>
       <c r="T156" s="189"/>
       <c r="U156">
-        <v>167649</v>
+        <v>53735</v>
       </c>
       <c r="V156" t="s">
-        <v>838</v>
+        <v>881</v>
       </c>
       <c r="W156">
-        <v>0.625</v>
+        <v>9</v>
       </c>
     </row>
     <row r="157" spans="1:23" x14ac:dyDescent="0.35">
@@ -15679,13 +15655,13 @@
       </c>
       <c r="T157" s="189"/>
       <c r="U157">
-        <v>48938</v>
+        <v>189324</v>
       </c>
       <c r="V157" t="s">
-        <v>975</v>
+        <v>999</v>
       </c>
       <c r="W157">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="158" spans="1:23" x14ac:dyDescent="0.35">
@@ -15722,13 +15698,13 @@
       </c>
       <c r="T158" s="189"/>
       <c r="U158">
-        <v>114015</v>
+        <v>188791</v>
       </c>
       <c r="V158" t="s">
-        <v>976</v>
+        <v>882</v>
       </c>
       <c r="W158">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:23" x14ac:dyDescent="0.35">
@@ -15765,13 +15741,13 @@
       </c>
       <c r="T159" s="189"/>
       <c r="U159">
-        <v>116409</v>
+        <v>146387</v>
       </c>
       <c r="V159" t="s">
-        <v>977</v>
+        <v>1000</v>
       </c>
       <c r="W159">
-        <v>0</v>
+        <v>0.81299999999999994</v>
       </c>
     </row>
     <row r="160" spans="1:23" x14ac:dyDescent="0.35">
@@ -15808,13 +15784,13 @@
       </c>
       <c r="T160" s="189"/>
       <c r="U160">
-        <v>165003</v>
+        <v>48320</v>
       </c>
       <c r="V160" t="s">
-        <v>978</v>
+        <v>1001</v>
       </c>
       <c r="W160">
-        <v>6</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="161" spans="1:23" x14ac:dyDescent="0.35">
@@ -15851,13 +15827,13 @@
       </c>
       <c r="T161" s="189"/>
       <c r="U161">
-        <v>167009</v>
+        <v>185944</v>
       </c>
       <c r="V161" t="s">
-        <v>979</v>
+        <v>1002</v>
       </c>
       <c r="W161">
-        <v>9</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="162" spans="1:23" x14ac:dyDescent="0.35">
@@ -15894,13 +15870,13 @@
       </c>
       <c r="T162" s="189"/>
       <c r="U162">
-        <v>175298</v>
+        <v>167649</v>
       </c>
       <c r="V162" t="s">
-        <v>979</v>
+        <v>822</v>
       </c>
       <c r="W162">
-        <v>10</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="163" spans="1:23" x14ac:dyDescent="0.35">
@@ -15937,13 +15913,13 @@
       </c>
       <c r="T163" s="189"/>
       <c r="U163">
-        <v>63006</v>
+        <v>56775</v>
       </c>
       <c r="V163" t="s">
-        <v>980</v>
+        <v>1003</v>
       </c>
       <c r="W163">
-        <v>0.25</v>
+        <v>0.56299999999999994</v>
       </c>
     </row>
     <row r="164" spans="1:23" x14ac:dyDescent="0.35">
@@ -15980,13 +15956,13 @@
       </c>
       <c r="T164" s="189"/>
       <c r="U164">
-        <v>189053</v>
+        <v>68160</v>
       </c>
       <c r="V164" t="s">
-        <v>981</v>
+        <v>1004</v>
       </c>
       <c r="W164">
-        <v>0.25</v>
+        <v>0.83299999999999996</v>
       </c>
     </row>
     <row r="165" spans="1:23" x14ac:dyDescent="0.35">
@@ -16023,13 +15999,13 @@
       </c>
       <c r="T165" s="189"/>
       <c r="U165">
-        <v>183258</v>
+        <v>186764</v>
       </c>
       <c r="V165" t="s">
-        <v>839</v>
+        <v>1005</v>
       </c>
       <c r="W165">
-        <v>0.70799999999999996</v>
+        <v>0.66700000000000004</v>
       </c>
     </row>
     <row r="166" spans="1:23" x14ac:dyDescent="0.35">
@@ -16066,13 +16042,13 @@
       </c>
       <c r="T166" s="189"/>
       <c r="U166">
-        <v>50187</v>
+        <v>127955</v>
       </c>
       <c r="V166" t="s">
-        <v>982</v>
+        <v>1006</v>
       </c>
       <c r="W166">
-        <v>13.833</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="167" spans="1:23" x14ac:dyDescent="0.35">
@@ -16109,13 +16085,13 @@
       </c>
       <c r="T167" s="189"/>
       <c r="U167">
-        <v>49988</v>
+        <v>167009</v>
       </c>
       <c r="V167" t="s">
-        <v>983</v>
+        <v>883</v>
       </c>
       <c r="W167">
-        <v>0.25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="168" spans="1:23" x14ac:dyDescent="0.35">
@@ -16152,13 +16128,13 @@
       </c>
       <c r="T168" s="189"/>
       <c r="U168">
-        <v>53972</v>
+        <v>175298</v>
       </c>
       <c r="V168" t="s">
-        <v>984</v>
+        <v>883</v>
       </c>
       <c r="W168">
-        <v>0.25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="169" spans="1:23" x14ac:dyDescent="0.35">
@@ -16195,13 +16171,13 @@
       </c>
       <c r="T169" s="189"/>
       <c r="U169">
-        <v>172002</v>
+        <v>55752</v>
       </c>
       <c r="V169" t="s">
-        <v>985</v>
+        <v>1007</v>
       </c>
       <c r="W169">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="170" spans="1:23" x14ac:dyDescent="0.35">
@@ -16238,13 +16214,13 @@
       </c>
       <c r="T170" s="189"/>
       <c r="U170">
-        <v>146471</v>
+        <v>158685</v>
       </c>
       <c r="V170" t="s">
-        <v>986</v>
+        <v>1007</v>
       </c>
       <c r="W170">
-        <v>8.3000000000000004E-2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="171" spans="1:23" x14ac:dyDescent="0.35">
@@ -16281,13 +16257,13 @@
       </c>
       <c r="T171" s="189"/>
       <c r="U171">
-        <v>172419</v>
+        <v>189053</v>
       </c>
       <c r="V171" t="s">
-        <v>987</v>
+        <v>884</v>
       </c>
       <c r="W171">
-        <v>0.83299999999999996</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="172" spans="1:23" x14ac:dyDescent="0.35">
@@ -16324,13 +16300,13 @@
       </c>
       <c r="T172" s="189"/>
       <c r="U172">
-        <v>167199</v>
+        <v>50187</v>
       </c>
       <c r="V172" t="s">
-        <v>988</v>
+        <v>885</v>
       </c>
       <c r="W172">
-        <v>0.75</v>
+        <v>13.833</v>
       </c>
     </row>
     <row r="173" spans="1:23" x14ac:dyDescent="0.35">
@@ -16367,13 +16343,13 @@
       </c>
       <c r="T173" s="189"/>
       <c r="U173">
-        <v>190208</v>
+        <v>49988</v>
       </c>
       <c r="V173" t="s">
-        <v>989</v>
+        <v>886</v>
       </c>
       <c r="W173">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="174" spans="1:23" x14ac:dyDescent="0.35">
@@ -16410,13 +16386,13 @@
       </c>
       <c r="T174" s="189"/>
       <c r="U174">
-        <v>171291</v>
+        <v>79053</v>
       </c>
       <c r="V174" t="s">
-        <v>990</v>
+        <v>1008</v>
       </c>
       <c r="W174">
-        <v>0.54200000000000004</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175" spans="1:23" x14ac:dyDescent="0.35">
@@ -16453,13 +16429,13 @@
       </c>
       <c r="T175" s="189"/>
       <c r="U175">
-        <v>118037</v>
+        <v>177863</v>
       </c>
       <c r="V175" t="s">
-        <v>991</v>
+        <v>1009</v>
       </c>
       <c r="W175">
-        <v>0.83299999999999996</v>
+        <v>0.41699999999999998</v>
       </c>
     </row>
     <row r="176" spans="1:23" x14ac:dyDescent="0.35">
@@ -16496,13 +16472,13 @@
       </c>
       <c r="T176" s="189"/>
       <c r="U176">
-        <v>151823</v>
+        <v>176938</v>
       </c>
       <c r="V176" t="s">
-        <v>992</v>
+        <v>1010</v>
       </c>
       <c r="W176">
-        <v>0.16700000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="177" spans="1:23" x14ac:dyDescent="0.35">
@@ -16539,13 +16515,13 @@
       </c>
       <c r="T177" s="189"/>
       <c r="U177">
-        <v>128658</v>
+        <v>68577</v>
       </c>
       <c r="V177" t="s">
-        <v>993</v>
+        <v>1011</v>
       </c>
       <c r="W177">
-        <v>0.25</v>
+        <v>0.89600000000000002</v>
       </c>
     </row>
     <row r="178" spans="1:23" x14ac:dyDescent="0.35">
@@ -16582,13 +16558,13 @@
       </c>
       <c r="T178" s="189"/>
       <c r="U178">
-        <v>115244</v>
+        <v>167929</v>
       </c>
       <c r="V178" t="s">
-        <v>994</v>
+        <v>1012</v>
       </c>
       <c r="W178">
-        <v>9</v>
+        <v>6.3E-2</v>
       </c>
     </row>
     <row r="179" spans="1:23" x14ac:dyDescent="0.35">
@@ -16625,13 +16601,13 @@
       </c>
       <c r="T179" s="189"/>
       <c r="U179">
-        <v>159418</v>
+        <v>172419</v>
       </c>
       <c r="V179" t="s">
-        <v>994</v>
+        <v>887</v>
       </c>
       <c r="W179">
-        <v>6.75</v>
+        <v>0.83299999999999996</v>
       </c>
     </row>
     <row r="180" spans="1:23" x14ac:dyDescent="0.35">
@@ -16668,13 +16644,13 @@
       </c>
       <c r="T180" s="189"/>
       <c r="U180">
-        <v>169080</v>
+        <v>192286</v>
       </c>
       <c r="V180" t="s">
-        <v>994</v>
+        <v>1013</v>
       </c>
       <c r="W180" s="6">
-        <v>10.25</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="181" spans="1:23" x14ac:dyDescent="0.35">
@@ -16711,13 +16687,13 @@
       </c>
       <c r="T181" s="189"/>
       <c r="U181">
-        <v>170882</v>
+        <v>191081</v>
       </c>
       <c r="V181" t="s">
-        <v>994</v>
+        <v>1014</v>
       </c>
       <c r="W181">
-        <v>10.667</v>
+        <v>0.54200000000000004</v>
       </c>
     </row>
     <row r="182" spans="1:23" x14ac:dyDescent="0.35">
@@ -16754,13 +16730,13 @@
       </c>
       <c r="T182" s="189"/>
       <c r="U182">
-        <v>175266</v>
+        <v>191234</v>
       </c>
       <c r="V182" t="s">
-        <v>994</v>
+        <v>1015</v>
       </c>
       <c r="W182">
-        <v>6.5</v>
+        <v>0.16700000000000001</v>
       </c>
     </row>
     <row r="183" spans="1:23" x14ac:dyDescent="0.35">
@@ -16797,13 +16773,13 @@
       </c>
       <c r="T183" s="189"/>
       <c r="U183">
-        <v>184835</v>
+        <v>81045</v>
       </c>
       <c r="V183" t="s">
-        <v>994</v>
+        <v>1016</v>
       </c>
       <c r="W183">
-        <v>9.75</v>
+        <v>1.1879999999999999</v>
       </c>
     </row>
     <row r="184" spans="1:23" x14ac:dyDescent="0.35">
@@ -16840,13 +16816,13 @@
       </c>
       <c r="T184" s="189"/>
       <c r="U184">
-        <v>187913</v>
+        <v>176773</v>
       </c>
       <c r="V184" t="s">
-        <v>994</v>
+        <v>1017</v>
       </c>
       <c r="W184">
-        <v>3.75</v>
+        <v>0.16700000000000001</v>
       </c>
     </row>
     <row r="185" spans="1:23" x14ac:dyDescent="0.35">
@@ -16883,13 +16859,13 @@
       </c>
       <c r="T185" s="184"/>
       <c r="U185">
-        <v>189548</v>
+        <v>115244</v>
       </c>
       <c r="V185" t="s">
-        <v>994</v>
+        <v>888</v>
       </c>
       <c r="W185">
-        <v>12.75</v>
+        <v>9</v>
       </c>
     </row>
     <row r="186" spans="1:23" x14ac:dyDescent="0.35">
@@ -16926,13 +16902,13 @@
       </c>
       <c r="T186" s="184"/>
       <c r="U186">
-        <v>178947</v>
+        <v>169080</v>
       </c>
       <c r="V186" t="s">
-        <v>995</v>
+        <v>888</v>
       </c>
       <c r="W186">
-        <v>0.875</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="187" spans="1:23" x14ac:dyDescent="0.35">
@@ -16969,13 +16945,13 @@
       </c>
       <c r="T187" s="184"/>
       <c r="U187">
-        <v>172089</v>
+        <v>170882</v>
       </c>
       <c r="V187" t="s">
-        <v>815</v>
+        <v>888</v>
       </c>
       <c r="W187">
-        <v>4.25</v>
+        <v>10.667</v>
       </c>
     </row>
     <row r="188" spans="1:23" x14ac:dyDescent="0.35">
@@ -17012,13 +16988,13 @@
       </c>
       <c r="T188" s="184"/>
       <c r="U188">
-        <v>147602</v>
+        <v>175266</v>
       </c>
       <c r="V188" t="s">
-        <v>996</v>
+        <v>888</v>
       </c>
       <c r="W188">
-        <v>3.0419999999999998</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="189" spans="1:23" x14ac:dyDescent="0.35">
@@ -17055,13 +17031,13 @@
       </c>
       <c r="T189" s="184"/>
       <c r="U189">
-        <v>179864</v>
+        <v>184835</v>
       </c>
       <c r="V189" t="s">
-        <v>997</v>
+        <v>888</v>
       </c>
       <c r="W189" s="6">
-        <v>0.33300000000000002</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="190" spans="1:23" x14ac:dyDescent="0.35">
@@ -17098,13 +17074,13 @@
       </c>
       <c r="T190" s="184"/>
       <c r="U190">
-        <v>107031</v>
+        <v>189548</v>
       </c>
       <c r="V190" t="s">
-        <v>998</v>
+        <v>888</v>
       </c>
       <c r="W190">
-        <v>9.1669999999999998</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="191" spans="1:23" x14ac:dyDescent="0.35">
@@ -17141,13 +17117,13 @@
       </c>
       <c r="T191" s="184"/>
       <c r="U191">
-        <v>133189</v>
+        <v>178947</v>
       </c>
       <c r="V191" t="s">
-        <v>998</v>
+        <v>889</v>
       </c>
       <c r="W191">
-        <v>7.3330000000000002</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="192" spans="1:23" x14ac:dyDescent="0.35">
@@ -17184,13 +17160,13 @@
       </c>
       <c r="T192" s="184"/>
       <c r="U192">
-        <v>154314</v>
+        <v>172089</v>
       </c>
       <c r="V192" t="s">
-        <v>998</v>
+        <v>812</v>
       </c>
       <c r="W192">
-        <v>3.5830000000000002</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="193" spans="1:23" x14ac:dyDescent="0.35">
@@ -17227,13 +17203,13 @@
       </c>
       <c r="T193" s="184"/>
       <c r="U193">
-        <v>167116</v>
+        <v>179864</v>
       </c>
       <c r="V193" t="s">
-        <v>998</v>
+        <v>890</v>
       </c>
       <c r="W193">
-        <v>4.3330000000000002</v>
+        <v>0.33300000000000002</v>
       </c>
     </row>
     <row r="194" spans="1:23" x14ac:dyDescent="0.35">
@@ -17270,13 +17246,13 @@
       </c>
       <c r="T194" s="184"/>
       <c r="U194">
-        <v>170024</v>
+        <v>191599</v>
       </c>
       <c r="V194" t="s">
-        <v>998</v>
+        <v>1018</v>
       </c>
       <c r="W194">
-        <v>8.0419999999999998</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="195" spans="1:23" x14ac:dyDescent="0.35">
@@ -17313,13 +17289,13 @@
       </c>
       <c r="T195" s="184"/>
       <c r="U195">
-        <v>170025</v>
+        <v>107031</v>
       </c>
       <c r="V195" t="s">
-        <v>998</v>
+        <v>891</v>
       </c>
       <c r="W195">
-        <v>3.6669999999999998</v>
+        <v>9.1669999999999998</v>
       </c>
     </row>
     <row r="196" spans="1:23" x14ac:dyDescent="0.35">
@@ -17356,13 +17332,13 @@
       </c>
       <c r="T196" s="184"/>
       <c r="U196">
-        <v>171933</v>
+        <v>133189</v>
       </c>
       <c r="V196" t="s">
-        <v>998</v>
+        <v>891</v>
       </c>
       <c r="W196">
-        <v>2.3330000000000002</v>
+        <v>7.3330000000000002</v>
       </c>
     </row>
     <row r="197" spans="1:23" x14ac:dyDescent="0.35">
@@ -17399,13 +17375,13 @@
       </c>
       <c r="T197" s="184"/>
       <c r="U197">
-        <v>179251</v>
+        <v>154314</v>
       </c>
       <c r="V197" t="s">
-        <v>998</v>
+        <v>891</v>
       </c>
       <c r="W197">
-        <v>4.0419999999999998</v>
+        <v>3.5830000000000002</v>
       </c>
     </row>
     <row r="198" spans="1:23" x14ac:dyDescent="0.35">
@@ -17442,13 +17418,13 @@
       </c>
       <c r="T198" s="184"/>
       <c r="U198">
-        <v>187615</v>
+        <v>167116</v>
       </c>
       <c r="V198" t="s">
-        <v>999</v>
+        <v>891</v>
       </c>
       <c r="W198">
-        <v>0.25</v>
+        <v>4.3330000000000002</v>
       </c>
     </row>
     <row r="199" spans="1:23" x14ac:dyDescent="0.35">
@@ -17485,13 +17461,13 @@
       </c>
       <c r="T199" s="184"/>
       <c r="U199">
-        <v>62048</v>
+        <v>170024</v>
       </c>
       <c r="V199" t="s">
-        <v>1000</v>
+        <v>891</v>
       </c>
       <c r="W199">
-        <v>20</v>
+        <v>8.0419999999999998</v>
       </c>
     </row>
     <row r="200" spans="1:23" x14ac:dyDescent="0.35">
@@ -17512,29 +17488,29 @@
       </c>
       <c r="G200" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>64883 JUL/2025</v>
+        <v>48248 JUN/2026</v>
       </c>
       <c r="H200">
-        <v>64883</v>
+        <v>48248</v>
       </c>
       <c r="I200" t="s">
         <v>50</v>
       </c>
       <c r="J200" t="s">
-        <v>512</v>
+        <v>782</v>
       </c>
       <c r="K200" s="6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T200" s="184"/>
       <c r="U200">
-        <v>189613</v>
+        <v>170025</v>
       </c>
       <c r="V200" t="s">
-        <v>1001</v>
+        <v>891</v>
       </c>
       <c r="W200">
-        <v>0.33300000000000002</v>
+        <v>3.6669999999999998</v>
       </c>
     </row>
     <row r="201" spans="1:23" x14ac:dyDescent="0.35">
@@ -17555,7 +17531,7 @@
       </c>
       <c r="G201" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>64883 AGO/2025</v>
+        <v>64883 JUL/2025</v>
       </c>
       <c r="H201">
         <v>64883</v>
@@ -17564,20 +17540,20 @@
         <v>50</v>
       </c>
       <c r="J201" s="6" t="s">
-        <v>773</v>
+        <v>512</v>
       </c>
       <c r="K201" s="6">
-        <v>224.875</v>
+        <v>-1</v>
       </c>
       <c r="T201" s="184"/>
       <c r="U201">
-        <v>190786</v>
+        <v>171933</v>
       </c>
       <c r="V201" t="s">
-        <v>1002</v>
+        <v>891</v>
       </c>
       <c r="W201">
-        <v>0.16700000000000001</v>
+        <v>2.3330000000000002</v>
       </c>
     </row>
     <row r="202" spans="1:23" x14ac:dyDescent="0.35">
@@ -17598,7 +17574,7 @@
       </c>
       <c r="G202" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>64883 SET/2025</v>
+        <v>64883 AGO/2025</v>
       </c>
       <c r="H202">
         <v>64883</v>
@@ -17607,20 +17583,20 @@
         <v>50</v>
       </c>
       <c r="J202" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="K202" s="6">
-        <v>1266</v>
+        <v>224.875</v>
       </c>
       <c r="T202" s="184"/>
       <c r="U202">
-        <v>181525</v>
+        <v>179251</v>
       </c>
       <c r="V202" t="s">
-        <v>1003</v>
+        <v>891</v>
       </c>
       <c r="W202">
-        <v>4.25</v>
+        <v>4.0419999999999998</v>
       </c>
     </row>
     <row r="203" spans="1:23" x14ac:dyDescent="0.35">
@@ -17641,7 +17617,7 @@
       </c>
       <c r="G203" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>64883 OUT/2025</v>
+        <v>64883 SET/2025</v>
       </c>
       <c r="H203">
         <v>64883</v>
@@ -17650,20 +17626,20 @@
         <v>50</v>
       </c>
       <c r="J203" t="s">
-        <v>774</v>
-      </c>
-      <c r="K203">
-        <v>25.542000000000002</v>
+        <v>772</v>
+      </c>
+      <c r="K203" s="6">
+        <v>1266</v>
       </c>
       <c r="T203" s="184"/>
       <c r="U203">
-        <v>177594</v>
+        <v>62048</v>
       </c>
       <c r="V203" t="s">
-        <v>1004</v>
+        <v>892</v>
       </c>
       <c r="W203">
-        <v>0.66700000000000004</v>
+        <v>20</v>
       </c>
     </row>
     <row r="204" spans="1:23" x14ac:dyDescent="0.35">
@@ -17684,7 +17660,7 @@
       </c>
       <c r="G204" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>64883 NOV/2025</v>
+        <v>64883 OUT/2025</v>
       </c>
       <c r="H204">
         <v>64883</v>
@@ -17693,20 +17669,20 @@
         <v>50</v>
       </c>
       <c r="J204" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="K204" s="6">
-        <v>107.167</v>
+        <v>25.542000000000002</v>
       </c>
       <c r="T204" s="184"/>
       <c r="U204">
-        <v>69639</v>
+        <v>189613</v>
       </c>
       <c r="V204" t="s">
-        <v>1005</v>
+        <v>893</v>
       </c>
       <c r="W204">
-        <v>1.5</v>
+        <v>0.33300000000000002</v>
       </c>
     </row>
     <row r="205" spans="1:23" x14ac:dyDescent="0.35">
@@ -17727,7 +17703,7 @@
       </c>
       <c r="G205" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>64883 DEZ/2025</v>
+        <v>64883 NOV/2025</v>
       </c>
       <c r="H205">
         <v>64883</v>
@@ -17736,20 +17712,20 @@
         <v>50</v>
       </c>
       <c r="J205" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="K205" s="6">
-        <v>39</v>
+        <v>107.167</v>
       </c>
       <c r="T205" s="184"/>
       <c r="U205">
-        <v>175736</v>
+        <v>184712</v>
       </c>
       <c r="V205" t="s">
-        <v>1006</v>
+        <v>1019</v>
       </c>
       <c r="W205">
-        <v>8.3000000000000004E-2</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="206" spans="1:23" x14ac:dyDescent="0.35">
@@ -17770,7 +17746,7 @@
       </c>
       <c r="G206" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>64883 JAN/2026</v>
+        <v>64883 DEZ/2025</v>
       </c>
       <c r="H206">
         <v>64883</v>
@@ -17779,20 +17755,20 @@
         <v>50</v>
       </c>
       <c r="J206" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="K206" s="6">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="T206" s="184"/>
       <c r="U206">
-        <v>165750</v>
+        <v>177594</v>
       </c>
       <c r="V206" t="s">
-        <v>840</v>
+        <v>894</v>
       </c>
       <c r="W206">
-        <v>0.5</v>
+        <v>0.66700000000000004</v>
       </c>
     </row>
     <row r="207" spans="1:23" x14ac:dyDescent="0.35">
@@ -17813,7 +17789,7 @@
       </c>
       <c r="G207" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>64883 FEV/2026</v>
+        <v>64883 JAN/2026</v>
       </c>
       <c r="H207">
         <v>64883</v>
@@ -17822,20 +17798,20 @@
         <v>50</v>
       </c>
       <c r="J207" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="K207" s="6">
-        <v>35.332999999999998</v>
+        <v>35</v>
       </c>
       <c r="T207" s="184"/>
       <c r="U207">
-        <v>129681</v>
+        <v>56277</v>
       </c>
       <c r="V207" t="s">
-        <v>1007</v>
+        <v>1020</v>
       </c>
       <c r="W207">
-        <v>0.54200000000000004</v>
+        <v>3.6669999999999998</v>
       </c>
     </row>
     <row r="208" spans="1:23" x14ac:dyDescent="0.35">
@@ -17856,7 +17832,7 @@
       </c>
       <c r="G208" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>64883 MAR/2026</v>
+        <v>64883 FEV/2026</v>
       </c>
       <c r="H208">
         <v>64883</v>
@@ -17865,20 +17841,20 @@
         <v>50</v>
       </c>
       <c r="J208" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="K208" s="6">
-        <v>106.917</v>
+        <v>35.332999999999998</v>
       </c>
       <c r="T208" s="184"/>
       <c r="U208">
-        <v>112101</v>
+        <v>175736</v>
       </c>
       <c r="V208" t="s">
-        <v>1008</v>
+        <v>895</v>
       </c>
       <c r="W208">
-        <v>6.3E-2</v>
+        <v>8.3000000000000004E-2</v>
       </c>
     </row>
     <row r="209" spans="1:23" x14ac:dyDescent="0.35">
@@ -17899,7 +17875,7 @@
       </c>
       <c r="G209" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>64883 ABR/2026</v>
+        <v>64883 MAR/2026</v>
       </c>
       <c r="H209">
         <v>64883</v>
@@ -17908,20 +17884,20 @@
         <v>50</v>
       </c>
       <c r="J209" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="K209" s="6">
-        <v>40.832999999999998</v>
+        <v>106.917</v>
       </c>
       <c r="T209" s="184"/>
       <c r="U209">
-        <v>80736</v>
+        <v>129681</v>
       </c>
       <c r="V209" t="s">
-        <v>841</v>
+        <v>896</v>
       </c>
       <c r="W209">
-        <v>0.68799999999999994</v>
+        <v>0.54200000000000004</v>
       </c>
     </row>
     <row r="210" spans="1:23" x14ac:dyDescent="0.35">
@@ -17942,7 +17918,7 @@
       </c>
       <c r="G210" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>64883 MAI/2026</v>
+        <v>64883 ABR/2026</v>
       </c>
       <c r="H210">
         <v>64883</v>
@@ -17951,17 +17927,17 @@
         <v>50</v>
       </c>
       <c r="J210" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="K210">
-        <v>28.582999999999998</v>
+        <v>40.832999999999998</v>
       </c>
       <c r="T210" s="184"/>
       <c r="U210">
         <v>181641</v>
       </c>
       <c r="V210" t="s">
-        <v>1009</v>
+        <v>897</v>
       </c>
       <c r="W210">
         <v>0.25</v>
@@ -17985,7 +17961,7 @@
       </c>
       <c r="G211" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>64883 JUN/2026</v>
+        <v>64883 MAI/2026</v>
       </c>
       <c r="H211">
         <v>64883</v>
@@ -17994,20 +17970,20 @@
         <v>50</v>
       </c>
       <c r="J211" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="K211">
-        <v>58</v>
+        <v>28.582999999999998</v>
       </c>
       <c r="T211" s="184"/>
       <c r="U211">
-        <v>181425</v>
+        <v>66561</v>
       </c>
       <c r="V211" t="s">
-        <v>1010</v>
+        <v>1021</v>
       </c>
       <c r="W211">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="212" spans="1:23" x14ac:dyDescent="0.35">
@@ -18028,29 +18004,29 @@
       </c>
       <c r="G212" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>73977 AGO/2025</v>
+        <v>64883 JUN/2026</v>
       </c>
       <c r="H212">
-        <v>73977</v>
+        <v>64883</v>
       </c>
       <c r="I212" t="s">
         <v>50</v>
       </c>
       <c r="J212" t="s">
-        <v>773</v>
+        <v>782</v>
       </c>
       <c r="K212">
-        <v>5.875</v>
+        <v>58</v>
       </c>
       <c r="T212" s="184"/>
       <c r="U212">
-        <v>60431</v>
+        <v>181425</v>
       </c>
       <c r="V212" t="s">
-        <v>1011</v>
+        <v>898</v>
       </c>
       <c r="W212">
-        <v>1.833</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="213" spans="1:23" x14ac:dyDescent="0.35">
@@ -18071,7 +18047,7 @@
       </c>
       <c r="G213" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>73977 MAR/2026</v>
+        <v>73977 AGO/2025</v>
       </c>
       <c r="H213">
         <v>73977</v>
@@ -18080,20 +18056,20 @@
         <v>50</v>
       </c>
       <c r="J213" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="K213" s="6">
-        <v>6.3330000000000002</v>
+        <v>5.875</v>
       </c>
       <c r="T213" s="184"/>
       <c r="U213">
-        <v>78434</v>
+        <v>49106</v>
       </c>
       <c r="V213" t="s">
-        <v>1012</v>
+        <v>1022</v>
       </c>
       <c r="W213">
-        <v>0.125</v>
+        <v>1.167</v>
       </c>
     </row>
     <row r="214" spans="1:23" x14ac:dyDescent="0.35">
@@ -18114,7 +18090,7 @@
       </c>
       <c r="G214" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>73977 ABR/2026</v>
+        <v>73977 MAR/2026</v>
       </c>
       <c r="H214">
         <v>73977</v>
@@ -18123,17 +18099,17 @@
         <v>50</v>
       </c>
       <c r="J214" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="K214" s="6">
-        <v>11.5</v>
+        <v>6.3330000000000002</v>
       </c>
       <c r="T214" s="184"/>
       <c r="U214">
         <v>178586</v>
       </c>
       <c r="V214" t="s">
-        <v>1013</v>
+        <v>899</v>
       </c>
       <c r="W214">
         <v>0.33300000000000002</v>
@@ -18157,7 +18133,7 @@
       </c>
       <c r="G215" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>73977 MAI/2026</v>
+        <v>73977 ABR/2026</v>
       </c>
       <c r="H215">
         <v>73977</v>
@@ -18166,17 +18142,17 @@
         <v>50</v>
       </c>
       <c r="J215" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="K215">
-        <v>16.417000000000002</v>
+        <v>11.5</v>
       </c>
       <c r="T215" s="184"/>
       <c r="U215">
         <v>185149</v>
       </c>
       <c r="V215" t="s">
-        <v>842</v>
+        <v>823</v>
       </c>
       <c r="W215">
         <v>3.9380000000000002</v>
@@ -18200,26 +18176,26 @@
       </c>
       <c r="G216" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>184994 AGO/2025</v>
+        <v>73977 MAI/2026</v>
       </c>
       <c r="H216">
-        <v>184994</v>
+        <v>73977</v>
       </c>
       <c r="I216" t="s">
         <v>50</v>
       </c>
       <c r="J216" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="K216" s="6">
-        <v>5.875</v>
+        <v>16.417000000000002</v>
       </c>
       <c r="T216" s="184"/>
       <c r="U216">
         <v>138518</v>
       </c>
       <c r="V216" t="s">
-        <v>1014</v>
+        <v>900</v>
       </c>
       <c r="W216">
         <v>0</v>
@@ -18243,7 +18219,7 @@
       </c>
       <c r="G217" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>184994 SET/2025</v>
+        <v>184994 AGO/2025</v>
       </c>
       <c r="H217">
         <v>184994</v>
@@ -18252,20 +18228,20 @@
         <v>50</v>
       </c>
       <c r="J217" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="K217">
-        <v>-8.3000000000000004E-2</v>
+        <v>5.875</v>
       </c>
       <c r="T217" s="184"/>
       <c r="U217">
-        <v>52498</v>
+        <v>182230</v>
       </c>
       <c r="V217" t="s">
-        <v>1015</v>
+        <v>1023</v>
       </c>
       <c r="W217">
-        <v>0.875</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="218" spans="1:23" x14ac:dyDescent="0.35">
@@ -18286,7 +18262,7 @@
       </c>
       <c r="G218" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>184994 OUT/2025</v>
+        <v>184994 SET/2025</v>
       </c>
       <c r="H218">
         <v>184994</v>
@@ -18295,20 +18271,20 @@
         <v>50</v>
       </c>
       <c r="J218" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="K218">
-        <v>22</v>
+        <v>-8.3000000000000004E-2</v>
       </c>
       <c r="T218" s="184"/>
       <c r="U218">
-        <v>176401</v>
+        <v>87430</v>
       </c>
       <c r="V218" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
       <c r="W218">
-        <v>1.167</v>
+        <v>0.33300000000000002</v>
       </c>
     </row>
     <row r="219" spans="1:23" x14ac:dyDescent="0.35">
@@ -18329,7 +18305,7 @@
       </c>
       <c r="G219" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>184994 DEZ/2025</v>
+        <v>184994 OUT/2025</v>
       </c>
       <c r="H219">
         <v>184994</v>
@@ -18338,20 +18314,20 @@
         <v>50</v>
       </c>
       <c r="J219" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="K219" s="6">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="T219" s="184"/>
       <c r="U219">
-        <v>167639</v>
+        <v>177364</v>
       </c>
       <c r="V219" t="s">
-        <v>1017</v>
+        <v>1025</v>
       </c>
       <c r="W219">
-        <v>2</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="220" spans="1:23" x14ac:dyDescent="0.35">
@@ -18372,7 +18348,7 @@
       </c>
       <c r="G220" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>184994 JAN/2026</v>
+        <v>184994 DEZ/2025</v>
       </c>
       <c r="H220">
         <v>184994</v>
@@ -18381,20 +18357,20 @@
         <v>50</v>
       </c>
       <c r="J220" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="K220" s="6">
-        <v>20.582999999999998</v>
+        <v>29</v>
       </c>
       <c r="T220" s="184"/>
       <c r="U220">
-        <v>167704</v>
+        <v>189228</v>
       </c>
       <c r="V220" t="s">
-        <v>1017</v>
+        <v>1026</v>
       </c>
       <c r="W220" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221" spans="1:23" x14ac:dyDescent="0.35">
@@ -18415,7 +18391,7 @@
       </c>
       <c r="G221" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>184994 FEV/2026</v>
+        <v>184994 JAN/2026</v>
       </c>
       <c r="H221">
         <v>184994</v>
@@ -18424,20 +18400,20 @@
         <v>50</v>
       </c>
       <c r="J221" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="K221" s="6">
-        <v>24</v>
+        <v>20.582999999999998</v>
       </c>
       <c r="T221" s="184"/>
       <c r="U221">
-        <v>169604</v>
+        <v>165184</v>
       </c>
       <c r="V221" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="W221">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="222" spans="1:23" x14ac:dyDescent="0.35">
@@ -18458,7 +18434,7 @@
       </c>
       <c r="G222" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>184994 MAR/2026</v>
+        <v>184994 FEV/2026</v>
       </c>
       <c r="H222">
         <v>184994</v>
@@ -18467,20 +18443,20 @@
         <v>50</v>
       </c>
       <c r="J222" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="K222" s="6">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="T222" s="184"/>
       <c r="U222">
-        <v>170853</v>
+        <v>167555</v>
       </c>
       <c r="V222" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="W222">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="223" spans="1:23" x14ac:dyDescent="0.35">
@@ -18501,7 +18477,7 @@
       </c>
       <c r="G223" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>184994 ABR/2026</v>
+        <v>184994 MAR/2026</v>
       </c>
       <c r="H223">
         <v>184994</v>
@@ -18510,20 +18486,20 @@
         <v>50</v>
       </c>
       <c r="J223" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="K223">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="T223" s="184"/>
       <c r="U223">
-        <v>60907</v>
+        <v>169605</v>
       </c>
       <c r="V223" t="s">
-        <v>1018</v>
+        <v>1027</v>
       </c>
       <c r="W223">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="224" spans="1:23" x14ac:dyDescent="0.35">
@@ -18544,7 +18520,7 @@
       </c>
       <c r="G224" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>184994 MAI/2026</v>
+        <v>184994 ABR/2026</v>
       </c>
       <c r="H224">
         <v>184994</v>
@@ -18553,20 +18529,20 @@
         <v>50</v>
       </c>
       <c r="J224" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="K224">
-        <v>35.417000000000002</v>
+        <v>17</v>
       </c>
       <c r="T224" s="184"/>
       <c r="U224">
-        <v>182903</v>
+        <v>170953</v>
       </c>
       <c r="V224" t="s">
-        <v>1018</v>
+        <v>1027</v>
       </c>
       <c r="W224">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="225" spans="1:23" x14ac:dyDescent="0.35">
@@ -18587,29 +18563,29 @@
       </c>
       <c r="G225" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>52169 ABR/2026</v>
+        <v>184994 MAI/2026</v>
       </c>
       <c r="H225">
-        <v>52169</v>
+        <v>184994</v>
       </c>
       <c r="I225" t="s">
-        <v>810</v>
+        <v>50</v>
       </c>
       <c r="J225" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="K225" s="6">
-        <v>6.5</v>
+        <v>35.417000000000002</v>
       </c>
       <c r="T225" s="184"/>
       <c r="U225">
-        <v>49796</v>
+        <v>171318</v>
       </c>
       <c r="V225" t="s">
-        <v>1019</v>
+        <v>1027</v>
       </c>
       <c r="W225">
-        <v>0.45800000000000002</v>
+        <v>7</v>
       </c>
     </row>
     <row r="226" spans="1:23" x14ac:dyDescent="0.35">
@@ -18630,10 +18606,10 @@
       </c>
       <c r="G226" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>135870 ABR/2026</v>
+        <v>52169 ABR/2026</v>
       </c>
       <c r="H226">
-        <v>135870</v>
+        <v>52169</v>
       </c>
       <c r="I226" t="s">
         <v>810</v>
@@ -18646,13 +18622,13 @@
       </c>
       <c r="T226" s="184"/>
       <c r="U226">
-        <v>175574</v>
+        <v>188883</v>
       </c>
       <c r="V226" t="s">
-        <v>1020</v>
+        <v>1028</v>
       </c>
       <c r="W226">
-        <v>0.5</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="227" spans="1:23" x14ac:dyDescent="0.35">
@@ -18673,29 +18649,29 @@
       </c>
       <c r="G227" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>136856 JUL/2025</v>
+        <v>135870 ABR/2026</v>
       </c>
       <c r="H227">
-        <v>136856</v>
+        <v>135870</v>
       </c>
       <c r="I227" t="s">
-        <v>51</v>
+        <v>810</v>
       </c>
       <c r="J227" t="s">
-        <v>512</v>
+        <v>780</v>
       </c>
       <c r="K227">
-        <v>25.875</v>
+        <v>6.5</v>
       </c>
       <c r="T227" s="184"/>
       <c r="U227">
-        <v>122780</v>
+        <v>167639</v>
       </c>
       <c r="V227" t="s">
-        <v>1021</v>
+        <v>901</v>
       </c>
       <c r="W227">
-        <v>0.75</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228" spans="1:23" x14ac:dyDescent="0.35">
@@ -18716,7 +18692,7 @@
       </c>
       <c r="G228" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>136856 AGO/2025</v>
+        <v>136856 JUL/2025</v>
       </c>
       <c r="H228">
         <v>136856</v>
@@ -18725,20 +18701,20 @@
         <v>51</v>
       </c>
       <c r="J228" t="s">
-        <v>773</v>
+        <v>512</v>
       </c>
       <c r="K228">
-        <v>-3.8330000000000002</v>
+        <v>25.875</v>
       </c>
       <c r="T228" s="184"/>
       <c r="U228">
-        <v>114305</v>
+        <v>167704</v>
       </c>
       <c r="V228" t="s">
-        <v>1022</v>
+        <v>901</v>
       </c>
       <c r="W228">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229" spans="1:23" x14ac:dyDescent="0.35">
@@ -18759,7 +18735,7 @@
       </c>
       <c r="G229" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>136856 SET/2025</v>
+        <v>136856 AGO/2025</v>
       </c>
       <c r="H229">
         <v>136856</v>
@@ -18768,20 +18744,20 @@
         <v>51</v>
       </c>
       <c r="J229" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="K229">
-        <v>296.75</v>
+        <v>-3.8330000000000002</v>
       </c>
       <c r="T229" s="184"/>
       <c r="U229">
-        <v>187856</v>
+        <v>169604</v>
       </c>
       <c r="V229" t="s">
-        <v>843</v>
+        <v>901</v>
       </c>
       <c r="W229" s="6">
-        <v>0.125</v>
+        <v>5</v>
       </c>
     </row>
     <row r="230" spans="1:23" x14ac:dyDescent="0.35">
@@ -18802,7 +18778,7 @@
       </c>
       <c r="G230" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>136856 OUT/2025</v>
+        <v>136856 SET/2025</v>
       </c>
       <c r="H230">
         <v>136856</v>
@@ -18811,20 +18787,20 @@
         <v>51</v>
       </c>
       <c r="J230" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="K230" s="6">
-        <v>7</v>
+        <v>296.75</v>
       </c>
       <c r="T230" s="184"/>
       <c r="U230">
-        <v>58550</v>
+        <v>170853</v>
       </c>
       <c r="V230" t="s">
-        <v>1023</v>
+        <v>901</v>
       </c>
       <c r="W230">
-        <v>0.25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="231" spans="1:23" x14ac:dyDescent="0.35">
@@ -18845,7 +18821,7 @@
       </c>
       <c r="G231" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>136856 NOV/2025</v>
+        <v>136856 OUT/2025</v>
       </c>
       <c r="H231">
         <v>136856</v>
@@ -18854,20 +18830,20 @@
         <v>51</v>
       </c>
       <c r="J231" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="K231">
-        <v>19.167000000000002</v>
+        <v>7</v>
       </c>
       <c r="T231" s="184"/>
       <c r="U231">
-        <v>54959</v>
+        <v>60907</v>
       </c>
       <c r="V231" t="s">
-        <v>1024</v>
+        <v>902</v>
       </c>
       <c r="W231">
-        <v>5.625</v>
+        <v>3</v>
       </c>
     </row>
     <row r="232" spans="1:23" x14ac:dyDescent="0.35">
@@ -18888,7 +18864,7 @@
       </c>
       <c r="G232" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>136856 DEZ/2025</v>
+        <v>136856 NOV/2025</v>
       </c>
       <c r="H232">
         <v>136856</v>
@@ -18897,20 +18873,20 @@
         <v>51</v>
       </c>
       <c r="J232" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="K232">
-        <v>50.667000000000002</v>
+        <v>19.167000000000002</v>
       </c>
       <c r="T232" s="184"/>
       <c r="U232">
-        <v>49053</v>
+        <v>182903</v>
       </c>
       <c r="V232" t="s">
-        <v>1025</v>
+        <v>902</v>
       </c>
       <c r="W232">
-        <v>0.75</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233" spans="1:23" x14ac:dyDescent="0.35">
@@ -18931,7 +18907,7 @@
       </c>
       <c r="G233" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>136856 JAN/2026</v>
+        <v>136856 DEZ/2025</v>
       </c>
       <c r="H233">
         <v>136856</v>
@@ -18940,20 +18916,20 @@
         <v>51</v>
       </c>
       <c r="J233" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="K233" s="6">
-        <v>50.917000000000002</v>
+        <v>50.667000000000002</v>
       </c>
       <c r="T233" s="184"/>
       <c r="U233">
-        <v>103245</v>
+        <v>175574</v>
       </c>
       <c r="V233" t="s">
-        <v>1026</v>
+        <v>903</v>
       </c>
       <c r="W233">
-        <v>8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="234" spans="1:23" x14ac:dyDescent="0.35">
@@ -18974,7 +18950,7 @@
       </c>
       <c r="G234" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>136856 FEV/2026</v>
+        <v>136856 JAN/2026</v>
       </c>
       <c r="H234">
         <v>136856</v>
@@ -18983,20 +18959,20 @@
         <v>51</v>
       </c>
       <c r="J234" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="K234">
-        <v>12.25</v>
+        <v>50.917000000000002</v>
       </c>
       <c r="T234" s="184"/>
       <c r="U234">
-        <v>188941</v>
+        <v>122780</v>
       </c>
       <c r="V234" t="s">
-        <v>1027</v>
+        <v>904</v>
       </c>
       <c r="W234">
-        <v>5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="235" spans="1:23" x14ac:dyDescent="0.35">
@@ -19017,7 +18993,7 @@
       </c>
       <c r="G235" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>136856 MAR/2026</v>
+        <v>136856 FEV/2026</v>
       </c>
       <c r="H235">
         <v>136856</v>
@@ -19026,20 +19002,20 @@
         <v>51</v>
       </c>
       <c r="J235" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="K235">
-        <v>63.957999999999998</v>
+        <v>12.25</v>
       </c>
       <c r="T235" s="184"/>
       <c r="U235">
-        <v>89921</v>
+        <v>114305</v>
       </c>
       <c r="V235" t="s">
-        <v>844</v>
+        <v>905</v>
       </c>
       <c r="W235">
-        <v>13.25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236" spans="1:23" x14ac:dyDescent="0.35">
@@ -19060,7 +19036,7 @@
       </c>
       <c r="G236" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>136856 ABR/2026</v>
+        <v>136856 MAR/2026</v>
       </c>
       <c r="H236">
         <v>136856</v>
@@ -19069,20 +19045,20 @@
         <v>51</v>
       </c>
       <c r="J236" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="K236">
-        <v>28.917000000000002</v>
+        <v>63.957999999999998</v>
       </c>
       <c r="T236" s="184"/>
       <c r="U236">
-        <v>116145</v>
+        <v>131746</v>
       </c>
       <c r="V236" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="W236">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="237" spans="1:23" x14ac:dyDescent="0.35">
@@ -19103,7 +19079,7 @@
       </c>
       <c r="G237" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>136856 MAI/2026</v>
+        <v>136856 ABR/2026</v>
       </c>
       <c r="H237">
         <v>136856</v>
@@ -19112,20 +19088,20 @@
         <v>51</v>
       </c>
       <c r="J237" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="K237" s="6">
-        <v>13.625</v>
+        <v>28.917000000000002</v>
       </c>
       <c r="T237" s="184"/>
       <c r="U237">
-        <v>178885</v>
+        <v>172369</v>
       </c>
       <c r="V237" t="s">
-        <v>816</v>
+        <v>1030</v>
       </c>
       <c r="W237">
-        <v>1.417</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="238" spans="1:23" x14ac:dyDescent="0.35">
@@ -19146,7 +19122,7 @@
       </c>
       <c r="G238" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>136856 JUN/2026</v>
+        <v>136856 MAI/2026</v>
       </c>
       <c r="H238">
         <v>136856</v>
@@ -19155,20 +19131,20 @@
         <v>51</v>
       </c>
       <c r="J238" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="K238">
-        <v>12.375</v>
+        <v>13.625</v>
       </c>
       <c r="T238" s="184"/>
       <c r="U238">
-        <v>59280</v>
+        <v>187856</v>
       </c>
       <c r="V238" t="s">
-        <v>83</v>
+        <v>824</v>
       </c>
       <c r="W238">
-        <v>45</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="239" spans="1:23" x14ac:dyDescent="0.35">
@@ -19189,29 +19165,29 @@
       </c>
       <c r="G239" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>74369 JUL/2025</v>
+        <v>136856 JUN/2026</v>
       </c>
       <c r="H239">
-        <v>74369</v>
+        <v>136856</v>
       </c>
       <c r="I239" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J239" t="s">
-        <v>512</v>
+        <v>782</v>
       </c>
       <c r="K239" s="6">
-        <v>29.082999999999998</v>
+        <v>12.375</v>
       </c>
       <c r="T239" s="184"/>
       <c r="U239">
-        <v>144260</v>
+        <v>89921</v>
       </c>
       <c r="V239" t="s">
-        <v>1029</v>
+        <v>825</v>
       </c>
       <c r="W239">
-        <v>49.667000000000002</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="240" spans="1:23" x14ac:dyDescent="0.35">
@@ -19232,7 +19208,7 @@
       </c>
       <c r="G240" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>74369 AGO/2025</v>
+        <v>74369 JUL/2025</v>
       </c>
       <c r="H240">
         <v>74369</v>
@@ -19241,20 +19217,20 @@
         <v>52</v>
       </c>
       <c r="J240" t="s">
-        <v>773</v>
+        <v>512</v>
       </c>
       <c r="K240">
-        <v>0.58299999999999996</v>
+        <v>29.082999999999998</v>
       </c>
       <c r="T240" s="184"/>
       <c r="U240">
-        <v>48248</v>
+        <v>116145</v>
       </c>
       <c r="V240" t="s">
-        <v>7</v>
+        <v>906</v>
       </c>
       <c r="W240">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241" spans="1:23" x14ac:dyDescent="0.35">
@@ -19275,7 +19251,7 @@
       </c>
       <c r="G241" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>74369 SET/2025</v>
+        <v>74369 AGO/2025</v>
       </c>
       <c r="H241">
         <v>74369</v>
@@ -19284,20 +19260,20 @@
         <v>52</v>
       </c>
       <c r="J241" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="K241">
-        <v>322.83300000000003</v>
+        <v>0.58299999999999996</v>
       </c>
       <c r="T241" s="184"/>
       <c r="U241">
-        <v>64883</v>
+        <v>178885</v>
       </c>
       <c r="V241" t="s">
-        <v>7</v>
+        <v>813</v>
       </c>
       <c r="W241">
-        <v>110</v>
+        <v>1.6040000000000001</v>
       </c>
     </row>
     <row r="242" spans="1:23" x14ac:dyDescent="0.35">
@@ -19318,7 +19294,7 @@
       </c>
       <c r="G242" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>74369 OUT/2025</v>
+        <v>74369 SET/2025</v>
       </c>
       <c r="H242">
         <v>74369</v>
@@ -19327,20 +19303,20 @@
         <v>52</v>
       </c>
       <c r="J242" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="K242">
-        <v>6</v>
+        <v>322.83300000000003</v>
       </c>
       <c r="T242" s="184"/>
       <c r="U242">
-        <v>184994</v>
+        <v>59280</v>
       </c>
       <c r="V242" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="W242">
-        <v>6</v>
+        <v>45</v>
       </c>
     </row>
     <row r="243" spans="1:23" x14ac:dyDescent="0.35">
@@ -19361,7 +19337,7 @@
       </c>
       <c r="G243" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>74369 NOV/2025</v>
+        <v>74369 OUT/2025</v>
       </c>
       <c r="H243">
         <v>74369</v>
@@ -19370,20 +19346,20 @@
         <v>52</v>
       </c>
       <c r="J243" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="K243" s="6">
-        <v>13.167</v>
+        <v>6</v>
       </c>
       <c r="T243" s="184"/>
       <c r="U243">
-        <v>171048</v>
+        <v>144260</v>
       </c>
       <c r="V243" t="s">
-        <v>1030</v>
+        <v>907</v>
       </c>
       <c r="W243">
-        <v>0.125</v>
+        <v>49.667000000000002</v>
       </c>
     </row>
     <row r="244" spans="1:23" x14ac:dyDescent="0.35">
@@ -19404,7 +19380,7 @@
       </c>
       <c r="G244" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>74369 DEZ/2025</v>
+        <v>74369 NOV/2025</v>
       </c>
       <c r="H244">
         <v>74369</v>
@@ -19413,20 +19389,20 @@
         <v>52</v>
       </c>
       <c r="J244" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="K244">
-        <v>55</v>
+        <v>13.167</v>
       </c>
       <c r="T244" s="184"/>
       <c r="U244">
-        <v>152098</v>
+        <v>64883</v>
       </c>
       <c r="V244" t="s">
-        <v>1031</v>
+        <v>7</v>
       </c>
       <c r="W244">
-        <v>0.85399999999999998</v>
+        <v>110</v>
       </c>
     </row>
     <row r="245" spans="1:23" x14ac:dyDescent="0.35">
@@ -19447,7 +19423,7 @@
       </c>
       <c r="G245" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>74369 JAN/2026</v>
+        <v>74369 DEZ/2025</v>
       </c>
       <c r="H245">
         <v>74369</v>
@@ -19456,20 +19432,20 @@
         <v>52</v>
       </c>
       <c r="J245" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="K245">
-        <v>58.292000000000002</v>
+        <v>55</v>
       </c>
       <c r="T245" s="184"/>
       <c r="U245">
-        <v>162069</v>
+        <v>184994</v>
       </c>
       <c r="V245" t="s">
-        <v>845</v>
+        <v>7</v>
       </c>
       <c r="W245">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="246" spans="1:23" x14ac:dyDescent="0.35">
@@ -19490,7 +19466,7 @@
       </c>
       <c r="G246" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>74369 FEV/2026</v>
+        <v>74369 JAN/2026</v>
       </c>
       <c r="H246">
         <v>74369</v>
@@ -19499,20 +19475,20 @@
         <v>52</v>
       </c>
       <c r="J246" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="K246" s="6">
-        <v>9.6669999999999998</v>
+        <v>58.292000000000002</v>
       </c>
       <c r="T246" s="184"/>
       <c r="U246">
-        <v>97274</v>
+        <v>162069</v>
       </c>
       <c r="V246" t="s">
-        <v>1032</v>
+        <v>826</v>
       </c>
       <c r="W246">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247" spans="1:23" x14ac:dyDescent="0.35">
@@ -19533,7 +19509,7 @@
       </c>
       <c r="G247" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>74369 MAR/2026</v>
+        <v>74369 FEV/2026</v>
       </c>
       <c r="H247">
         <v>74369</v>
@@ -19542,20 +19518,20 @@
         <v>52</v>
       </c>
       <c r="J247" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="K247">
-        <v>51.167000000000002</v>
+        <v>9.6669999999999998</v>
       </c>
       <c r="T247" s="184"/>
       <c r="U247">
-        <v>49996</v>
+        <v>113922</v>
       </c>
       <c r="V247" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="W247">
-        <v>7.6040000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="248" spans="1:23" x14ac:dyDescent="0.35">
@@ -19576,7 +19552,7 @@
       </c>
       <c r="G248" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>74369 ABR/2026</v>
+        <v>74369 MAR/2026</v>
       </c>
       <c r="H248">
         <v>74369</v>
@@ -19585,20 +19561,20 @@
         <v>52</v>
       </c>
       <c r="J248" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="K248">
-        <v>53.082999999999998</v>
+        <v>51.167000000000002</v>
       </c>
       <c r="T248" s="184"/>
       <c r="U248">
-        <v>90442</v>
+        <v>49996</v>
       </c>
       <c r="V248" t="s">
-        <v>1034</v>
+        <v>908</v>
       </c>
       <c r="W248">
-        <v>0</v>
+        <v>7.6040000000000001</v>
       </c>
     </row>
     <row r="249" spans="1:23" x14ac:dyDescent="0.35">
@@ -19619,7 +19595,7 @@
       </c>
       <c r="G249" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>74369 MAI/2026</v>
+        <v>74369 ABR/2026</v>
       </c>
       <c r="H249">
         <v>74369</v>
@@ -19628,20 +19604,20 @@
         <v>52</v>
       </c>
       <c r="J249" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="K249" s="6">
-        <v>14.542</v>
+        <v>53.082999999999998</v>
       </c>
       <c r="T249" s="184"/>
       <c r="U249">
-        <v>53601</v>
+        <v>90442</v>
       </c>
       <c r="V249" t="s">
-        <v>1035</v>
+        <v>909</v>
       </c>
       <c r="W249">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250" spans="1:23" x14ac:dyDescent="0.35">
@@ -19662,7 +19638,7 @@
       </c>
       <c r="G250" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>74369 JUN/2026</v>
+        <v>74369 MAI/2026</v>
       </c>
       <c r="H250">
         <v>74369</v>
@@ -19671,20 +19647,20 @@
         <v>52</v>
       </c>
       <c r="J250" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="K250" s="6">
-        <v>18</v>
+        <v>14.542</v>
       </c>
       <c r="T250" s="184"/>
       <c r="U250">
-        <v>74369</v>
+        <v>53601</v>
       </c>
       <c r="V250" t="s">
-        <v>8</v>
+        <v>910</v>
       </c>
       <c r="W250">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="251" spans="1:23" x14ac:dyDescent="0.35">
@@ -19705,26 +19681,26 @@
       </c>
       <c r="G251" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>53581 JUL/2025</v>
+        <v>74369 JUN/2026</v>
       </c>
       <c r="H251">
-        <v>53581</v>
+        <v>74369</v>
       </c>
       <c r="I251" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="J251" t="s">
-        <v>512</v>
+        <v>782</v>
       </c>
       <c r="K251">
-        <v>15.875</v>
+        <v>18</v>
       </c>
       <c r="T251" s="184"/>
       <c r="U251">
-        <v>53581</v>
+        <v>74369</v>
       </c>
       <c r="V251" t="s">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="W251">
         <v>0</v>
@@ -19748,7 +19724,7 @@
       </c>
       <c r="G252" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>53581 AGO/2025</v>
+        <v>53581 JUL/2025</v>
       </c>
       <c r="H252">
         <v>53581</v>
@@ -19757,20 +19733,20 @@
         <v>86</v>
       </c>
       <c r="J252" t="s">
-        <v>773</v>
+        <v>512</v>
       </c>
       <c r="K252">
-        <v>13.75</v>
+        <v>15.875</v>
       </c>
       <c r="T252" s="184"/>
       <c r="U252">
-        <v>55502</v>
+        <v>53581</v>
       </c>
       <c r="V252" t="s">
-        <v>1036</v>
+        <v>100</v>
       </c>
       <c r="W252">
-        <v>5.5830000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253" spans="1:23" x14ac:dyDescent="0.35">
@@ -19791,7 +19767,7 @@
       </c>
       <c r="G253" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>53581 SET/2025</v>
+        <v>53581 AGO/2025</v>
       </c>
       <c r="H253">
         <v>53581</v>
@@ -19800,20 +19776,20 @@
         <v>86</v>
       </c>
       <c r="J253" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="K253" s="6">
-        <v>515.65300000000002</v>
+        <v>13.75</v>
       </c>
       <c r="T253" s="184"/>
       <c r="U253">
-        <v>49419</v>
+        <v>55230</v>
       </c>
       <c r="V253" t="s">
-        <v>1037</v>
+        <v>911</v>
       </c>
       <c r="W253">
-        <v>4.7080000000000002</v>
+        <v>11</v>
       </c>
     </row>
     <row r="254" spans="1:23" x14ac:dyDescent="0.35">
@@ -19834,7 +19810,7 @@
       </c>
       <c r="G254" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>53581 OUT/2025</v>
+        <v>53581 SET/2025</v>
       </c>
       <c r="H254">
         <v>53581</v>
@@ -19843,17 +19819,17 @@
         <v>86</v>
       </c>
       <c r="J254" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="K254" s="6">
-        <v>9.1669999999999998</v>
+        <v>515.65300000000002</v>
       </c>
       <c r="T254" s="184"/>
       <c r="U254">
-        <v>55230</v>
+        <v>60905</v>
       </c>
       <c r="V254" t="s">
-        <v>1038</v>
+        <v>827</v>
       </c>
       <c r="W254">
         <v>11</v>
@@ -19877,7 +19853,7 @@
       </c>
       <c r="G255" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>53581 NOV/2025</v>
+        <v>53581 OUT/2025</v>
       </c>
       <c r="H255">
         <v>53581</v>
@@ -19886,20 +19862,20 @@
         <v>86</v>
       </c>
       <c r="J255" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="K255">
-        <v>9.9510000000000005</v>
+        <v>9.1669999999999998</v>
       </c>
       <c r="T255" s="184"/>
       <c r="U255">
-        <v>184838</v>
+        <v>57679</v>
       </c>
       <c r="V255" t="s">
-        <v>1039</v>
+        <v>112</v>
       </c>
       <c r="W255">
-        <v>5.625</v>
+        <v>59</v>
       </c>
     </row>
     <row r="256" spans="1:23" x14ac:dyDescent="0.35">
@@ -19920,7 +19896,7 @@
       </c>
       <c r="G256" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>53581 DEZ/2025</v>
+        <v>53581 NOV/2025</v>
       </c>
       <c r="H256">
         <v>53581</v>
@@ -19929,20 +19905,20 @@
         <v>86</v>
       </c>
       <c r="J256" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="K256" s="6">
-        <v>89</v>
+        <v>9.9510000000000005</v>
       </c>
       <c r="T256" s="184"/>
       <c r="U256">
-        <v>60905</v>
+        <v>94520</v>
       </c>
       <c r="V256" t="s">
-        <v>846</v>
+        <v>19</v>
       </c>
       <c r="W256">
-        <v>11</v>
+        <v>152.167</v>
       </c>
     </row>
     <row r="257" spans="1:23" x14ac:dyDescent="0.35">
@@ -19963,7 +19939,7 @@
       </c>
       <c r="G257" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>53581 JAN/2026</v>
+        <v>53581 DEZ/2025</v>
       </c>
       <c r="H257">
         <v>53581</v>
@@ -19972,20 +19948,20 @@
         <v>86</v>
       </c>
       <c r="J257" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="K257">
-        <v>74.457999999999998</v>
+        <v>89</v>
       </c>
       <c r="T257" s="184"/>
       <c r="U257">
-        <v>185862</v>
+        <v>185567</v>
       </c>
       <c r="V257" t="s">
-        <v>846</v>
+        <v>912</v>
       </c>
       <c r="W257">
-        <v>2</v>
+        <v>0.16700000000000001</v>
       </c>
     </row>
     <row r="258" spans="1:23" x14ac:dyDescent="0.35">
@@ -20006,7 +19982,7 @@
       </c>
       <c r="G258" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>53581 FEV/2026</v>
+        <v>53581 JAN/2026</v>
       </c>
       <c r="H258">
         <v>53581</v>
@@ -20015,20 +19991,20 @@
         <v>86</v>
       </c>
       <c r="J258" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="K258">
-        <v>15.417</v>
+        <v>74.457999999999998</v>
       </c>
       <c r="T258" s="184"/>
       <c r="U258">
-        <v>57679</v>
+        <v>168161</v>
       </c>
       <c r="V258" t="s">
-        <v>112</v>
+        <v>1032</v>
       </c>
       <c r="W258">
-        <v>59</v>
+        <v>1.1879999999999999</v>
       </c>
     </row>
     <row r="259" spans="1:23" x14ac:dyDescent="0.35">
@@ -20049,7 +20025,7 @@
       </c>
       <c r="G259" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>53581 MAR/2026</v>
+        <v>53581 FEV/2026</v>
       </c>
       <c r="H259">
         <v>53581</v>
@@ -20058,20 +20034,20 @@
         <v>86</v>
       </c>
       <c r="J259" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="K259">
-        <v>63.125</v>
+        <v>15.417</v>
       </c>
       <c r="T259" s="184"/>
       <c r="U259">
-        <v>180012</v>
+        <v>120886</v>
       </c>
       <c r="V259" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
       <c r="W259">
-        <v>1.917</v>
+        <v>4.5419999999999998</v>
       </c>
     </row>
     <row r="260" spans="1:23" x14ac:dyDescent="0.35">
@@ -20092,7 +20068,7 @@
       </c>
       <c r="G260" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>53581 ABR/2026</v>
+        <v>53581 MAR/2026</v>
       </c>
       <c r="H260">
         <v>53581</v>
@@ -20101,20 +20077,20 @@
         <v>86</v>
       </c>
       <c r="J260" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="K260" s="6">
-        <v>20.457999999999998</v>
+        <v>63.125</v>
       </c>
       <c r="T260" s="184"/>
       <c r="U260">
-        <v>128748</v>
+        <v>77969</v>
       </c>
       <c r="V260" t="s">
-        <v>1041</v>
+        <v>1034</v>
       </c>
       <c r="W260">
-        <v>2.1669999999999998</v>
+        <v>4.7080000000000002</v>
       </c>
     </row>
     <row r="261" spans="1:23" x14ac:dyDescent="0.35">
@@ -20134,8 +20110,8 @@
         <v>160.792</v>
       </c>
       <c r="G261" s="29" t="str">
-        <f t="shared" ref="G261:G322" si="6">H261&amp;J261</f>
-        <v>53581 MAI/2026</v>
+        <f t="shared" ref="G261:G323" si="6">H261&amp;J261</f>
+        <v>53581 ABR/2026</v>
       </c>
       <c r="H261">
         <v>53581</v>
@@ -20144,20 +20120,20 @@
         <v>86</v>
       </c>
       <c r="J261" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="K261">
-        <v>22</v>
+        <v>20.457999999999998</v>
       </c>
       <c r="T261" s="184"/>
       <c r="U261">
-        <v>190491</v>
+        <v>128744</v>
       </c>
       <c r="V261" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
       <c r="W261">
-        <v>0.5</v>
+        <v>3.5830000000000002</v>
       </c>
     </row>
     <row r="262" spans="1:23" x14ac:dyDescent="0.35">
@@ -20178,7 +20154,7 @@
       </c>
       <c r="G262" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>53581 JUN/2026</v>
+        <v>53581 MAI/2026</v>
       </c>
       <c r="H262">
         <v>53581</v>
@@ -20187,54 +20163,54 @@
         <v>86</v>
       </c>
       <c r="J262" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="K262">
-        <v>19.082999999999998</v>
+        <v>22</v>
       </c>
       <c r="T262" s="184"/>
       <c r="U262">
-        <v>185567</v>
+        <v>179516</v>
       </c>
       <c r="V262" t="s">
-        <v>1042</v>
+        <v>1036</v>
       </c>
       <c r="W262">
-        <v>0.16700000000000001</v>
+        <v>4.6669999999999998</v>
       </c>
     </row>
     <row r="263" spans="1:23" x14ac:dyDescent="0.35">
       <c r="G263" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>57679 JUL/2025</v>
+        <v>53581 JUN/2026</v>
       </c>
       <c r="H263">
-        <v>57679</v>
+        <v>53581</v>
       </c>
       <c r="I263" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="J263" t="s">
-        <v>512</v>
+        <v>782</v>
       </c>
       <c r="K263" s="6">
-        <v>109</v>
+        <v>19.082999999999998</v>
       </c>
       <c r="T263" s="184"/>
       <c r="U263">
-        <v>156888</v>
+        <v>75</v>
       </c>
       <c r="V263" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="W263">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="264" spans="1:23" x14ac:dyDescent="0.35">
       <c r="G264" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>57679 AGO/2025</v>
+        <v>57679 JUL/2025</v>
       </c>
       <c r="H264">
         <v>57679</v>
@@ -20243,26 +20219,26 @@
         <v>137</v>
       </c>
       <c r="J264" t="s">
-        <v>773</v>
+        <v>512</v>
       </c>
       <c r="K264" s="6">
-        <v>1458</v>
+        <v>109</v>
       </c>
       <c r="T264" s="184"/>
       <c r="U264">
-        <v>109789</v>
+        <v>189422</v>
       </c>
       <c r="V264" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="W264">
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="265" spans="1:23" x14ac:dyDescent="0.35">
       <c r="G265" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>57679 SET/2025</v>
+        <v>57679 AGO/2025</v>
       </c>
       <c r="H265">
         <v>57679</v>
@@ -20271,26 +20247,26 @@
         <v>137</v>
       </c>
       <c r="J265" t="s">
-        <v>772</v>
-      </c>
-      <c r="K265">
-        <v>261</v>
+        <v>773</v>
+      </c>
+      <c r="K265" s="6">
+        <v>1458</v>
       </c>
       <c r="T265" s="184"/>
       <c r="U265">
-        <v>179633</v>
+        <v>156888</v>
       </c>
       <c r="V265" t="s">
-        <v>1045</v>
+        <v>913</v>
       </c>
       <c r="W265">
-        <v>0.625</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="266" spans="1:23" x14ac:dyDescent="0.35">
       <c r="G266" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>57679 OUT/2025</v>
+        <v>57679 SET/2025</v>
       </c>
       <c r="H266">
         <v>57679</v>
@@ -20299,26 +20275,26 @@
         <v>137</v>
       </c>
       <c r="J266" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="K266" s="6">
-        <v>548.75</v>
+        <v>261</v>
       </c>
       <c r="T266" s="184"/>
       <c r="U266">
-        <v>91230</v>
+        <v>179633</v>
       </c>
       <c r="V266" t="s">
-        <v>1046</v>
+        <v>914</v>
       </c>
       <c r="W266">
-        <v>1</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="267" spans="1:23" x14ac:dyDescent="0.35">
       <c r="G267" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>57679 NOV/2025</v>
+        <v>57679 OUT/2025</v>
       </c>
       <c r="H267">
         <v>57679</v>
@@ -20327,26 +20303,26 @@
         <v>137</v>
       </c>
       <c r="J267" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="K267" s="6">
-        <v>578</v>
+        <v>548.75</v>
       </c>
       <c r="T267" s="184"/>
       <c r="U267">
-        <v>164081</v>
+        <v>91230</v>
       </c>
       <c r="V267" t="s">
-        <v>1047</v>
+        <v>915</v>
       </c>
       <c r="W267">
-        <v>2.125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268" spans="1:23" x14ac:dyDescent="0.35">
       <c r="G268" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>57679 DEZ/2025</v>
+        <v>57679 NOV/2025</v>
       </c>
       <c r="H268">
         <v>57679</v>
@@ -20355,17 +20331,26 @@
         <v>137</v>
       </c>
       <c r="J268" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="K268">
-        <v>615</v>
+        <v>578</v>
       </c>
       <c r="T268" s="184"/>
+      <c r="U268">
+        <v>179227</v>
+      </c>
+      <c r="V268" t="s">
+        <v>1039</v>
+      </c>
+      <c r="W268">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="269" spans="1:23" x14ac:dyDescent="0.35">
       <c r="G269" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>57679 JAN/2026</v>
+        <v>57679 DEZ/2025</v>
       </c>
       <c r="H269">
         <v>57679</v>
@@ -20374,17 +20359,17 @@
         <v>137</v>
       </c>
       <c r="J269" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="K269">
-        <v>235.917</v>
+        <v>615</v>
       </c>
       <c r="T269" s="184"/>
     </row>
     <row r="270" spans="1:23" x14ac:dyDescent="0.35">
       <c r="G270" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>57679 FEV/2026</v>
+        <v>57679 JAN/2026</v>
       </c>
       <c r="H270">
         <v>57679</v>
@@ -20393,17 +20378,17 @@
         <v>137</v>
       </c>
       <c r="J270" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="K270" s="6">
-        <v>790.95799999999997</v>
+        <v>235.917</v>
       </c>
       <c r="T270" s="184"/>
     </row>
     <row r="271" spans="1:23" x14ac:dyDescent="0.35">
       <c r="G271" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>57679 MAR/2026</v>
+        <v>57679 FEV/2026</v>
       </c>
       <c r="H271">
         <v>57679</v>
@@ -20412,17 +20397,17 @@
         <v>137</v>
       </c>
       <c r="J271" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="K271">
-        <v>688</v>
+        <v>790.95799999999997</v>
       </c>
       <c r="T271" s="184"/>
     </row>
     <row r="272" spans="1:23" x14ac:dyDescent="0.35">
       <c r="G272" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>57679 ABR/2026</v>
+        <v>57679 MAR/2026</v>
       </c>
       <c r="H272">
         <v>57679</v>
@@ -20431,17 +20416,17 @@
         <v>137</v>
       </c>
       <c r="J272" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="K272">
-        <v>365</v>
+        <v>688</v>
       </c>
       <c r="T272" s="184"/>
     </row>
     <row r="273" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G273" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>57679 MAI/2026</v>
+        <v>57679 ABR/2026</v>
       </c>
       <c r="H273">
         <v>57679</v>
@@ -20450,10 +20435,10 @@
         <v>137</v>
       </c>
       <c r="J273" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="K273" s="6">
-        <v>518</v>
+        <v>365</v>
       </c>
       <c r="T273" s="184"/>
       <c r="W273" s="6"/>
@@ -20461,7 +20446,7 @@
     <row r="274" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G274" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>57679 JUN/2026</v>
+        <v>57679 MAI/2026</v>
       </c>
       <c r="H274">
         <v>57679</v>
@@ -20470,36 +20455,36 @@
         <v>137</v>
       </c>
       <c r="J274" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="K274">
-        <v>204</v>
+        <v>518</v>
       </c>
       <c r="T274" s="184"/>
     </row>
     <row r="275" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G275" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>184217 AGO/2025</v>
+        <v>57679 JUN/2026</v>
       </c>
       <c r="H275">
-        <v>184217</v>
+        <v>57679</v>
       </c>
       <c r="I275" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="J275" t="s">
-        <v>773</v>
+        <v>782</v>
       </c>
       <c r="K275">
-        <v>5.875</v>
+        <v>204</v>
       </c>
       <c r="T275" s="184"/>
     </row>
     <row r="276" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G276" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>184217 FEV/2026</v>
+        <v>184217 AGO/2025</v>
       </c>
       <c r="H276">
         <v>184217</v>
@@ -20508,36 +20493,36 @@
         <v>142</v>
       </c>
       <c r="J276" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="K276">
-        <v>3</v>
+        <v>5.875</v>
       </c>
       <c r="T276" s="184"/>
     </row>
     <row r="277" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G277" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>184335 JUL/2025</v>
+        <v>184217 FEV/2026</v>
       </c>
       <c r="H277">
-        <v>184335</v>
+        <v>184217</v>
       </c>
       <c r="I277" t="s">
         <v>142</v>
       </c>
       <c r="J277" t="s">
-        <v>512</v>
+        <v>778</v>
       </c>
       <c r="K277">
-        <v>5.375</v>
+        <v>3</v>
       </c>
       <c r="T277" s="184"/>
     </row>
     <row r="278" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G278" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>184335 AGO/2025</v>
+        <v>184335 JUL/2025</v>
       </c>
       <c r="H278">
         <v>184335</v>
@@ -20546,17 +20531,17 @@
         <v>142</v>
       </c>
       <c r="J278" t="s">
-        <v>773</v>
+        <v>512</v>
       </c>
       <c r="K278">
-        <v>0.5</v>
+        <v>5.375</v>
       </c>
       <c r="T278" s="184"/>
     </row>
     <row r="279" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G279" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>184335 FEV/2026</v>
+        <v>184335 AGO/2025</v>
       </c>
       <c r="H279">
         <v>184335</v>
@@ -20565,36 +20550,36 @@
         <v>142</v>
       </c>
       <c r="J279" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="K279">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="T279" s="184"/>
     </row>
     <row r="280" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G280" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>94520 JUL/2025</v>
+        <v>184335 FEV/2026</v>
       </c>
       <c r="H280">
-        <v>94520</v>
+        <v>184335</v>
       </c>
       <c r="I280" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="J280" t="s">
-        <v>512</v>
+        <v>778</v>
       </c>
       <c r="K280">
-        <v>397.625</v>
+        <v>3</v>
       </c>
       <c r="T280" s="184"/>
     </row>
     <row r="281" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G281" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>94520 AGO/2025</v>
+        <v>94520 JUL/2025</v>
       </c>
       <c r="H281">
         <v>94520</v>
@@ -20603,17 +20588,17 @@
         <v>53</v>
       </c>
       <c r="J281" t="s">
-        <v>773</v>
+        <v>512</v>
       </c>
       <c r="K281" s="6">
-        <v>49.146000000000001</v>
+        <v>397.625</v>
       </c>
       <c r="T281" s="184"/>
     </row>
     <row r="282" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G282" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>94520 SET/2025</v>
+        <v>94520 AGO/2025</v>
       </c>
       <c r="H282">
         <v>94520</v>
@@ -20622,17 +20607,17 @@
         <v>53</v>
       </c>
       <c r="J282" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="K282" s="6">
-        <v>1314.6669999999999</v>
+        <v>49.146000000000001</v>
       </c>
       <c r="T282" s="184"/>
     </row>
     <row r="283" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G283" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>94520 OUT/2025</v>
+        <v>94520 SET/2025</v>
       </c>
       <c r="H283">
         <v>94520</v>
@@ -20641,17 +20626,17 @@
         <v>53</v>
       </c>
       <c r="J283" t="s">
-        <v>774</v>
-      </c>
-      <c r="K283">
-        <v>74.082999999999998</v>
+        <v>772</v>
+      </c>
+      <c r="K283" s="6">
+        <v>1314.6669999999999</v>
       </c>
       <c r="T283" s="184"/>
     </row>
     <row r="284" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G284" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>94520 NOV/2025</v>
+        <v>94520 OUT/2025</v>
       </c>
       <c r="H284">
         <v>94520</v>
@@ -20660,17 +20645,17 @@
         <v>53</v>
       </c>
       <c r="J284" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="K284">
-        <v>397.76400000000001</v>
+        <v>74.082999999999998</v>
       </c>
       <c r="T284" s="184"/>
     </row>
     <row r="285" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G285" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>94520 DEZ/2025</v>
+        <v>94520 NOV/2025</v>
       </c>
       <c r="H285">
         <v>94520</v>
@@ -20679,17 +20664,17 @@
         <v>53</v>
       </c>
       <c r="J285" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="K285">
-        <v>592.20799999999997</v>
+        <v>397.76400000000001</v>
       </c>
       <c r="T285" s="184"/>
     </row>
     <row r="286" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G286" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>94520 JAN/2026</v>
+        <v>94520 DEZ/2025</v>
       </c>
       <c r="H286">
         <v>94520</v>
@@ -20698,17 +20683,17 @@
         <v>53</v>
       </c>
       <c r="J286" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="K286">
-        <v>294.02100000000002</v>
+        <v>592.20799999999997</v>
       </c>
       <c r="T286" s="184"/>
     </row>
     <row r="287" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G287" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>94520 FEV/2026</v>
+        <v>94520 JAN/2026</v>
       </c>
       <c r="H287">
         <v>94520</v>
@@ -20717,17 +20702,17 @@
         <v>53</v>
       </c>
       <c r="J287" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="K287">
-        <v>80.582999999999998</v>
+        <v>294.02100000000002</v>
       </c>
       <c r="T287" s="184"/>
     </row>
     <row r="288" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G288" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>94520 MAR/2026</v>
+        <v>94520 FEV/2026</v>
       </c>
       <c r="H288">
         <v>94520</v>
@@ -20736,17 +20721,17 @@
         <v>53</v>
       </c>
       <c r="J288" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="K288">
-        <v>397.25</v>
+        <v>80.582999999999998</v>
       </c>
       <c r="T288" s="184"/>
     </row>
     <row r="289" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G289" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>94520 ABR/2026</v>
+        <v>94520 MAR/2026</v>
       </c>
       <c r="H289">
         <v>94520</v>
@@ -20755,17 +20740,17 @@
         <v>53</v>
       </c>
       <c r="J289" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="K289">
-        <v>220.667</v>
+        <v>397.25</v>
       </c>
       <c r="T289" s="184"/>
     </row>
     <row r="290" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G290" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>94520 MAI/2026</v>
+        <v>94520 ABR/2026</v>
       </c>
       <c r="H290">
         <v>94520</v>
@@ -20774,17 +20759,17 @@
         <v>53</v>
       </c>
       <c r="J290" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="K290">
-        <v>215.179</v>
+        <v>220.667</v>
       </c>
       <c r="T290" s="184"/>
     </row>
     <row r="291" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G291" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>94520 JUN/2026</v>
+        <v>94520 MAI/2026</v>
       </c>
       <c r="H291">
         <v>94520</v>
@@ -20793,29 +20778,29 @@
         <v>53</v>
       </c>
       <c r="J291" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="K291">
-        <v>-8.7789999999999999</v>
+        <v>215.179</v>
       </c>
       <c r="T291" s="184"/>
     </row>
     <row r="292" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G292" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>53461 AGO/2025</v>
+        <v>94520 JUN/2026</v>
       </c>
       <c r="H292">
-        <v>53461</v>
+        <v>94520</v>
       </c>
       <c r="I292" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="J292" t="s">
-        <v>773</v>
+        <v>782</v>
       </c>
       <c r="K292">
-        <v>5.875</v>
+        <v>-8.7789999999999999</v>
       </c>
       <c r="T292" s="184"/>
       <c r="W292" s="6"/>
@@ -20823,7 +20808,7 @@
     <row r="293" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G293" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>53461 FEV/2026</v>
+        <v>53461 AGO/2025</v>
       </c>
       <c r="H293">
         <v>53461</v>
@@ -20832,10 +20817,10 @@
         <v>87</v>
       </c>
       <c r="J293" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="K293">
-        <v>3</v>
+        <v>5.875</v>
       </c>
       <c r="T293" s="184"/>
       <c r="W293" s="6"/>
@@ -20843,26 +20828,26 @@
     <row r="294" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G294" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>56110 AGO/2025</v>
+        <v>53461 FEV/2026</v>
       </c>
       <c r="H294">
-        <v>56110</v>
+        <v>53461</v>
       </c>
       <c r="I294" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J294" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="K294">
-        <v>5.875</v>
+        <v>3</v>
       </c>
       <c r="T294" s="184"/>
     </row>
     <row r="295" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G295" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>56110 FEV/2026</v>
+        <v>56110 AGO/2025</v>
       </c>
       <c r="H295">
         <v>56110</v>
@@ -20871,36 +20856,36 @@
         <v>88</v>
       </c>
       <c r="J295" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="K295">
-        <v>3</v>
+        <v>5.875</v>
       </c>
       <c r="T295" s="184"/>
     </row>
     <row r="296" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G296" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>73922 AGO/2025</v>
+        <v>56110 FEV/2026</v>
       </c>
       <c r="H296">
-        <v>73922</v>
+        <v>56110</v>
       </c>
       <c r="I296" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J296" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="K296">
-        <v>5.875</v>
+        <v>3</v>
       </c>
       <c r="T296" s="184"/>
     </row>
     <row r="297" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G297" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>73922 FEV/2026</v>
+        <v>73922 AGO/2025</v>
       </c>
       <c r="H297">
         <v>73922</v>
@@ -20909,36 +20894,36 @@
         <v>89</v>
       </c>
       <c r="J297" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="K297">
-        <v>3</v>
+        <v>5.875</v>
       </c>
       <c r="T297" s="184"/>
     </row>
     <row r="298" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G298" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>102953 AGO/2025</v>
+        <v>73922 FEV/2026</v>
       </c>
       <c r="H298">
-        <v>102953</v>
+        <v>73922</v>
       </c>
       <c r="I298" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J298" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="K298">
-        <v>5.875</v>
+        <v>3</v>
       </c>
       <c r="T298" s="184"/>
     </row>
     <row r="299" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G299" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>102953 FEV/2026</v>
+        <v>102953 AGO/2025</v>
       </c>
       <c r="H299">
         <v>102953</v>
@@ -20947,36 +20932,36 @@
         <v>90</v>
       </c>
       <c r="J299" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="K299">
-        <v>3</v>
+        <v>5.875</v>
       </c>
       <c r="T299" s="184"/>
     </row>
     <row r="300" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G300" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>119456 AGO/2025</v>
+        <v>102953 FEV/2026</v>
       </c>
       <c r="H300">
-        <v>119456</v>
+        <v>102953</v>
       </c>
       <c r="I300" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="J300" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="K300">
-        <v>5.875</v>
+        <v>3</v>
       </c>
       <c r="T300" s="184"/>
     </row>
     <row r="301" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G301" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>119456 FEV/2026</v>
+        <v>119456 AGO/2025</v>
       </c>
       <c r="H301">
         <v>119456</v>
@@ -20985,36 +20970,36 @@
         <v>94</v>
       </c>
       <c r="J301" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="K301">
-        <v>3</v>
+        <v>5.875</v>
       </c>
       <c r="T301" s="184"/>
     </row>
     <row r="302" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G302" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>150368 JUL/2025</v>
+        <v>119456 FEV/2026</v>
       </c>
       <c r="H302">
-        <v>150368</v>
+        <v>119456</v>
       </c>
       <c r="I302" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J302" t="s">
-        <v>512</v>
+        <v>778</v>
       </c>
       <c r="K302">
-        <v>5.625</v>
+        <v>3</v>
       </c>
       <c r="T302" s="184"/>
     </row>
     <row r="303" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G303" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>150368 AGO/2025</v>
+        <v>150368 JUL/2025</v>
       </c>
       <c r="H303">
         <v>150368</v>
@@ -21023,17 +21008,17 @@
         <v>91</v>
       </c>
       <c r="J303" t="s">
-        <v>773</v>
+        <v>512</v>
       </c>
       <c r="K303">
-        <v>-0.25</v>
+        <v>5.625</v>
       </c>
       <c r="T303" s="184"/>
     </row>
     <row r="304" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G304" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>150368 SET/2025</v>
+        <v>150368 AGO/2025</v>
       </c>
       <c r="H304">
         <v>150368</v>
@@ -21042,17 +21027,17 @@
         <v>91</v>
       </c>
       <c r="J304" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="K304">
-        <v>0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="T304" s="184"/>
     </row>
     <row r="305" spans="7:20" x14ac:dyDescent="0.35">
       <c r="G305" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>150368 FEV/2026</v>
+        <v>150368 SET/2025</v>
       </c>
       <c r="H305">
         <v>150368</v>
@@ -21061,36 +21046,36 @@
         <v>91</v>
       </c>
       <c r="J305" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="K305">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="T305" s="184"/>
     </row>
     <row r="306" spans="7:20" x14ac:dyDescent="0.35">
       <c r="G306" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>164006 JUL/2025</v>
+        <v>150368 FEV/2026</v>
       </c>
       <c r="H306">
-        <v>164006</v>
+        <v>150368</v>
       </c>
       <c r="I306" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J306" t="s">
-        <v>512</v>
+        <v>778</v>
       </c>
       <c r="K306">
-        <v>5.875</v>
+        <v>3</v>
       </c>
       <c r="T306" s="184"/>
     </row>
     <row r="307" spans="7:20" x14ac:dyDescent="0.35">
       <c r="G307" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>164006 FEV/2026</v>
+        <v>164006 JUL/2025</v>
       </c>
       <c r="H307">
         <v>164006</v>
@@ -21099,36 +21084,36 @@
         <v>93</v>
       </c>
       <c r="J307" t="s">
-        <v>778</v>
+        <v>512</v>
       </c>
       <c r="K307">
-        <v>3</v>
+        <v>5.875</v>
       </c>
       <c r="T307" s="184"/>
     </row>
     <row r="308" spans="7:20" x14ac:dyDescent="0.35">
       <c r="G308" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>167265 JUL/2025</v>
+        <v>164006 FEV/2026</v>
       </c>
       <c r="H308">
-        <v>167265</v>
+        <v>164006</v>
       </c>
       <c r="I308" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J308" t="s">
-        <v>512</v>
+        <v>778</v>
       </c>
       <c r="K308">
-        <v>5.375</v>
+        <v>3</v>
       </c>
       <c r="T308" s="184"/>
     </row>
     <row r="309" spans="7:20" x14ac:dyDescent="0.35">
       <c r="G309" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>167265 AGO/2025</v>
+        <v>167265 JUL/2025</v>
       </c>
       <c r="H309">
         <v>167265</v>
@@ -21137,17 +21122,17 @@
         <v>92</v>
       </c>
       <c r="J309" t="s">
-        <v>773</v>
+        <v>512</v>
       </c>
       <c r="K309">
-        <v>0.5</v>
+        <v>5.375</v>
       </c>
       <c r="T309" s="184"/>
     </row>
     <row r="310" spans="7:20" x14ac:dyDescent="0.35">
       <c r="G310" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>167265 FEV/2026</v>
+        <v>167265 AGO/2025</v>
       </c>
       <c r="H310">
         <v>167265</v>
@@ -21156,36 +21141,36 @@
         <v>92</v>
       </c>
       <c r="J310" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="K310">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="T310" s="184"/>
     </row>
     <row r="311" spans="7:20" x14ac:dyDescent="0.35">
       <c r="G311" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>48374 JUL/2025</v>
+        <v>167265 FEV/2026</v>
       </c>
       <c r="H311">
-        <v>48374</v>
+        <v>167265</v>
       </c>
       <c r="I311" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="J311" t="s">
-        <v>512</v>
+        <v>778</v>
       </c>
       <c r="K311">
-        <v>130.708</v>
+        <v>3</v>
       </c>
       <c r="T311" s="184"/>
     </row>
     <row r="312" spans="7:20" x14ac:dyDescent="0.35">
       <c r="G312" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>48374 AGO/2025</v>
+        <v>48374 JUL/2025</v>
       </c>
       <c r="H312">
         <v>48374</v>
@@ -21194,17 +21179,17 @@
         <v>54</v>
       </c>
       <c r="J312" t="s">
-        <v>773</v>
+        <v>512</v>
       </c>
       <c r="K312">
-        <v>64</v>
+        <v>130.708</v>
       </c>
       <c r="T312" s="184"/>
     </row>
     <row r="313" spans="7:20" x14ac:dyDescent="0.35">
       <c r="G313" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>48374 SET/2025</v>
+        <v>48374 AGO/2025</v>
       </c>
       <c r="H313">
         <v>48374</v>
@@ -21213,17 +21198,17 @@
         <v>54</v>
       </c>
       <c r="J313" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="K313">
-        <v>136.542</v>
+        <v>64</v>
       </c>
       <c r="T313" s="184"/>
     </row>
     <row r="314" spans="7:20" x14ac:dyDescent="0.35">
       <c r="G314" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>48374 OUT/2025</v>
+        <v>48374 SET/2025</v>
       </c>
       <c r="H314">
         <v>48374</v>
@@ -21232,17 +21217,17 @@
         <v>54</v>
       </c>
       <c r="J314" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="K314">
-        <v>214</v>
+        <v>136.542</v>
       </c>
       <c r="T314" s="184"/>
     </row>
     <row r="315" spans="7:20" x14ac:dyDescent="0.35">
       <c r="G315" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>48374 NOV/2025</v>
+        <v>48374 OUT/2025</v>
       </c>
       <c r="H315">
         <v>48374</v>
@@ -21251,17 +21236,17 @@
         <v>54</v>
       </c>
       <c r="J315" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="K315">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="T315" s="184"/>
     </row>
     <row r="316" spans="7:20" x14ac:dyDescent="0.35">
       <c r="G316" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>48374 DEZ/2025</v>
+        <v>48374 NOV/2025</v>
       </c>
       <c r="H316">
         <v>48374</v>
@@ -21270,17 +21255,17 @@
         <v>54</v>
       </c>
       <c r="J316" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="K316">
-        <v>129.417</v>
+        <v>204</v>
       </c>
       <c r="T316" s="184"/>
     </row>
     <row r="317" spans="7:20" x14ac:dyDescent="0.35">
       <c r="G317" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>48374 JAN/2026</v>
+        <v>48374 DEZ/2025</v>
       </c>
       <c r="H317">
         <v>48374</v>
@@ -21289,17 +21274,17 @@
         <v>54</v>
       </c>
       <c r="J317" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="K317">
-        <v>9.9789999999999992</v>
+        <v>129.417</v>
       </c>
       <c r="T317" s="184"/>
     </row>
     <row r="318" spans="7:20" x14ac:dyDescent="0.35">
       <c r="G318" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>48374 FEV/2026</v>
+        <v>48374 JAN/2026</v>
       </c>
       <c r="H318">
         <v>48374</v>
@@ -21308,17 +21293,17 @@
         <v>54</v>
       </c>
       <c r="J318" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="K318">
-        <v>192.167</v>
+        <v>9.9789999999999992</v>
       </c>
       <c r="T318" s="184"/>
     </row>
     <row r="319" spans="7:20" x14ac:dyDescent="0.35">
       <c r="G319" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>48374 MAR/2026</v>
+        <v>48374 FEV/2026</v>
       </c>
       <c r="H319">
         <v>48374</v>
@@ -21327,17 +21312,17 @@
         <v>54</v>
       </c>
       <c r="J319" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="K319">
-        <v>395.5</v>
+        <v>192.167</v>
       </c>
       <c r="T319" s="184"/>
     </row>
     <row r="320" spans="7:20" x14ac:dyDescent="0.35">
       <c r="G320" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>48374 ABR/2026</v>
+        <v>48374 MAR/2026</v>
       </c>
       <c r="H320">
         <v>48374</v>
@@ -21346,17 +21331,17 @@
         <v>54</v>
       </c>
       <c r="J320" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="K320">
-        <v>-8.3000000000000004E-2</v>
+        <v>395.5</v>
       </c>
       <c r="T320" s="184"/>
     </row>
     <row r="321" spans="7:20" x14ac:dyDescent="0.35">
       <c r="G321" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>48374 MAI/2026</v>
+        <v>48374 ABR/2026</v>
       </c>
       <c r="H321">
         <v>48374</v>
@@ -21365,17 +21350,17 @@
         <v>54</v>
       </c>
       <c r="J321" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="K321">
-        <v>186.167</v>
+        <v>-8.3000000000000004E-2</v>
       </c>
       <c r="T321" s="184"/>
     </row>
     <row r="322" spans="7:20" x14ac:dyDescent="0.35">
       <c r="G322" s="29" t="str">
         <f t="shared" si="6"/>
-        <v>48374 JUN/2026</v>
+        <v>48374 MAI/2026</v>
       </c>
       <c r="H322">
         <v>48374</v>
@@ -21384,14 +21369,30 @@
         <v>54</v>
       </c>
       <c r="J322" t="s">
+        <v>781</v>
+      </c>
+      <c r="K322">
+        <v>186.167</v>
+      </c>
+      <c r="T322" s="184"/>
+    </row>
+    <row r="323" spans="7:20" x14ac:dyDescent="0.35">
+      <c r="G323" s="29" t="str">
+        <f t="shared" si="6"/>
+        <v>48374 JUN/2026</v>
+      </c>
+      <c r="H323">
+        <v>48374</v>
+      </c>
+      <c r="I323" t="s">
+        <v>54</v>
+      </c>
+      <c r="J323" t="s">
         <v>782</v>
       </c>
-      <c r="K322">
+      <c r="K323">
         <v>149.625</v>
       </c>
-      <c r="T322" s="184"/>
-    </row>
-    <row r="323" spans="7:20" x14ac:dyDescent="0.35">
       <c r="T323" s="184"/>
     </row>
     <row r="324" spans="7:20" x14ac:dyDescent="0.35">
@@ -22473,138 +22474,138 @@
       <c r="B2" s="150"/>
     </row>
     <row r="3" spans="2:99" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="E3" s="193" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" s="191" t="s">
+      <c r="E3" s="206" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="201" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="202" t="s">
+      <c r="G3" s="203" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="203"/>
-      <c r="I3" s="203"/>
-      <c r="J3" s="203"/>
-      <c r="K3" s="203"/>
-      <c r="L3" s="203"/>
-      <c r="M3" s="203"/>
-      <c r="N3" s="204"/>
-      <c r="O3" s="198" t="s">
+      <c r="H3" s="204"/>
+      <c r="I3" s="204"/>
+      <c r="J3" s="204"/>
+      <c r="K3" s="204"/>
+      <c r="L3" s="204"/>
+      <c r="M3" s="204"/>
+      <c r="N3" s="205"/>
+      <c r="O3" s="191" t="s">
         <v>23</v>
       </c>
-      <c r="P3" s="199"/>
-      <c r="Q3" s="199"/>
-      <c r="R3" s="200"/>
-      <c r="S3" s="198" t="s">
+      <c r="P3" s="192"/>
+      <c r="Q3" s="192"/>
+      <c r="R3" s="193"/>
+      <c r="S3" s="191" t="s">
         <v>24</v>
       </c>
-      <c r="T3" s="199"/>
-      <c r="U3" s="199"/>
-      <c r="V3" s="200"/>
-      <c r="W3" s="198" t="s">
+      <c r="T3" s="192"/>
+      <c r="U3" s="192"/>
+      <c r="V3" s="193"/>
+      <c r="W3" s="191" t="s">
         <v>25</v>
       </c>
-      <c r="X3" s="199"/>
-      <c r="Y3" s="199"/>
-      <c r="Z3" s="201"/>
-      <c r="AB3" s="202" t="s">
+      <c r="X3" s="192"/>
+      <c r="Y3" s="192"/>
+      <c r="Z3" s="194"/>
+      <c r="AB3" s="203" t="s">
         <v>30</v>
       </c>
-      <c r="AC3" s="203"/>
-      <c r="AD3" s="203"/>
-      <c r="AE3" s="203"/>
-      <c r="AF3" s="203"/>
-      <c r="AG3" s="203"/>
-      <c r="AH3" s="203"/>
-      <c r="AI3" s="204"/>
-      <c r="AJ3" s="198" t="s">
+      <c r="AC3" s="204"/>
+      <c r="AD3" s="204"/>
+      <c r="AE3" s="204"/>
+      <c r="AF3" s="204"/>
+      <c r="AG3" s="204"/>
+      <c r="AH3" s="204"/>
+      <c r="AI3" s="205"/>
+      <c r="AJ3" s="191" t="s">
         <v>27</v>
       </c>
-      <c r="AK3" s="199"/>
-      <c r="AL3" s="199"/>
-      <c r="AM3" s="200"/>
-      <c r="AN3" s="198" t="s">
+      <c r="AK3" s="192"/>
+      <c r="AL3" s="192"/>
+      <c r="AM3" s="193"/>
+      <c r="AN3" s="191" t="s">
         <v>28</v>
       </c>
-      <c r="AO3" s="199"/>
-      <c r="AP3" s="199"/>
-      <c r="AQ3" s="200"/>
-      <c r="AR3" s="198" t="s">
+      <c r="AO3" s="192"/>
+      <c r="AP3" s="192"/>
+      <c r="AQ3" s="193"/>
+      <c r="AR3" s="191" t="s">
         <v>29</v>
       </c>
-      <c r="AS3" s="199"/>
-      <c r="AT3" s="199"/>
-      <c r="AU3" s="201"/>
-      <c r="AW3" s="202" t="s">
+      <c r="AS3" s="192"/>
+      <c r="AT3" s="192"/>
+      <c r="AU3" s="194"/>
+      <c r="AW3" s="203" t="s">
         <v>66</v>
       </c>
-      <c r="AX3" s="203"/>
-      <c r="AY3" s="203"/>
-      <c r="AZ3" s="203"/>
-      <c r="BA3" s="203"/>
-      <c r="BB3" s="203"/>
-      <c r="BC3" s="203"/>
-      <c r="BD3" s="204"/>
-      <c r="BE3" s="198" t="s">
+      <c r="AX3" s="204"/>
+      <c r="AY3" s="204"/>
+      <c r="AZ3" s="204"/>
+      <c r="BA3" s="204"/>
+      <c r="BB3" s="204"/>
+      <c r="BC3" s="204"/>
+      <c r="BD3" s="205"/>
+      <c r="BE3" s="191" t="s">
         <v>67</v>
       </c>
-      <c r="BF3" s="199"/>
-      <c r="BG3" s="199"/>
-      <c r="BH3" s="200"/>
-      <c r="BI3" s="198" t="s">
+      <c r="BF3" s="192"/>
+      <c r="BG3" s="192"/>
+      <c r="BH3" s="193"/>
+      <c r="BI3" s="191" t="s">
         <v>68</v>
       </c>
-      <c r="BJ3" s="199"/>
-      <c r="BK3" s="199"/>
-      <c r="BL3" s="200"/>
-      <c r="BM3" s="198" t="s">
+      <c r="BJ3" s="192"/>
+      <c r="BK3" s="192"/>
+      <c r="BL3" s="193"/>
+      <c r="BM3" s="191" t="s">
         <v>72</v>
       </c>
-      <c r="BN3" s="199"/>
-      <c r="BO3" s="199"/>
-      <c r="BP3" s="201"/>
-      <c r="BR3" s="202" t="s">
+      <c r="BN3" s="192"/>
+      <c r="BO3" s="192"/>
+      <c r="BP3" s="194"/>
+      <c r="BR3" s="203" t="s">
         <v>73</v>
       </c>
-      <c r="BS3" s="203"/>
-      <c r="BT3" s="203"/>
-      <c r="BU3" s="203"/>
-      <c r="BV3" s="203"/>
-      <c r="BW3" s="203"/>
-      <c r="BX3" s="203"/>
-      <c r="BY3" s="204"/>
+      <c r="BS3" s="204"/>
+      <c r="BT3" s="204"/>
+      <c r="BU3" s="204"/>
+      <c r="BV3" s="204"/>
+      <c r="BW3" s="204"/>
+      <c r="BX3" s="204"/>
+      <c r="BY3" s="205"/>
       <c r="BZ3" s="185" t="s">
         <v>69</v>
       </c>
       <c r="CA3" s="186"/>
       <c r="CB3" s="186"/>
       <c r="CC3" s="186"/>
-      <c r="CD3" s="198" t="s">
+      <c r="CD3" s="191" t="s">
         <v>70</v>
       </c>
-      <c r="CE3" s="199"/>
-      <c r="CF3" s="199"/>
-      <c r="CG3" s="200"/>
-      <c r="CH3" s="198" t="s">
+      <c r="CE3" s="192"/>
+      <c r="CF3" s="192"/>
+      <c r="CG3" s="193"/>
+      <c r="CH3" s="191" t="s">
         <v>71</v>
       </c>
-      <c r="CI3" s="199"/>
-      <c r="CJ3" s="199"/>
-      <c r="CK3" s="201"/>
-      <c r="CM3" s="195" t="s">
+      <c r="CI3" s="192"/>
+      <c r="CJ3" s="192"/>
+      <c r="CK3" s="194"/>
+      <c r="CM3" s="208" t="s">
         <v>783</v>
       </c>
-      <c r="CN3" s="196"/>
-      <c r="CO3" s="196"/>
-      <c r="CP3" s="196"/>
-      <c r="CQ3" s="196"/>
-      <c r="CR3" s="196"/>
-      <c r="CS3" s="196"/>
-      <c r="CT3" s="197"/>
+      <c r="CN3" s="209"/>
+      <c r="CO3" s="209"/>
+      <c r="CP3" s="209"/>
+      <c r="CQ3" s="209"/>
+      <c r="CR3" s="209"/>
+      <c r="CS3" s="209"/>
+      <c r="CT3" s="210"/>
     </row>
     <row r="4" spans="2:99" ht="26" x14ac:dyDescent="0.3">
-      <c r="E4" s="194"/>
-      <c r="F4" s="192"/>
+      <c r="E4" s="207"/>
+      <c r="F4" s="202"/>
       <c r="G4" s="146" t="s">
         <v>169</v>
       </c>
@@ -23136,7 +23137,7 @@
       </c>
       <c r="BU5" s="34">
         <f>SUMIF(Rede!$C:$C,Geral!E5,Rede!$BU:$BU)</f>
-        <v>0</v>
+        <v>169.167</v>
       </c>
       <c r="BV5" s="34">
         <f>SUMIF(Rede!$C:$C,Geral!E5,Rede!$BV:$BV)</f>
@@ -23144,15 +23145,15 @@
       </c>
       <c r="BW5" s="36">
         <f>(BT5+BU5+BV5)/BS5</f>
-        <v>0.55766202737183956</v>
+        <v>0.59690280677337049</v>
       </c>
       <c r="BX5" s="37">
         <f>IFERROR(((BT5+BU5+BV5)/BR5-1),0)</f>
-        <v>0.74174311893371803</v>
+        <v>0.86430365587097602</v>
       </c>
       <c r="BY5" s="40">
         <f>BS5-BT5-BU5-BV5</f>
-        <v>1906.9189999999999</v>
+        <v>1737.752</v>
       </c>
       <c r="BZ5" s="67">
         <f>SUMIF(Rede!$C:$C,Geral!E5,Rede!$BZ:$BZ)</f>
@@ -23200,7 +23201,7 @@
       </c>
       <c r="CK5" s="64">
         <f>SUMIF(Rede!$C:$C,Geral!E5,Rede!$CK:$CK)</f>
-        <v>0</v>
+        <v>169.167</v>
       </c>
       <c r="CL5" s="7"/>
       <c r="CM5" s="39">
@@ -23217,7 +23218,7 @@
       </c>
       <c r="CP5" s="34">
         <f t="shared" si="1"/>
-        <v>429.33199999999999</v>
+        <v>598.49900000000002</v>
       </c>
       <c r="CQ5" s="34">
         <f t="shared" si="1"/>
@@ -23225,15 +23226,15 @@
       </c>
       <c r="CR5" s="36">
         <f t="shared" ref="CR5:CR6" si="2">(CO5+CP5+CQ5)/CN5</f>
-        <v>1.1505239341832791</v>
+        <v>1.1600994689560054</v>
       </c>
       <c r="CS5" s="37">
         <f t="shared" ref="CS5:CS6" si="3">IFERROR(((CO5+CP5+CQ5)/CM5-1),0)</f>
-        <v>0.21202825625018806</v>
+        <v>0.22211567674482446</v>
       </c>
       <c r="CT5" s="40">
         <f t="shared" ref="CT5:CT6" si="4">CN5-CO5-CQ5-CP5</f>
-        <v>-2659.243893773014</v>
+        <v>-2828.4108937730143</v>
       </c>
       <c r="CU5" s="21"/>
     </row>
@@ -23497,11 +23498,11 @@
       </c>
       <c r="BT6" s="34">
         <f>SUMIF(Rede!$C:$C,Geral!E6,Rede!$BT:$BT)</f>
-        <v>3378.96</v>
+        <v>3383.96</v>
       </c>
       <c r="BU6" s="34">
         <f>SUMIF(Rede!$C:$C,Geral!E6,Rede!$BU:$BU)</f>
-        <v>225</v>
+        <v>1126</v>
       </c>
       <c r="BV6" s="34">
         <f>SUMIF(Rede!$C:$C,Geral!E6,Rede!$BV:$BV)</f>
@@ -23509,15 +23510,15 @@
       </c>
       <c r="BW6" s="36">
         <f>(BT6+BU6+BV6)/BS6</f>
-        <v>0.5708004888481516</v>
+        <v>0.7092056217537428</v>
       </c>
       <c r="BX6" s="37">
         <f>IFERROR(((BT6+BU6+BV6)/BR6-1),0)</f>
-        <v>4.1252314034916138E-2</v>
+        <v>0.29373048763121679</v>
       </c>
       <c r="BY6" s="40">
         <f>BS6-BT6-BU6-BV6</f>
-        <v>2809.54</v>
+        <v>1903.54</v>
       </c>
       <c r="BZ6" s="67">
         <f>SUMIF(Rede!$C:$C,Geral!E6,Rede!$BZ:$BZ)</f>
@@ -23557,7 +23558,7 @@
       </c>
       <c r="CI6" s="64">
         <f>SUMIF(Rede!$C:$C,Geral!E6,Rede!$CI:$CI)</f>
-        <v>697.43799999999999</v>
+        <v>702.43799999999999</v>
       </c>
       <c r="CJ6" s="64">
         <f>SUMIF(Rede!$C:$C,Geral!E6,Rede!$CJ:$CJ)</f>
@@ -23565,7 +23566,7 @@
       </c>
       <c r="CK6" s="64">
         <f>SUMIF(Rede!$C:$C,Geral!E6,Rede!$CK:$CK)</f>
-        <v>225</v>
+        <v>1126</v>
       </c>
       <c r="CL6" s="7"/>
       <c r="CM6" s="39">
@@ -23578,11 +23579,11 @@
       </c>
       <c r="CO6" s="34">
         <f t="shared" si="1"/>
-        <v>21891.319</v>
+        <v>21896.319</v>
       </c>
       <c r="CP6" s="34">
         <f t="shared" si="1"/>
-        <v>462.25</v>
+        <v>1363.25</v>
       </c>
       <c r="CQ6" s="34">
         <f t="shared" si="1"/>
@@ -23590,15 +23591,15 @@
       </c>
       <c r="CR6" s="36">
         <f t="shared" si="2"/>
-        <v>0.83718685546257399</v>
+        <v>0.87091846462240941</v>
       </c>
       <c r="CS6" s="37">
         <f t="shared" si="3"/>
-        <v>-0.11348353655351318</v>
+        <v>-7.7764357897496583E-2</v>
       </c>
       <c r="CT6" s="40">
         <f t="shared" si="4"/>
-        <v>4373.0113275042931</v>
+        <v>3467.0113275042931</v>
       </c>
       <c r="CU6" s="21"/>
     </row>
@@ -23863,11 +23864,11 @@
       </c>
       <c r="BT7" s="49">
         <f>SUM(BT5:BT6)</f>
-        <v>5715.7080000000005</v>
+        <v>5720.7080000000005</v>
       </c>
       <c r="BU7" s="49">
         <f>SUM(BU5:BU6)</f>
-        <v>225</v>
+        <v>1295.1669999999999</v>
       </c>
       <c r="BV7" s="49">
         <f>SUM(BV5:BV6)</f>
@@ -23875,15 +23876,15 @@
       </c>
       <c r="BW7" s="48">
         <f t="shared" ref="BW7" si="12">(BT7+BU7+BV7)/BS7</f>
-        <v>0.56558358662613983</v>
+        <v>0.6646134291240674</v>
       </c>
       <c r="BX7" s="47">
         <f t="shared" ref="BX7" si="13">IFERROR(((BT7+BU7+BV7)/BR7-1),0)</f>
-        <v>0.23584408966365866</v>
+        <v>0.45223199137319958</v>
       </c>
       <c r="BY7" s="46">
         <f t="shared" ref="BY7" si="14">BS7-BT7-BU7-BV7</f>
-        <v>4716.4589999999998</v>
+        <v>3641.2919999999995</v>
       </c>
       <c r="BZ7" s="68">
         <f t="shared" ref="BZ7:CK7" si="15">SUM(BZ5:BZ6)</f>
@@ -23923,7 +23924,7 @@
       </c>
       <c r="CI7" s="69">
         <f t="shared" si="15"/>
-        <v>1606.7559999999999</v>
+        <v>1611.7559999999999</v>
       </c>
       <c r="CJ7" s="69">
         <f t="shared" si="15"/>
@@ -23931,7 +23932,7 @@
       </c>
       <c r="CK7" s="69">
         <f t="shared" si="15"/>
-        <v>225</v>
+        <v>1295.1669999999999</v>
       </c>
       <c r="CL7" s="8"/>
       <c r="CM7" s="41">
@@ -23944,11 +23945,11 @@
       </c>
       <c r="CO7" s="49">
         <f>SUM(CO5:CO6)</f>
-        <v>41720.483</v>
+        <v>41725.483</v>
       </c>
       <c r="CP7" s="49">
         <f>SUM(CP5:CP6)</f>
-        <v>891.58199999999999</v>
+        <v>1961.749</v>
       </c>
       <c r="CQ7" s="49">
         <f>SUM(CQ5:CQ6)</f>
@@ -23956,15 +23957,15 @@
       </c>
       <c r="CR7" s="48">
         <f t="shared" ref="CR7" si="16">(CO7+CP7+CQ7)/CN7</f>
-        <v>0.96151057110461557</v>
+        <v>0.98565770039570277</v>
       </c>
       <c r="CS7" s="47">
         <f t="shared" ref="CS7" si="17">IFERROR(((CO7+CP7+CQ7)/CM7-1),0)</f>
-        <v>1.6074145204110213E-2</v>
+        <v>4.1591570067559758E-2</v>
       </c>
       <c r="CT7" s="46">
         <f>CN7-CO7-CQ7-CP7</f>
-        <v>1713.7674337312792</v>
+        <v>638.60043373127905</v>
       </c>
       <c r="CU7" s="21"/>
     </row>
@@ -23972,14 +23973,14 @@
       <c r="B8" s="3"/>
       <c r="C8" s="2"/>
       <c r="E8" s="133" t="s">
-        <v>847</v>
+        <v>828</v>
       </c>
     </row>
     <row r="9" spans="2:99" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="3"/>
       <c r="C9" s="2"/>
       <c r="E9" s="190">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
@@ -24007,137 +24008,137 @@
       <c r="CK9" s="11"/>
     </row>
     <row r="10" spans="2:99" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="208" t="s">
+      <c r="B10" s="198" t="s">
         <v>784</v>
       </c>
-      <c r="C10" s="209"/>
-      <c r="D10" s="209"/>
-      <c r="E10" s="210"/>
-      <c r="F10" s="191" t="s">
+      <c r="C10" s="199"/>
+      <c r="D10" s="199"/>
+      <c r="E10" s="200"/>
+      <c r="F10" s="201" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="202" t="s">
+      <c r="G10" s="203" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="203"/>
-      <c r="I10" s="203"/>
-      <c r="J10" s="203"/>
-      <c r="K10" s="203"/>
-      <c r="L10" s="203"/>
-      <c r="M10" s="203"/>
-      <c r="N10" s="204"/>
-      <c r="O10" s="198" t="s">
+      <c r="H10" s="204"/>
+      <c r="I10" s="204"/>
+      <c r="J10" s="204"/>
+      <c r="K10" s="204"/>
+      <c r="L10" s="204"/>
+      <c r="M10" s="204"/>
+      <c r="N10" s="205"/>
+      <c r="O10" s="191" t="s">
         <v>23</v>
       </c>
-      <c r="P10" s="199"/>
-      <c r="Q10" s="199"/>
-      <c r="R10" s="200"/>
-      <c r="S10" s="198" t="s">
+      <c r="P10" s="192"/>
+      <c r="Q10" s="192"/>
+      <c r="R10" s="193"/>
+      <c r="S10" s="191" t="s">
         <v>24</v>
       </c>
-      <c r="T10" s="199"/>
-      <c r="U10" s="199"/>
-      <c r="V10" s="200"/>
-      <c r="W10" s="198" t="s">
+      <c r="T10" s="192"/>
+      <c r="U10" s="192"/>
+      <c r="V10" s="193"/>
+      <c r="W10" s="191" t="s">
         <v>25</v>
       </c>
-      <c r="X10" s="199"/>
-      <c r="Y10" s="199"/>
-      <c r="Z10" s="201"/>
-      <c r="AB10" s="202" t="s">
+      <c r="X10" s="192"/>
+      <c r="Y10" s="192"/>
+      <c r="Z10" s="194"/>
+      <c r="AB10" s="203" t="s">
         <v>30</v>
       </c>
-      <c r="AC10" s="203"/>
-      <c r="AD10" s="203"/>
-      <c r="AE10" s="203"/>
-      <c r="AF10" s="203"/>
-      <c r="AG10" s="203"/>
-      <c r="AH10" s="203"/>
-      <c r="AI10" s="204"/>
-      <c r="AJ10" s="198" t="s">
+      <c r="AC10" s="204"/>
+      <c r="AD10" s="204"/>
+      <c r="AE10" s="204"/>
+      <c r="AF10" s="204"/>
+      <c r="AG10" s="204"/>
+      <c r="AH10" s="204"/>
+      <c r="AI10" s="205"/>
+      <c r="AJ10" s="191" t="s">
         <v>27</v>
       </c>
-      <c r="AK10" s="199"/>
-      <c r="AL10" s="199"/>
-      <c r="AM10" s="200"/>
-      <c r="AN10" s="198" t="s">
+      <c r="AK10" s="192"/>
+      <c r="AL10" s="192"/>
+      <c r="AM10" s="193"/>
+      <c r="AN10" s="191" t="s">
         <v>28</v>
       </c>
-      <c r="AO10" s="199"/>
-      <c r="AP10" s="199"/>
-      <c r="AQ10" s="200"/>
-      <c r="AR10" s="198" t="s">
+      <c r="AO10" s="192"/>
+      <c r="AP10" s="192"/>
+      <c r="AQ10" s="193"/>
+      <c r="AR10" s="191" t="s">
         <v>29</v>
       </c>
-      <c r="AS10" s="199"/>
-      <c r="AT10" s="199"/>
-      <c r="AU10" s="201"/>
-      <c r="AW10" s="202" t="s">
+      <c r="AS10" s="192"/>
+      <c r="AT10" s="192"/>
+      <c r="AU10" s="194"/>
+      <c r="AW10" s="203" t="s">
         <v>66</v>
       </c>
-      <c r="AX10" s="203"/>
-      <c r="AY10" s="203"/>
-      <c r="AZ10" s="203"/>
-      <c r="BA10" s="203"/>
-      <c r="BB10" s="203"/>
-      <c r="BC10" s="203"/>
-      <c r="BD10" s="204"/>
-      <c r="BE10" s="198" t="s">
+      <c r="AX10" s="204"/>
+      <c r="AY10" s="204"/>
+      <c r="AZ10" s="204"/>
+      <c r="BA10" s="204"/>
+      <c r="BB10" s="204"/>
+      <c r="BC10" s="204"/>
+      <c r="BD10" s="205"/>
+      <c r="BE10" s="191" t="s">
         <v>67</v>
       </c>
-      <c r="BF10" s="199"/>
-      <c r="BG10" s="199"/>
-      <c r="BH10" s="200"/>
-      <c r="BI10" s="198" t="s">
+      <c r="BF10" s="192"/>
+      <c r="BG10" s="192"/>
+      <c r="BH10" s="193"/>
+      <c r="BI10" s="191" t="s">
         <v>68</v>
       </c>
-      <c r="BJ10" s="199"/>
-      <c r="BK10" s="199"/>
-      <c r="BL10" s="200"/>
-      <c r="BM10" s="198" t="s">
+      <c r="BJ10" s="192"/>
+      <c r="BK10" s="192"/>
+      <c r="BL10" s="193"/>
+      <c r="BM10" s="191" t="s">
         <v>72</v>
       </c>
-      <c r="BN10" s="199"/>
-      <c r="BO10" s="199"/>
-      <c r="BP10" s="201"/>
-      <c r="BR10" s="202" t="s">
+      <c r="BN10" s="192"/>
+      <c r="BO10" s="192"/>
+      <c r="BP10" s="194"/>
+      <c r="BR10" s="203" t="s">
         <v>73</v>
       </c>
-      <c r="BS10" s="203"/>
-      <c r="BT10" s="203"/>
-      <c r="BU10" s="203"/>
-      <c r="BV10" s="203"/>
-      <c r="BW10" s="203"/>
-      <c r="BX10" s="203"/>
-      <c r="BY10" s="204"/>
+      <c r="BS10" s="204"/>
+      <c r="BT10" s="204"/>
+      <c r="BU10" s="204"/>
+      <c r="BV10" s="204"/>
+      <c r="BW10" s="204"/>
+      <c r="BX10" s="204"/>
+      <c r="BY10" s="205"/>
       <c r="BZ10" s="185" t="s">
         <v>69</v>
       </c>
       <c r="CA10" s="186"/>
       <c r="CB10" s="186"/>
       <c r="CC10" s="186"/>
-      <c r="CD10" s="198" t="s">
+      <c r="CD10" s="191" t="s">
         <v>70</v>
       </c>
-      <c r="CE10" s="199"/>
-      <c r="CF10" s="199"/>
-      <c r="CG10" s="200"/>
-      <c r="CH10" s="198" t="s">
+      <c r="CE10" s="192"/>
+      <c r="CF10" s="192"/>
+      <c r="CG10" s="193"/>
+      <c r="CH10" s="191" t="s">
         <v>71</v>
       </c>
-      <c r="CI10" s="199"/>
-      <c r="CJ10" s="199"/>
-      <c r="CK10" s="201"/>
-      <c r="CM10" s="195" t="s">
+      <c r="CI10" s="192"/>
+      <c r="CJ10" s="192"/>
+      <c r="CK10" s="194"/>
+      <c r="CM10" s="208" t="s">
         <v>783</v>
       </c>
-      <c r="CN10" s="196"/>
-      <c r="CO10" s="196"/>
-      <c r="CP10" s="196"/>
-      <c r="CQ10" s="196"/>
-      <c r="CR10" s="196"/>
-      <c r="CS10" s="196"/>
-      <c r="CT10" s="197"/>
+      <c r="CN10" s="209"/>
+      <c r="CO10" s="209"/>
+      <c r="CP10" s="209"/>
+      <c r="CQ10" s="209"/>
+      <c r="CR10" s="209"/>
+      <c r="CS10" s="209"/>
+      <c r="CT10" s="210"/>
     </row>
     <row r="11" spans="2:99" ht="26" x14ac:dyDescent="0.3">
       <c r="B11" s="52" t="s">
@@ -24152,7 +24153,7 @@
       <c r="E11" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="192"/>
+      <c r="F11" s="202"/>
       <c r="G11" s="38" t="s">
         <v>169</v>
       </c>
@@ -25065,7 +25066,7 @@
       </c>
       <c r="BU13" s="35">
         <f>SUMIF(Rede!$D:$D,Geral!C13,Rede!$BU:$BU)</f>
-        <v>0</v>
+        <v>169.167</v>
       </c>
       <c r="BV13" s="35">
         <f>SUMIF(Rede!$D:$D,Geral!C13,Rede!$BV:$BV)</f>
@@ -25073,15 +25074,15 @@
       </c>
       <c r="BW13" s="36">
         <f t="shared" si="24"/>
-        <v>0.67331558441558448</v>
+        <v>0.74654805194805196</v>
       </c>
       <c r="BX13" s="37">
         <f t="shared" si="25"/>
-        <v>1.4302408429973661</v>
+        <v>1.694563454489205</v>
       </c>
       <c r="BY13" s="40">
         <f t="shared" si="26"/>
-        <v>754.64099999999996</v>
+        <v>585.47399999999993</v>
       </c>
       <c r="BZ13" s="67">
         <f>SUMIF(Rede!$D:$D,Geral!C13,Rede!$BZ:$BZ)</f>
@@ -25129,7 +25130,7 @@
       </c>
       <c r="CK13" s="64">
         <f>SUMIF(Rede!$D:$D,Geral!C13,Rede!$CK:$CK)</f>
-        <v>0</v>
+        <v>169.167</v>
       </c>
       <c r="CL13" s="7"/>
       <c r="CM13" s="39">
@@ -25146,7 +25147,7 @@
       </c>
       <c r="CP13" s="34">
         <f t="shared" si="27"/>
-        <v>333.62400000000002</v>
+        <v>502.79100000000005</v>
       </c>
       <c r="CQ13" s="34">
         <f t="shared" si="27"/>
@@ -25154,15 +25155,15 @@
       </c>
       <c r="CR13" s="36">
         <f t="shared" ref="CR13:CR19" si="31">(CO13+CP13+CQ13)/CN13</f>
-        <v>1.3673891398955544</v>
+        <v>1.3852631728048863</v>
       </c>
       <c r="CS13" s="37">
         <f t="shared" ref="CS13:CS19" si="32">IFERROR(((CO13+CP13+CQ13)/CM13-1),0)</f>
-        <v>0.47485552327867286</v>
+        <v>0.4941343191901324</v>
       </c>
       <c r="CT13" s="40">
         <f t="shared" ref="CT13:CT19" si="33">CN13-CO13-CQ13-CP13</f>
-        <v>-3477.117835911733</v>
+        <v>-3646.2848359117329</v>
       </c>
       <c r="CU13" s="21"/>
     </row>
@@ -26553,11 +26554,11 @@
       </c>
       <c r="BT17" s="35">
         <f>SUMIF(Rede!$D:$D,Geral!C17,Rede!$BT:$BT)</f>
-        <v>902.79300000000012</v>
+        <v>907.79300000000012</v>
       </c>
       <c r="BU17" s="35">
         <f>SUMIF(Rede!$D:$D,Geral!C17,Rede!$BU:$BU)</f>
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="BV17" s="35">
         <f>SUMIF(Rede!$D:$D,Geral!C17,Rede!$BV:$BV)</f>
@@ -26613,7 +26614,7 @@
       </c>
       <c r="CI17" s="64">
         <f>SUMIF(Rede!$D:$D,Geral!C17,Rede!$CI:$CI)</f>
-        <v>394.10500000000002</v>
+        <v>399.10500000000002</v>
       </c>
       <c r="CJ17" s="64">
         <f>SUMIF(Rede!$D:$D,Geral!C17,Rede!$CJ:$CJ)</f>
@@ -26621,7 +26622,7 @@
       </c>
       <c r="CK17" s="64">
         <f>SUMIF(Rede!$D:$D,Geral!C17,Rede!$CK:$CK)</f>
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="CL17" s="7"/>
       <c r="CM17" s="39">
@@ -26634,11 +26635,11 @@
       </c>
       <c r="CO17" s="34">
         <f t="shared" si="27"/>
-        <v>5387.7520000000004</v>
+        <v>5392.7520000000004</v>
       </c>
       <c r="CP17" s="34">
         <f t="shared" si="27"/>
-        <v>250.583</v>
+        <v>245.583</v>
       </c>
       <c r="CQ17" s="34">
         <f t="shared" si="27"/>
@@ -27303,7 +27304,7 @@
       </c>
       <c r="BU19" s="35">
         <f>SUMIF(Rede!$D:$D,Geral!C19,Rede!$BU:$BU)</f>
-        <v>0</v>
+        <v>906</v>
       </c>
       <c r="BV19" s="35">
         <f>SUMIF(Rede!$D:$D,Geral!C19,Rede!$BV:$BV)</f>
@@ -27311,15 +27312,15 @@
       </c>
       <c r="BW19" s="36">
         <f t="shared" si="24"/>
-        <v>0.56095890410958904</v>
+        <v>0.97465753424657531</v>
       </c>
       <c r="BX19" s="37">
         <f t="shared" si="25"/>
-        <v>9.2487771535980645E-3</v>
+        <v>0.7535543466295116</v>
       </c>
       <c r="BY19" s="40">
         <f>BS19-BT19-BU19-BV19</f>
-        <v>961.5</v>
+        <v>55.5</v>
       </c>
       <c r="BZ19" s="67">
         <f>SUMIF(Rede!$D:$D,Geral!C19,Rede!$BZ:$BZ)</f>
@@ -27367,7 +27368,7 @@
       </c>
       <c r="CK19" s="64">
         <f>SUMIF(Rede!$D:$D,Geral!C19,Rede!$CK:$CK)</f>
-        <v>0</v>
+        <v>906</v>
       </c>
       <c r="CL19" s="7"/>
       <c r="CM19" s="39">
@@ -27384,7 +27385,7 @@
       </c>
       <c r="CP19" s="34">
         <f t="shared" si="27"/>
-        <v>22.417000000000002</v>
+        <v>928.41700000000003</v>
       </c>
       <c r="CQ19" s="34">
         <f t="shared" si="27"/>
@@ -27392,25 +27393,25 @@
       </c>
       <c r="CR19" s="36">
         <f t="shared" si="31"/>
-        <v>1.0136822059843611</v>
+        <v>1.1145006987284869</v>
       </c>
       <c r="CS19" s="37">
         <f t="shared" si="32"/>
-        <v>5.3425482708173044E-2</v>
+        <v>0.15819675003229294</v>
       </c>
       <c r="CT19" s="40">
         <f t="shared" si="33"/>
-        <v>-122.95441326713862</v>
+        <v>-1028.9544132671385</v>
       </c>
       <c r="CU19" s="21"/>
     </row>
     <row r="20" spans="2:99" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="205" t="s">
+      <c r="B20" s="195" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="206"/>
-      <c r="D20" s="206"/>
-      <c r="E20" s="207"/>
+      <c r="C20" s="196"/>
+      <c r="D20" s="196"/>
+      <c r="E20" s="197"/>
       <c r="F20" s="113">
         <f>SUM(F12:F19)</f>
         <v>14</v>
@@ -27665,11 +27666,11 @@
       </c>
       <c r="BT20" s="56">
         <f>SUBTOTAL(9,BT12:BT19)</f>
-        <v>5715.7080000000005</v>
+        <v>5720.7080000000005</v>
       </c>
       <c r="BU20" s="56">
         <f>SUBTOTAL(9,BU12:BU19)</f>
-        <v>225</v>
+        <v>1295.1669999999999</v>
       </c>
       <c r="BV20" s="56">
         <f>SUBTOTAL(9,BV12:BV19)</f>
@@ -27677,15 +27678,15 @@
       </c>
       <c r="BW20" s="47">
         <f t="shared" si="24"/>
-        <v>0.56558358662613983</v>
+        <v>0.6646134291240674</v>
       </c>
       <c r="BX20" s="47">
         <f t="shared" si="25"/>
-        <v>0.23584408966365866</v>
+        <v>0.45223199137319958</v>
       </c>
       <c r="BY20" s="57">
         <f t="shared" si="26"/>
-        <v>4716.4589999999998</v>
+        <v>3641.2919999999995</v>
       </c>
       <c r="BZ20" s="70">
         <f t="shared" ref="BZ20:CK20" si="59">SUM(BZ12:BZ19)</f>
@@ -27725,7 +27726,7 @@
       </c>
       <c r="CI20" s="71">
         <f t="shared" si="59"/>
-        <v>1606.7560000000001</v>
+        <v>1611.7560000000001</v>
       </c>
       <c r="CJ20" s="71">
         <f t="shared" si="59"/>
@@ -27733,7 +27734,7 @@
       </c>
       <c r="CK20" s="71">
         <f t="shared" si="59"/>
-        <v>225</v>
+        <v>1295.1669999999999</v>
       </c>
       <c r="CM20" s="55">
         <f>SUBTOTAL(9,CM12:CM19)</f>
@@ -27745,11 +27746,11 @@
       </c>
       <c r="CO20" s="56">
         <f>SUBTOTAL(9,CO12:CO19)</f>
-        <v>41720.482999999993</v>
+        <v>41725.482999999993</v>
       </c>
       <c r="CP20" s="56">
         <f>SUBTOTAL(9,CP12:CP19)</f>
-        <v>891.58200000000011</v>
+        <v>1961.7489999999998</v>
       </c>
       <c r="CQ20" s="56">
         <f>SUBTOTAL(9,CQ12:CQ19)</f>
@@ -27757,15 +27758,15 @@
       </c>
       <c r="CR20" s="47">
         <f t="shared" ref="CR20" si="60">(CO20+CP20+CQ20)/CN20</f>
-        <v>0.96151057110461557</v>
+        <v>0.98565770039570255</v>
       </c>
       <c r="CS20" s="47">
         <f t="shared" ref="CS20" si="61">IFERROR(((CO20+CP20+CQ20)/CM20-1),0)</f>
-        <v>1.6074145204109769E-2</v>
+        <v>4.1591570067559314E-2</v>
       </c>
       <c r="CT20" s="57">
         <f>CN20-CO20-CQ20-CP20</f>
-        <v>1713.767433731279</v>
+        <v>638.60043373127928</v>
       </c>
       <c r="CU20" s="21"/>
     </row>
@@ -27987,11 +27988,22 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="AN10:AQ10"/>
-    <mergeCell ref="AR10:AU10"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="CM3:CT3"/>
+    <mergeCell ref="CM10:CT10"/>
+    <mergeCell ref="CD10:CG10"/>
+    <mergeCell ref="CH10:CK10"/>
+    <mergeCell ref="BR3:BY3"/>
+    <mergeCell ref="BR10:BY10"/>
+    <mergeCell ref="CD3:CG3"/>
+    <mergeCell ref="CH3:CK3"/>
+    <mergeCell ref="BI3:BL3"/>
+    <mergeCell ref="BM3:BP3"/>
+    <mergeCell ref="BE3:BH3"/>
+    <mergeCell ref="BE10:BH10"/>
+    <mergeCell ref="AW10:BD10"/>
+    <mergeCell ref="BI10:BL10"/>
     <mergeCell ref="BM10:BP10"/>
     <mergeCell ref="AW3:BD3"/>
     <mergeCell ref="G3:N3"/>
@@ -28008,22 +28020,11 @@
     <mergeCell ref="O3:R3"/>
     <mergeCell ref="S3:V3"/>
     <mergeCell ref="W3:Z3"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="CM3:CT3"/>
-    <mergeCell ref="CM10:CT10"/>
-    <mergeCell ref="CD10:CG10"/>
-    <mergeCell ref="CH10:CK10"/>
-    <mergeCell ref="BR3:BY3"/>
-    <mergeCell ref="BR10:BY10"/>
-    <mergeCell ref="CD3:CG3"/>
-    <mergeCell ref="CH3:CK3"/>
-    <mergeCell ref="BI3:BL3"/>
-    <mergeCell ref="BM3:BP3"/>
-    <mergeCell ref="BE3:BH3"/>
-    <mergeCell ref="BE10:BH10"/>
-    <mergeCell ref="AW10:BD10"/>
-    <mergeCell ref="BI10:BL10"/>
+    <mergeCell ref="AN10:AQ10"/>
+    <mergeCell ref="AR10:AU10"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="F10:F11"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="L5:L7 AG5:AG7 BB5:BB7 BW5:BW7 CR5:CR7 L12:L20 AG12:AG20 BB12:BB20 BW12:BW20 CR12:CR20">
@@ -29246,11 +29247,11 @@
       </c>
       <c r="BT7" s="75">
         <f>SUBTOTAL(9,BT10:BT23)</f>
-        <v>5715.7080000000005</v>
+        <v>5720.7080000000005</v>
       </c>
       <c r="BU7" s="75">
         <f>SUBTOTAL(9,BU10:BU23)</f>
-        <v>225</v>
+        <v>1295.1669999999999</v>
       </c>
       <c r="BV7" s="75">
         <f>SUBTOTAL(9,BV10:BV23)</f>
@@ -29258,15 +29259,15 @@
       </c>
       <c r="BW7" s="76">
         <f>IFERROR(((BT7+BV7+BU7)/BS7),0)</f>
-        <v>0.56558358662613983</v>
+        <v>0.66461342912406751</v>
       </c>
       <c r="BX7" s="77">
         <f>IFERROR(((BT7+BU7+BV7)/BR7-1),0)</f>
-        <v>0.23584408966365866</v>
+        <v>0.45223199137319958</v>
       </c>
       <c r="BY7" s="78">
         <f>BS7-BT7-BU7-BV7</f>
-        <v>4716.4589999999998</v>
+        <v>3641.2919999999995</v>
       </c>
       <c r="BZ7" s="74">
         <f t="shared" ref="BZ7:CK7" si="3">SUBTOTAL(9,BZ10:BZ23)</f>
@@ -29306,7 +29307,7 @@
       </c>
       <c r="CI7" s="75">
         <f t="shared" si="3"/>
-        <v>1606.7560000000001</v>
+        <v>1611.7560000000001</v>
       </c>
       <c r="CJ7" s="75">
         <f t="shared" si="3"/>
@@ -29314,7 +29315,7 @@
       </c>
       <c r="CK7" s="75">
         <f t="shared" si="3"/>
-        <v>225</v>
+        <v>1295.1669999999999</v>
       </c>
       <c r="CM7" s="74">
         <f>SUBTOTAL(9,CM10:CM23)</f>
@@ -29326,11 +29327,11 @@
       </c>
       <c r="CO7" s="75">
         <f>SUBTOTAL(9,CO10:CO23)</f>
-        <v>41720.483</v>
+        <v>41725.483</v>
       </c>
       <c r="CP7" s="75">
         <f>SUBTOTAL(9,CP10:CP23)</f>
-        <v>891.58200000000011</v>
+        <v>1961.7489999999998</v>
       </c>
       <c r="CQ7" s="75">
         <f>SUBTOTAL(9,CQ10:CQ23)</f>
@@ -29338,15 +29339,15 @@
       </c>
       <c r="CR7" s="76">
         <f>IFERROR(((CO7+CQ7+CP7)/CN7),0)</f>
-        <v>0.96151057110461569</v>
+        <v>0.98565770039570288</v>
       </c>
       <c r="CS7" s="77">
         <f>IFERROR(((CO7+CP7+CQ7)/CM7-1),0)</f>
-        <v>1.6074145204110213E-2</v>
+        <v>4.1591570067559758E-2</v>
       </c>
       <c r="CT7" s="78">
         <f>CN7-CO7-CP7-CQ7</f>
-        <v>1713.7674337312717</v>
+        <v>638.60043373127212</v>
       </c>
     </row>
     <row r="8" spans="2:102" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -30399,7 +30400,7 @@
       </c>
       <c r="BU11" s="73">
         <f t="shared" ref="BU11:BU23" si="32">CC11+CG11+CK11</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BV11" s="73">
         <f t="shared" ref="BV11:BV23" si="33">CB11+CF11+CJ11</f>
@@ -30407,15 +30408,15 @@
       </c>
       <c r="BW11" s="37">
         <f t="shared" ref="BW11" si="34">IFERROR(((BT11+BV11+BU11)/BS11),0)</f>
-        <v>0.41212121212121211</v>
+        <v>0.44646464646464645</v>
       </c>
       <c r="BX11" s="37">
         <f t="shared" ref="BX11" si="35">IFERROR(((BT11+BU11+BV11)/BR11-1),0)</f>
-        <v>9.1393506208637953E-2</v>
+        <v>0.18234296505935799</v>
       </c>
       <c r="BY11" s="80">
         <f t="shared" ref="BY11" si="36">BS11-BT11-BU11-BV11</f>
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="BZ11" s="79">
         <f>SUMIF(Cliente!$H:$H,Rede!F11,Cliente!$BM:$BM)</f>
@@ -30463,7 +30464,7 @@
       </c>
       <c r="CK11" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F11,Cliente!$BX:$BX)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="CM11" s="79">
         <f t="shared" si="17"/>
@@ -30479,7 +30480,7 @@
       </c>
       <c r="CP11" s="73">
         <f t="shared" si="20"/>
-        <v>128.041</v>
+        <v>145.041</v>
       </c>
       <c r="CQ11" s="73">
         <f t="shared" si="21"/>
@@ -30487,15 +30488,15 @@
       </c>
       <c r="CR11" s="37">
         <f t="shared" ref="CR11" si="37">IFERROR(((CO11+CQ11+CP11)/CN11),0)</f>
-        <v>1.7432724869607064</v>
+        <v>1.7516657221824652</v>
       </c>
       <c r="CS11" s="37">
         <f t="shared" ref="CS11" si="38">IFERROR(((CO11+CP11+CQ11)/CM11-1),0)</f>
-        <v>0.88845180854989758</v>
+        <v>0.89754403042150477</v>
       </c>
       <c r="CT11" s="80">
         <f>CN11-CO11-CP11-CQ11</f>
-        <v>-1505.4543265480204</v>
+        <v>-1522.4543265480204</v>
       </c>
       <c r="CU11" s="139"/>
       <c r="CV11" s="139"/>
@@ -30772,7 +30773,7 @@
       </c>
       <c r="BU12" s="73">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>152.167</v>
       </c>
       <c r="BV12" s="73">
         <f t="shared" si="33"/>
@@ -30780,15 +30781,15 @@
       </c>
       <c r="BW12" s="37">
         <f>IFERROR(((BT12+BV12+BU12)/BS12),0)</f>
-        <v>0.53378308823529408</v>
+        <v>0.72026225490196083</v>
       </c>
       <c r="BX12" s="37">
         <f>IFERROR(((BT12+BU12+BV12)/BR12-1),0)</f>
-        <v>2.2125013828963378</v>
+        <v>3.3348010473134932</v>
       </c>
       <c r="BY12" s="80">
         <f>BS12-BT12-BU12-BV12</f>
-        <v>380.43299999999999</v>
+        <v>228.26599999999999</v>
       </c>
       <c r="BZ12" s="79">
         <f>SUMIF(Cliente!$H:$H,Rede!F12,Cliente!$BM:$BM)</f>
@@ -30836,7 +30837,7 @@
       </c>
       <c r="CK12" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F12,Cliente!$BX:$BX)</f>
-        <v>0</v>
+        <v>152.167</v>
       </c>
       <c r="CM12" s="79">
         <f t="shared" si="17"/>
@@ -30852,7 +30853,7 @@
       </c>
       <c r="CP12" s="73">
         <f t="shared" si="20"/>
-        <v>117.583</v>
+        <v>269.75</v>
       </c>
       <c r="CQ12" s="73">
         <f t="shared" si="21"/>
@@ -30860,15 +30861,15 @@
       </c>
       <c r="CR12" s="37">
         <f>IFERROR(((CO12+CQ12+CP12)/CN12),0)</f>
-        <v>1.2208296408986898</v>
+        <v>1.2663252927577693</v>
       </c>
       <c r="CS12" s="37">
         <f>IFERROR(((CO12+CP12+CQ12)/CM12-1),0)</f>
-        <v>0.32377697441728004</v>
+        <v>0.37310907969187013</v>
       </c>
       <c r="CT12" s="80">
         <f>CN12-CO12-CP12-CQ12</f>
-        <v>-738.59770315445655</v>
+        <v>-890.76470315445658</v>
       </c>
       <c r="CU12" s="139"/>
       <c r="CV12" s="139"/>
@@ -34125,11 +34126,11 @@
       </c>
       <c r="BT21" s="73">
         <f t="shared" si="31"/>
-        <v>237.167</v>
+        <v>242.167</v>
       </c>
       <c r="BU21" s="73">
         <f t="shared" si="32"/>
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="BV21" s="73">
         <f t="shared" si="33"/>
@@ -34185,7 +34186,7 @@
       </c>
       <c r="CI21" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F21,Cliente!$BV:$BV)</f>
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="CJ21" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F21,Cliente!$BW:$BW)</f>
@@ -34193,7 +34194,7 @@
       </c>
       <c r="CK21" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F21,Cliente!$BX:$BX)</f>
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="CM21" s="79">
         <f t="shared" si="17"/>
@@ -34205,11 +34206,11 @@
       </c>
       <c r="CO21" s="73">
         <f t="shared" si="19"/>
-        <v>2328.3759999999997</v>
+        <v>2333.3759999999997</v>
       </c>
       <c r="CP21" s="73">
         <f t="shared" si="20"/>
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="CQ21" s="73">
         <f t="shared" si="21"/>
@@ -34875,7 +34876,7 @@
       </c>
       <c r="BU23" s="73">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>906</v>
       </c>
       <c r="BV23" s="73">
         <f t="shared" si="33"/>
@@ -34883,15 +34884,15 @@
       </c>
       <c r="BW23" s="37">
         <f t="shared" ref="BW23" si="69">IFERROR(((BT23+BV23+BU23)/BS23),0)</f>
-        <v>0.56095890410958904</v>
+        <v>0.97465753424657531</v>
       </c>
       <c r="BX23" s="37">
         <f t="shared" ref="BX23" si="70">IFERROR(((BT23+BU23+BV23)/BR23-1),0)</f>
-        <v>9.2487771535980645E-3</v>
+        <v>0.7535543466295116</v>
       </c>
       <c r="BY23" s="80">
         <f t="shared" ref="BY23" si="71">BS23-BT23-BU23-BV23</f>
-        <v>961.5</v>
+        <v>55.5</v>
       </c>
       <c r="BZ23" s="79">
         <f>SUMIF(Cliente!$H:$H,Rede!F23,Cliente!$BM:$BM)</f>
@@ -34939,7 +34940,7 @@
       </c>
       <c r="CK23" s="64">
         <f>SUMIF(Cliente!$H:$H,Rede!$F23,Cliente!$BX:$BX)</f>
-        <v>0</v>
+        <v>906</v>
       </c>
       <c r="CM23" s="79">
         <f t="shared" si="17"/>
@@ -34955,7 +34956,7 @@
       </c>
       <c r="CP23" s="73">
         <f t="shared" si="20"/>
-        <v>22.417000000000002</v>
+        <v>928.41700000000003</v>
       </c>
       <c r="CQ23" s="73">
         <f t="shared" si="21"/>
@@ -34963,15 +34964,15 @@
       </c>
       <c r="CR23" s="37">
         <f t="shared" ref="CR23" si="72">IFERROR(((CO23+CQ23+CP23)/CN23),0)</f>
-        <v>1.0136822059843611</v>
+        <v>1.1145006987284869</v>
       </c>
       <c r="CS23" s="37">
         <f t="shared" ref="CS23" si="73">IFERROR(((CO23+CP23+CQ23)/CM23-1),0)</f>
-        <v>5.3425482708173044E-2</v>
+        <v>0.15819675003229294</v>
       </c>
       <c r="CT23" s="80">
         <f>CN23-CO23-CP23-CQ23</f>
-        <v>-122.95441326713862</v>
+        <v>-1028.9544132671385</v>
       </c>
       <c r="CU23" s="139"/>
       <c r="CV23" s="139"/>
@@ -36405,7 +36406,7 @@
       </c>
       <c r="BJ7" s="75">
         <f t="shared" si="0"/>
-        <v>5715.7080000000014</v>
+        <v>5720.7080000000014</v>
       </c>
       <c r="BK7" s="75">
         <f t="shared" si="0"/>
@@ -36413,7 +36414,7 @@
       </c>
       <c r="BL7" s="78">
         <f t="shared" si="0"/>
-        <v>225</v>
+        <v>1295.1669999999999</v>
       </c>
       <c r="BM7" s="74">
         <f t="shared" si="0"/>
@@ -36453,7 +36454,7 @@
       </c>
       <c r="BV7" s="75">
         <f t="shared" si="0"/>
-        <v>1606.7559999999999</v>
+        <v>1611.7559999999999</v>
       </c>
       <c r="BW7" s="75">
         <f t="shared" ref="BW7:BX7" si="1">SUBTOTAL(9,BW10:BW107)</f>
@@ -36461,7 +36462,7 @@
       </c>
       <c r="BX7" s="78">
         <f t="shared" si="1"/>
-        <v>225</v>
+        <v>1295.1669999999999</v>
       </c>
     </row>
     <row r="8" spans="2:76" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -41653,7 +41654,7 @@
       </c>
       <c r="BL28" s="111">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>152.167</v>
       </c>
       <c r="BM28" s="108">
         <f>IFERROR(VLOOKUP($E28&amp;BM$6,Base!$A:$E,5,0),0)</f>
@@ -41699,7 +41700,7 @@
       </c>
       <c r="BX28" s="109">
         <f>IFERROR(VLOOKUP($E28,Base!$U:$W,3,0),0)</f>
-        <v>0</v>
+        <v>152.167</v>
       </c>
     </row>
     <row r="29" spans="2:76" x14ac:dyDescent="0.35">
@@ -42948,7 +42949,7 @@
       </c>
       <c r="BL33" s="111">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BM33" s="108">
         <f>IFERROR(VLOOKUP($E33&amp;BM$6,Base!$A:$E,5,0),0)</f>
@@ -42994,7 +42995,7 @@
       </c>
       <c r="BX33" s="109">
         <f>IFERROR(VLOOKUP($E33,Base!$U:$W,3,0),0)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="2:76" x14ac:dyDescent="0.35">
@@ -53818,7 +53819,7 @@
       </c>
       <c r="BJ75" s="99">
         <f t="shared" si="45"/>
-        <v>29.417000000000002</v>
+        <v>34.417000000000002</v>
       </c>
       <c r="BK75" s="99">
         <f t="shared" si="46"/>
@@ -53826,7 +53827,7 @@
       </c>
       <c r="BL75" s="111">
         <f t="shared" si="47"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BM75" s="108">
         <f>IFERROR(VLOOKUP($E75&amp;BM$6,Base!$A:$E,5,0),0)</f>
@@ -53864,7 +53865,7 @@
       </c>
       <c r="BV75" s="101">
         <f>IFERROR(VLOOKUP($E75&amp;BV$6,Base!$G:$K,5,0),0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BW75" s="101">
         <f>IFERROR(VLOOKUP($E75&amp;BV$6,Base!$M:$Q,5,0),0)</f>
@@ -53872,7 +53873,7 @@
       </c>
       <c r="BX75" s="109">
         <f>IFERROR(VLOOKUP($E75,Base!$U:$W,3,0),0)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="2:76" x14ac:dyDescent="0.35">
@@ -56157,7 +56158,7 @@
       </c>
       <c r="BL84" s="111">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>906</v>
       </c>
       <c r="BM84" s="108">
         <f>IFERROR(VLOOKUP($E84&amp;BM$6,Base!$A:$E,5,0),0)</f>
@@ -56203,7 +56204,7 @@
       </c>
       <c r="BX84" s="109">
         <f>IFERROR(VLOOKUP($E84,Base!$U:$W,3,0),0)</f>
-        <v>0</v>
+        <v>906</v>
       </c>
     </row>
     <row r="85" spans="2:76" x14ac:dyDescent="0.35">

--- a/MECÂNICAS/PAUTA D/JOHNSON/Campanha Johnson - Top Contas Q4 FY26.xlsx
+++ b/MECÂNICAS/PAUTA D/JOHNSON/Campanha Johnson - Top Contas Q4 FY26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\Nicolas\Acompanhamentos\JOHNSON\2025.26\Q4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C70782EA-2AFD-4C11-847E-2A1D75BDC714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9057351A-AC16-43C8-9461-17DFDF629D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="705" firstSheet="1" activeTab="3" xr2:uid="{1E3193F5-9832-4B59-8D54-14EFCF6055F0}"/>
   </bookViews>
@@ -4412,6 +4412,27 @@
     <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4422,6 +4443,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4440,36 +4470,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="11" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6256,9 +6256,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>960452</xdr:colOff>
+      <xdr:colOff>963627</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>9582</xdr:rowOff>
+      <xdr:rowOff>6407</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6336,9 +6336,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>597342</xdr:colOff>
+      <xdr:colOff>600517</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>122720</xdr:rowOff>
+      <xdr:rowOff>125895</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -22474,138 +22474,138 @@
       <c r="B2" s="150"/>
     </row>
     <row r="3" spans="2:99" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="E3" s="206" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" s="201" t="s">
+      <c r="E3" s="193" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="191" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="203" t="s">
+      <c r="G3" s="202" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="204"/>
-      <c r="I3" s="204"/>
-      <c r="J3" s="204"/>
-      <c r="K3" s="204"/>
-      <c r="L3" s="204"/>
-      <c r="M3" s="204"/>
-      <c r="N3" s="205"/>
-      <c r="O3" s="191" t="s">
+      <c r="H3" s="203"/>
+      <c r="I3" s="203"/>
+      <c r="J3" s="203"/>
+      <c r="K3" s="203"/>
+      <c r="L3" s="203"/>
+      <c r="M3" s="203"/>
+      <c r="N3" s="204"/>
+      <c r="O3" s="198" t="s">
         <v>23</v>
       </c>
-      <c r="P3" s="192"/>
-      <c r="Q3" s="192"/>
-      <c r="R3" s="193"/>
-      <c r="S3" s="191" t="s">
+      <c r="P3" s="199"/>
+      <c r="Q3" s="199"/>
+      <c r="R3" s="200"/>
+      <c r="S3" s="198" t="s">
         <v>24</v>
       </c>
-      <c r="T3" s="192"/>
-      <c r="U3" s="192"/>
-      <c r="V3" s="193"/>
-      <c r="W3" s="191" t="s">
+      <c r="T3" s="199"/>
+      <c r="U3" s="199"/>
+      <c r="V3" s="200"/>
+      <c r="W3" s="198" t="s">
         <v>25</v>
       </c>
-      <c r="X3" s="192"/>
-      <c r="Y3" s="192"/>
-      <c r="Z3" s="194"/>
-      <c r="AB3" s="203" t="s">
+      <c r="X3" s="199"/>
+      <c r="Y3" s="199"/>
+      <c r="Z3" s="201"/>
+      <c r="AB3" s="202" t="s">
         <v>30</v>
       </c>
-      <c r="AC3" s="204"/>
-      <c r="AD3" s="204"/>
-      <c r="AE3" s="204"/>
-      <c r="AF3" s="204"/>
-      <c r="AG3" s="204"/>
-      <c r="AH3" s="204"/>
-      <c r="AI3" s="205"/>
-      <c r="AJ3" s="191" t="s">
+      <c r="AC3" s="203"/>
+      <c r="AD3" s="203"/>
+      <c r="AE3" s="203"/>
+      <c r="AF3" s="203"/>
+      <c r="AG3" s="203"/>
+      <c r="AH3" s="203"/>
+      <c r="AI3" s="204"/>
+      <c r="AJ3" s="198" t="s">
         <v>27</v>
       </c>
-      <c r="AK3" s="192"/>
-      <c r="AL3" s="192"/>
-      <c r="AM3" s="193"/>
-      <c r="AN3" s="191" t="s">
+      <c r="AK3" s="199"/>
+      <c r="AL3" s="199"/>
+      <c r="AM3" s="200"/>
+      <c r="AN3" s="198" t="s">
         <v>28</v>
       </c>
-      <c r="AO3" s="192"/>
-      <c r="AP3" s="192"/>
-      <c r="AQ3" s="193"/>
-      <c r="AR3" s="191" t="s">
+      <c r="AO3" s="199"/>
+      <c r="AP3" s="199"/>
+      <c r="AQ3" s="200"/>
+      <c r="AR3" s="198" t="s">
         <v>29</v>
       </c>
-      <c r="AS3" s="192"/>
-      <c r="AT3" s="192"/>
-      <c r="AU3" s="194"/>
-      <c r="AW3" s="203" t="s">
+      <c r="AS3" s="199"/>
+      <c r="AT3" s="199"/>
+      <c r="AU3" s="201"/>
+      <c r="AW3" s="202" t="s">
         <v>66</v>
       </c>
-      <c r="AX3" s="204"/>
-      <c r="AY3" s="204"/>
-      <c r="AZ3" s="204"/>
-      <c r="BA3" s="204"/>
-      <c r="BB3" s="204"/>
-      <c r="BC3" s="204"/>
-      <c r="BD3" s="205"/>
-      <c r="BE3" s="191" t="s">
+      <c r="AX3" s="203"/>
+      <c r="AY3" s="203"/>
+      <c r="AZ3" s="203"/>
+      <c r="BA3" s="203"/>
+      <c r="BB3" s="203"/>
+      <c r="BC3" s="203"/>
+      <c r="BD3" s="204"/>
+      <c r="BE3" s="198" t="s">
         <v>67</v>
       </c>
-      <c r="BF3" s="192"/>
-      <c r="BG3" s="192"/>
-      <c r="BH3" s="193"/>
-      <c r="BI3" s="191" t="s">
+      <c r="BF3" s="199"/>
+      <c r="BG3" s="199"/>
+      <c r="BH3" s="200"/>
+      <c r="BI3" s="198" t="s">
         <v>68</v>
       </c>
-      <c r="BJ3" s="192"/>
-      <c r="BK3" s="192"/>
-      <c r="BL3" s="193"/>
-      <c r="BM3" s="191" t="s">
+      <c r="BJ3" s="199"/>
+      <c r="BK3" s="199"/>
+      <c r="BL3" s="200"/>
+      <c r="BM3" s="198" t="s">
         <v>72</v>
       </c>
-      <c r="BN3" s="192"/>
-      <c r="BO3" s="192"/>
-      <c r="BP3" s="194"/>
-      <c r="BR3" s="203" t="s">
+      <c r="BN3" s="199"/>
+      <c r="BO3" s="199"/>
+      <c r="BP3" s="201"/>
+      <c r="BR3" s="202" t="s">
         <v>73</v>
       </c>
-      <c r="BS3" s="204"/>
-      <c r="BT3" s="204"/>
-      <c r="BU3" s="204"/>
-      <c r="BV3" s="204"/>
-      <c r="BW3" s="204"/>
-      <c r="BX3" s="204"/>
-      <c r="BY3" s="205"/>
+      <c r="BS3" s="203"/>
+      <c r="BT3" s="203"/>
+      <c r="BU3" s="203"/>
+      <c r="BV3" s="203"/>
+      <c r="BW3" s="203"/>
+      <c r="BX3" s="203"/>
+      <c r="BY3" s="204"/>
       <c r="BZ3" s="185" t="s">
         <v>69</v>
       </c>
       <c r="CA3" s="186"/>
       <c r="CB3" s="186"/>
       <c r="CC3" s="186"/>
-      <c r="CD3" s="191" t="s">
+      <c r="CD3" s="198" t="s">
         <v>70</v>
       </c>
-      <c r="CE3" s="192"/>
-      <c r="CF3" s="192"/>
-      <c r="CG3" s="193"/>
-      <c r="CH3" s="191" t="s">
+      <c r="CE3" s="199"/>
+      <c r="CF3" s="199"/>
+      <c r="CG3" s="200"/>
+      <c r="CH3" s="198" t="s">
         <v>71</v>
       </c>
-      <c r="CI3" s="192"/>
-      <c r="CJ3" s="192"/>
-      <c r="CK3" s="194"/>
-      <c r="CM3" s="208" t="s">
+      <c r="CI3" s="199"/>
+      <c r="CJ3" s="199"/>
+      <c r="CK3" s="201"/>
+      <c r="CM3" s="195" t="s">
         <v>783</v>
       </c>
-      <c r="CN3" s="209"/>
-      <c r="CO3" s="209"/>
-      <c r="CP3" s="209"/>
-      <c r="CQ3" s="209"/>
-      <c r="CR3" s="209"/>
-      <c r="CS3" s="209"/>
-      <c r="CT3" s="210"/>
+      <c r="CN3" s="196"/>
+      <c r="CO3" s="196"/>
+      <c r="CP3" s="196"/>
+      <c r="CQ3" s="196"/>
+      <c r="CR3" s="196"/>
+      <c r="CS3" s="196"/>
+      <c r="CT3" s="197"/>
     </row>
     <row r="4" spans="2:99" ht="26" x14ac:dyDescent="0.3">
-      <c r="E4" s="207"/>
-      <c r="F4" s="202"/>
+      <c r="E4" s="194"/>
+      <c r="F4" s="192"/>
       <c r="G4" s="146" t="s">
         <v>169</v>
       </c>
@@ -24008,137 +24008,137 @@
       <c r="CK9" s="11"/>
     </row>
     <row r="10" spans="2:99" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="198" t="s">
+      <c r="B10" s="208" t="s">
         <v>784</v>
       </c>
-      <c r="C10" s="199"/>
-      <c r="D10" s="199"/>
-      <c r="E10" s="200"/>
-      <c r="F10" s="201" t="s">
+      <c r="C10" s="209"/>
+      <c r="D10" s="209"/>
+      <c r="E10" s="210"/>
+      <c r="F10" s="191" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="203" t="s">
+      <c r="G10" s="202" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="204"/>
-      <c r="I10" s="204"/>
-      <c r="J10" s="204"/>
-      <c r="K10" s="204"/>
-      <c r="L10" s="204"/>
-      <c r="M10" s="204"/>
-      <c r="N10" s="205"/>
-      <c r="O10" s="191" t="s">
+      <c r="H10" s="203"/>
+      <c r="I10" s="203"/>
+      <c r="J10" s="203"/>
+      <c r="K10" s="203"/>
+      <c r="L10" s="203"/>
+      <c r="M10" s="203"/>
+      <c r="N10" s="204"/>
+      <c r="O10" s="198" t="s">
         <v>23</v>
       </c>
-      <c r="P10" s="192"/>
-      <c r="Q10" s="192"/>
-      <c r="R10" s="193"/>
-      <c r="S10" s="191" t="s">
+      <c r="P10" s="199"/>
+      <c r="Q10" s="199"/>
+      <c r="R10" s="200"/>
+      <c r="S10" s="198" t="s">
         <v>24</v>
       </c>
-      <c r="T10" s="192"/>
-      <c r="U10" s="192"/>
-      <c r="V10" s="193"/>
-      <c r="W10" s="191" t="s">
+      <c r="T10" s="199"/>
+      <c r="U10" s="199"/>
+      <c r="V10" s="200"/>
+      <c r="W10" s="198" t="s">
         <v>25</v>
       </c>
-      <c r="X10" s="192"/>
-      <c r="Y10" s="192"/>
-      <c r="Z10" s="194"/>
-      <c r="AB10" s="203" t="s">
+      <c r="X10" s="199"/>
+      <c r="Y10" s="199"/>
+      <c r="Z10" s="201"/>
+      <c r="AB10" s="202" t="s">
         <v>30</v>
       </c>
-      <c r="AC10" s="204"/>
-      <c r="AD10" s="204"/>
-      <c r="AE10" s="204"/>
-      <c r="AF10" s="204"/>
-      <c r="AG10" s="204"/>
-      <c r="AH10" s="204"/>
-      <c r="AI10" s="205"/>
-      <c r="AJ10" s="191" t="s">
+      <c r="AC10" s="203"/>
+      <c r="AD10" s="203"/>
+      <c r="AE10" s="203"/>
+      <c r="AF10" s="203"/>
+      <c r="AG10" s="203"/>
+      <c r="AH10" s="203"/>
+      <c r="AI10" s="204"/>
+      <c r="AJ10" s="198" t="s">
         <v>27</v>
       </c>
-      <c r="AK10" s="192"/>
-      <c r="AL10" s="192"/>
-      <c r="AM10" s="193"/>
-      <c r="AN10" s="191" t="s">
+      <c r="AK10" s="199"/>
+      <c r="AL10" s="199"/>
+      <c r="AM10" s="200"/>
+      <c r="AN10" s="198" t="s">
         <v>28</v>
       </c>
-      <c r="AO10" s="192"/>
-      <c r="AP10" s="192"/>
-      <c r="AQ10" s="193"/>
-      <c r="AR10" s="191" t="s">
+      <c r="AO10" s="199"/>
+      <c r="AP10" s="199"/>
+      <c r="AQ10" s="200"/>
+      <c r="AR10" s="198" t="s">
         <v>29</v>
       </c>
-      <c r="AS10" s="192"/>
-      <c r="AT10" s="192"/>
-      <c r="AU10" s="194"/>
-      <c r="AW10" s="203" t="s">
+      <c r="AS10" s="199"/>
+      <c r="AT10" s="199"/>
+      <c r="AU10" s="201"/>
+      <c r="AW10" s="202" t="s">
         <v>66</v>
       </c>
-      <c r="AX10" s="204"/>
-      <c r="AY10" s="204"/>
-      <c r="AZ10" s="204"/>
-      <c r="BA10" s="204"/>
-      <c r="BB10" s="204"/>
-      <c r="BC10" s="204"/>
-      <c r="BD10" s="205"/>
-      <c r="BE10" s="191" t="s">
+      <c r="AX10" s="203"/>
+      <c r="AY10" s="203"/>
+      <c r="AZ10" s="203"/>
+      <c r="BA10" s="203"/>
+      <c r="BB10" s="203"/>
+      <c r="BC10" s="203"/>
+      <c r="BD10" s="204"/>
+      <c r="BE10" s="198" t="s">
         <v>67</v>
       </c>
-      <c r="BF10" s="192"/>
-      <c r="BG10" s="192"/>
-      <c r="BH10" s="193"/>
-      <c r="BI10" s="191" t="s">
+      <c r="BF10" s="199"/>
+      <c r="BG10" s="199"/>
+      <c r="BH10" s="200"/>
+      <c r="BI10" s="198" t="s">
         <v>68</v>
       </c>
-      <c r="BJ10" s="192"/>
-      <c r="BK10" s="192"/>
-      <c r="BL10" s="193"/>
-      <c r="BM10" s="191" t="s">
+      <c r="BJ10" s="199"/>
+      <c r="BK10" s="199"/>
+      <c r="BL10" s="200"/>
+      <c r="BM10" s="198" t="s">
         <v>72</v>
       </c>
-      <c r="BN10" s="192"/>
-      <c r="BO10" s="192"/>
-      <c r="BP10" s="194"/>
-      <c r="BR10" s="203" t="s">
+      <c r="BN10" s="199"/>
+      <c r="BO10" s="199"/>
+      <c r="BP10" s="201"/>
+      <c r="BR10" s="202" t="s">
         <v>73</v>
       </c>
-      <c r="BS10" s="204"/>
-      <c r="BT10" s="204"/>
-      <c r="BU10" s="204"/>
-      <c r="BV10" s="204"/>
-      <c r="BW10" s="204"/>
-      <c r="BX10" s="204"/>
-      <c r="BY10" s="205"/>
+      <c r="BS10" s="203"/>
+      <c r="BT10" s="203"/>
+      <c r="BU10" s="203"/>
+      <c r="BV10" s="203"/>
+      <c r="BW10" s="203"/>
+      <c r="BX10" s="203"/>
+      <c r="BY10" s="204"/>
       <c r="BZ10" s="185" t="s">
         <v>69</v>
       </c>
       <c r="CA10" s="186"/>
       <c r="CB10" s="186"/>
       <c r="CC10" s="186"/>
-      <c r="CD10" s="191" t="s">
+      <c r="CD10" s="198" t="s">
         <v>70</v>
       </c>
-      <c r="CE10" s="192"/>
-      <c r="CF10" s="192"/>
-      <c r="CG10" s="193"/>
-      <c r="CH10" s="191" t="s">
+      <c r="CE10" s="199"/>
+      <c r="CF10" s="199"/>
+      <c r="CG10" s="200"/>
+      <c r="CH10" s="198" t="s">
         <v>71</v>
       </c>
-      <c r="CI10" s="192"/>
-      <c r="CJ10" s="192"/>
-      <c r="CK10" s="194"/>
-      <c r="CM10" s="208" t="s">
+      <c r="CI10" s="199"/>
+      <c r="CJ10" s="199"/>
+      <c r="CK10" s="201"/>
+      <c r="CM10" s="195" t="s">
         <v>783</v>
       </c>
-      <c r="CN10" s="209"/>
-      <c r="CO10" s="209"/>
-      <c r="CP10" s="209"/>
-      <c r="CQ10" s="209"/>
-      <c r="CR10" s="209"/>
-      <c r="CS10" s="209"/>
-      <c r="CT10" s="210"/>
+      <c r="CN10" s="196"/>
+      <c r="CO10" s="196"/>
+      <c r="CP10" s="196"/>
+      <c r="CQ10" s="196"/>
+      <c r="CR10" s="196"/>
+      <c r="CS10" s="196"/>
+      <c r="CT10" s="197"/>
     </row>
     <row r="11" spans="2:99" ht="26" x14ac:dyDescent="0.3">
       <c r="B11" s="52" t="s">
@@ -24153,7 +24153,7 @@
       <c r="E11" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="202"/>
+      <c r="F11" s="192"/>
       <c r="G11" s="38" t="s">
         <v>169</v>
       </c>
@@ -27406,12 +27406,12 @@
       <c r="CU19" s="21"/>
     </row>
     <row r="20" spans="2:99" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="195" t="s">
+      <c r="B20" s="205" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="196"/>
-      <c r="D20" s="196"/>
-      <c r="E20" s="197"/>
+      <c r="C20" s="206"/>
+      <c r="D20" s="206"/>
+      <c r="E20" s="207"/>
       <c r="F20" s="113">
         <f>SUM(F12:F19)</f>
         <v>14</v>
@@ -27988,6 +27988,27 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="AN10:AQ10"/>
+    <mergeCell ref="AR10:AU10"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="BM10:BP10"/>
+    <mergeCell ref="AW3:BD3"/>
+    <mergeCell ref="G3:N3"/>
+    <mergeCell ref="G10:N10"/>
+    <mergeCell ref="AB3:AI3"/>
+    <mergeCell ref="AB10:AI10"/>
+    <mergeCell ref="AJ3:AM3"/>
+    <mergeCell ref="O10:R10"/>
+    <mergeCell ref="S10:V10"/>
+    <mergeCell ref="W10:Z10"/>
+    <mergeCell ref="AJ10:AM10"/>
+    <mergeCell ref="AN3:AQ3"/>
+    <mergeCell ref="AR3:AU3"/>
+    <mergeCell ref="O3:R3"/>
+    <mergeCell ref="S3:V3"/>
+    <mergeCell ref="W3:Z3"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="CM3:CT3"/>
@@ -28004,27 +28025,6 @@
     <mergeCell ref="BE10:BH10"/>
     <mergeCell ref="AW10:BD10"/>
     <mergeCell ref="BI10:BL10"/>
-    <mergeCell ref="BM10:BP10"/>
-    <mergeCell ref="AW3:BD3"/>
-    <mergeCell ref="G3:N3"/>
-    <mergeCell ref="G10:N10"/>
-    <mergeCell ref="AB3:AI3"/>
-    <mergeCell ref="AB10:AI10"/>
-    <mergeCell ref="AJ3:AM3"/>
-    <mergeCell ref="O10:R10"/>
-    <mergeCell ref="S10:V10"/>
-    <mergeCell ref="W10:Z10"/>
-    <mergeCell ref="AJ10:AM10"/>
-    <mergeCell ref="AN3:AQ3"/>
-    <mergeCell ref="AR3:AU3"/>
-    <mergeCell ref="O3:R3"/>
-    <mergeCell ref="S3:V3"/>
-    <mergeCell ref="W3:Z3"/>
-    <mergeCell ref="AN10:AQ10"/>
-    <mergeCell ref="AR10:AU10"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="F10:F11"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="L5:L7 AG5:AG7 BB5:BB7 BW5:BW7 CR5:CR7 L12:L20 AG12:AG20 BB12:BB20 BW12:BW20 CR12:CR20">
